--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -62886,6 +62886,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2719">
+      <c r="A2719" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2719" t="n">
+        <v>251943</v>
+      </c>
+      <c r="C2719" t="n">
+        <v>6.51999998092651</v>
+      </c>
+      <c r="D2719" t="n">
+        <v>6.26000022888184</v>
+      </c>
+      <c r="E2719" t="n">
+        <v>6.36999988555908</v>
+      </c>
+      <c r="F2719" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -62897,7 +62897,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="D2719" t="n">
-        <v>6.26000022888184</v>
+        <v>6.25</v>
       </c>
       <c r="E2719" t="n">
         <v>6.36999988555908</v>
@@ -62906,6 +62906,29 @@
         <v>6.25</v>
       </c>
       <c r="G2719" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2720">
+      <c r="A2720" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2720" t="n">
+        <v>1440043</v>
+      </c>
+      <c r="C2720" t="n">
+        <v>7.15000009536743</v>
+      </c>
+      <c r="D2720" t="n">
+        <v>6.34999990463257</v>
+      </c>
+      <c r="E2720" t="n">
+        <v>6.46000003814697</v>
+      </c>
+      <c r="F2720" t="n">
+        <v>6.90000009536743</v>
+      </c>
+      <c r="G2720" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -62932,6 +62932,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2721">
+      <c r="A2721" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2721" t="n">
+        <v>490859</v>
+      </c>
+      <c r="C2721" t="n">
+        <v>7.23999977111816</v>
+      </c>
+      <c r="D2721" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="E2721" t="n">
+        <v>6.92000007629395</v>
+      </c>
+      <c r="F2721" t="n">
+        <v>7.05999994277954</v>
+      </c>
+      <c r="G2721" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -62955,6 +62955,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2722">
+      <c r="A2722" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2722" t="n">
+        <v>246831</v>
+      </c>
+      <c r="C2722" t="n">
+        <v>7.09000015258789</v>
+      </c>
+      <c r="D2722" t="n">
+        <v>6.86999988555908</v>
+      </c>
+      <c r="E2722" t="n">
+        <v>7.07999992370605</v>
+      </c>
+      <c r="F2722" t="n">
+        <v>6.98000001907349</v>
+      </c>
+      <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -62796,22 +62796,22 @@
     </row>
     <row r="2715">
       <c r="A2715" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2715" t="n">
-        <v>199199</v>
+        <v>47636</v>
       </c>
       <c r="C2715" t="n">
-        <v>6.21000003814697</v>
+        <v>6.09000015258789</v>
       </c>
       <c r="D2715" t="n">
-        <v>6.01000022888184</v>
+        <v>5.96000003814697</v>
       </c>
       <c r="E2715" t="n">
         <v>6.01000022888184</v>
       </c>
       <c r="F2715" t="n">
-        <v>6.17000007629395</v>
+        <v>5.96000003814697</v>
       </c>
       <c r="G2715" t="s">
         <v>7</v>
@@ -62819,22 +62819,22 @@
     </row>
     <row r="2716">
       <c r="A2716" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2716" t="n">
-        <v>124088</v>
+        <v>199199</v>
       </c>
       <c r="C2716" t="n">
-        <v>6.26999998092651</v>
+        <v>6.21000003814697</v>
       </c>
       <c r="D2716" t="n">
-        <v>6.1100001335144</v>
+        <v>6.01000022888184</v>
       </c>
       <c r="E2716" t="n">
-        <v>6.23000001907349</v>
+        <v>6.01000022888184</v>
       </c>
       <c r="F2716" t="n">
-        <v>6.15999984741211</v>
+        <v>6.17000007629395</v>
       </c>
       <c r="G2716" t="s">
         <v>7</v>
@@ -62842,22 +62842,22 @@
     </row>
     <row r="2717">
       <c r="A2717" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2717" t="n">
-        <v>271412</v>
+        <v>124088</v>
       </c>
       <c r="C2717" t="n">
-        <v>6.46999979019165</v>
+        <v>6.26999998092651</v>
       </c>
       <c r="D2717" t="n">
-        <v>6.15000009536743</v>
+        <v>6.1100001335144</v>
       </c>
       <c r="E2717" t="n">
-        <v>6.15000009536743</v>
+        <v>6.23000001907349</v>
       </c>
       <c r="F2717" t="n">
-        <v>6.44999980926514</v>
+        <v>6.15999984741211</v>
       </c>
       <c r="G2717" t="s">
         <v>7</v>
@@ -62865,22 +62865,22 @@
     </row>
     <row r="2718">
       <c r="A2718" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2718" t="n">
-        <v>224630</v>
+        <v>271412</v>
       </c>
       <c r="C2718" t="n">
-        <v>6.55000019073486</v>
+        <v>6.46999979019165</v>
       </c>
       <c r="D2718" t="n">
-        <v>6.32000017166138</v>
+        <v>6.15000009536743</v>
       </c>
       <c r="E2718" t="n">
-        <v>6.48999977111816</v>
+        <v>6.15000009536743</v>
       </c>
       <c r="F2718" t="n">
-        <v>6.32000017166138</v>
+        <v>6.44999980926514</v>
       </c>
       <c r="G2718" t="s">
         <v>7</v>
@@ -62888,22 +62888,22 @@
     </row>
     <row r="2719">
       <c r="A2719" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2719" t="n">
-        <v>251943</v>
+        <v>224630</v>
       </c>
       <c r="C2719" t="n">
-        <v>6.51999998092651</v>
+        <v>6.55000019073486</v>
       </c>
       <c r="D2719" t="n">
-        <v>6.25</v>
+        <v>6.32000017166138</v>
       </c>
       <c r="E2719" t="n">
-        <v>6.36999988555908</v>
+        <v>6.48999977111816</v>
       </c>
       <c r="F2719" t="n">
-        <v>6.25</v>
+        <v>6.32000017166138</v>
       </c>
       <c r="G2719" t="s">
         <v>7</v>
@@ -62911,22 +62911,22 @@
     </row>
     <row r="2720">
       <c r="A2720" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2720" t="n">
-        <v>1440043</v>
+        <v>251943</v>
       </c>
       <c r="C2720" t="n">
-        <v>7.15000009536743</v>
+        <v>6.51999998092651</v>
       </c>
       <c r="D2720" t="n">
-        <v>6.34999990463257</v>
+        <v>6.25</v>
       </c>
       <c r="E2720" t="n">
-        <v>6.46000003814697</v>
+        <v>6.36999988555908</v>
       </c>
       <c r="F2720" t="n">
-        <v>6.90000009536743</v>
+        <v>6.25</v>
       </c>
       <c r="G2720" t="s">
         <v>7</v>
@@ -62934,22 +62934,22 @@
     </row>
     <row r="2721">
       <c r="A2721" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2721" t="n">
-        <v>490859</v>
+        <v>1440043</v>
       </c>
       <c r="C2721" t="n">
-        <v>7.23999977111816</v>
+        <v>7.15000009536743</v>
       </c>
       <c r="D2721" t="n">
-        <v>6.92000007629395</v>
+        <v>6.34999990463257</v>
       </c>
       <c r="E2721" t="n">
-        <v>6.92000007629395</v>
+        <v>6.46000003814697</v>
       </c>
       <c r="F2721" t="n">
-        <v>7.05999994277954</v>
+        <v>6.90000009536743</v>
       </c>
       <c r="G2721" t="s">
         <v>7</v>
@@ -62957,24 +62957,47 @@
     </row>
     <row r="2722">
       <c r="A2722" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2722" t="n">
-        <v>246831</v>
+        <v>490859</v>
       </c>
       <c r="C2722" t="n">
-        <v>7.09000015258789</v>
+        <v>7.23999977111816</v>
       </c>
       <c r="D2722" t="n">
-        <v>6.86999988555908</v>
+        <v>6.92000007629395</v>
       </c>
       <c r="E2722" t="n">
-        <v>7.07999992370605</v>
+        <v>6.92000007629395</v>
       </c>
       <c r="F2722" t="n">
-        <v>6.98000001907349</v>
+        <v>7.05999994277954</v>
       </c>
       <c r="G2722" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2723">
+      <c r="A2723" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2723" t="n">
+        <v>329407</v>
+      </c>
+      <c r="C2723" t="n">
+        <v>7.19000005722046</v>
+      </c>
+      <c r="D2723" t="n">
+        <v>6.80000019073486</v>
+      </c>
+      <c r="E2723" t="n">
+        <v>7.01000022888184</v>
+      </c>
+      <c r="F2723" t="n">
+        <v>7.11999988555908</v>
+      </c>
+      <c r="G2723" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92757678031921</v>
+        <v>2.92757654190063</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>2.93566417694092</v>
+        <v>2.93566393852234</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G5" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G10" t="n">
-        <v>2.98418736457825</v>
+        <v>2.98418712615967</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74965786933899</v>
+        <v>2.74965763092041</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62026214599609</v>
+        <v>2.62026190757751</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G18" t="n">
-        <v>2.54909443855286</v>
+        <v>2.54909420013428</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36470580101013</v>
+        <v>2.36470556259155</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3</v>
       </c>
       <c r="G33" t="n">
-        <v>2.42616868019104</v>
+        <v>2.42616844177246</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45043039321899</v>
+        <v>2.45042991638184</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3</v>
       </c>
       <c r="G35" t="n">
-        <v>2.42616868019104</v>
+        <v>2.42616844177246</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>2.50704073905945</v>
+        <v>2.50704097747803</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G38" t="n">
-        <v>2.57659101486206</v>
+        <v>2.57659077644348</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3</v>
       </c>
       <c r="G40" t="n">
-        <v>2.42616868019104</v>
+        <v>2.42616844177246</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.49086618423462</v>
+        <v>2.49086594581604</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G44" t="n">
-        <v>2.47469186782837</v>
+        <v>2.47469162940979</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G45" t="n">
-        <v>2.50542330741882</v>
+        <v>2.5054235458374</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G46" t="n">
-        <v>2.56203365325928</v>
+        <v>2.56203389167786</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57497334480286</v>
+        <v>2.57497358322144</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.66069793701172</v>
+        <v>2.6606981754303</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G53" t="n">
-        <v>2.58791303634644</v>
+        <v>2.58791327476501</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.58791303634644</v>
+        <v>2.58791327476501</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.50704073905945</v>
+        <v>2.50704097747803</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G61" t="n">
-        <v>2.55394649505615</v>
+        <v>2.55394697189331</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G62" t="n">
-        <v>2.58467841148376</v>
+        <v>2.58467864990234</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>2.57497334480286</v>
+        <v>2.57497358322144</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G66" t="n">
-        <v>2.56688594818115</v>
+        <v>2.56688618659973</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.46660447120667</v>
+        <v>2.46660470962524</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>2.53130269050598</v>
+        <v>2.5313024520874</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G79" t="n">
-        <v>2.54100704193115</v>
+        <v>2.54100728034973</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G80" t="n">
-        <v>2.54100704193115</v>
+        <v>2.54100728034973</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G83" t="n">
-        <v>2.54909443855286</v>
+        <v>2.54909420013428</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G86" t="n">
-        <v>2.5377721786499</v>
+        <v>2.53777241706848</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G87" t="n">
-        <v>2.53453755378723</v>
+        <v>2.53453731536865</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.12599992752075</v>
       </c>
       <c r="G88" t="n">
-        <v>2.52806758880615</v>
+        <v>2.52806735038757</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>2.46660447120667</v>
+        <v>2.46660470962524</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G90" t="n">
-        <v>2.44072508811951</v>
+        <v>2.44072532653809</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>3</v>
       </c>
       <c r="G92" t="n">
-        <v>2.42616868019104</v>
+        <v>2.42616844177246</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.46660447120667</v>
+        <v>2.46660470962524</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G94" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G95" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G96" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G98" t="n">
-        <v>2.38411474227905</v>
+        <v>2.38411498069763</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G99" t="n">
-        <v>2.3808798789978</v>
+        <v>2.38088011741638</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.88599991798401</v>
       </c>
       <c r="G104" t="n">
-        <v>2.41604042053223</v>
+        <v>2.41604065895081</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G113" t="n">
-        <v>2.24191188812256</v>
+        <v>2.24191164970398</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G117" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G118" t="n">
-        <v>2.17493915557861</v>
+        <v>2.17493891716003</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G119" t="n">
-        <v>2.16656756401062</v>
+        <v>2.16656732559204</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G120" t="n">
-        <v>2.26702642440796</v>
+        <v>2.26702618598938</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G124" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G126" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G127" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G128" t="n">
-        <v>2.14480137825012</v>
+        <v>2.14480113983154</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G129" t="n">
-        <v>2.14480137825012</v>
+        <v>2.14480113983154</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G131" t="n">
-        <v>2.14480137825012</v>
+        <v>2.14480113983154</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615447044373</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615447044373</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G136" t="n">
-        <v>2.13140678405762</v>
+        <v>2.13140654563904</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>2.1849844455719</v>
+        <v>2.18498468399048</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G142" t="n">
-        <v>2.1849844455719</v>
+        <v>2.18498468399048</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G143" t="n">
-        <v>2.1849844455719</v>
+        <v>2.18498468399048</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>2.1849844455719</v>
+        <v>2.18498468399048</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G147" t="n">
-        <v>2.14647531509399</v>
+        <v>2.14647507667542</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G148" t="n">
-        <v>2.14647531509399</v>
+        <v>2.14647507667542</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G151" t="n">
-        <v>2.18331027030945</v>
+        <v>2.18331050872803</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G152" t="n">
-        <v>2.18331027030945</v>
+        <v>2.18331050872803</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G153" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G154" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G155" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G156" t="n">
-        <v>2.26702642440796</v>
+        <v>2.26702618598938</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G159" t="n">
-        <v>2.24526047706604</v>
+        <v>2.24526023864746</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G160" t="n">
-        <v>2.26702642440796</v>
+        <v>2.26702618598938</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G165" t="n">
-        <v>2.25028300285339</v>
+        <v>2.25028324127197</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G166" t="n">
-        <v>2.25028300285339</v>
+        <v>2.25028324127197</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>2.26870059967041</v>
+        <v>2.26870083808899</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G173" t="n">
-        <v>2.26870059967041</v>
+        <v>2.26870083808899</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G174" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G175" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G179" t="n">
-        <v>2.15317296981812</v>
+        <v>2.15317273139954</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.21177387237549</v>
+        <v>2.21177411079407</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G187" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G191" t="n">
-        <v>2.17493915557861</v>
+        <v>2.17493891716003</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G192" t="n">
-        <v>2.09959483146667</v>
+        <v>2.09959435462952</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>2.5</v>
       </c>
       <c r="G193" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>2.5</v>
       </c>
       <c r="G197" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G201" t="n">
-        <v>2.06945657730103</v>
+        <v>2.0694568157196</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>2.5</v>
       </c>
       <c r="G202" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>2.5</v>
       </c>
       <c r="G204" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G207" t="n">
-        <v>2.00750708580017</v>
+        <v>2.00750732421875</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G217" t="n">
-        <v>1.98908960819244</v>
+        <v>1.98908936977386</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G220" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>1.99411237239838</v>
+        <v>1.99411249160767</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G223" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G224" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G225" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G226" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G228" t="n">
-        <v>1.93216276168823</v>
+        <v>1.93216288089752</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G229" t="n">
-        <v>1.91207075119019</v>
+        <v>1.91207087039948</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G232" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G235" t="n">
-        <v>1.90202510356903</v>
+        <v>1.90202486515045</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G236" t="n">
-        <v>1.94053447246552</v>
+        <v>1.9405345916748</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G243" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G248" t="n">
-        <v>2.07447981834412</v>
+        <v>2.07447957992554</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G250" t="n">
-        <v>2.07447981834412</v>
+        <v>2.07447957992554</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G251" t="n">
-        <v>2.07447981834412</v>
+        <v>2.07447957992554</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.4779999256134</v>
       </c>
       <c r="G252" t="n">
-        <v>2.07447981834412</v>
+        <v>2.07447957992554</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>2.03262186050415</v>
+        <v>2.03262209892273</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.5</v>
       </c>
       <c r="G258" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>2.46794438362122</v>
+        <v>2.46794414520264</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G260" t="n">
-        <v>2.80448198318481</v>
+        <v>2.80448246002197</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61193585395813</v>
+        <v>2.61193561553955</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G266" t="n">
-        <v>2.52654528617859</v>
+        <v>2.52654576301575</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.57844948768616</v>
+        <v>2.57844924926758</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G269" t="n">
-        <v>2.55835795402527</v>
+        <v>2.55835771560669</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G270" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.53659176826477</v>
+        <v>2.53659152984619</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51315116882324</v>
+        <v>2.51315140724182</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G275" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G276" t="n">
-        <v>2.59686708450317</v>
+        <v>2.59686684608459</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G279" t="n">
-        <v>2.53826570510864</v>
+        <v>2.53826594352722</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G285" t="n">
-        <v>2.48636221885681</v>
+        <v>2.48636198043823</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G286" t="n">
-        <v>2.5031054019928</v>
+        <v>2.50310516357422</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G287" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.53659176826477</v>
+        <v>2.53659152984619</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G290" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>2.4947338104248</v>
+        <v>2.49473404884338</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>2.50143074989319</v>
+        <v>2.50143098831177</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G294" t="n">
-        <v>2.54328894615173</v>
+        <v>2.54328870773315</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G296" t="n">
-        <v>2.54663729667664</v>
+        <v>2.54663753509521</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>2.52821969985962</v>
+        <v>2.5282199382782</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.51984834671021</v>
+        <v>2.51984858512878</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G299" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G301" t="n">
-        <v>2.43110966682434</v>
+        <v>2.43110942840576</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>2.36915993690491</v>
+        <v>2.36915969848633</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.44450449943542</v>
+        <v>2.44450426101685</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G309" t="n">
-        <v>2.4461784362793</v>
+        <v>2.44617819786072</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.46961903572083</v>
+        <v>2.46961879730225</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G311" t="n">
-        <v>2.46794438362122</v>
+        <v>2.46794414520264</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44282984733582</v>
+        <v>2.44282960891724</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>2.8840000629425</v>
       </c>
       <c r="G314" t="n">
-        <v>2.41436648368835</v>
+        <v>2.41436624526978</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40766906738281</v>
+        <v>2.40766882896423</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G317" t="n">
-        <v>2.43278384208679</v>
+        <v>2.43278360366821</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G318" t="n">
-        <v>2.47631597518921</v>
+        <v>2.47631621360779</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42943525314331</v>
+        <v>2.42943501472473</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.5031054019928</v>
+        <v>2.50310516357422</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>2.4461784362793</v>
+        <v>2.44617819786072</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G323" t="n">
-        <v>2.44115543365479</v>
+        <v>2.44115519523621</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G326" t="n">
-        <v>2.46794438362122</v>
+        <v>2.46794414520264</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.44450449943542</v>
+        <v>2.44450426101685</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G331" t="n">
-        <v>2.42943525314331</v>
+        <v>2.42943501472473</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43780660629272</v>
+        <v>2.4378068447113</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39929699897766</v>
+        <v>2.39929747581482</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G336" t="n">
-        <v>2.43780660629272</v>
+        <v>2.4378068447113</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G337" t="n">
-        <v>2.4461784362793</v>
+        <v>2.44617819786072</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42776107788086</v>
+        <v>2.42776083946228</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>2.44450449943542</v>
+        <v>2.44450426101685</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G346" t="n">
-        <v>2.4629213809967</v>
+        <v>2.46292161941528</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>2.90400004386902</v>
       </c>
       <c r="G347" t="n">
-        <v>2.43110966682434</v>
+        <v>2.43110942840576</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>2.4947338104248</v>
+        <v>2.49473404884338</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.46124744415283</v>
+        <v>2.46124720573425</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>2.42776107788086</v>
+        <v>2.42776083946228</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>2.36915993690491</v>
+        <v>2.36915969848633</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>2.31893038749695</v>
+        <v>2.31893014907837</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G370" t="n">
-        <v>2.31725573539734</v>
+        <v>2.31725549697876</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>2.26870059967041</v>
+        <v>2.26870083808899</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26870059967041</v>
+        <v>2.26870083808899</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G373" t="n">
-        <v>2.22349405288696</v>
+        <v>2.22349429130554</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>2.24191188812256</v>
+        <v>2.24191164970398</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G378" t="n">
-        <v>2.28376984596252</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G379" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G382" t="n">
-        <v>2.20005369186401</v>
+        <v>2.20005393028259</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>2.26870059967041</v>
+        <v>2.26870083808899</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G398" t="n">
-        <v>2.25028300285339</v>
+        <v>2.25028324127197</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G399" t="n">
-        <v>2.28376984596252</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G400" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>2.31893038749695</v>
+        <v>2.31893014907837</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27874660491943</v>
+        <v>2.27874636650085</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>2.25195717811584</v>
+        <v>2.251957654953</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G406" t="n">
-        <v>2.22181987762451</v>
+        <v>2.22181963920593</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.4947338104248</v>
+        <v>2.49473404884338</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G413" t="n">
-        <v>2.54328894615173</v>
+        <v>2.54328870773315</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>2.44450449943542</v>
+        <v>2.44450426101685</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>2.42776107788086</v>
+        <v>2.42776083946228</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G421" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25195717811584</v>
+        <v>2.251957654953</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G423" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G424" t="n">
-        <v>2.27874660491943</v>
+        <v>2.27874636650085</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G426" t="n">
-        <v>2.30888438224792</v>
+        <v>2.30888414382935</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G427" t="n">
-        <v>2.3775315284729</v>
+        <v>2.37753129005432</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G429" t="n">
-        <v>2.28042101860046</v>
+        <v>2.28042078018188</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.26870059967041</v>
+        <v>2.26870083808899</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>2.27204918861389</v>
+        <v>2.27204895019531</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G436" t="n">
-        <v>2.31558156013489</v>
+        <v>2.31558179855347</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G439" t="n">
-        <v>2.31725573539734</v>
+        <v>2.31725549697876</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G445" t="n">
-        <v>2.37083435058594</v>
+        <v>2.37083411216736</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G446" t="n">
-        <v>2.36246228218079</v>
+        <v>2.36246252059937</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>2.35743951797485</v>
+        <v>2.35743927955627</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G453" t="n">
-        <v>2.38757705688477</v>
+        <v>2.38757729530334</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G455" t="n">
-        <v>2.3557653427124</v>
+        <v>2.35576510429382</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>2.31055879592896</v>
+        <v>2.31055855751038</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="n">
-        <v>2.32227873802185</v>
+        <v>2.32227897644043</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G468" t="n">
-        <v>2.30720996856689</v>
+        <v>2.30720973014832</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G470" t="n">
-        <v>2.36078810691833</v>
+        <v>2.36078834533691</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G472" t="n">
-        <v>2.3808798789978</v>
+        <v>2.38088011741638</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G473" t="n">
-        <v>2.3808798789978</v>
+        <v>2.38088011741638</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G475" t="n">
-        <v>2.3557653427124</v>
+        <v>2.35576510429382</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G476" t="n">
-        <v>2.31725573539734</v>
+        <v>2.31725549697876</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G477" t="n">
-        <v>2.31055879592896</v>
+        <v>2.31055855751038</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>2.29214119911194</v>
+        <v>2.29214096069336</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G482" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G488" t="n">
-        <v>2.28376984596252</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G489" t="n">
-        <v>2.27874660491943</v>
+        <v>2.27874636650085</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G490" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G491" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.24191188812256</v>
+        <v>2.24191164970398</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>2.7960000038147</v>
       </c>
       <c r="G500" t="n">
-        <v>2.34069633483887</v>
+        <v>2.34069657325745</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G501" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>2.26870059967041</v>
+        <v>2.26870083808899</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G504" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G505" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G510" t="n">
-        <v>2.18665909767151</v>
+        <v>2.18665957450867</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G511" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G512" t="n">
-        <v>2.1849844455719</v>
+        <v>2.18498468399048</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G516" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G524" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G530" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>2.1849844455719</v>
+        <v>2.18498468399048</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>2.1849844455719</v>
+        <v>2.18498468399048</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G543" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G545" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G550" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.5</v>
       </c>
       <c r="G551" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G552" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615447044373</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G558" t="n">
-        <v>2.04266810417175</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>2.04266810417175</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>2.04266810417175</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.04266810417175</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G562" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G566" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G567" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G570" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G571" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G574" t="n">
-        <v>2.05941081047058</v>
+        <v>2.05941104888916</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G577" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G583" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G584" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G587" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G590" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>2.5</v>
       </c>
       <c r="G601" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G603" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615447044373</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G604" t="n">
-        <v>2.04266810417175</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>2.04266810417175</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G609" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G611" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G612" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G613" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G615" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G616" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G617" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G618" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G619" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G621" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G622" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G631" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G637" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G639" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G641" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G647" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G652" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G655" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>2.05941081047058</v>
+        <v>2.05941104888916</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G664" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G667" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G670" t="n">
-        <v>2.01755309104919</v>
+        <v>2.01755285263062</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G671" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G675" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G676" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G684" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G686" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G689" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G692" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G694" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G700" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G705" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G712" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G713" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>1.75803375244141</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G719" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G720" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G723" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G727" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G728" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G734" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G735" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G737" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G738" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G753" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G757" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G758" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G762" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G766" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G768" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G770" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G786" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G799" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G805" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G813" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G818" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G822" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G824" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G826" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G839" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G848" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G850" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G852" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G854" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G861" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G863" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G865" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G866" t="n">
-        <v>1.75803375244141</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>1.74129045009613</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>1.68268942832947</v>
+        <v>1.68268930912018</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G873" t="n">
-        <v>1.73291885852814</v>
+        <v>1.73291897773743</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G875" t="n">
-        <v>1.66594636440277</v>
+        <v>1.66594624519348</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.63245987892151</v>
+        <v>1.6324599981308</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G879" t="n">
-        <v>1.63245987892151</v>
+        <v>1.6324599981308</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G880" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G882" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G884" t="n">
-        <v>1.6492030620575</v>
+        <v>1.64920318126678</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.65338897705078</v>
+        <v>1.6533887386322</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G887" t="n">
-        <v>1.63245987892151</v>
+        <v>1.6324599981308</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G889" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G890" t="n">
-        <v>1.69943249225616</v>
+        <v>1.69943261146545</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.69106113910675</v>
+        <v>1.69106101989746</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.69106113910675</v>
+        <v>1.69106101989746</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G895" t="n">
-        <v>1.74129045009613</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.74129045009613</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G897" t="n">
-        <v>1.76640522480011</v>
+        <v>1.7664053440094</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G898" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G900" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G904" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G905" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G908" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G915" t="n">
-        <v>1.76640522480011</v>
+        <v>1.7664053440094</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74129045009613</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G920" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G921" t="n">
-        <v>1.76640522480011</v>
+        <v>1.7664053440094</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G922" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G928" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G929" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G930" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G932" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G937" t="n">
-        <v>1.76640522480011</v>
+        <v>1.7664053440094</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G939" t="n">
-        <v>1.75803375244141</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G944" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G948" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G955" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G964" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G966" t="n">
-        <v>1.76640522480011</v>
+        <v>1.7664053440094</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G972" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G976" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G978" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G981" t="n">
-        <v>1.85012137889862</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G982" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G983" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G990" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>2.26032900810242</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G995" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>2.5</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>2.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615447044373</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.8919792175293</v>
+        <v>1.89197945594788</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.90035092830658</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.95058035850525</v>
+        <v>1.95058023929596</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.92546534538269</v>
+        <v>1.9254652261734</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.93383705615997</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500636577606</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174990653992</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.86686432361603</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.68268942832947</v>
+        <v>1.68268930912018</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.23062372207642</v>
+        <v>1.23062360286713</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.23480951786041</v>
+        <v>1.23480939865112</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.13435029983521</v>
+        <v>1.13435041904449</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.19295132160187</v>
+        <v>1.19295144081116</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.19295132160187</v>
+        <v>1.19295144081116</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.48500001430511</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.24318110942841</v>
+        <v>1.24318099021912</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1075" t="n">
-        <v>1.35619747638702</v>
+        <v>1.35619735717773</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.6282742023468</v>
+        <v>1.62827408313751</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.49432861804962</v>
+        <v>1.49432873725891</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.52362942695618</v>
+        <v>1.52362930774689</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.55292999744415</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.54037249088287</v>
+        <v>1.54037237167358</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177146911621</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.46502804756165</v>
+        <v>1.46502816677094</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1108" t="n">
-        <v>1.42735588550568</v>
+        <v>1.42735600471497</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.75</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.46502804756165</v>
+        <v>1.46502816677094</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177146911621</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.49014294147491</v>
+        <v>1.49014282226562</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.49432861804962</v>
+        <v>1.49432873725891</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.49014294147491</v>
+        <v>1.49014282226562</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>1.75</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.46502804756165</v>
+        <v>1.46502816677094</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.49014294147491</v>
+        <v>1.49014282226562</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.54037249088287</v>
+        <v>1.54037237167358</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177146911621</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.49014294147491</v>
+        <v>1.49014282226562</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177146911621</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1138" t="n">
-        <v>1.42735588550568</v>
+        <v>1.42735600471497</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.54037249088287</v>
+        <v>1.54037237167358</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.47758543491364</v>
+        <v>1.47758555412292</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.49014294147491</v>
+        <v>1.49014282226562</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.49432861804962</v>
+        <v>1.49432873725891</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.46921384334564</v>
+        <v>1.46921408176422</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.46921384334564</v>
+        <v>1.46921408176422</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.36875486373901</v>
+        <v>1.36875474452972</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.36456894874573</v>
+        <v>1.36456906795502</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1163" t="n">
-        <v>1.35619747638702</v>
+        <v>1.35619735717773</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.381312251091</v>
+        <v>1.38131201267242</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.41479861736298</v>
+        <v>1.41479873657227</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.41479861736298</v>
+        <v>1.41479873657227</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1192" t="n">
-        <v>1.42735588550568</v>
+        <v>1.42735600471497</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>1.70500004291534</v>
       </c>
       <c r="G1193" t="n">
-        <v>1.42735588550568</v>
+        <v>1.42735600471497</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.46921384334564</v>
+        <v>1.46921408176422</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.55292999744415</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.5027003288269</v>
+        <v>1.50270020961761</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.52781522274017</v>
+        <v>1.52781498432159</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.49014294147491</v>
+        <v>1.49014282226562</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>1.75</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.46502804756165</v>
+        <v>1.46502816677094</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>1.67499995231628</v>
       </c>
       <c r="G1222" t="n">
-        <v>1.40224099159241</v>
+        <v>1.40224123001099</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32167,7 +32167,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1223" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665669441223</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1247" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.6282742023468</v>
+        <v>1.62827408313751</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.6492030620575</v>
+        <v>1.64920318126678</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.54037249088287</v>
+        <v>1.54037237167358</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.55292999744415</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33649,7 +33649,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.52362942695618</v>
+        <v>1.52362930774689</v>
       </c>
       <c r="H1280" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.49014294147491</v>
+        <v>1.49014282226562</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.79499995708466</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.5027003288269</v>
+        <v>1.50270020961761</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.55292999744415</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.54037249088287</v>
+        <v>1.54037237167358</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.52781522274017</v>
+        <v>1.52781498432159</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.54037249088287</v>
+        <v>1.54037237167358</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.55292999744415</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1351" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1358" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1359" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1365" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1366" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G1377" t="n">
-        <v>1.57804465293884</v>
+        <v>1.57804453372955</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.63664567470551</v>
+        <v>1.63664579391479</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.54037249088287</v>
+        <v>1.54037237167358</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.55292999744415</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37003,7 +37003,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.52781522274017</v>
+        <v>1.52781498432159</v>
       </c>
       <c r="H1409" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.59478771686554</v>
+        <v>1.59478783607483</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130146980286</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.55292999744415</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315918922424</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59060204029083</v>
+        <v>1.59060180187225</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.6282742023468</v>
+        <v>1.62827408313751</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.66594636440277</v>
+        <v>1.66594624519348</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.74129045009613</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.73291885852814</v>
+        <v>1.73291897773743</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.76640522480011</v>
+        <v>1.7664053440094</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.94220876693726</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G1453" t="n">
-        <v>2.48636221885681</v>
+        <v>2.48636198043823</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.76262450218201</v>
+        <v>2.76262402534485</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1456" t="n">
-        <v>3.00540065765381</v>
+        <v>3.00540041923523</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38303,7 +38303,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G1459" t="n">
-        <v>3.15608930587769</v>
+        <v>3.15608906745911</v>
       </c>
       <c r="H1459" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>3.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.93005609512329</v>
+        <v>2.93005633354187</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.25</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.72076630592346</v>
+        <v>2.72076654434204</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.18957543373108</v>
+        <v>3.18957567214966</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38563,7 +38563,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.30677795410156</v>
+        <v>3.3067774772644</v>
       </c>
       <c r="H1469" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.33189272880554</v>
+        <v>3.33189249038696</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.30677795410156</v>
+        <v>3.3067774772644</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.33189272880554</v>
+        <v>3.33189249038696</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.20631861686707</v>
+        <v>3.20631837844849</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.08074498176575</v>
+        <v>3.08074474334717</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.05563044548035</v>
+        <v>3.05562996864319</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.08074498176575</v>
+        <v>3.08074474334717</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842816352844</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.98865723609924</v>
+        <v>2.98865747451782</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.98028588294983</v>
+        <v>2.98028564453125</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.05563044548035</v>
+        <v>3.05562996864319</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>3.5</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.93005609512329</v>
+        <v>2.93005633354187</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842816352844</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1499" t="n">
-        <v>2.80448198318481</v>
+        <v>2.80448246002197</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39395,7 +39395,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.73750972747803</v>
+        <v>2.73750948905945</v>
       </c>
       <c r="H1501" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.93005609512329</v>
+        <v>2.93005633354187</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>3.5</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.93005609512329</v>
+        <v>2.93005633354187</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842816352844</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1514" t="n">
-        <v>2.85471177101135</v>
+        <v>2.85471200942993</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.82959723472595</v>
+        <v>2.82959747314453</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G1519" t="n">
-        <v>2.69565176963806</v>
+        <v>2.69565200805664</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1527" t="n">
-        <v>2.85471177101135</v>
+        <v>2.85471200942993</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40097,7 +40097,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1528" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1530" t="n">
-        <v>2.85471177101135</v>
+        <v>2.85471200942993</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.7961106300354</v>
+        <v>2.79611086845398</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.72913789749146</v>
+        <v>2.72913813591003</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.44450449943542</v>
+        <v>2.44450426101685</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40487,7 +40487,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.57844948768616</v>
+        <v>2.57844924926758</v>
       </c>
       <c r="H1543" t="s">
         <v>8</v>
@@ -40513,7 +40513,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1544" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.53659176826477</v>
+        <v>2.53659152984619</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.51984834671021</v>
+        <v>2.51984858512878</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40669,7 +40669,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.57844948768616</v>
+        <v>2.57844924926758</v>
       </c>
       <c r="H1550" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.51984834671021</v>
+        <v>2.51984858512878</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40773,7 +40773,7 @@
         <v>3</v>
       </c>
       <c r="G1554" t="n">
-        <v>2.51147699356079</v>
+        <v>2.51147675514221</v>
       </c>
       <c r="H1554" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.52821969985962</v>
+        <v>2.5282199382782</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.44450449943542</v>
+        <v>2.44450426101685</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.25</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.72076630592346</v>
+        <v>2.72076654434204</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1562" t="n">
-        <v>2.80448198318481</v>
+        <v>2.80448246002197</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.52065801620483</v>
+        <v>4.52065849304199</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.95139002799988</v>
+        <v>3.95138955116272</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G1568" t="n">
-        <v>4.7550630569458</v>
+        <v>4.75506258010864</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.52065801620483</v>
+        <v>4.52065849304199</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41189,7 +41189,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1570" t="n">
-        <v>4.11882162094116</v>
+        <v>4.11882209777832</v>
       </c>
       <c r="H1570" t="s">
         <v>8</v>
@@ -41215,7 +41215,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.30677795410156</v>
+        <v>3.3067774772644</v>
       </c>
       <c r="H1571" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.61652660369873</v>
+        <v>3.61652684211731</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1584" t="n">
-        <v>2.80448198318481</v>
+        <v>2.80448246002197</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>3.5</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.93005609512329</v>
+        <v>2.93005633354187</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41631,7 +41631,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1587" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.91331315040588</v>
+        <v>2.91331338882446</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.30677795410156</v>
+        <v>3.3067774772644</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.4072368144989</v>
+        <v>3.40723705291748</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41787,7 +41787,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1593" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.18957543373108</v>
+        <v>3.18957567214966</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.28166317939758</v>
+        <v>3.281662940979</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41917,7 +41917,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.27329134941101</v>
+        <v>3.27329158782959</v>
       </c>
       <c r="H1598" t="s">
         <v>8</v>
@@ -41943,7 +41943,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1599" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.18120408058167</v>
+        <v>3.18120360374451</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.04725885391235</v>
+        <v>3.04725861549377</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.98028588294983</v>
+        <v>2.98028564453125</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42151,7 +42151,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.20631861686707</v>
+        <v>3.20631837844849</v>
       </c>
       <c r="H1607" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.32352066040039</v>
+        <v>3.32352089881897</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42203,7 +42203,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.33189272880554</v>
+        <v>3.33189249038696</v>
       </c>
       <c r="H1609" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.23143339157104</v>
+        <v>3.23143315315247</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.28166317939758</v>
+        <v>3.281662940979</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.22306180000305</v>
+        <v>3.22306156158447</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.05563044548035</v>
+        <v>3.05562996864319</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842816352844</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42411,7 +42411,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1617" t="n">
-        <v>3.00540065765381</v>
+        <v>3.00540041923523</v>
       </c>
       <c r="H1617" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.04725885391235</v>
+        <v>3.04725861549377</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.10585999488831</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.13097453117371</v>
+        <v>3.13097429275513</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.10585999488831</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.03051543235779</v>
+        <v>3.03051495552063</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1627" t="n">
-        <v>3.00540065765381</v>
+        <v>3.00540041923523</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1628" t="n">
-        <v>3.00540065765381</v>
+        <v>3.00540041923523</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.98865723609924</v>
+        <v>2.98865747451782</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42879,7 +42879,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1635" t="s">
         <v>8</v>
@@ -42931,7 +42931,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1637" t="n">
-        <v>2.85471177101135</v>
+        <v>2.85471200942993</v>
       </c>
       <c r="H1637" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.76262450218201</v>
+        <v>2.76262402534485</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.54496312141418</v>
+        <v>2.54496335983276</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354293823242</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.10585999488831</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1648" t="n">
-        <v>3.00540065765381</v>
+        <v>3.00540041923523</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43243,7 +43243,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1649" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G1650" t="n">
-        <v>3.00540065765381</v>
+        <v>3.00540041923523</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.91331315040588</v>
+        <v>2.91331338882446</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G1657" t="n">
-        <v>2.80448198318481</v>
+        <v>2.80448246002197</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.98865723609924</v>
+        <v>2.98865747451782</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1667" t="n">
-        <v>2.93079710006714</v>
+        <v>2.93079733848572</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G1670" t="n">
-        <v>2.89681673049927</v>
+        <v>2.89681696891785</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.99026226997375</v>
+        <v>2.99026250839233</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.99026226997375</v>
+        <v>2.99026250839233</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.93929195404053</v>
+        <v>2.93929219245911</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.93929195404053</v>
+        <v>2.93929219245911</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>3.5</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.9732723236084</v>
+        <v>2.97327256202698</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.93929195404053</v>
+        <v>2.93929219245911</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44075,7 +44075,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1681" t="n">
-        <v>2.93079710006714</v>
+        <v>2.93079733848572</v>
       </c>
       <c r="H1681" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.90531206130981</v>
+        <v>2.90531182289124</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1684" t="n">
-        <v>2.93079710006714</v>
+        <v>2.93079733848572</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44179,7 +44179,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.90531206130981</v>
+        <v>2.90531182289124</v>
       </c>
       <c r="H1685" t="s">
         <v>8</v>
@@ -44387,7 +44387,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1693" t="n">
-        <v>3.29608488082886</v>
+        <v>3.29608511924744</v>
       </c>
       <c r="H1693" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1694" t="n">
-        <v>3.31307506561279</v>
+        <v>3.31307482719421</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.14317393302917</v>
+        <v>3.1431736946106</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1696" t="n">
-        <v>3.06671810150146</v>
+        <v>3.06671786308289</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44491,7 +44491,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.93929195404053</v>
+        <v>2.93929219245911</v>
       </c>
       <c r="H1697" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G1698" t="n">
-        <v>3.06671810150146</v>
+        <v>3.06671786308289</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.75</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.18564915657043</v>
+        <v>3.18564891815186</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>3.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.9732723236084</v>
+        <v>2.97327256202698</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>2.75</v>
       </c>
       <c r="G1704" t="n">
-        <v>2.33614253997803</v>
+        <v>2.33614277839661</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.1747362613678</v>
+        <v>2.17473649978638</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.82643890380859</v>
+        <v>1.82643902301788</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.86041903495789</v>
+        <v>1.8604189157486</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.78396332263947</v>
+        <v>1.78396344184875</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45141,7 +45141,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1722" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.89439916610718</v>
+        <v>1.89439940452576</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.86041903495789</v>
+        <v>1.8604189157486</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.87740933895111</v>
+        <v>1.87740921974182</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.89439916610718</v>
+        <v>1.89439940452576</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>2.25</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.91138935089111</v>
+        <v>1.91138911247253</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.25</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.91138935089111</v>
+        <v>1.91138911247253</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.91988444328308</v>
+        <v>1.91988456249237</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.25</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.91138935089111</v>
+        <v>1.91138911247253</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1733" t="n">
-        <v>1.85192406177521</v>
+        <v>1.85192394256592</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1734" t="n">
-        <v>1.85192406177521</v>
+        <v>1.85192394256592</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.3701229095459</v>
+        <v>2.37012267112732</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.31915235519409</v>
+        <v>2.31915259361267</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45817,7 +45817,7 @@
         <v>2.75</v>
       </c>
       <c r="G1748" t="n">
-        <v>2.33614253997803</v>
+        <v>2.33614277839661</v>
       </c>
       <c r="H1748" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>2.75</v>
       </c>
       <c r="G1749" t="n">
-        <v>2.33614253997803</v>
+        <v>2.33614277839661</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.31915235519409</v>
+        <v>2.31915259361267</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.21721148490906</v>
+        <v>2.21721172332764</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46103,7 +46103,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.31065726280212</v>
+        <v>2.3106575012207</v>
       </c>
       <c r="H1759" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.31065726280212</v>
+        <v>2.3106575012207</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.31065726280212</v>
+        <v>2.3106575012207</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46623,7 +46623,7 @@
         <v>2.5</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1779" t="s">
         <v>8</v>
@@ -46883,7 +46883,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1789" t="s">
         <v>8</v>
@@ -46909,7 +46909,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1790" t="s">
         <v>8</v>
@@ -47117,7 +47117,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1798" t="s">
         <v>8</v>
@@ -47143,7 +47143,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1799" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.1152708530426</v>
+        <v>2.11527109146118</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47403,7 +47403,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1809" t="s">
         <v>8</v>
@@ -47429,7 +47429,7 @@
         <v>2.5</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1810" t="s">
         <v>8</v>
@@ -47481,7 +47481,7 @@
         <v>2.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1812" t="s">
         <v>8</v>
@@ -47507,7 +47507,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.1152708530426</v>
+        <v>2.11527109146118</v>
       </c>
       <c r="H1813" t="s">
         <v>8</v>
@@ -47533,7 +47533,7 @@
         <v>2.5</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1814" t="s">
         <v>8</v>
@@ -47637,7 +47637,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1818" t="s">
         <v>8</v>
@@ -47663,7 +47663,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1819" t="s">
         <v>8</v>
@@ -47715,7 +47715,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1821" t="s">
         <v>8</v>
@@ -47845,7 +47845,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1826" t="s">
         <v>8</v>
@@ -47871,7 +47871,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1827" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48131,7 +48131,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.91988444328308</v>
+        <v>1.91988456249237</v>
       </c>
       <c r="H1837" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1839" t="n">
-        <v>1.92837965488434</v>
+        <v>1.92837941646576</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1844" t="n">
-        <v>2.02182555198669</v>
+        <v>2.02182531356812</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48339,7 +48339,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1845" t="s">
         <v>8</v>
@@ -48417,7 +48417,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.1152708530426</v>
+        <v>2.11527109146118</v>
       </c>
       <c r="H1848" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48573,7 +48573,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1854" t="s">
         <v>8</v>
@@ -48755,7 +48755,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.07704329490662</v>
+        <v>2.07704281806946</v>
       </c>
       <c r="H1861" t="s">
         <v>8</v>
@@ -48911,7 +48911,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.02182555198669</v>
+        <v>2.02182531356812</v>
       </c>
       <c r="H1867" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49041,7 +49041,7 @@
         <v>2.5</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1872" t="s">
         <v>8</v>
@@ -49067,7 +49067,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1873" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49223,7 +49223,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.15349912643433</v>
+        <v>2.15349888801575</v>
       </c>
       <c r="H1879" t="s">
         <v>8</v>
@@ -49275,7 +49275,7 @@
         <v>2.5</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1881" t="s">
         <v>8</v>
@@ -49301,7 +49301,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.12801384925842</v>
+        <v>2.12801361083984</v>
       </c>
       <c r="H1882" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49535,7 +49535,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.06430053710938</v>
+        <v>2.06430077552795</v>
       </c>
       <c r="H1891" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.12801384925842</v>
+        <v>2.12801361083984</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49613,7 +49613,7 @@
         <v>2.5</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1894" t="s">
         <v>8</v>
@@ -49639,7 +49639,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1895" t="s">
         <v>8</v>
@@ -49665,7 +49665,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.15349912643433</v>
+        <v>2.15349888801575</v>
       </c>
       <c r="H1896" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.17898416519165</v>
+        <v>2.17898392677307</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50029,7 +50029,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1910" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50107,7 +50107,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1913" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>2.5</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50159,7 +50159,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.14075589179993</v>
+        <v>2.14075613021851</v>
       </c>
       <c r="H1915" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.17898416519165</v>
+        <v>2.17898392677307</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50341,7 +50341,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1922" t="s">
         <v>8</v>
@@ -50393,7 +50393,7 @@
         <v>2.5</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1924" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.22145938873291</v>
+        <v>2.22145915031433</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.625</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.27267360687256</v>
+        <v>2.27267384529114</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.24670052528381</v>
+        <v>2.24670028686523</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.24237155914307</v>
+        <v>2.24237132072449</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.24237155914307</v>
+        <v>2.24237132072449</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.36358046531677</v>
+        <v>2.36358070373535</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.24237155914307</v>
+        <v>2.24237132072449</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.16012239456177</v>
+        <v>2.16012215614319</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.1774377822876</v>
+        <v>2.17743802070618</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>2.375</v>
       </c>
       <c r="G1994" t="n">
-        <v>2.05622887611389</v>
+        <v>2.05622863769531</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1995" t="n">
-        <v>2.16012239456177</v>
+        <v>2.16012215614319</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.31163382530212</v>
+        <v>2.3116340637207</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.31596255302429</v>
+        <v>2.31596279144287</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.31163382530212</v>
+        <v>2.3116340637207</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2023" t="n">
-        <v>2.28566074371338</v>
+        <v>2.2856605052948</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>2.625</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.27267360687256</v>
+        <v>2.27267384529114</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.24670052528381</v>
+        <v>2.24670028686523</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2039" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G2046" t="n">
-        <v>2.1774377822876</v>
+        <v>2.17743802070618</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2061" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.06488633155823</v>
+        <v>2.06488656997681</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>2.375</v>
       </c>
       <c r="G2081" t="n">
-        <v>2.05622887611389</v>
+        <v>2.05622863769531</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G2083" t="n">
-        <v>2.03025507926941</v>
+        <v>2.03025531768799</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2086" t="n">
-        <v>2.02592611312866</v>
+        <v>2.02592635154724</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2089" t="n">
-        <v>2.06921529769897</v>
+        <v>2.06921553611755</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2091" t="n">
-        <v>2.06921529769897</v>
+        <v>2.06921553611755</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2092" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2093" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2094" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.02592611312866</v>
+        <v>2.02592635154724</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2112" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.99129486083984</v>
+        <v>1.99129498004913</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.99129486083984</v>
+        <v>1.99129498004913</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.02592611312866</v>
+        <v>2.02592635154724</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2127" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2129" t="n">
-        <v>2.06921529769897</v>
+        <v>2.06921553611755</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -56685,7 +56685,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2166" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56867,7 +56867,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2173" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2173" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -56971,7 +56971,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2177" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2177" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2180" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2182" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -71222,6 +71222,32 @@
         <v>6.98999977111816</v>
       </c>
       <c r="H2725" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2726">
+      <c r="A2726" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B2726" t="n">
+        <v>288612</v>
+      </c>
+      <c r="C2726" t="n">
+        <v>6.98999977111816</v>
+      </c>
+      <c r="D2726" t="n">
+        <v>6.67000007629395</v>
+      </c>
+      <c r="E2726" t="n">
+        <v>6.92999982833862</v>
+      </c>
+      <c r="F2726" t="n">
+        <v>6.71000003814697</v>
+      </c>
+      <c r="G2726" t="n">
+        <v>6.71000003814697</v>
+      </c>
+      <c r="H2726" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -63270,8 +63270,31 @@
       <c r="E2735" t="n">
         <v>6.65999984741211</v>
       </c>
-      <c r="F2735"/>
+      <c r="F2735" t="n">
+        <v>6.67000007629395</v>
+      </c>
       <c r="G2735" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2736">
+      <c r="A2736" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2736" t="n">
+        <v>53975</v>
+      </c>
+      <c r="C2736" t="n">
+        <v>6.73000001907349</v>
+      </c>
+      <c r="D2736" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="E2736" t="n">
+        <v>6.67000007629395</v>
+      </c>
+      <c r="F2736"/>
+      <c r="G2736" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -63293,8 +63293,31 @@
       <c r="E2736" t="n">
         <v>6.67000007629395</v>
       </c>
-      <c r="F2736"/>
+      <c r="F2736" t="n">
+        <v>6.63000011444092</v>
+      </c>
       <c r="G2736" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2737">
+      <c r="A2737" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2737" t="n">
+        <v>70655</v>
+      </c>
+      <c r="C2737" t="n">
+        <v>6.67000007629395</v>
+      </c>
+      <c r="D2737" t="n">
+        <v>6.44999980926514</v>
+      </c>
+      <c r="E2737" t="n">
+        <v>6.57999992370605</v>
+      </c>
+      <c r="F2737"/>
+      <c r="G2737" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -63316,8 +63316,31 @@
       <c r="E2737" t="n">
         <v>6.57999992370605</v>
       </c>
-      <c r="F2737"/>
+      <c r="F2737" t="n">
+        <v>6.48999977111816</v>
+      </c>
       <c r="G2737" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2738">
+      <c r="A2738" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2738" t="n">
+        <v>61176</v>
+      </c>
+      <c r="C2738" t="n">
+        <v>6.69999980926514</v>
+      </c>
+      <c r="D2738" t="n">
+        <v>6.42999982833862</v>
+      </c>
+      <c r="E2738" t="n">
+        <v>6.42999982833862</v>
+      </c>
+      <c r="F2738"/>
+      <c r="G2738" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -63339,8 +63339,31 @@
       <c r="E2738" t="n">
         <v>6.42999982833862</v>
       </c>
-      <c r="F2738"/>
+      <c r="F2738" t="n">
+        <v>6.6399998664856</v>
+      </c>
       <c r="G2738" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2739">
+      <c r="A2739" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2739" t="n">
+        <v>102599</v>
+      </c>
+      <c r="C2739" t="n">
+        <v>6.71000003814697</v>
+      </c>
+      <c r="D2739" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="E2739" t="n">
+        <v>6.55000019073486</v>
+      </c>
+      <c r="F2739"/>
+      <c r="G2739" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -63369,6 +63369,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2740">
+      <c r="A2740" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2740" t="n">
+        <v>37139</v>
+      </c>
+      <c r="C2740" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="D2740" t="n">
+        <v>6.6100001335144</v>
+      </c>
+      <c r="E2740" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="F2740" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="G2740" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>2.93566393852234</v>
+        <v>2.93566417694092</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G9" t="n">
-        <v>2.91140198707581</v>
+        <v>2.91140222549438</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G10" t="n">
-        <v>2.98418736457825</v>
+        <v>2.98418712615967</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G11" t="n">
-        <v>2.95022058486938</v>
+        <v>2.95022082328796</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74965739250183</v>
+        <v>2.74965763092041</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G17" t="n">
-        <v>2.57173871994019</v>
+        <v>2.57173848152161</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G18" t="n">
-        <v>2.54909443855286</v>
+        <v>2.54909420013428</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G19" t="n">
-        <v>2.55556416511536</v>
+        <v>2.55556440353394</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G20" t="n">
-        <v>2.55556416511536</v>
+        <v>2.55556440353394</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.57173871994019</v>
+        <v>2.57173848152161</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G27" t="n">
-        <v>2.20619583129883</v>
+        <v>2.20619606971741</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24339723587036</v>
+        <v>2.24339699745178</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45043015480042</v>
+        <v>2.45042991638184</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G36" t="n">
-        <v>2.4649875164032</v>
+        <v>2.46498727798462</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G38" t="n">
-        <v>2.57659077644348</v>
+        <v>2.57659101486206</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.49086618423462</v>
+        <v>2.49086594581604</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G47" t="n">
-        <v>2.4649875164032</v>
+        <v>2.46498727798462</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52159762382507</v>
+        <v>2.52159786224365</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57497334480286</v>
+        <v>2.57497358322144</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G51" t="n">
-        <v>2.61379218101501</v>
+        <v>2.61379241943359</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.6606981754303</v>
+        <v>2.66069793701172</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>2.60408735275269</v>
+        <v>2.60408759117126</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54747700691223</v>
+        <v>2.54747724533081</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>2.54747700691223</v>
+        <v>2.54747724533081</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>2.54747700691223</v>
+        <v>2.54747724533081</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G62" t="n">
-        <v>2.58467817306519</v>
+        <v>2.58467841148376</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G63" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G64" t="n">
-        <v>2.57820844650269</v>
+        <v>2.57820820808411</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>2.57497334480286</v>
+        <v>2.57497358322144</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52968502044678</v>
+        <v>2.52968525886536</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>2.53130221366882</v>
+        <v>2.5313024520874</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G73" t="n">
-        <v>2.55556416511536</v>
+        <v>2.55556440353394</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G74" t="n">
-        <v>2.60408735275269</v>
+        <v>2.60408759117126</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>2.60408735275269</v>
+        <v>2.60408759117126</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G78" t="n">
-        <v>2.60408735275269</v>
+        <v>2.60408759117126</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.15199995040894</v>
       </c>
       <c r="G83" t="n">
-        <v>2.54909443855286</v>
+        <v>2.54909420013428</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G86" t="n">
-        <v>2.53777241706848</v>
+        <v>2.5377721786499</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.1340000629425</v>
       </c>
       <c r="G87" t="n">
-        <v>2.53453755378723</v>
+        <v>2.53453731536865</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G94" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G95" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G96" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G98" t="n">
-        <v>2.38411498069763</v>
+        <v>2.38411474227905</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.86800003051758</v>
       </c>
       <c r="G103" t="n">
-        <v>2.40097188949585</v>
+        <v>2.40097165107727</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G108" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>2.28544402122498</v>
+        <v>2.2854437828064</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>2.75</v>
       </c>
       <c r="G111" t="n">
-        <v>2.30218720436096</v>
+        <v>2.30218696594238</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G114" t="n">
-        <v>2.28879237174988</v>
+        <v>2.2887921333313</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G118" t="n">
-        <v>2.17493891716003</v>
+        <v>2.17493867874146</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G120" t="n">
-        <v>2.26702618598938</v>
+        <v>2.26702642440796</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G125" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>2.07615447044373</v>
+        <v>2.07615423202515</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.07615447044373</v>
+        <v>2.07615423202515</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G136" t="n">
-        <v>2.13140678405762</v>
+        <v>2.13140654563904</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G137" t="n">
-        <v>2.13810396194458</v>
+        <v>2.138103723526</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G147" t="n">
-        <v>2.14647507667542</v>
+        <v>2.14647531509399</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G148" t="n">
-        <v>2.14647507667542</v>
+        <v>2.14647531509399</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G153" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G154" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G155" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G156" t="n">
-        <v>2.26702618598938</v>
+        <v>2.26702642440796</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G157" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G160" t="n">
-        <v>2.26702618598938</v>
+        <v>2.26702642440796</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G163" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G173" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23521423339844</v>
+        <v>2.23521447181702</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>2.57200002670288</v>
       </c>
       <c r="G179" t="n">
-        <v>2.15317296981812</v>
+        <v>2.15317273139954</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G184" t="n">
-        <v>2.17828750610352</v>
+        <v>2.17828726768494</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G191" t="n">
-        <v>2.17493891716003</v>
+        <v>2.17493867874146</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G192" t="n">
-        <v>2.09959435462952</v>
+        <v>2.0995945930481</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G198" t="n">
-        <v>2.03764486312866</v>
+        <v>2.03764510154724</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G199" t="n">
-        <v>2.06610822677612</v>
+        <v>2.0661084651947</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G200" t="n">
-        <v>2.06610822677612</v>
+        <v>2.0661084651947</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G205" t="n">
-        <v>2.06108522415161</v>
+        <v>2.06108546257019</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G206" t="n">
-        <v>2.03429627418518</v>
+        <v>2.03429651260376</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>2.39800000190735</v>
       </c>
       <c r="G207" t="n">
-        <v>2.00750732421875</v>
+        <v>2.00750708580017</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G208" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>2.04936456680298</v>
+        <v>2.04936504364014</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>2.01587891578674</v>
+        <v>2.01587867736816</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>1.99411249160767</v>
+        <v>1.99411225318909</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G233" t="n">
-        <v>1.94890582561493</v>
+        <v>1.94890594482422</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G234" t="n">
-        <v>1.94890582561493</v>
+        <v>1.94890594482422</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G236" t="n">
-        <v>1.94053447246552</v>
+        <v>1.9405345916748</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G242" t="n">
-        <v>2.06610822677612</v>
+        <v>2.0661084651947</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G244" t="n">
-        <v>2.01253008842468</v>
+        <v>2.0125298500061</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G245" t="n">
-        <v>2.06610822677612</v>
+        <v>2.0661084651947</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G249" t="n">
-        <v>2.06610822677612</v>
+        <v>2.0661084651947</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G253" t="n">
-        <v>2.02927350997925</v>
+        <v>2.02927327156067</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G254" t="n">
-        <v>2.02927350997925</v>
+        <v>2.02927327156067</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>2.42799997329712</v>
       </c>
       <c r="G255" t="n">
-        <v>2.03262186050415</v>
+        <v>2.03262209892273</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G257" t="n">
-        <v>2.03094744682312</v>
+        <v>2.0309476852417</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>2.46794414520264</v>
+        <v>2.46794438362122</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61193561553955</v>
+        <v>2.61193537712097</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>2.58347225189209</v>
+        <v>2.58347201347351</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G272" t="n">
-        <v>2.56505465507507</v>
+        <v>2.56505489349365</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G276" t="n">
-        <v>2.59686684608459</v>
+        <v>2.59686660766602</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G277" t="n">
-        <v>2.58347225189209</v>
+        <v>2.58347201347351</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.63705062866211</v>
+        <v>2.63705086708069</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G284" t="n">
-        <v>2.53491759300232</v>
+        <v>2.53491735458374</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G289" t="n">
-        <v>2.53491759300232</v>
+        <v>2.53491735458374</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>2.49473404884338</v>
+        <v>2.4947338104248</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>2.50143074989319</v>
+        <v>2.50143098831177</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G293" t="n">
-        <v>2.47296762466431</v>
+        <v>2.47296738624573</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G294" t="n">
-        <v>2.54328870773315</v>
+        <v>2.54328894615173</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G296" t="n">
-        <v>2.54663729667664</v>
+        <v>2.54663753509521</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G298" t="n">
-        <v>2.51984858512878</v>
+        <v>2.51984834671021</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G300" t="n">
-        <v>2.45287561416626</v>
+        <v>2.45287585258484</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G302" t="n">
-        <v>2.45789885520935</v>
+        <v>2.45789861679077</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>2.36915969848633</v>
+        <v>2.36915993690491</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.38590288162231</v>
+        <v>2.38590264320374</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G306" t="n">
-        <v>2.39260005950928</v>
+        <v>2.39260029792786</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>2.39594888687134</v>
+        <v>2.39594864845276</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.46961879730225</v>
+        <v>2.46961903572083</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G311" t="n">
-        <v>2.46794414520264</v>
+        <v>2.46794438362122</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40766882896423</v>
+        <v>2.40766906738281</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39594888687134</v>
+        <v>2.39594864845276</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G317" t="n">
-        <v>2.43278384208679</v>
+        <v>2.43278360366821</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G326" t="n">
-        <v>2.46794414520264</v>
+        <v>2.46794438362122</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G330" t="n">
-        <v>2.47799015045166</v>
+        <v>2.47799038887024</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39594888687134</v>
+        <v>2.39594864845276</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G348" t="n">
-        <v>2.44785308837891</v>
+        <v>2.44785284996033</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G350" t="n">
-        <v>2.47799015045166</v>
+        <v>2.47799038887024</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>2.49473404884338</v>
+        <v>2.4947338104248</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G354" t="n">
-        <v>2.47799015045166</v>
+        <v>2.47799038887024</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G355" t="n">
-        <v>2.47296762466431</v>
+        <v>2.47296738624573</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G356" t="n">
-        <v>2.44785308837891</v>
+        <v>2.44785284996033</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>2.96000003814697</v>
       </c>
       <c r="G357" t="n">
-        <v>2.47799015045166</v>
+        <v>2.47799038887024</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>2.36915969848633</v>
+        <v>2.36915993690491</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G366" t="n">
-        <v>2.34404492378235</v>
+        <v>2.34404516220093</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G368" t="n">
-        <v>2.28879237174988</v>
+        <v>2.2887921333313</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>2.31893038749695</v>
+        <v>2.31893014907837</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G374" t="n">
-        <v>2.28879237174988</v>
+        <v>2.2887921333313</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G376" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G378" t="n">
-        <v>2.28376936912537</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G382" t="n">
-        <v>2.20005393028259</v>
+        <v>2.20005369186401</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G391" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G399" t="n">
-        <v>2.28376936912537</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G400" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G401" t="n">
-        <v>2.3423707485199</v>
+        <v>2.34237098693848</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>2.31893038749695</v>
+        <v>2.31893014907837</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G403" t="n">
-        <v>2.27874660491943</v>
+        <v>2.27874636650085</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>2.25195741653442</v>
+        <v>2.251957654953</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G411" t="n">
-        <v>2.37920570373535</v>
+        <v>2.37920546531677</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.49473404884338</v>
+        <v>2.4947338104248</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G413" t="n">
-        <v>2.54328870773315</v>
+        <v>2.54328894615173</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G420" t="n">
-        <v>2.32562756538391</v>
+        <v>2.32562732696533</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G421" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25195741653442</v>
+        <v>2.251957654953</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G424" t="n">
-        <v>2.27874660491943</v>
+        <v>2.27874636650085</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G425" t="n">
-        <v>2.26535201072693</v>
+        <v>2.26535224914551</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>2.78800010681152</v>
       </c>
       <c r="G428" t="n">
-        <v>2.3339991569519</v>
+        <v>2.33399939537048</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G430" t="n">
-        <v>2.28879237174988</v>
+        <v>2.2887921333313</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G431" t="n">
-        <v>2.28879237174988</v>
+        <v>2.2887921333313</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27037477493286</v>
+        <v>2.27037501335144</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>2.29381561279297</v>
+        <v>2.29381537437439</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>2.34404492378235</v>
+        <v>2.34404516220093</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G438" t="n">
-        <v>2.34404492378235</v>
+        <v>2.34404516220093</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G440" t="n">
-        <v>2.35241651535034</v>
+        <v>2.35241675376892</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G443" t="n">
-        <v>2.3457190990448</v>
+        <v>2.34571957588196</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G445" t="n">
-        <v>2.37083411216736</v>
+        <v>2.37083435058594</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G446" t="n">
-        <v>2.36246252059937</v>
+        <v>2.36246275901794</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G448" t="n">
-        <v>2.39260005950928</v>
+        <v>2.39260029792786</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>2.35241651535034</v>
+        <v>2.35241675376892</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>2.35743927955627</v>
+        <v>2.35743951797485</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>2.85199999809265</v>
       </c>
       <c r="G453" t="n">
-        <v>2.38757753372192</v>
+        <v>2.38757729530334</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G454" t="n">
-        <v>2.3457190990448</v>
+        <v>2.34571957588196</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G455" t="n">
-        <v>2.35576510429382</v>
+        <v>2.3557653427124</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G456" t="n">
-        <v>2.33065032958984</v>
+        <v>2.33065056800842</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G457" t="n">
-        <v>2.33065032958984</v>
+        <v>2.33065056800842</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G458" t="n">
-        <v>2.34404492378235</v>
+        <v>2.34404516220093</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>2.38590288162231</v>
+        <v>2.38590264320374</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>2.38590288162231</v>
+        <v>2.38590264320374</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>2.38590288162231</v>
+        <v>2.38590264320374</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>2.31055879592896</v>
+        <v>2.31055855751038</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="n">
-        <v>2.32227897644043</v>
+        <v>2.32227873802185</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G468" t="n">
-        <v>2.30720996856689</v>
+        <v>2.30720973014832</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G470" t="n">
-        <v>2.36078810691833</v>
+        <v>2.36078834533691</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G475" t="n">
-        <v>2.35576510429382</v>
+        <v>2.3557653427124</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G477" t="n">
-        <v>2.31055879592896</v>
+        <v>2.31055855751038</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G478" t="n">
-        <v>2.23521423339844</v>
+        <v>2.23521447181702</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>2.29214119911194</v>
+        <v>2.29214096069336</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G482" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G483" t="n">
-        <v>2.22516846656799</v>
+        <v>2.22516822814941</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G484" t="n">
-        <v>2.22516846656799</v>
+        <v>2.22516822814941</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G488" t="n">
-        <v>2.28376936912537</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>2.72199988365173</v>
       </c>
       <c r="G489" t="n">
-        <v>2.27874660491943</v>
+        <v>2.27874636650085</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G497" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>2.70600008964539</v>
       </c>
       <c r="G498" t="n">
-        <v>2.26535201072693</v>
+        <v>2.26535224914551</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>2.28544402122498</v>
+        <v>2.2854437828064</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G507" t="n">
-        <v>2.16154432296753</v>
+        <v>2.16154456138611</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G508" t="n">
-        <v>2.16321897506714</v>
+        <v>2.16321873664856</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G509" t="n">
-        <v>2.16154432296753</v>
+        <v>2.16154456138611</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G511" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G515" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G552" t="n">
-        <v>2.07615447044373</v>
+        <v>2.07615423202515</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G553" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G557" t="n">
-        <v>2.10126900672913</v>
+        <v>2.10126876831055</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G558" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G563" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G565" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G573" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G576" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G578" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G580" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G585" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G589" t="n">
-        <v>2.17661333084106</v>
+        <v>2.17661309242249</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G602" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G603" t="n">
-        <v>2.07615447044373</v>
+        <v>2.07615423202515</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G604" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G607" t="n">
-        <v>2.03429627418518</v>
+        <v>2.03429651260376</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G611" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G613" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895195007324</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G616" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G618" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895195007324</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G622" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895195007324</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G651" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G652" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895195007324</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G654" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G655" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895195007324</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G657" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G658" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.03429627418518</v>
+        <v>2.03429651260376</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G662" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G663" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G665" t="n">
-        <v>2.03429627418518</v>
+        <v>2.03429651260376</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G672" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G676" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G677" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G678" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G686" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G688" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G694" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G696" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G697" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G720" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G721" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G722" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G734" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G738" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G739" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>2.25</v>
       </c>
       <c r="G740" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>2.25</v>
       </c>
       <c r="G741" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895195007324</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G748" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G756" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G758" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G762" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>2.25</v>
       </c>
       <c r="G765" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G770" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>2.25</v>
       </c>
       <c r="G771" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G777" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G784" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G785" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G788" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.25</v>
       </c>
       <c r="G794" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G796" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G805" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G813" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G822" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G823" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G824" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.25</v>
       </c>
       <c r="G827" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G833" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G838" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G840" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>2.25</v>
       </c>
       <c r="G844" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G848" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G850" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G860" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G864" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G867" t="n">
-        <v>1.74129068851471</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>1.68268930912018</v>
+        <v>1.68268942832947</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G873" t="n">
-        <v>1.73291885852814</v>
+        <v>1.73291897773743</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G881" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G882" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G883" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G884" t="n">
-        <v>1.64920318126678</v>
+        <v>1.6492030620575</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G889" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>1.69106113910675</v>
+        <v>1.69106101989746</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G892" t="n">
-        <v>1.69106113910675</v>
+        <v>1.69106101989746</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G895" t="n">
-        <v>1.74129068851471</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G896" t="n">
-        <v>1.74129068851471</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G898" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G900" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G902" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G903" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G905" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G907" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G908" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G914" t="n">
-        <v>1.77477669715881</v>
+        <v>1.7747768163681</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G918" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G919" t="n">
-        <v>1.74129068851471</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G920" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G932" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G934" t="n">
-        <v>1.77477669715881</v>
+        <v>1.7747768163681</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G936" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G938" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G940" t="n">
-        <v>1.77477669715881</v>
+        <v>1.7747768163681</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G941" t="n">
-        <v>1.77477669715881</v>
+        <v>1.7747768163681</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G942" t="n">
-        <v>1.77477669715881</v>
+        <v>1.7747768163681</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G944" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.25</v>
       </c>
       <c r="G945" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G948" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G950" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G951" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.25</v>
       </c>
       <c r="G953" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.25</v>
       </c>
       <c r="G954" t="n">
-        <v>1.88360750675201</v>
+        <v>1.88360726833344</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G955" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G961" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G962" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G965" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G967" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77477669715881</v>
+        <v>1.7747768163681</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G969" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G971" t="n">
-        <v>1.77477669715881</v>
+        <v>1.7747768163681</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G979" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G982" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G992" t="n">
-        <v>2.10126900672913</v>
+        <v>2.10126876831055</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G993" t="n">
-        <v>2.14312648773193</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.03429627418518</v>
+        <v>2.03429651260376</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.07615447044373</v>
+        <v>2.07615423202515</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.03429627418518</v>
+        <v>2.03429651260376</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1014" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.03429627418518</v>
+        <v>2.03429651260376</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1018" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1019" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1020" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1022" t="n">
-        <v>2.0091814994812</v>
+        <v>2.00918126106262</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.9924384355545</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G1024" t="n">
-        <v>1.98406672477722</v>
+        <v>1.98406648635864</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.89197933673859</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035057067871</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.85849297046661</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895195007324</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.9254652261734</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.93383729457855</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.84174990653992</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337795734406</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.74966216087341</v>
+        <v>1.74966204166412</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.74966216087341</v>
+        <v>1.74966204166412</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.68268930912018</v>
+        <v>1.68268942832947</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.59500002861023</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.33526849746704</v>
+        <v>1.33526861667633</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.23480939865112</v>
+        <v>1.23480951786041</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.13435041904449</v>
+        <v>1.13435053825378</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.19295144081116</v>
+        <v>1.19295132160187</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.19295144081116</v>
+        <v>1.19295132160187</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.22643780708313</v>
+        <v>1.22643792629242</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.22643780708313</v>
+        <v>1.22643792629242</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.32689690589905</v>
+        <v>1.32689702510834</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.61571645736694</v>
+        <v>1.61571669578552</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.62827396392822</v>
+        <v>1.6282742023468</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.61571645736694</v>
+        <v>1.61571669578552</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1088" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.49432873725891</v>
+        <v>1.49432861804962</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.61571645736694</v>
+        <v>1.61571669578552</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1100" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1114" t="n">
-        <v>1.49014282226562</v>
+        <v>1.49014294147491</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.49432873725891</v>
+        <v>1.49432861804962</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.49014282226562</v>
+        <v>1.49014294147491</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.49014282226562</v>
+        <v>1.49014294147491</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.49014282226562</v>
+        <v>1.49014294147491</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.49014282226562</v>
+        <v>1.49014294147491</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.49432873725891</v>
+        <v>1.49432861804962</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.46921408176422</v>
+        <v>1.46921396255493</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.46921408176422</v>
+        <v>1.46921396255493</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G1162" t="n">
-        <v>1.36456918716431</v>
+        <v>1.36456906795502</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.33108258247375</v>
+        <v>1.33108270168304</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.43572759628296</v>
+        <v>1.43572771549225</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.41479873657227</v>
+        <v>1.41479861736298</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.41479873657227</v>
+        <v>1.41479861736298</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.46921408176422</v>
+        <v>1.46921396255493</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1209" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.61571645736694</v>
+        <v>1.61571669578552</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1216" t="n">
-        <v>1.49014282226562</v>
+        <v>1.49014294147491</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.43572759628296</v>
+        <v>1.43572771549225</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32609,7 +32609,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.45665669441223</v>
+        <v>1.45665657520294</v>
       </c>
       <c r="H1240" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1245" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.62827396392822</v>
+        <v>1.6282742023468</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33051,7 +33051,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1257" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1257" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.64920318126678</v>
+        <v>1.6492030620575</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1266" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1272" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1279" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.61990249156952</v>
+        <v>1.61990261077881</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1288" t="n">
-        <v>1.49014282226562</v>
+        <v>1.49014294147491</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34533,7 +34533,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1314" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1314" t="s">
         <v>8</v>
@@ -34559,7 +34559,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1315" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1315" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1318" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1320" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1321" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1330" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1334" t="n">
-        <v>1.53200101852417</v>
+        <v>1.53200089931488</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1335" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.61571645736694</v>
+        <v>1.61571669578552</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1350" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1354" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1378" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153078079224</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1385" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1397" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1399" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -37055,7 +37055,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1411" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1411" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1413" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>1.90499997138977</v>
       </c>
       <c r="G1415" t="n">
-        <v>1.59478783607483</v>
+        <v>1.59478771686554</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.56130146980286</v>
+        <v>1.56130135059357</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1422" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.56548702716827</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1438" t="n">
-        <v>1.59060180187225</v>
+        <v>1.59060192108154</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.58641624450684</v>
+        <v>1.58641612529755</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.61571645736694</v>
+        <v>1.61571669578552</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>1.94500005245209</v>
       </c>
       <c r="G1441" t="n">
-        <v>1.62827396392822</v>
+        <v>1.6282742023468</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1444" t="n">
-        <v>1.79152023792267</v>
+        <v>1.79152047634125</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1445" t="n">
-        <v>1.74129068851471</v>
+        <v>1.74129056930542</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37965,7 +37965,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1446" t="n">
-        <v>1.73291885852814</v>
+        <v>1.73291897773743</v>
       </c>
       <c r="H1446" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.74966216087341</v>
+        <v>1.74966204166412</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.78314852714539</v>
+        <v>1.78314864635468</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.17283248901367</v>
+        <v>3.17283225059509</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>3.25</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.72076654434204</v>
+        <v>2.72076630592346</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.97191405296326</v>
+        <v>2.97191429138184</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1465" t="n">
-        <v>3.18957567214966</v>
+        <v>3.18957543373108</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.23980498313904</v>
+        <v>3.23980522155762</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.93842816352844</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.98865747451782</v>
+        <v>2.98865723609924</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1488" t="n">
-        <v>2.98028564453125</v>
+        <v>2.98028588294983</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.93842816352844</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39291,7 +39291,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1497" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.87145519256592</v>
+        <v>2.8714554309845</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.93842816352844</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39681,7 +39681,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1512" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.82959747314453</v>
+        <v>2.82959723472595</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.87145519256592</v>
+        <v>2.8714554309845</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40279,7 +40279,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.7961106300354</v>
+        <v>2.79611086845398</v>
       </c>
       <c r="H1535" t="s">
         <v>8</v>
@@ -40383,7 +40383,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G1539" t="n">
-        <v>2.72913837432861</v>
+        <v>2.72913813591003</v>
       </c>
       <c r="H1539" t="s">
         <v>8</v>
@@ -40409,7 +40409,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.66216516494751</v>
+        <v>2.66216540336609</v>
       </c>
       <c r="H1540" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.6203076839447</v>
+        <v>2.62030744552612</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1548" t="n">
-        <v>2.51984858512878</v>
+        <v>2.51984834671021</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G1553" t="n">
-        <v>2.51984858512878</v>
+        <v>2.51984834671021</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1557" t="n">
-        <v>3.06400203704834</v>
+        <v>3.06400179862976</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>3.25</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.72076654434204</v>
+        <v>2.72076630592346</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.87145519256592</v>
+        <v>2.8714554309845</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G1564" t="n">
-        <v>3.58304047584534</v>
+        <v>3.5830409526825</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1567" t="n">
-        <v>4.82203578948975</v>
+        <v>4.82203531265259</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41657,7 +41657,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.91331338882446</v>
+        <v>2.91331315040588</v>
       </c>
       <c r="H1588" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.40723705291748</v>
+        <v>3.4072368144989</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G1596" t="n">
-        <v>3.18957567214966</v>
+        <v>3.18957543373108</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41891,7 +41891,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.281662940979</v>
+        <v>3.28166317939758</v>
       </c>
       <c r="H1597" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G1600" t="n">
-        <v>3.18120360374451</v>
+        <v>3.18120384216309</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G1606" t="n">
-        <v>2.98028564453125</v>
+        <v>2.98028588294983</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.23143291473389</v>
+        <v>3.23143339157104</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.281662940979</v>
+        <v>3.28166317939758</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.22306180000305</v>
+        <v>3.22306156158447</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1613" t="n">
-        <v>3.06400203704834</v>
+        <v>3.06400179862976</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42385,7 +42385,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.93842816352844</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1616" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1619" t="n">
-        <v>3.06400203704834</v>
+        <v>3.06400179862976</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.10585951805115</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42515,7 +42515,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.13097405433655</v>
+        <v>3.13097429275513</v>
       </c>
       <c r="H1621" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.10585951805115</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.98865747451782</v>
+        <v>2.98865723609924</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42827,7 +42827,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1633" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.60356426239014</v>
+        <v>2.60356402397156</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43139,7 +43139,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.10585951805115</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1645" t="s">
         <v>8</v>
@@ -43165,7 +43165,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G1646" t="n">
-        <v>3.06400203704834</v>
+        <v>3.06400179862976</v>
       </c>
       <c r="H1646" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.91331338882446</v>
+        <v>2.91331315040588</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.98865747451782</v>
+        <v>2.98865723609924</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1668" t="n">
-        <v>2.82885646820068</v>
+        <v>2.8288562297821</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43841,7 +43841,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.99026274681091</v>
+        <v>2.99026250839233</v>
       </c>
       <c r="H1672" t="s">
         <v>8</v>
@@ -43867,7 +43867,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.99026274681091</v>
+        <v>2.99026250839233</v>
       </c>
       <c r="H1673" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.0582230091095</v>
+        <v>3.05822324752808</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G1688" t="n">
-        <v>3.41501545906067</v>
+        <v>3.41501569747925</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44439,7 +44439,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.14317393302917</v>
+        <v>3.1431736946106</v>
       </c>
       <c r="H1695" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>3.75</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.18564915657043</v>
+        <v>3.18564891815186</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.20022177696228</v>
+        <v>2.2002215385437</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.1747362613678</v>
+        <v>2.17473649978638</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1708" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1711" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.82643890380859</v>
+        <v>1.82643902301788</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.80944871902466</v>
+        <v>1.80944859981537</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.86041903495789</v>
+        <v>1.8604189157486</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.80944871902466</v>
+        <v>1.80944859981537</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45115,7 +45115,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1721" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1721" t="s">
         <v>8</v>
@@ -45167,7 +45167,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.95386457443237</v>
+        <v>1.95386469364166</v>
       </c>
       <c r="H1723" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.89439916610718</v>
+        <v>1.89439940452576</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.86041903495789</v>
+        <v>1.8604189157486</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.87740933895111</v>
+        <v>1.87740921974182</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.89439916610718</v>
+        <v>1.89439940452576</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>2.25</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.91138923168182</v>
+        <v>1.91138911247253</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>2.25</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.91138923168182</v>
+        <v>1.91138911247253</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>2.25</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.91138923168182</v>
+        <v>1.91138911247253</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1743" t="n">
-        <v>2.44657874107361</v>
+        <v>2.44657850265503</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45791,7 +45791,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.31915235519409</v>
+        <v>2.31915259361267</v>
       </c>
       <c r="H1747" t="s">
         <v>8</v>
@@ -45869,7 +45869,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.31915235519409</v>
+        <v>2.31915259361267</v>
       </c>
       <c r="H1750" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1767" t="n">
-        <v>2.24269723892212</v>
+        <v>2.24269700050354</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46389,7 +46389,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G1770" t="n">
-        <v>2.24269723892212</v>
+        <v>2.24269700050354</v>
       </c>
       <c r="H1770" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1772" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.16624140739441</v>
+        <v>2.16624116897583</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46701,7 +46701,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1782" t="n">
-        <v>2.03881549835205</v>
+        <v>2.03881525993347</v>
       </c>
       <c r="H1782" t="s">
         <v>8</v>
@@ -47351,7 +47351,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1807" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1807" t="s">
         <v>8</v>
@@ -47455,7 +47455,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.16624140739441</v>
+        <v>2.16624116897583</v>
       </c>
       <c r="H1811" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1820" t="n">
-        <v>2.03881549835205</v>
+        <v>2.03881525993347</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -48053,7 +48053,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1834" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1834" t="s">
         <v>8</v>
@@ -48079,7 +48079,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1835" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1835" t="s">
         <v>8</v>
@@ -48105,7 +48105,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1836" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1836" t="s">
         <v>8</v>
@@ -48183,7 +48183,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1839" t="n">
-        <v>1.92837953567505</v>
+        <v>1.92837941646576</v>
       </c>
       <c r="H1839" t="s">
         <v>8</v>
@@ -48209,7 +48209,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.93687474727631</v>
+        <v>1.93687462806702</v>
       </c>
       <c r="H1840" t="s">
         <v>8</v>
@@ -48261,7 +48261,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1842" t="n">
-        <v>1.98784482479095</v>
+        <v>1.98784506320953</v>
       </c>
       <c r="H1842" t="s">
         <v>8</v>
@@ -48625,7 +48625,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.11951851844788</v>
+        <v>2.1195182800293</v>
       </c>
       <c r="H1856" t="s">
         <v>8</v>
@@ -48781,7 +48781,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.03881549835205</v>
+        <v>2.03881525993347</v>
       </c>
       <c r="H1862" t="s">
         <v>8</v>
@@ -48807,7 +48807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.03881549835205</v>
+        <v>2.03881525993347</v>
       </c>
       <c r="H1863" t="s">
         <v>8</v>
@@ -48833,7 +48833,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.03881549835205</v>
+        <v>2.03881525993347</v>
       </c>
       <c r="H1864" t="s">
         <v>8</v>
@@ -48937,7 +48937,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.02607274055481</v>
+        <v>2.02607297897339</v>
       </c>
       <c r="H1868" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.03032040596008</v>
+        <v>2.03032064437866</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49197,7 +49197,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.13650846481323</v>
+        <v>2.13650870323181</v>
       </c>
       <c r="H1878" t="s">
         <v>8</v>
@@ -49691,7 +49691,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1897" t="s">
         <v>8</v>
@@ -49717,7 +49717,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1898" t="s">
         <v>8</v>
@@ -49769,7 +49769,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.20022177696228</v>
+        <v>2.2002215385437</v>
       </c>
       <c r="H1900" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.19172620773315</v>
+        <v>2.19172644615173</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -50003,7 +50003,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.17898368835449</v>
+        <v>2.17898392677307</v>
       </c>
       <c r="H1909" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50185,7 +50185,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.17898368835449</v>
+        <v>2.17898392677307</v>
       </c>
       <c r="H1916" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50315,7 +50315,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.13650846481323</v>
+        <v>2.13650870323181</v>
       </c>
       <c r="H1921" t="s">
         <v>8</v>
@@ -50445,7 +50445,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.20022177696228</v>
+        <v>2.2002215385437</v>
       </c>
       <c r="H1926" t="s">
         <v>8</v>
@@ -50809,7 +50809,7 @@
         <v>2.625</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.27267360687256</v>
+        <v>2.27267384529114</v>
       </c>
       <c r="H1940" t="s">
         <v>8</v>
@@ -50861,7 +50861,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1942" t="s">
         <v>8</v>
@@ -50939,7 +50939,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.24670052528381</v>
+        <v>2.24670028686523</v>
       </c>
       <c r="H1945" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.24237155914307</v>
+        <v>2.24237132072449</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51173,7 +51173,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.24237155914307</v>
+        <v>2.24237132072449</v>
       </c>
       <c r="H1954" t="s">
         <v>8</v>
@@ -51251,7 +51251,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.36358046531677</v>
+        <v>2.36358070373535</v>
       </c>
       <c r="H1957" t="s">
         <v>8</v>
@@ -51381,7 +51381,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.24237155914307</v>
+        <v>2.24237132072449</v>
       </c>
       <c r="H1962" t="s">
         <v>8</v>
@@ -51433,7 +51433,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1964" t="s">
         <v>8</v>
@@ -51459,7 +51459,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H1965" t="s">
         <v>8</v>
@@ -51485,7 +51485,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H1966" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51589,7 +51589,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1970" t="s">
         <v>8</v>
@@ -51641,7 +51641,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H1972" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51771,7 +51771,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.16012239456177</v>
+        <v>2.16012215614319</v>
       </c>
       <c r="H1977" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.1774377822876</v>
+        <v>2.17743802070618</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52083,7 +52083,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1989" t="s">
         <v>8</v>
@@ -52135,7 +52135,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1991" t="s">
         <v>8</v>
@@ -52161,7 +52161,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1992" t="s">
         <v>8</v>
@@ -52213,7 +52213,7 @@
         <v>2.375</v>
       </c>
       <c r="G1994" t="n">
-        <v>2.05622887611389</v>
+        <v>2.05622863769531</v>
       </c>
       <c r="H1994" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1995" t="n">
-        <v>2.16012239456177</v>
+        <v>2.16012215614319</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2006" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52837,7 +52837,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.31163382530212</v>
+        <v>2.3116340637207</v>
       </c>
       <c r="H2018" t="s">
         <v>8</v>
@@ -52863,7 +52863,7 @@
         <v>2.67499995231628</v>
       </c>
       <c r="G2019" t="n">
-        <v>2.31596255302429</v>
+        <v>2.31596279144287</v>
       </c>
       <c r="H2019" t="s">
         <v>8</v>
@@ -52889,7 +52889,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.31163382530212</v>
+        <v>2.3116340637207</v>
       </c>
       <c r="H2020" t="s">
         <v>8</v>
@@ -52967,7 +52967,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G2023" t="n">
-        <v>2.28566074371338</v>
+        <v>2.2856605052948</v>
       </c>
       <c r="H2023" t="s">
         <v>8</v>
@@ -53149,7 +53149,7 @@
         <v>2.625</v>
       </c>
       <c r="G2030" t="n">
-        <v>2.27267360687256</v>
+        <v>2.27267384529114</v>
       </c>
       <c r="H2030" t="s">
         <v>8</v>
@@ -53201,7 +53201,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.24670052528381</v>
+        <v>2.24670028686523</v>
       </c>
       <c r="H2032" t="s">
         <v>8</v>
@@ -53227,7 +53227,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2033" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2033" t="s">
         <v>8</v>
@@ -53357,7 +53357,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2038" t="s">
         <v>8</v>
@@ -53383,7 +53383,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2039" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H2039" t="s">
         <v>8</v>
@@ -53409,7 +53409,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.22072672843933</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H2040" t="s">
         <v>8</v>
@@ -53565,7 +53565,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G2046" t="n">
-        <v>2.1774377822876</v>
+        <v>2.17743802070618</v>
       </c>
       <c r="H2046" t="s">
         <v>8</v>
@@ -53903,7 +53903,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2059" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2059" t="s">
         <v>8</v>
@@ -53955,7 +53955,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2061" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2061" t="s">
         <v>8</v>
@@ -54085,7 +54085,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2066" t="s">
         <v>8</v>
@@ -54163,7 +54163,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2069" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2069" t="s">
         <v>8</v>
@@ -54241,7 +54241,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2072" t="s">
         <v>8</v>
@@ -54267,7 +54267,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.06488633155823</v>
+        <v>2.06488656997681</v>
       </c>
       <c r="H2073" t="s">
         <v>8</v>
@@ -54475,7 +54475,7 @@
         <v>2.375</v>
       </c>
       <c r="G2081" t="n">
-        <v>2.05622887611389</v>
+        <v>2.05622863769531</v>
       </c>
       <c r="H2081" t="s">
         <v>8</v>
@@ -54527,7 +54527,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G2083" t="n">
-        <v>2.03025507926941</v>
+        <v>2.03025531768799</v>
       </c>
       <c r="H2083" t="s">
         <v>8</v>
@@ -54605,7 +54605,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2086" t="n">
-        <v>2.02592611312866</v>
+        <v>2.02592635154724</v>
       </c>
       <c r="H2086" t="s">
         <v>8</v>
@@ -54683,7 +54683,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2089" t="n">
-        <v>2.06921529769897</v>
+        <v>2.06921553611755</v>
       </c>
       <c r="H2089" t="s">
         <v>8</v>
@@ -54735,7 +54735,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2091" t="n">
-        <v>2.06921529769897</v>
+        <v>2.06921553611755</v>
       </c>
       <c r="H2091" t="s">
         <v>8</v>
@@ -54761,7 +54761,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2092" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2092" t="s">
         <v>8</v>
@@ -54787,7 +54787,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2093" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2093" t="s">
         <v>8</v>
@@ -54813,7 +54813,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2094" t="n">
-        <v>2.09951782226562</v>
+        <v>2.09951758384705</v>
       </c>
       <c r="H2094" t="s">
         <v>8</v>
@@ -55203,7 +55203,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2109" t="n">
-        <v>2.02592611312866</v>
+        <v>2.02592635154724</v>
       </c>
       <c r="H2109" t="s">
         <v>8</v>
@@ -55281,7 +55281,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2112" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2112" t="s">
         <v>8</v>
@@ -55515,7 +55515,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.99129486083984</v>
+        <v>1.99129498004913</v>
       </c>
       <c r="H2121" t="s">
         <v>8</v>
@@ -55541,7 +55541,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.99129486083984</v>
+        <v>1.99129498004913</v>
       </c>
       <c r="H2122" t="s">
         <v>8</v>
@@ -55593,7 +55593,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G2124" t="n">
-        <v>2.02592611312866</v>
+        <v>2.02592635154724</v>
       </c>
       <c r="H2124" t="s">
         <v>8</v>
@@ -55671,7 +55671,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2127" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2127" t="s">
         <v>8</v>
@@ -55723,7 +55723,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G2129" t="n">
-        <v>2.06921529769897</v>
+        <v>2.06921553611755</v>
       </c>
       <c r="H2129" t="s">
         <v>8</v>
@@ -56685,7 +56685,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2166" t="s">
         <v>8</v>
@@ -56763,7 +56763,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2169" t="s">
         <v>8</v>
@@ -56815,7 +56815,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2171" t="s">
         <v>8</v>
@@ -56841,7 +56841,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2172" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2172" t="s">
         <v>8</v>
@@ -56867,7 +56867,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2173" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2173" t="s">
         <v>8</v>
@@ -56893,7 +56893,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2174" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2174" t="s">
         <v>8</v>
@@ -56919,7 +56919,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2175" t="s">
         <v>8</v>
@@ -56945,7 +56945,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2176" t="s">
         <v>8</v>
@@ -56971,7 +56971,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2177" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2177" t="s">
         <v>8</v>
@@ -57023,7 +57023,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2179" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2179" t="s">
         <v>8</v>
@@ -57049,7 +57049,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2180" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2180" t="s">
         <v>8</v>
@@ -57075,7 +57075,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G2181" t="n">
-        <v>2.23371338844299</v>
+        <v>2.23371362686157</v>
       </c>
       <c r="H2181" t="s">
         <v>8</v>
@@ -57101,7 +57101,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2182" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2182" t="s">
         <v>8</v>
@@ -71690,6 +71690,32 @@
         <v>6.65999984741211</v>
       </c>
       <c r="H2743" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2744">
+      <c r="A2744" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2744" t="n">
+        <v>38723</v>
+      </c>
+      <c r="C2744" t="n">
+        <v>6.76000022888184</v>
+      </c>
+      <c r="D2744" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="E2744" t="n">
+        <v>6.73999977111816</v>
+      </c>
+      <c r="F2744" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="G2744" t="n">
+        <v>6.65999984741211</v>
+      </c>
+      <c r="H2744" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>2.93566393852234</v>
+        <v>2.93566417694092</v>
       </c>
       <c r="H3" t="n">
         <v>1711</v>
@@ -514,7 +514,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G5" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H5" t="n">
         <v>10591</v>
@@ -543,7 +543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H6" t="n">
         <v>3694</v>
@@ -572,7 +572,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H7" t="n">
         <v>588</v>
@@ -601,7 +601,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91948938369751</v>
+        <v>2.91948914527893</v>
       </c>
       <c r="H8" t="n">
         <v>928</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74965763092041</v>
+        <v>2.74965786933899</v>
       </c>
       <c r="H12" t="n">
         <v>9032</v>
@@ -746,7 +746,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>2.66878533363342</v>
+        <v>2.668785572052</v>
       </c>
       <c r="H13" t="n">
         <v>9675</v>
@@ -804,7 +804,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.53938984870911</v>
+        <v>2.53939008712769</v>
       </c>
       <c r="H15" t="n">
         <v>4837</v>
@@ -833,7 +833,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G16" t="n">
-        <v>2.62026214599609</v>
+        <v>2.62026190757751</v>
       </c>
       <c r="H16" t="n">
         <v>4337</v>
@@ -862,7 +862,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G17" t="n">
-        <v>2.57173895835876</v>
+        <v>2.57173848152161</v>
       </c>
       <c r="H17" t="n">
         <v>10526</v>
@@ -920,7 +920,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G19" t="n">
-        <v>2.55556416511536</v>
+        <v>2.55556440353394</v>
       </c>
       <c r="H19" t="n">
         <v>1500</v>
@@ -949,7 +949,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G20" t="n">
-        <v>2.55556416511536</v>
+        <v>2.55556440353394</v>
       </c>
       <c r="H20" t="n">
         <v>5266</v>
@@ -1007,7 +1007,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G22" t="n">
-        <v>2.49895334243774</v>
+        <v>2.49895358085632</v>
       </c>
       <c r="H22" t="n">
         <v>6946</v>
@@ -1036,7 +1036,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.57173895835876</v>
+        <v>2.57173848152161</v>
       </c>
       <c r="H23" t="n">
         <v>7787</v>
@@ -1094,7 +1094,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.49895334243774</v>
+        <v>2.49895358085632</v>
       </c>
       <c r="H25" t="n">
         <v>10756</v>
@@ -1123,7 +1123,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G26" t="n">
-        <v>2.41808128356934</v>
+        <v>2.41808152198792</v>
       </c>
       <c r="H26" t="n">
         <v>1304</v>
@@ -1210,7 +1210,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G29" t="n">
-        <v>2.28868556022644</v>
+        <v>2.28868579864502</v>
       </c>
       <c r="H29" t="n">
         <v>1500</v>
@@ -1239,7 +1239,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G30" t="n">
-        <v>2.28868556022644</v>
+        <v>2.28868579864502</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24339699745178</v>
+        <v>2.24339723587036</v>
       </c>
       <c r="H31" t="n">
         <v>4200</v>
@@ -1355,7 +1355,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45043015480042</v>
+        <v>2.45042991638184</v>
       </c>
       <c r="H34" t="n">
         <v>1550</v>
@@ -1442,7 +1442,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>2.50704073905945</v>
+        <v>2.50704050064087</v>
       </c>
       <c r="H37" t="n">
         <v>1284</v>
@@ -1500,7 +1500,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49895334243774</v>
+        <v>2.49895358085632</v>
       </c>
       <c r="H39" t="n">
         <v>10945</v>
@@ -1674,7 +1674,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G45" t="n">
-        <v>2.50542330741882</v>
+        <v>2.50542306900024</v>
       </c>
       <c r="H45" t="n">
         <v>1234</v>
@@ -1703,7 +1703,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G46" t="n">
-        <v>2.56203389167786</v>
+        <v>2.56203413009644</v>
       </c>
       <c r="H46" t="n">
         <v>11008</v>
@@ -1761,7 +1761,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52159786224365</v>
+        <v>2.52159810066223</v>
       </c>
       <c r="H48" t="n">
         <v>3370</v>
@@ -1819,7 +1819,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>2.66878533363342</v>
+        <v>2.668785572052</v>
       </c>
       <c r="H50" t="n">
         <v>2150</v>
@@ -1964,7 +1964,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54747676849365</v>
+        <v>2.54747700691223</v>
       </c>
       <c r="H55" t="n">
         <v>2341</v>
@@ -1993,7 +1993,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>2.54747676849365</v>
+        <v>2.54747700691223</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>2.54747676849365</v>
+        <v>2.54747700691223</v>
       </c>
       <c r="H59" t="n">
         <v>1600</v>
@@ -2109,7 +2109,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.50704073905945</v>
+        <v>2.50704050064087</v>
       </c>
       <c r="H60" t="n">
         <v>1650</v>
@@ -2167,7 +2167,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G62" t="n">
-        <v>2.58467817306519</v>
+        <v>2.58467793464661</v>
       </c>
       <c r="H62" t="n">
         <v>1431</v>
@@ -2283,7 +2283,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G66" t="n">
-        <v>2.56688642501831</v>
+        <v>2.56688618659973</v>
       </c>
       <c r="H66" t="n">
         <v>792</v>
@@ -2312,7 +2312,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G67" t="n">
-        <v>2.46660447120667</v>
+        <v>2.46660470962524</v>
       </c>
       <c r="H67" t="n">
         <v>6500</v>
@@ -2370,7 +2370,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>2.5313024520874</v>
+        <v>2.53130221366882</v>
       </c>
       <c r="H69" t="n">
         <v>600</v>
@@ -2399,7 +2399,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G70" t="n">
-        <v>2.49895334243774</v>
+        <v>2.49895358085632</v>
       </c>
       <c r="H70" t="n">
         <v>4213</v>
@@ -2457,7 +2457,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G72" t="n">
-        <v>2.49895334243774</v>
+        <v>2.49895358085632</v>
       </c>
       <c r="H72" t="n">
         <v>9046</v>
@@ -2486,7 +2486,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G73" t="n">
-        <v>2.55556416511536</v>
+        <v>2.55556440353394</v>
       </c>
       <c r="H73" t="n">
         <v>793</v>
@@ -2544,7 +2544,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59438276290894</v>
+        <v>2.59438252449036</v>
       </c>
       <c r="H75" t="n">
         <v>1200</v>
@@ -2573,7 +2573,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>2.59600043296814</v>
+        <v>2.59600019454956</v>
       </c>
       <c r="H76" t="n">
         <v>50</v>
@@ -2660,7 +2660,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G79" t="n">
-        <v>2.54100728034973</v>
+        <v>2.54100704193115</v>
       </c>
       <c r="H79" t="n">
         <v>5900</v>
@@ -2689,7 +2689,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G80" t="n">
-        <v>2.54100728034973</v>
+        <v>2.54100704193115</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G84" t="n">
-        <v>2.53938984870911</v>
+        <v>2.53939008712769</v>
       </c>
       <c r="H84" t="n">
         <v>3909</v>
@@ -2834,7 +2834,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G85" t="n">
-        <v>2.54262495040894</v>
+        <v>2.54262471199036</v>
       </c>
       <c r="H85" t="n">
         <v>12001</v>
@@ -2863,7 +2863,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G86" t="n">
-        <v>2.53777241706848</v>
+        <v>2.5377721786499</v>
       </c>
       <c r="H86" t="n">
         <v>201</v>
@@ -2950,7 +2950,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G89" t="n">
-        <v>2.46660447120667</v>
+        <v>2.46660470962524</v>
       </c>
       <c r="H89" t="n">
         <v>5393</v>
@@ -2979,7 +2979,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G90" t="n">
-        <v>2.44072556495667</v>
+        <v>2.44072532653809</v>
       </c>
       <c r="H90" t="n">
         <v>1954</v>
@@ -3066,7 +3066,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G93" t="n">
-        <v>2.46660447120667</v>
+        <v>2.46660470962524</v>
       </c>
       <c r="H93" t="n">
         <v>9728</v>
@@ -3211,7 +3211,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G98" t="n">
-        <v>2.38411498069763</v>
+        <v>2.38411474227905</v>
       </c>
       <c r="H98" t="n">
         <v>4757</v>
@@ -3240,7 +3240,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G99" t="n">
-        <v>2.38088035583496</v>
+        <v>2.38088011741638</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H100" t="n">
         <v>711</v>
@@ -3298,7 +3298,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G102" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H102" t="n">
         <v>5002</v>
@@ -3501,7 +3501,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G108" t="n">
-        <v>2.41101765632629</v>
+        <v>2.41101789474487</v>
       </c>
       <c r="H108" t="n">
         <v>1200</v>
@@ -3588,7 +3588,7 @@
         <v>2.75</v>
       </c>
       <c r="G111" t="n">
-        <v>2.30218696594238</v>
+        <v>2.30218720436096</v>
       </c>
       <c r="H111" t="n">
         <v>3120</v>
@@ -3617,7 +3617,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G112" t="n">
-        <v>2.22684288024902</v>
+        <v>2.22684264183044</v>
       </c>
       <c r="H112" t="n">
         <v>8946</v>
@@ -3675,7 +3675,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G114" t="n">
-        <v>2.28879261016846</v>
+        <v>2.28879237174988</v>
       </c>
       <c r="H114" t="n">
         <v>6870</v>
@@ -3733,7 +3733,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G116" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H116" t="n">
         <v>2109</v>
@@ -3762,7 +3762,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G117" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H117" t="n">
         <v>1936</v>
@@ -3791,7 +3791,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G118" t="n">
-        <v>2.17493891716003</v>
+        <v>2.17493915557861</v>
       </c>
       <c r="H118" t="n">
         <v>1145</v>
@@ -3907,7 +3907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H122" t="n">
         <v>2550</v>
@@ -3936,7 +3936,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H123" t="n">
         <v>5450</v>
@@ -3994,7 +3994,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G125" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H125" t="n">
         <v>3129</v>
@@ -4023,7 +4023,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G126" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H126" t="n">
         <v>850</v>
@@ -4052,7 +4052,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G127" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13308072090149</v>
+        <v>2.13308119773865</v>
       </c>
       <c r="H130" t="n">
         <v>7449</v>
@@ -4226,7 +4226,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G133" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H133" t="n">
         <v>1000</v>
@@ -4255,7 +4255,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G134" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G146" t="n">
-        <v>2.13642954826355</v>
+        <v>2.13642978668213</v>
       </c>
       <c r="H146" t="n">
         <v>2790</v>
@@ -4632,7 +4632,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G147" t="n">
-        <v>2.14647531509399</v>
+        <v>2.14647555351257</v>
       </c>
       <c r="H147" t="n">
         <v>875</v>
@@ -4661,7 +4661,7 @@
         <v>2.56399989128113</v>
       </c>
       <c r="G148" t="n">
-        <v>2.14647531509399</v>
+        <v>2.14647555351257</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4922,7 +4922,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G157" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H157" t="n">
         <v>2500</v>
@@ -4951,7 +4951,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H158" t="n">
         <v>7741</v>
@@ -4980,7 +4980,7 @@
         <v>2.68199992179871</v>
       </c>
       <c r="G159" t="n">
-        <v>2.24526023864746</v>
+        <v>2.24526000022888</v>
       </c>
       <c r="H159" t="n">
         <v>1495</v>
@@ -5096,7 +5096,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G163" t="n">
-        <v>2.22014546394348</v>
+        <v>2.2201452255249</v>
       </c>
       <c r="H163" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H164" t="n">
         <v>2682</v>
@@ -5154,7 +5154,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G165" t="n">
-        <v>2.25028324127197</v>
+        <v>2.25028300285339</v>
       </c>
       <c r="H165" t="n">
         <v>276</v>
@@ -5183,7 +5183,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G166" t="n">
-        <v>2.25028324127197</v>
+        <v>2.25028300285339</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H168" t="n">
         <v>1861</v>
@@ -5270,7 +5270,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G171" t="n">
-        <v>2.25698065757751</v>
+        <v>2.25698041915894</v>
       </c>
       <c r="H171" t="n">
         <v>25</v>
@@ -5415,7 +5415,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G174" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H174" t="n">
         <v>3952</v>
@@ -5444,7 +5444,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G175" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H176" t="n">
         <v>10046</v>
@@ -5502,7 +5502,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>2.22014546394348</v>
+        <v>2.2201452255249</v>
       </c>
       <c r="H177" t="n">
         <v>3110</v>
@@ -5618,7 +5618,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.21177363395691</v>
+        <v>2.21177411079407</v>
       </c>
       <c r="H181" t="n">
         <v>126</v>
@@ -5676,7 +5676,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H183" t="n">
         <v>1410</v>
@@ -5734,7 +5734,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H185" t="n">
         <v>3000</v>
@@ -5763,7 +5763,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H186" t="n">
         <v>1200</v>
@@ -5792,7 +5792,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G187" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G191" t="n">
-        <v>2.17493891716003</v>
+        <v>2.17493915557861</v>
       </c>
       <c r="H191" t="n">
         <v>2700</v>
@@ -5995,7 +5995,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G194" t="n">
-        <v>2.14145255088806</v>
+        <v>2.14145278930664</v>
       </c>
       <c r="H194" t="n">
         <v>800</v>
@@ -6024,7 +6024,7 @@
         <v>2.55800008773804</v>
       </c>
       <c r="G195" t="n">
-        <v>2.14145255088806</v>
+        <v>2.14145278930664</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>2.55200004577637</v>
       </c>
       <c r="G196" t="n">
-        <v>2.13642954826355</v>
+        <v>2.13642978668213</v>
       </c>
       <c r="H196" t="n">
         <v>455</v>
@@ -6140,7 +6140,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G199" t="n">
-        <v>2.06610822677612</v>
+        <v>2.06610798835754</v>
       </c>
       <c r="H199" t="n">
         <v>2340</v>
@@ -6169,7 +6169,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G200" t="n">
-        <v>2.06610822677612</v>
+        <v>2.06610798835754</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>2.53200006484985</v>
       </c>
       <c r="G203" t="n">
-        <v>2.11968660354614</v>
+        <v>2.11968636512756</v>
       </c>
       <c r="H203" t="n">
         <v>2159</v>
@@ -6314,7 +6314,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G205" t="n">
-        <v>2.06108522415161</v>
+        <v>2.06108498573303</v>
       </c>
       <c r="H205" t="n">
         <v>731</v>
@@ -6430,7 +6430,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G209" t="n">
-        <v>2.01085591316223</v>
+        <v>2.01085567474365</v>
       </c>
       <c r="H209" t="n">
         <v>8377</v>
@@ -6604,7 +6604,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H215" t="n">
         <v>295</v>
@@ -6662,7 +6662,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G217" t="n">
-        <v>1.98908948898315</v>
+        <v>1.98908972740173</v>
       </c>
       <c r="H217" t="n">
         <v>262</v>
@@ -6778,7 +6778,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>1.99411261081696</v>
+        <v>1.99411249160767</v>
       </c>
       <c r="H221" t="n">
         <v>2900</v>
@@ -6865,7 +6865,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G224" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H224" t="n">
         <v>4828</v>
@@ -6894,7 +6894,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G225" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H225" t="n">
         <v>554</v>
@@ -7010,7 +7010,7 @@
         <v>2.28399991989136</v>
       </c>
       <c r="G229" t="n">
-        <v>1.91207075119019</v>
+        <v>1.91207098960876</v>
       </c>
       <c r="H229" t="n">
         <v>1365</v>
@@ -7039,7 +7039,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H230" t="n">
         <v>1213</v>
@@ -7126,7 +7126,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G233" t="n">
-        <v>1.94890606403351</v>
+        <v>1.94890582561493</v>
       </c>
       <c r="H233" t="n">
         <v>105</v>
@@ -7155,7 +7155,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G234" t="n">
-        <v>1.94890606403351</v>
+        <v>1.94890582561493</v>
       </c>
       <c r="H234" t="n">
         <v>1000</v>
@@ -7184,7 +7184,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G235" t="n">
-        <v>1.90202522277832</v>
+        <v>1.90202486515045</v>
       </c>
       <c r="H235" t="n">
         <v>400</v>
@@ -7213,7 +7213,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G236" t="n">
-        <v>1.94053447246552</v>
+        <v>1.9405345916748</v>
       </c>
       <c r="H236" t="n">
         <v>6530</v>
@@ -7271,7 +7271,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H238" t="n">
         <v>100</v>
@@ -7300,7 +7300,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H239" t="n">
         <v>300</v>
@@ -7387,7 +7387,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G242" t="n">
-        <v>2.06610822677612</v>
+        <v>2.06610798835754</v>
       </c>
       <c r="H242" t="n">
         <v>7658</v>
@@ -7474,7 +7474,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G245" t="n">
-        <v>2.06610822677612</v>
+        <v>2.06610798835754</v>
       </c>
       <c r="H245" t="n">
         <v>3362</v>
@@ -7503,7 +7503,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.06778264045715</v>
+        <v>2.06778287887573</v>
       </c>
       <c r="H246" t="n">
         <v>6984</v>
@@ -7532,7 +7532,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.06778264045715</v>
+        <v>2.06778287887573</v>
       </c>
       <c r="H247" t="n">
         <v>1952</v>
@@ -7590,7 +7590,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G249" t="n">
-        <v>2.06610822677612</v>
+        <v>2.06610798835754</v>
       </c>
       <c r="H249" t="n">
         <v>2070</v>
@@ -7706,7 +7706,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G253" t="n">
-        <v>2.02927327156067</v>
+        <v>2.02927303314209</v>
       </c>
       <c r="H253" t="n">
         <v>3787</v>
@@ -7735,7 +7735,7 @@
         <v>2.42400002479553</v>
       </c>
       <c r="G254" t="n">
-        <v>2.02927327156067</v>
+        <v>2.02927303314209</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H256" t="n">
         <v>15415</v>
@@ -7880,7 +7880,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>2.46794462203979</v>
+        <v>2.46794438362122</v>
       </c>
       <c r="H259" t="n">
         <v>27965</v>
@@ -8054,7 +8054,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>2.58347249031067</v>
+        <v>2.58347225189209</v>
       </c>
       <c r="H265" t="n">
         <v>10919</v>
@@ -8083,7 +8083,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G266" t="n">
-        <v>2.52654576301575</v>
+        <v>2.52654552459717</v>
       </c>
       <c r="H266" t="n">
         <v>6706</v>
@@ -8112,7 +8112,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.57844948768616</v>
+        <v>2.57844924926758</v>
       </c>
       <c r="H267" t="n">
         <v>30844</v>
@@ -8170,7 +8170,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G269" t="n">
-        <v>2.55835747718811</v>
+        <v>2.55835771560669</v>
       </c>
       <c r="H269" t="n">
         <v>5829</v>
@@ -8286,7 +8286,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.53659152984619</v>
+        <v>2.53659129142761</v>
       </c>
       <c r="H273" t="n">
         <v>3204</v>
@@ -8315,7 +8315,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51315116882324</v>
+        <v>2.51315140724182</v>
       </c>
       <c r="H274" t="n">
         <v>5505</v>
@@ -8344,7 +8344,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G275" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H275" t="n">
         <v>11977</v>
@@ -8373,7 +8373,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G276" t="n">
-        <v>2.59686708450317</v>
+        <v>2.59686684608459</v>
       </c>
       <c r="H276" t="n">
         <v>75318</v>
@@ -8402,7 +8402,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G277" t="n">
-        <v>2.58347249031067</v>
+        <v>2.58347225189209</v>
       </c>
       <c r="H277" t="n">
         <v>10559</v>
@@ -8431,7 +8431,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G278" t="n">
-        <v>2.57007765769958</v>
+        <v>2.57007789611816</v>
       </c>
       <c r="H278" t="n">
         <v>11457</v>
@@ -8460,7 +8460,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G279" t="n">
-        <v>2.53826594352722</v>
+        <v>2.5382661819458</v>
       </c>
       <c r="H279" t="n">
         <v>1753</v>
@@ -8518,7 +8518,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.63705039024353</v>
+        <v>2.63705062866211</v>
       </c>
       <c r="H281" t="n">
         <v>6600</v>
@@ -8576,7 +8576,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G283" t="n">
-        <v>2.57007765769958</v>
+        <v>2.57007789611816</v>
       </c>
       <c r="H283" t="n">
         <v>18978</v>
@@ -8605,7 +8605,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G284" t="n">
-        <v>2.53491759300232</v>
+        <v>2.53491735458374</v>
       </c>
       <c r="H284" t="n">
         <v>1583</v>
@@ -8663,7 +8663,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G286" t="n">
-        <v>2.5031054019928</v>
+        <v>2.50310516357422</v>
       </c>
       <c r="H286" t="n">
         <v>1752</v>
@@ -8692,7 +8692,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G287" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H287" t="n">
         <v>1050</v>
@@ -8721,7 +8721,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.53659152984619</v>
+        <v>2.53659129142761</v>
       </c>
       <c r="H288" t="n">
         <v>7934</v>
@@ -8750,7 +8750,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G289" t="n">
-        <v>2.53491759300232</v>
+        <v>2.53491735458374</v>
       </c>
       <c r="H289" t="n">
         <v>902</v>
@@ -8779,7 +8779,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G290" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H290" t="n">
         <v>13966</v>
@@ -8808,7 +8808,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>2.49473357200623</v>
+        <v>2.4947338104248</v>
       </c>
       <c r="H291" t="n">
         <v>10449</v>
@@ -8866,7 +8866,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G293" t="n">
-        <v>2.47296738624573</v>
+        <v>2.47296714782715</v>
       </c>
       <c r="H293" t="n">
         <v>1769</v>
@@ -8924,7 +8924,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53324294090271</v>
+        <v>2.53324317932129</v>
       </c>
       <c r="H295" t="n">
         <v>10626</v>
@@ -8953,7 +8953,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G296" t="n">
-        <v>2.54663753509521</v>
+        <v>2.54663729667664</v>
       </c>
       <c r="H296" t="n">
         <v>3490</v>
@@ -8982,7 +8982,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>2.5282199382782</v>
+        <v>2.52821969985962</v>
       </c>
       <c r="H297" t="n">
         <v>3951</v>
@@ -9040,7 +9040,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G299" t="n">
-        <v>2.50477957725525</v>
+        <v>2.50477933883667</v>
       </c>
       <c r="H299" t="n">
         <v>5295</v>
@@ -9127,7 +9127,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G302" t="n">
-        <v>2.45789861679077</v>
+        <v>2.45789837837219</v>
       </c>
       <c r="H302" t="n">
         <v>7753</v>
@@ -9185,7 +9185,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G304" t="n">
-        <v>2.36915969848633</v>
+        <v>2.36915993690491</v>
       </c>
       <c r="H304" t="n">
         <v>6034</v>
@@ -9214,7 +9214,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G305" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H305" t="n">
         <v>3433</v>
@@ -9272,7 +9272,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>2.39594888687134</v>
+        <v>2.39594912528992</v>
       </c>
       <c r="H307" t="n">
         <v>3117</v>
@@ -9301,7 +9301,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G308" t="n">
-        <v>2.44450426101685</v>
+        <v>2.44450402259827</v>
       </c>
       <c r="H308" t="n">
         <v>3572</v>
@@ -9330,7 +9330,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G309" t="n">
-        <v>2.44617819786072</v>
+        <v>2.4461784362793</v>
       </c>
       <c r="H309" t="n">
         <v>12902</v>
@@ -9359,7 +9359,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.46961855888367</v>
+        <v>2.46961903572083</v>
       </c>
       <c r="H310" t="n">
         <v>51</v>
@@ -9388,7 +9388,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G311" t="n">
-        <v>2.46794462203979</v>
+        <v>2.46794438362122</v>
       </c>
       <c r="H311" t="n">
         <v>401</v>
@@ -9446,7 +9446,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44282960891724</v>
+        <v>2.44282984733582</v>
       </c>
       <c r="H313" t="n">
         <v>2152</v>
@@ -9504,7 +9504,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40766906738281</v>
+        <v>2.40766882896423</v>
       </c>
       <c r="H315" t="n">
         <v>4362</v>
@@ -9533,7 +9533,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39594888687134</v>
+        <v>2.39594912528992</v>
       </c>
       <c r="H316" t="n">
         <v>2861</v>
@@ -9562,7 +9562,7 @@
         <v>2.90599989891052</v>
       </c>
       <c r="G317" t="n">
-        <v>2.43278360366821</v>
+        <v>2.43278384208679</v>
       </c>
       <c r="H317" t="n">
         <v>6707</v>
@@ -9591,7 +9591,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G318" t="n">
-        <v>2.47631621360779</v>
+        <v>2.47631597518921</v>
       </c>
       <c r="H318" t="n">
         <v>6900</v>
@@ -9620,7 +9620,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>2.48133873939514</v>
+        <v>2.48133897781372</v>
       </c>
       <c r="H319" t="n">
         <v>65060</v>
@@ -9649,7 +9649,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42943525314331</v>
+        <v>2.42943501472473</v>
       </c>
       <c r="H320" t="n">
         <v>35143</v>
@@ -9678,7 +9678,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.5031054019928</v>
+        <v>2.50310516357422</v>
       </c>
       <c r="H321" t="n">
         <v>5160</v>
@@ -9707,7 +9707,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>2.44617819786072</v>
+        <v>2.4461784362793</v>
       </c>
       <c r="H322" t="n">
         <v>6960</v>
@@ -9765,7 +9765,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41101765632629</v>
+        <v>2.41101789474487</v>
       </c>
       <c r="H324" t="n">
         <v>1615</v>
@@ -9794,7 +9794,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43613266944885</v>
+        <v>2.43613219261169</v>
       </c>
       <c r="H325" t="n">
         <v>2400</v>
@@ -9823,7 +9823,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G326" t="n">
-        <v>2.46794462203979</v>
+        <v>2.46794438362122</v>
       </c>
       <c r="H326" t="n">
         <v>5877</v>
@@ -9852,7 +9852,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.41101765632629</v>
+        <v>2.41101789474487</v>
       </c>
       <c r="H327" t="n">
         <v>1890</v>
@@ -9910,7 +9910,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G329" t="n">
-        <v>2.44450426101685</v>
+        <v>2.44450402259827</v>
       </c>
       <c r="H329" t="n">
         <v>5474</v>
@@ -9968,7 +9968,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G331" t="n">
-        <v>2.42943525314331</v>
+        <v>2.42943501472473</v>
       </c>
       <c r="H331" t="n">
         <v>21229</v>
@@ -9997,7 +9997,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39594888687134</v>
+        <v>2.39594912528992</v>
       </c>
       <c r="H332" t="n">
         <v>3946</v>
@@ -10142,7 +10142,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G337" t="n">
-        <v>2.44617819786072</v>
+        <v>2.4461784362793</v>
       </c>
       <c r="H337" t="n">
         <v>1</v>
@@ -10200,7 +10200,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G339" t="n">
-        <v>2.43445801734924</v>
+        <v>2.43445825576782</v>
       </c>
       <c r="H339" t="n">
         <v>10452</v>
@@ -10258,7 +10258,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42776083946228</v>
+        <v>2.42776107788086</v>
       </c>
       <c r="H341" t="n">
         <v>1060</v>
@@ -10316,7 +10316,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G343" t="n">
-        <v>2.44952726364136</v>
+        <v>2.44952702522278</v>
       </c>
       <c r="H343" t="n">
         <v>10691</v>
@@ -10345,7 +10345,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G344" t="n">
-        <v>2.44450426101685</v>
+        <v>2.44450402259827</v>
       </c>
       <c r="H344" t="n">
         <v>10916</v>
@@ -10374,7 +10374,7 @@
         <v>2.95199990272522</v>
       </c>
       <c r="G345" t="n">
-        <v>2.47129344940186</v>
+        <v>2.47129321098328</v>
       </c>
       <c r="H345" t="n">
         <v>13651</v>
@@ -10461,7 +10461,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G348" t="n">
-        <v>2.44785284996033</v>
+        <v>2.44785261154175</v>
       </c>
       <c r="H348" t="n">
         <v>1200</v>
@@ -10490,7 +10490,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>2.48133873939514</v>
+        <v>2.48133897781372</v>
       </c>
       <c r="H349" t="n">
         <v>9683</v>
@@ -10548,7 +10548,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>2.49473357200623</v>
+        <v>2.4947338104248</v>
       </c>
       <c r="H351" t="n">
         <v>392</v>
@@ -10577,7 +10577,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.46124720573425</v>
+        <v>2.46124744415283</v>
       </c>
       <c r="H352" t="n">
         <v>4538</v>
@@ -10664,7 +10664,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G355" t="n">
-        <v>2.47296738624573</v>
+        <v>2.47296714782715</v>
       </c>
       <c r="H355" t="n">
         <v>888</v>
@@ -10693,7 +10693,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G356" t="n">
-        <v>2.44785284996033</v>
+        <v>2.44785261154175</v>
       </c>
       <c r="H356" t="n">
         <v>309</v>
@@ -10751,7 +10751,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H358" t="n">
         <v>3191</v>
@@ -10780,7 +10780,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10809,7 +10809,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G360" t="n">
-        <v>2.42776083946228</v>
+        <v>2.42776107788086</v>
       </c>
       <c r="H360" t="n">
         <v>6125</v>
@@ -10954,7 +10954,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G365" t="n">
-        <v>2.36915969848633</v>
+        <v>2.36915993690491</v>
       </c>
       <c r="H365" t="n">
         <v>2480</v>
@@ -11012,7 +11012,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H367" t="n">
         <v>13209</v>
@@ -11041,7 +11041,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G368" t="n">
-        <v>2.28879261016846</v>
+        <v>2.28879237174988</v>
       </c>
       <c r="H368" t="n">
         <v>107</v>
@@ -11070,7 +11070,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>2.31893014907837</v>
+        <v>2.31892991065979</v>
       </c>
       <c r="H369" t="n">
         <v>1602</v>
@@ -11186,7 +11186,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G373" t="n">
-        <v>2.22349381446838</v>
+        <v>2.22349405288696</v>
       </c>
       <c r="H373" t="n">
         <v>8601</v>
@@ -11215,7 +11215,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G374" t="n">
-        <v>2.28879261016846</v>
+        <v>2.28879237174988</v>
       </c>
       <c r="H374" t="n">
         <v>1060</v>
@@ -11244,7 +11244,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H375" t="n">
         <v>2969</v>
@@ -11273,7 +11273,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G376" t="n">
-        <v>2.22014546394348</v>
+        <v>2.2201452255249</v>
       </c>
       <c r="H376" t="n">
         <v>4195</v>
@@ -11360,7 +11360,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G379" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H379" t="n">
         <v>11587</v>
@@ -11389,7 +11389,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G380" t="n">
-        <v>2.20842528343201</v>
+        <v>2.20842504501343</v>
       </c>
       <c r="H380" t="n">
         <v>750</v>
@@ -11418,7 +11418,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G381" t="n">
-        <v>2.21009969711304</v>
+        <v>2.21009993553162</v>
       </c>
       <c r="H381" t="n">
         <v>1050</v>
@@ -11476,7 +11476,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G383" t="n">
-        <v>2.25698065757751</v>
+        <v>2.25698041915894</v>
       </c>
       <c r="H383" t="n">
         <v>210</v>
@@ -11505,7 +11505,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>2.2034022808075</v>
+        <v>2.20340204238892</v>
       </c>
       <c r="H384" t="n">
         <v>5239</v>
@@ -11534,7 +11534,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.27539777755737</v>
+        <v>2.27539801597595</v>
       </c>
       <c r="H385" t="n">
         <v>5752</v>
@@ -11563,7 +11563,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H386" t="n">
         <v>2103</v>
@@ -11592,7 +11592,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H388" t="n">
         <v>971</v>
@@ -11650,7 +11650,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G389" t="n">
-        <v>2.22684288024902</v>
+        <v>2.22684264183044</v>
       </c>
       <c r="H389" t="n">
         <v>1926</v>
@@ -11708,7 +11708,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G391" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H391" t="n">
         <v>1101</v>
@@ -11737,7 +11737,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>2.20842528343201</v>
+        <v>2.20842504501343</v>
       </c>
       <c r="H392" t="n">
         <v>750</v>
@@ -11766,7 +11766,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.21009969711304</v>
+        <v>2.21009993553162</v>
       </c>
       <c r="H393" t="n">
         <v>700</v>
@@ -11795,7 +11795,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H394" t="n">
         <v>3419</v>
@@ -11824,7 +11824,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G395" t="n">
-        <v>2.23186564445496</v>
+        <v>2.23186588287354</v>
       </c>
       <c r="H395" t="n">
         <v>10542</v>
@@ -11853,7 +11853,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G396" t="n">
-        <v>2.23186564445496</v>
+        <v>2.23186588287354</v>
       </c>
       <c r="H396" t="n">
         <v>850</v>
@@ -11911,7 +11911,7 @@
         <v>2.68799996376038</v>
       </c>
       <c r="G398" t="n">
-        <v>2.25028324127197</v>
+        <v>2.25028300285339</v>
       </c>
       <c r="H398" t="n">
         <v>3902</v>
@@ -11969,7 +11969,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G400" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H400" t="n">
         <v>3716</v>
@@ -11998,7 +11998,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G401" t="n">
-        <v>2.34237051010132</v>
+        <v>2.3423707485199</v>
       </c>
       <c r="H401" t="n">
         <v>1800</v>
@@ -12027,7 +12027,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>2.31893014907837</v>
+        <v>2.31892991065979</v>
       </c>
       <c r="H402" t="n">
         <v>2066</v>
@@ -12143,7 +12143,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G406" t="n">
-        <v>2.22181987762451</v>
+        <v>2.22181963920593</v>
       </c>
       <c r="H406" t="n">
         <v>2807</v>
@@ -12172,7 +12172,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G407" t="n">
-        <v>2.25698065757751</v>
+        <v>2.25698041915894</v>
       </c>
       <c r="H407" t="n">
         <v>19</v>
@@ -12201,7 +12201,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.22684288024902</v>
+        <v>2.22684264183044</v>
       </c>
       <c r="H408" t="n">
         <v>670</v>
@@ -12259,7 +12259,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H410" t="n">
         <v>9850</v>
@@ -12288,7 +12288,7 @@
         <v>2.84200000762939</v>
       </c>
       <c r="G411" t="n">
-        <v>2.37920546531677</v>
+        <v>2.37920570373535</v>
       </c>
       <c r="H411" t="n">
         <v>41494</v>
@@ -12317,7 +12317,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.49473357200623</v>
+        <v>2.4947338104248</v>
       </c>
       <c r="H412" t="n">
         <v>58936</v>
@@ -12375,7 +12375,7 @@
         <v>2.9760000705719</v>
       </c>
       <c r="G414" t="n">
-        <v>2.49138522148132</v>
+        <v>2.49138498306274</v>
       </c>
       <c r="H414" t="n">
         <v>11685</v>
@@ -12433,7 +12433,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G416" t="n">
-        <v>2.44450426101685</v>
+        <v>2.44450402259827</v>
       </c>
       <c r="H416" t="n">
         <v>11158</v>
@@ -12462,7 +12462,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>2.41101765632629</v>
+        <v>2.41101789474487</v>
       </c>
       <c r="H417" t="n">
         <v>2024</v>
@@ -12491,7 +12491,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G418" t="n">
-        <v>2.42776083946228</v>
+        <v>2.42776107788086</v>
       </c>
       <c r="H418" t="n">
         <v>2150</v>
@@ -12578,7 +12578,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G421" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H421" t="n">
         <v>27452</v>
@@ -12636,7 +12636,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G423" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H423" t="n">
         <v>6752</v>
@@ -12723,7 +12723,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G426" t="n">
-        <v>2.30888438224792</v>
+        <v>2.30888414382935</v>
       </c>
       <c r="H426" t="n">
         <v>3750</v>
@@ -12839,7 +12839,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G430" t="n">
-        <v>2.28879261016846</v>
+        <v>2.28879237174988</v>
       </c>
       <c r="H430" t="n">
         <v>925</v>
@@ -12868,7 +12868,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G431" t="n">
-        <v>2.28879261016846</v>
+        <v>2.28879237174988</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12897,7 +12897,7 @@
         <v>2.71199989318848</v>
       </c>
       <c r="G432" t="n">
-        <v>2.27037501335144</v>
+        <v>2.27037477493286</v>
       </c>
       <c r="H432" t="n">
         <v>1000</v>
@@ -12955,7 +12955,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>2.29381561279297</v>
+        <v>2.29381537437439</v>
       </c>
       <c r="H434" t="n">
         <v>7223</v>
@@ -12984,7 +12984,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>2.27204895019531</v>
+        <v>2.27204918861389</v>
       </c>
       <c r="H435" t="n">
         <v>900</v>
@@ -13129,7 +13129,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G440" t="n">
-        <v>2.35241675376892</v>
+        <v>2.35241651535034</v>
       </c>
       <c r="H440" t="n">
         <v>13100</v>
@@ -13158,7 +13158,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G441" t="n">
-        <v>2.39427447319031</v>
+        <v>2.39427423477173</v>
       </c>
       <c r="H441" t="n">
         <v>6951</v>
@@ -13187,7 +13187,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G442" t="n">
-        <v>2.35409092903137</v>
+        <v>2.35409116744995</v>
       </c>
       <c r="H442" t="n">
         <v>297</v>
@@ -13216,7 +13216,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G443" t="n">
-        <v>2.34571933746338</v>
+        <v>2.34571957588196</v>
       </c>
       <c r="H443" t="n">
         <v>3719</v>
@@ -13303,7 +13303,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G446" t="n">
-        <v>2.36246252059937</v>
+        <v>2.36246228218079</v>
       </c>
       <c r="H446" t="n">
         <v>10257</v>
@@ -13332,7 +13332,7 @@
         <v>2.82399988174438</v>
       </c>
       <c r="G447" t="n">
-        <v>2.3641369342804</v>
+        <v>2.36413669586182</v>
       </c>
       <c r="H447" t="n">
         <v>8879</v>
@@ -13390,7 +13390,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G449" t="n">
-        <v>2.39427447319031</v>
+        <v>2.39427423477173</v>
       </c>
       <c r="H449" t="n">
         <v>1492</v>
@@ -13419,7 +13419,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>2.35241675376892</v>
+        <v>2.35241651535034</v>
       </c>
       <c r="H450" t="n">
         <v>3361</v>
@@ -13448,7 +13448,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>2.35743951797485</v>
+        <v>2.35743927955627</v>
       </c>
       <c r="H451" t="n">
         <v>2696</v>
@@ -13477,7 +13477,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>2.38925170898438</v>
+        <v>2.3892514705658</v>
       </c>
       <c r="H452" t="n">
         <v>13423</v>
@@ -13535,7 +13535,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G454" t="n">
-        <v>2.34571933746338</v>
+        <v>2.34571957588196</v>
       </c>
       <c r="H454" t="n">
         <v>6227</v>
@@ -13564,7 +13564,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G455" t="n">
-        <v>2.35576486587524</v>
+        <v>2.35576510429382</v>
       </c>
       <c r="H455" t="n">
         <v>20</v>
@@ -13593,7 +13593,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G456" t="n">
-        <v>2.33065032958984</v>
+        <v>2.33065056800842</v>
       </c>
       <c r="H456" t="n">
         <v>16903</v>
@@ -13622,7 +13622,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G457" t="n">
-        <v>2.33065032958984</v>
+        <v>2.33065056800842</v>
       </c>
       <c r="H457" t="n">
         <v>121</v>
@@ -13680,7 +13680,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G459" t="n">
-        <v>2.35409092903137</v>
+        <v>2.35409116744995</v>
       </c>
       <c r="H459" t="n">
         <v>800</v>
@@ -13709,7 +13709,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>2.32730174064636</v>
+        <v>2.32730197906494</v>
       </c>
       <c r="H460" t="n">
         <v>4081</v>
@@ -13767,7 +13767,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G462" t="n">
-        <v>2.39427447319031</v>
+        <v>2.39427423477173</v>
       </c>
       <c r="H462" t="n">
         <v>16300</v>
@@ -13796,7 +13796,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G463" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H463" t="n">
         <v>1</v>
@@ -13825,7 +13825,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G464" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H464" t="n">
         <v>0</v>
@@ -13854,7 +13854,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G465" t="n">
-        <v>2.38590264320374</v>
+        <v>2.38590288162231</v>
       </c>
       <c r="H465" t="n">
         <v>7352</v>
@@ -13883,7 +13883,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>2.31055855751038</v>
+        <v>2.31055879592896</v>
       </c>
       <c r="H466" t="n">
         <v>2372</v>
@@ -13912,7 +13912,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="n">
-        <v>2.32227873802185</v>
+        <v>2.32227897644043</v>
       </c>
       <c r="H467" t="n">
         <v>5887</v>
@@ -13941,7 +13941,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G468" t="n">
-        <v>2.30720973014832</v>
+        <v>2.30720996856689</v>
       </c>
       <c r="H468" t="n">
         <v>9061</v>
@@ -13970,7 +13970,7 @@
         <v>2.76200008392334</v>
       </c>
       <c r="G469" t="n">
-        <v>2.31223320960999</v>
+        <v>2.31223297119141</v>
       </c>
       <c r="H469" t="n">
         <v>22755</v>
@@ -14028,7 +14028,7 @@
         <v>2.78200006484985</v>
       </c>
       <c r="G471" t="n">
-        <v>2.32897639274597</v>
+        <v>2.32897615432739</v>
       </c>
       <c r="H471" t="n">
         <v>4737</v>
@@ -14057,7 +14057,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G472" t="n">
-        <v>2.38088035583496</v>
+        <v>2.38088011741638</v>
       </c>
       <c r="H472" t="n">
         <v>1133</v>
@@ -14086,7 +14086,7 @@
         <v>2.84400010108948</v>
       </c>
       <c r="G473" t="n">
-        <v>2.38088035583496</v>
+        <v>2.38088011741638</v>
       </c>
       <c r="H473" t="n">
         <v>0</v>
@@ -14144,7 +14144,7 @@
         <v>2.81399989128113</v>
       </c>
       <c r="G475" t="n">
-        <v>2.35576486587524</v>
+        <v>2.35576510429382</v>
       </c>
       <c r="H475" t="n">
         <v>690</v>
@@ -14202,7 +14202,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G477" t="n">
-        <v>2.31055855751038</v>
+        <v>2.31055879592896</v>
       </c>
       <c r="H477" t="n">
         <v>7084</v>
@@ -14347,7 +14347,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G482" t="n">
-        <v>2.30051279067993</v>
+        <v>2.30051255226135</v>
       </c>
       <c r="H482" t="n">
         <v>3600</v>
@@ -14434,7 +14434,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H485" t="n">
         <v>10072</v>
@@ -14579,7 +14579,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G490" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H490" t="n">
         <v>1000</v>
@@ -14608,7 +14608,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G491" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H491" t="n">
         <v>794</v>
@@ -14666,7 +14666,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G493" t="n">
-        <v>2.25363159179688</v>
+        <v>2.25363206863403</v>
       </c>
       <c r="H493" t="n">
         <v>11875</v>
@@ -14753,7 +14753,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H496" t="n">
         <v>1605</v>
@@ -14782,7 +14782,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G497" t="n">
-        <v>2.22014546394348</v>
+        <v>2.2201452255249</v>
       </c>
       <c r="H497" t="n">
         <v>3373</v>
@@ -14869,7 +14869,7 @@
         <v>2.7960000038147</v>
       </c>
       <c r="G500" t="n">
-        <v>2.34069657325745</v>
+        <v>2.34069633483887</v>
       </c>
       <c r="H500" t="n">
         <v>17797</v>
@@ -14898,7 +14898,7 @@
         <v>2.7260000705719</v>
       </c>
       <c r="G501" t="n">
-        <v>2.28209543228149</v>
+        <v>2.28209519386292</v>
       </c>
       <c r="H501" t="n">
         <v>7848</v>
@@ -14927,7 +14927,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G502" t="n">
-        <v>2.25363159179688</v>
+        <v>2.25363206863403</v>
       </c>
       <c r="H502" t="n">
         <v>495</v>
@@ -14985,7 +14985,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G504" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H504" t="n">
         <v>2250</v>
@@ -15014,7 +15014,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G505" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H505" t="n">
         <v>7001</v>
@@ -15072,7 +15072,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G507" t="n">
-        <v>2.16154456138611</v>
+        <v>2.16154432296753</v>
       </c>
       <c r="H507" t="n">
         <v>16456</v>
@@ -15101,7 +15101,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G508" t="n">
-        <v>2.16321849822998</v>
+        <v>2.16321897506714</v>
       </c>
       <c r="H508" t="n">
         <v>8399</v>
@@ -15130,7 +15130,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G509" t="n">
-        <v>2.16154456138611</v>
+        <v>2.16154432296753</v>
       </c>
       <c r="H509" t="n">
         <v>5173</v>
@@ -15246,7 +15246,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H513" t="n">
         <v>7544</v>
@@ -15275,7 +15275,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G514" t="n">
-        <v>2.15149831771851</v>
+        <v>2.15149855613708</v>
       </c>
       <c r="H514" t="n">
         <v>8228</v>
@@ -15333,7 +15333,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G516" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H516" t="n">
         <v>5412</v>
@@ -15362,7 +15362,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>2.21009969711304</v>
+        <v>2.21009993553162</v>
       </c>
       <c r="H517" t="n">
         <v>3706</v>
@@ -15391,7 +15391,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H518" t="n">
         <v>6410</v>
@@ -15449,7 +15449,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H520" t="n">
         <v>60857</v>
@@ -15478,7 +15478,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H521" t="n">
         <v>14606</v>
@@ -15507,7 +15507,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H522" t="n">
         <v>5832</v>
@@ -15565,7 +15565,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G524" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H524" t="n">
         <v>1330</v>
@@ -15594,7 +15594,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H525" t="n">
         <v>4875</v>
@@ -15623,7 +15623,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H526" t="n">
         <v>1009</v>
@@ -15652,7 +15652,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G527" t="n">
-        <v>2.21009969711304</v>
+        <v>2.21009993553162</v>
       </c>
       <c r="H527" t="n">
         <v>6584</v>
@@ -15681,7 +15681,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>2.21847105026245</v>
+        <v>2.21847128868103</v>
       </c>
       <c r="H528" t="n">
         <v>4342</v>
@@ -15710,7 +15710,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H529" t="n">
         <v>1800</v>
@@ -15739,7 +15739,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G530" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H530" t="n">
         <v>3093</v>
@@ -15797,7 +15797,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G532" t="n">
-        <v>2.22684288024902</v>
+        <v>2.22684264183044</v>
       </c>
       <c r="H532" t="n">
         <v>4342</v>
@@ -15855,7 +15855,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H534" t="n">
         <v>984</v>
@@ -15884,7 +15884,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H535" t="n">
         <v>1855</v>
@@ -15913,7 +15913,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.1598699092865</v>
+        <v>2.15987014770508</v>
       </c>
       <c r="H536" t="n">
         <v>2307</v>
@@ -15942,7 +15942,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H537" t="n">
         <v>5685</v>
@@ -16000,7 +16000,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H539" t="n">
         <v>9044</v>
@@ -16029,7 +16029,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.1598699092865</v>
+        <v>2.15987014770508</v>
       </c>
       <c r="H540" t="n">
         <v>1963</v>
@@ -16058,7 +16058,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>2.1598699092865</v>
+        <v>2.15987014770508</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G543" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H543" t="n">
         <v>7722</v>
@@ -16145,7 +16145,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H544" t="n">
         <v>2673</v>
@@ -16174,7 +16174,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G545" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H545" t="n">
         <v>1800</v>
@@ -16203,7 +16203,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H546" t="n">
         <v>1300</v>
@@ -16232,7 +16232,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H547" t="n">
         <v>1985</v>
@@ -16261,7 +16261,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H548" t="n">
         <v>1390</v>
@@ -16290,7 +16290,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16406,7 +16406,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G553" t="n">
-        <v>2.06778264045715</v>
+        <v>2.06778287887573</v>
       </c>
       <c r="H553" t="n">
         <v>10951</v>
@@ -16435,7 +16435,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G554" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475489616394</v>
       </c>
       <c r="H554" t="n">
         <v>19861</v>
@@ -16464,7 +16464,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06778264045715</v>
+        <v>2.06778287887573</v>
       </c>
       <c r="H555" t="n">
         <v>3370</v>
@@ -16493,7 +16493,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H556" t="n">
         <v>3626</v>
@@ -16551,7 +16551,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G558" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266762733459</v>
       </c>
       <c r="H558" t="n">
         <v>1420</v>
@@ -16580,7 +16580,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266762733459</v>
       </c>
       <c r="H559" t="n">
         <v>1988</v>
@@ -16609,7 +16609,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266762733459</v>
       </c>
       <c r="H560" t="n">
         <v>2000</v>
@@ -16638,7 +16638,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266762733459</v>
       </c>
       <c r="H561" t="n">
         <v>75</v>
@@ -16725,7 +16725,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H564" t="n">
         <v>28258</v>
@@ -16899,7 +16899,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G570" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H570" t="n">
         <v>4499</v>
@@ -16928,7 +16928,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G571" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H571" t="n">
         <v>5450</v>
@@ -16957,7 +16957,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H572" t="n">
         <v>810</v>
@@ -16986,7 +16986,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G573" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H573" t="n">
         <v>69257</v>
@@ -17044,7 +17044,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H575" t="n">
         <v>19688</v>
@@ -17160,7 +17160,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H579" t="n">
         <v>8071</v>
@@ -17189,7 +17189,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G580" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H580" t="n">
         <v>11844</v>
@@ -17218,7 +17218,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H581" t="n">
         <v>28615</v>
@@ -17305,7 +17305,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G584" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H584" t="n">
         <v>14481</v>
@@ -17334,7 +17334,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G585" t="n">
-        <v>2.06778264045715</v>
+        <v>2.06778287887573</v>
       </c>
       <c r="H585" t="n">
         <v>16930</v>
@@ -17363,7 +17363,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G586" t="n">
-        <v>2.22684288024902</v>
+        <v>2.22684264183044</v>
       </c>
       <c r="H586" t="n">
         <v>62764</v>
@@ -17392,7 +17392,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G587" t="n">
-        <v>2.19335651397705</v>
+        <v>2.19335627555847</v>
       </c>
       <c r="H587" t="n">
         <v>20156</v>
@@ -17479,7 +17479,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G590" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H590" t="n">
         <v>4774</v>
@@ -17508,7 +17508,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H591" t="n">
         <v>9720</v>
@@ -17537,7 +17537,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H592" t="n">
         <v>37954</v>
@@ -17566,7 +17566,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H593" t="n">
         <v>2336</v>
@@ -17624,7 +17624,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475489616394</v>
       </c>
       <c r="H595" t="n">
         <v>8105</v>
@@ -17653,7 +17653,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G596" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H596" t="n">
         <v>10304</v>
@@ -17682,7 +17682,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G597" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H597" t="n">
         <v>31964</v>
@@ -17711,7 +17711,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G598" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H598" t="n">
         <v>5068</v>
@@ -17740,7 +17740,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H599" t="n">
         <v>16850</v>
@@ -17769,7 +17769,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H600" t="n">
         <v>15758</v>
@@ -17827,7 +17827,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G602" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H602" t="n">
         <v>929</v>
@@ -17885,7 +17885,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G604" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266762733459</v>
       </c>
       <c r="H604" t="n">
         <v>1612</v>
@@ -17943,7 +17943,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266762733459</v>
       </c>
       <c r="H606" t="n">
         <v>8516</v>
@@ -18001,7 +18001,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H608" t="n">
         <v>34072</v>
@@ -18146,7 +18146,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G613" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H613" t="n">
         <v>9679</v>
@@ -18175,7 +18175,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H614" t="n">
         <v>11769</v>
@@ -18291,7 +18291,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G618" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H618" t="n">
         <v>13572</v>
@@ -18320,7 +18320,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G619" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H619" t="n">
         <v>2150</v>
@@ -18349,7 +18349,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H620" t="n">
         <v>11523</v>
@@ -18378,7 +18378,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G621" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H621" t="n">
         <v>18421</v>
@@ -18407,7 +18407,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G622" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H622" t="n">
         <v>7799</v>
@@ -18436,7 +18436,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H623" t="n">
         <v>6806</v>
@@ -18465,7 +18465,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H625" t="n">
         <v>2432</v>
@@ -18552,7 +18552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H627" t="n">
         <v>16352</v>
@@ -18581,7 +18581,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H628" t="n">
         <v>1464</v>
@@ -18610,7 +18610,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H629" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G631" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H631" t="n">
         <v>17617</v>
@@ -18697,7 +18697,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H632" t="n">
         <v>750</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H633" t="n">
         <v>29390</v>
@@ -18755,7 +18755,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H634" t="n">
         <v>11440</v>
@@ -18784,7 +18784,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H635" t="n">
         <v>11880</v>
@@ -18871,7 +18871,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H638" t="n">
         <v>9880</v>
@@ -18900,7 +18900,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G639" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H639" t="n">
         <v>5501</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H640" t="n">
         <v>18356</v>
@@ -18987,7 +18987,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H642" t="n">
         <v>12670</v>
@@ -19016,7 +19016,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H643" t="n">
         <v>23302</v>
@@ -19045,7 +19045,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H644" t="n">
         <v>2768</v>
@@ -19074,7 +19074,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19103,7 +19103,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H646" t="n">
         <v>1650</v>
@@ -19132,7 +19132,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G647" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H647" t="n">
         <v>2390</v>
@@ -19161,7 +19161,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H648" t="n">
         <v>19602</v>
@@ -19277,7 +19277,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G652" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H652" t="n">
         <v>150</v>
@@ -19364,7 +19364,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G655" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H655" t="n">
         <v>1900</v>
@@ -19422,7 +19422,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G657" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H657" t="n">
         <v>14198</v>
@@ -19480,7 +19480,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H659" t="n">
         <v>5758</v>
@@ -19857,7 +19857,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G672" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H672" t="n">
         <v>201</v>
@@ -19886,7 +19886,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H673" t="n">
         <v>62</v>
@@ -19915,7 +19915,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H674" t="n">
         <v>7700</v>
@@ -19973,7 +19973,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G676" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H676" t="n">
         <v>17668</v>
@@ -20060,7 +20060,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H679" t="n">
         <v>1532</v>
@@ -20089,7 +20089,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H680" t="n">
         <v>12081</v>
@@ -20118,7 +20118,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H681" t="n">
         <v>1528</v>
@@ -20176,7 +20176,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H683" t="n">
         <v>18382</v>
@@ -20205,7 +20205,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G684" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H684" t="n">
         <v>84</v>
@@ -20234,7 +20234,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H685" t="n">
         <v>6020</v>
@@ -20263,7 +20263,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G686" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H686" t="n">
         <v>567</v>
@@ -20292,7 +20292,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H687" t="n">
         <v>9265</v>
@@ -20350,7 +20350,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G689" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H689" t="n">
         <v>5573</v>
@@ -20379,7 +20379,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H690" t="n">
         <v>24561</v>
@@ -20408,7 +20408,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H691" t="n">
         <v>13491</v>
@@ -20437,7 +20437,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G692" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H692" t="n">
         <v>1155</v>
@@ -20466,7 +20466,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H693" t="n">
         <v>8645</v>
@@ -20524,7 +20524,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H695" t="n">
         <v>11225</v>
@@ -20611,7 +20611,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H698" t="n">
         <v>913</v>
@@ -20698,7 +20698,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H701" t="n">
         <v>2949</v>
@@ -20785,7 +20785,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H704" t="n">
         <v>12905</v>
@@ -20814,7 +20814,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G705" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H705" t="n">
         <v>3197</v>
@@ -20843,7 +20843,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H706" t="n">
         <v>2800</v>
@@ -20872,7 +20872,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G707" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H707" t="n">
         <v>7584</v>
@@ -20901,7 +20901,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H708" t="n">
         <v>12307</v>
@@ -20930,7 +20930,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H709" t="n">
         <v>11172</v>
@@ -20959,7 +20959,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G710" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H710" t="n">
         <v>3380</v>
@@ -20988,7 +20988,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H711" t="n">
         <v>8295</v>
@@ -21017,7 +21017,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G712" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H712" t="n">
         <v>201</v>
@@ -21046,7 +21046,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G713" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H713" t="n">
         <v>1200</v>
@@ -21075,7 +21075,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G714" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H714" t="n">
         <v>3223</v>
@@ -21104,7 +21104,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H715" t="n">
         <v>8942</v>
@@ -21133,7 +21133,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>1.75803375244141</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H716" t="n">
         <v>8743</v>
@@ -21162,7 +21162,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G717" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H717" t="n">
         <v>4607</v>
@@ -21191,7 +21191,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H718" t="n">
         <v>453</v>
@@ -21249,7 +21249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G720" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H720" t="n">
         <v>2261</v>
@@ -21336,7 +21336,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G723" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H723" t="n">
         <v>4248</v>
@@ -21365,7 +21365,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G724" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H724" t="n">
         <v>15763</v>
@@ -21394,7 +21394,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G725" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H725" t="n">
         <v>150</v>
@@ -21423,7 +21423,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H726" t="n">
         <v>5624</v>
@@ -21452,7 +21452,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G727" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H727" t="n">
         <v>6793</v>
@@ -21481,7 +21481,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G728" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H728" t="n">
         <v>2505</v>
@@ -21510,7 +21510,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G729" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H729" t="n">
         <v>10871</v>
@@ -21539,7 +21539,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H730" t="n">
         <v>13567</v>
@@ -21568,7 +21568,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H731" t="n">
         <v>2175</v>
@@ -21597,7 +21597,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H732" t="n">
         <v>1000</v>
@@ -21626,7 +21626,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H733" t="n">
         <v>9925</v>
@@ -21684,7 +21684,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G735" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H735" t="n">
         <v>1932</v>
@@ -21742,7 +21742,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G737" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H737" t="n">
         <v>11972</v>
@@ -21771,7 +21771,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G738" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H738" t="n">
         <v>18808</v>
@@ -21887,7 +21887,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H742" t="n">
         <v>4228</v>
@@ -21916,7 +21916,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H743" t="n">
         <v>2159</v>
@@ -21974,7 +21974,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H745" t="n">
         <v>4281</v>
@@ -22003,7 +22003,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H746" t="n">
         <v>10786</v>
@@ -22032,7 +22032,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H747" t="n">
         <v>650</v>
@@ -22090,7 +22090,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H749" t="n">
         <v>1080</v>
@@ -22119,7 +22119,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>1.97569501399994</v>
+        <v>1.97569513320923</v>
       </c>
       <c r="H750" t="n">
         <v>2189</v>
@@ -22177,7 +22177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H752" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H754" t="n">
         <v>3184</v>
@@ -22264,7 +22264,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H755" t="n">
         <v>5896</v>
@@ -22293,7 +22293,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G756" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H756" t="n">
         <v>3784</v>
@@ -22351,7 +22351,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G758" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H758" t="n">
         <v>2200</v>
@@ -22380,7 +22380,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H759" t="n">
         <v>5639</v>
@@ -22409,7 +22409,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H760" t="n">
         <v>2200</v>
@@ -22467,7 +22467,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G762" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H762" t="n">
         <v>1526</v>
@@ -22496,7 +22496,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H763" t="n">
         <v>591</v>
@@ -22525,7 +22525,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H767" t="n">
         <v>10550</v>
@@ -22670,7 +22670,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H769" t="n">
         <v>2742</v>
@@ -22699,7 +22699,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G770" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H770" t="n">
         <v>450</v>
@@ -22786,7 +22786,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H773" t="n">
         <v>3986</v>
@@ -22815,7 +22815,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H774" t="n">
         <v>3700</v>
@@ -22844,7 +22844,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H776" t="n">
         <v>1303</v>
@@ -22902,7 +22902,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G777" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H777" t="n">
         <v>4737</v>
@@ -22931,7 +22931,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H778" t="n">
         <v>6827</v>
@@ -22960,7 +22960,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H779" t="n">
         <v>780</v>
@@ -22989,7 +22989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H780" t="n">
         <v>5010</v>
@@ -23018,7 +23018,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H781" t="n">
         <v>3509</v>
@@ -23047,7 +23047,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H782" t="n">
         <v>256</v>
@@ -23076,7 +23076,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H783" t="n">
         <v>400</v>
@@ -23163,7 +23163,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G786" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H786" t="n">
         <v>800</v>
@@ -23192,7 +23192,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H787" t="n">
         <v>2220</v>
@@ -23221,7 +23221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G788" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H788" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H789" t="n">
         <v>1100</v>
@@ -23279,7 +23279,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H790" t="n">
         <v>12087</v>
@@ -23308,7 +23308,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H791" t="n">
         <v>1232</v>
@@ -23337,7 +23337,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H792" t="n">
         <v>5850</v>
@@ -23453,7 +23453,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G796" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H796" t="n">
         <v>1400</v>
@@ -23482,7 +23482,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H797" t="n">
         <v>3229</v>
@@ -23569,7 +23569,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H800" t="n">
         <v>2600</v>
@@ -23598,7 +23598,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H801" t="n">
         <v>100</v>
@@ -23627,7 +23627,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H802" t="n">
         <v>3832</v>
@@ -23656,7 +23656,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H803" t="n">
         <v>1268</v>
@@ -23685,7 +23685,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H804" t="n">
         <v>1209</v>
@@ -23714,7 +23714,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G805" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H805" t="n">
         <v>3425</v>
@@ -23743,7 +23743,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H806" t="n">
         <v>802</v>
@@ -23772,7 +23772,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H807" t="n">
         <v>15527</v>
@@ -23801,7 +23801,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H808" t="n">
         <v>6096</v>
@@ -23830,7 +23830,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H809" t="n">
         <v>2001</v>
@@ -23859,7 +23859,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H810" t="n">
         <v>10120</v>
@@ -23888,7 +23888,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H811" t="n">
         <v>1012</v>
@@ -23917,7 +23917,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H812" t="n">
         <v>2405</v>
@@ -23946,7 +23946,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G813" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H813" t="n">
         <v>2826</v>
@@ -23975,7 +23975,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H814" t="n">
         <v>461</v>
@@ -24004,7 +24004,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H815" t="n">
         <v>3</v>
@@ -24033,7 +24033,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H816" t="n">
         <v>6014</v>
@@ -24062,7 +24062,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H817" t="n">
         <v>3239</v>
@@ -24120,7 +24120,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H819" t="n">
         <v>2968</v>
@@ -24149,7 +24149,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H820" t="n">
         <v>5121</v>
@@ -24207,7 +24207,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G822" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H822" t="n">
         <v>2411</v>
@@ -24265,7 +24265,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G824" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H824" t="n">
         <v>4424</v>
@@ -24294,7 +24294,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H825" t="n">
         <v>11252</v>
@@ -24381,7 +24381,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H828" t="n">
         <v>11857</v>
@@ -24410,7 +24410,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H829" t="n">
         <v>2204</v>
@@ -24439,7 +24439,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H830" t="n">
         <v>3888</v>
@@ -24497,7 +24497,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H832" t="n">
         <v>2898</v>
@@ -24526,7 +24526,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G833" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H833" t="n">
         <v>2103</v>
@@ -24555,7 +24555,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H834" t="n">
         <v>300</v>
@@ -24584,7 +24584,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H835" t="n">
         <v>2305</v>
@@ -24613,7 +24613,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H836" t="n">
         <v>2886</v>
@@ -24642,7 +24642,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H837" t="n">
         <v>1000</v>
@@ -24700,7 +24700,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G839" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H839" t="n">
         <v>2588</v>
@@ -24758,7 +24758,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H841" t="n">
         <v>4430</v>
@@ -24787,7 +24787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24874,7 +24874,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H845" t="n">
         <v>4803</v>
@@ -24903,7 +24903,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H846" t="n">
         <v>1750</v>
@@ -24932,7 +24932,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H847" t="n">
         <v>3200</v>
@@ -24961,7 +24961,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G848" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H848" t="n">
         <v>8445</v>
@@ -24990,7 +24990,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H849" t="n">
         <v>9330</v>
@@ -25019,7 +25019,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G850" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H850" t="n">
         <v>765</v>
@@ -25048,7 +25048,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H851" t="n">
         <v>6863</v>
@@ -25077,7 +25077,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G852" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H852" t="n">
         <v>1000</v>
@@ -25135,7 +25135,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G854" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H854" t="n">
         <v>3872</v>
@@ -25164,7 +25164,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H855" t="n">
         <v>2728</v>
@@ -25193,7 +25193,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H856" t="n">
         <v>21184</v>
@@ -25222,7 +25222,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G857" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H857" t="n">
         <v>29</v>
@@ -25251,7 +25251,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G858" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H858" t="n">
         <v>96</v>
@@ -25280,7 +25280,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H859" t="n">
         <v>1117</v>
@@ -25338,7 +25338,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G861" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H861" t="n">
         <v>4010</v>
@@ -25367,7 +25367,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H862" t="n">
         <v>3300</v>
@@ -25396,7 +25396,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G863" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H863" t="n">
         <v>1000</v>
@@ -25425,7 +25425,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G864" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H864" t="n">
         <v>4645</v>
@@ -25454,7 +25454,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G865" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H865" t="n">
         <v>5</v>
@@ -25483,7 +25483,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G866" t="n">
-        <v>1.75803375244141</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H866" t="n">
         <v>6120</v>
@@ -25570,7 +25570,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.72454738616943</v>
+        <v>1.72454750537872</v>
       </c>
       <c r="H869" t="n">
         <v>8586</v>
@@ -25599,7 +25599,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G870" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H870" t="n">
         <v>8670</v>
@@ -25744,7 +25744,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G875" t="n">
-        <v>1.66594612598419</v>
+        <v>1.66594636440277</v>
       </c>
       <c r="H875" t="n">
         <v>12403</v>
@@ -25802,7 +25802,7 @@
         <v>2</v>
       </c>
       <c r="G877" t="n">
-        <v>1.67431795597076</v>
+        <v>1.67431783676147</v>
       </c>
       <c r="H877" t="n">
         <v>3127</v>
@@ -25831,7 +25831,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.6324599981308</v>
+        <v>1.63245987892151</v>
       </c>
       <c r="H878" t="n">
         <v>2912</v>
@@ -25860,7 +25860,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G879" t="n">
-        <v>1.6324599981308</v>
+        <v>1.63245987892151</v>
       </c>
       <c r="H879" t="n">
         <v>13775</v>
@@ -25976,7 +25976,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G883" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H883" t="n">
         <v>536</v>
@@ -26005,7 +26005,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G884" t="n">
-        <v>1.64920318126678</v>
+        <v>1.6492030620575</v>
       </c>
       <c r="H884" t="n">
         <v>13029</v>
@@ -26034,7 +26034,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.65338897705078</v>
+        <v>1.65338885784149</v>
       </c>
       <c r="H885" t="n">
         <v>503</v>
@@ -26063,7 +26063,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G886" t="n">
-        <v>1.62408828735352</v>
+        <v>1.62408840656281</v>
       </c>
       <c r="H886" t="n">
         <v>7320</v>
@@ -26092,7 +26092,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G887" t="n">
-        <v>1.6324599981308</v>
+        <v>1.63245987892151</v>
       </c>
       <c r="H887" t="n">
         <v>19316</v>
@@ -26150,7 +26150,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G889" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H889" t="n">
         <v>18350</v>
@@ -26266,7 +26266,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G893" t="n">
-        <v>1.70780408382416</v>
+        <v>1.70780420303345</v>
       </c>
       <c r="H893" t="n">
         <v>1710</v>
@@ -26382,7 +26382,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G897" t="n">
-        <v>1.76640522480011</v>
+        <v>1.76640510559082</v>
       </c>
       <c r="H897" t="n">
         <v>5396</v>
@@ -26440,7 +26440,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H899" t="n">
         <v>5146</v>
@@ -26469,7 +26469,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G900" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H900" t="n">
         <v>3694</v>
@@ -26498,7 +26498,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H901" t="n">
         <v>2716</v>
@@ -26556,7 +26556,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G903" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H903" t="n">
         <v>4103</v>
@@ -26585,7 +26585,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G904" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H904" t="n">
         <v>2094</v>
@@ -26614,7 +26614,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G905" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H905" t="n">
         <v>4903</v>
@@ -26643,7 +26643,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H906" t="n">
         <v>1414</v>
@@ -26701,7 +26701,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G908" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H908" t="n">
         <v>3344</v>
@@ -26730,7 +26730,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -26759,7 +26759,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G910" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H910" t="n">
         <v>6803</v>
@@ -26788,7 +26788,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G911" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H911" t="n">
         <v>0</v>
@@ -26817,7 +26817,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G912" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H912" t="n">
         <v>1000</v>
@@ -26846,7 +26846,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H913" t="n">
         <v>1600</v>
@@ -26904,7 +26904,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G915" t="n">
-        <v>1.76640522480011</v>
+        <v>1.76640510559082</v>
       </c>
       <c r="H915" t="n">
         <v>2527</v>
@@ -26933,7 +26933,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G916" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H916" t="n">
         <v>19450</v>
@@ -26962,7 +26962,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H917" t="n">
         <v>2716</v>
@@ -27078,7 +27078,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G921" t="n">
-        <v>1.76640522480011</v>
+        <v>1.76640510559082</v>
       </c>
       <c r="H921" t="n">
         <v>6074</v>
@@ -27107,7 +27107,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G922" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H922" t="n">
         <v>2463</v>
@@ -27136,7 +27136,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H923" t="n">
         <v>1865</v>
@@ -27165,7 +27165,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G924" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H924" t="n">
         <v>6648</v>
@@ -27194,7 +27194,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H925" t="n">
         <v>5083</v>
@@ -27223,7 +27223,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G926" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H926" t="n">
         <v>2754</v>
@@ -27252,7 +27252,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G927" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H927" t="n">
         <v>16295</v>
@@ -27281,7 +27281,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G928" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H928" t="n">
         <v>977</v>
@@ -27310,7 +27310,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G929" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H929" t="n">
         <v>256</v>
@@ -27339,7 +27339,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G930" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H930" t="n">
         <v>2800</v>
@@ -27368,7 +27368,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G931" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H931" t="n">
         <v>1435</v>
@@ -27542,7 +27542,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G937" t="n">
-        <v>1.76640522480011</v>
+        <v>1.76640510559082</v>
       </c>
       <c r="H937" t="n">
         <v>1540</v>
@@ -27600,7 +27600,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G939" t="n">
-        <v>1.75803375244141</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H939" t="n">
         <v>6005</v>
@@ -27716,7 +27716,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H943" t="n">
         <v>24151</v>
@@ -27745,7 +27745,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G944" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H944" t="n">
         <v>37350</v>
@@ -27803,7 +27803,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H946" t="n">
         <v>6198</v>
@@ -27832,7 +27832,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H947" t="n">
         <v>10416</v>
@@ -27861,7 +27861,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G948" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H948" t="n">
         <v>5166</v>
@@ -27890,7 +27890,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G949" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H949" t="n">
         <v>4411</v>
@@ -27919,7 +27919,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G950" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H950" t="n">
         <v>3240</v>
@@ -27948,7 +27948,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G951" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H951" t="n">
         <v>1947</v>
@@ -27977,7 +27977,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H952" t="n">
         <v>27709</v>
@@ -28064,7 +28064,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G955" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H955" t="n">
         <v>9230</v>
@@ -28093,7 +28093,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H956" t="n">
         <v>3149</v>
@@ -28122,7 +28122,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H957" t="n">
         <v>6241</v>
@@ -28151,7 +28151,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G958" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H958" t="n">
         <v>9624</v>
@@ -28180,7 +28180,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G959" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H959" t="n">
         <v>1792</v>
@@ -28209,7 +28209,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G960" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H960" t="n">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G961" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H961" t="n">
         <v>1234</v>
@@ -28296,7 +28296,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G963" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H963" t="n">
         <v>2281</v>
@@ -28325,7 +28325,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G964" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H964" t="n">
         <v>29139</v>
@@ -28383,7 +28383,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G966" t="n">
-        <v>1.76640522480011</v>
+        <v>1.76640510559082</v>
       </c>
       <c r="H966" t="n">
         <v>6985</v>
@@ -28499,7 +28499,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H970" t="n">
         <v>7180</v>
@@ -28557,7 +28557,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G972" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H972" t="n">
         <v>7551</v>
@@ -28586,7 +28586,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79989182949066</v>
+        <v>1.79989171028137</v>
       </c>
       <c r="H973" t="n">
         <v>3487</v>
@@ -28615,7 +28615,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G974" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H974" t="n">
         <v>1474</v>
@@ -28673,7 +28673,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G976" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H976" t="n">
         <v>226</v>
@@ -28702,7 +28702,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G977" t="n">
-        <v>1.81663489341736</v>
+        <v>1.81663501262665</v>
       </c>
       <c r="H977" t="n">
         <v>24</v>
@@ -28731,7 +28731,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G978" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H978" t="n">
         <v>15981</v>
@@ -28789,7 +28789,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H980" t="n">
         <v>12200</v>
@@ -28818,7 +28818,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G981" t="n">
-        <v>1.85012114048004</v>
+        <v>1.85012125968933</v>
       </c>
       <c r="H981" t="n">
         <v>2107</v>
@@ -28847,7 +28847,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G982" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H982" t="n">
         <v>4216</v>
@@ -28905,7 +28905,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.1598699092865</v>
+        <v>2.15987014770508</v>
       </c>
       <c r="H984" t="n">
         <v>228846</v>
@@ -28963,7 +28963,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>2.1598699092865</v>
+        <v>2.15987014770508</v>
       </c>
       <c r="H986" t="n">
         <v>38716</v>
@@ -28992,7 +28992,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H987" t="n">
         <v>40415</v>
@@ -29021,7 +29021,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G988" t="n">
-        <v>2.15149831771851</v>
+        <v>2.15149855613708</v>
       </c>
       <c r="H988" t="n">
         <v>35149</v>
@@ -29050,7 +29050,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H989" t="n">
         <v>11373</v>
@@ -29166,7 +29166,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G993" t="n">
-        <v>2.14312696456909</v>
+        <v>2.14312672615051</v>
       </c>
       <c r="H993" t="n">
         <v>32055</v>
@@ -29195,7 +29195,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>2.26032876968384</v>
+        <v>2.260329246521</v>
       </c>
       <c r="H994" t="n">
         <v>135284</v>
@@ -29224,7 +29224,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G995" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H995" t="n">
         <v>88276</v>
@@ -29282,7 +29282,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>2.20172810554504</v>
+        <v>2.20172786712646</v>
       </c>
       <c r="H997" t="n">
         <v>20429</v>
@@ -29311,7 +29311,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475489616394</v>
       </c>
       <c r="H998" t="n">
         <v>21041</v>
@@ -29340,7 +29340,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G999" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H999" t="n">
         <v>18143</v>
@@ -29369,7 +29369,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1000" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H1000" t="n">
         <v>22474</v>
@@ -29456,7 +29456,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1003" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H1003" t="n">
         <v>2978</v>
@@ -29485,7 +29485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475489616394</v>
       </c>
       <c r="H1004" t="n">
         <v>4848</v>
@@ -29514,7 +29514,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1005" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H1005" t="n">
         <v>6059</v>
@@ -29543,7 +29543,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475489616394</v>
       </c>
       <c r="H1006" t="n">
         <v>593</v>
@@ -29572,7 +29572,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1007" t="n">
-        <v>2.10964035987854</v>
+        <v>2.10964059829712</v>
       </c>
       <c r="H1007" t="n">
         <v>11864</v>
@@ -29659,7 +29659,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H1010" t="n">
         <v>6972</v>
@@ -29804,7 +29804,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.02592468261719</v>
+        <v>2.02592492103577</v>
       </c>
       <c r="H1015" t="n">
         <v>5825</v>
@@ -30036,7 +30036,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.99243831634521</v>
+        <v>1.99243819713593</v>
       </c>
       <c r="H1023" t="n">
         <v>34472</v>
@@ -30152,7 +30152,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H1027" t="n">
         <v>26611</v>
@@ -30181,7 +30181,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1028" t="n">
         <v>6112</v>
@@ -30210,7 +30210,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H1029" t="n">
         <v>1805</v>
@@ -30239,7 +30239,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H1030" t="n">
         <v>8304</v>
@@ -30268,7 +30268,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.96732354164124</v>
+        <v>1.96732342243195</v>
       </c>
       <c r="H1031" t="n">
         <v>3685</v>
@@ -30297,7 +30297,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1032" t="n">
         <v>7041</v>
@@ -30355,7 +30355,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1034" t="n">
         <v>1887</v>
@@ -30384,7 +30384,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1035" t="n">
         <v>500</v>
@@ -30442,7 +30442,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.89197897911072</v>
+        <v>1.89197909832001</v>
       </c>
       <c r="H1037" t="n">
         <v>8973</v>
@@ -30471,7 +30471,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.87523603439331</v>
+        <v>1.87523579597473</v>
       </c>
       <c r="H1038" t="n">
         <v>18702</v>
@@ -30500,7 +30500,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.90035080909729</v>
+        <v>1.900350689888</v>
       </c>
       <c r="H1039" t="n">
         <v>1542</v>
@@ -30558,7 +30558,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.95895183086395</v>
+        <v>1.95895171165466</v>
       </c>
       <c r="H1041" t="n">
         <v>8505</v>
@@ -30587,7 +30587,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.91709399223328</v>
+        <v>1.91709387302399</v>
       </c>
       <c r="H1042" t="n">
         <v>2690</v>
@@ -30674,7 +30674,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1045" t="n">
         <v>8755</v>
@@ -30848,7 +30848,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.92546570301056</v>
+        <v>1.92546546459198</v>
       </c>
       <c r="H1051" t="n">
         <v>1484</v>
@@ -30877,7 +30877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.93383681774139</v>
+        <v>1.93383717536926</v>
       </c>
       <c r="H1052" t="n">
         <v>3790</v>
@@ -30906,7 +30906,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.82500660419464</v>
+        <v>1.82500648498535</v>
       </c>
       <c r="H1053" t="n">
         <v>14075</v>
@@ -30935,7 +30935,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.84174966812134</v>
+        <v>1.84174978733063</v>
       </c>
       <c r="H1054" t="n">
         <v>2093</v>
@@ -30964,7 +30964,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H1055" t="n">
         <v>3728</v>
@@ -30993,7 +30993,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686456203461</v>
       </c>
       <c r="H1056" t="n">
         <v>61</v>
@@ -31022,7 +31022,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.83337819576263</v>
+        <v>1.83337807655334</v>
       </c>
       <c r="H1057" t="n">
         <v>8027</v>
@@ -31051,7 +31051,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.80826330184937</v>
+        <v>1.80826342105865</v>
       </c>
       <c r="H1058" t="n">
         <v>2815</v>
@@ -31080,7 +31080,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.74966204166412</v>
+        <v>1.74966216087341</v>
       </c>
       <c r="H1059" t="n">
         <v>10342</v>
@@ -31109,7 +31109,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.74966204166412</v>
+        <v>1.74966216087341</v>
       </c>
       <c r="H1060" t="n">
         <v>3550</v>
@@ -31225,7 +31225,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.23062360286713</v>
+        <v>1.23062372207642</v>
       </c>
       <c r="H1064" t="n">
         <v>26217</v>
@@ -31254,7 +31254,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.23480927944183</v>
+        <v>1.23480951786041</v>
       </c>
       <c r="H1065" t="n">
         <v>4894</v>
@@ -31312,7 +31312,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1067" t="n">
-        <v>1.19295132160187</v>
+        <v>1.19295144081116</v>
       </c>
       <c r="H1067" t="n">
         <v>3142</v>
@@ -31341,7 +31341,7 @@
         <v>1.42499995231628</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.19295132160187</v>
+        <v>1.19295144081116</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -31399,7 +31399,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.16365087032318</v>
+        <v>1.16365098953247</v>
       </c>
       <c r="H1070" t="n">
         <v>15128</v>
@@ -31428,7 +31428,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.21806633472443</v>
+        <v>1.21806609630585</v>
       </c>
       <c r="H1071" t="n">
         <v>7190</v>
@@ -31515,7 +31515,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.32689702510834</v>
+        <v>1.32689690589905</v>
       </c>
       <c r="H1074" t="n">
         <v>17265</v>
@@ -31776,7 +31776,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1083" t="n">
         <v>14296</v>
@@ -31863,7 +31863,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1086" t="n">
         <v>3453</v>
@@ -31979,7 +31979,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.5152575969696</v>
+        <v>1.51525771617889</v>
       </c>
       <c r="H1090" t="n">
         <v>15050</v>
@@ -32008,7 +32008,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.5152575969696</v>
+        <v>1.51525771617889</v>
       </c>
       <c r="H1091" t="n">
         <v>3000</v>
@@ -32182,7 +32182,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1097" t="n">
         <v>14855</v>
@@ -32240,7 +32240,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1099" t="n">
         <v>6020</v>
@@ -32298,7 +32298,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.54037237167358</v>
+        <v>1.54037249088287</v>
       </c>
       <c r="H1101" t="n">
         <v>2254</v>
@@ -32356,7 +32356,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1103" t="n">
         <v>1475</v>
@@ -32385,7 +32385,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177123069763</v>
       </c>
       <c r="H1104" t="n">
         <v>20622</v>
@@ -32414,7 +32414,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.48595714569092</v>
+        <v>1.48595702648163</v>
       </c>
       <c r="H1105" t="n">
         <v>22966</v>
@@ -32530,7 +32530,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1109" t="n">
         <v>21164</v>
@@ -32588,7 +32588,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177123069763</v>
       </c>
       <c r="H1111" t="n">
         <v>1230</v>
@@ -32849,7 +32849,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.54037237167358</v>
+        <v>1.54037249088287</v>
       </c>
       <c r="H1120" t="n">
         <v>3099</v>
@@ -32907,7 +32907,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1122" t="n">
         <v>5260</v>
@@ -32936,7 +32936,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1123" t="n">
         <v>0</v>
@@ -33052,7 +33052,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.48595714569092</v>
+        <v>1.48595702648163</v>
       </c>
       <c r="H1127" t="n">
         <v>1050</v>
@@ -33081,7 +33081,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1128" t="n">
         <v>3000</v>
@@ -33110,7 +33110,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177123069763</v>
       </c>
       <c r="H1129" t="n">
         <v>5185</v>
@@ -33284,7 +33284,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.48177134990692</v>
+        <v>1.48177123069763</v>
       </c>
       <c r="H1135" t="n">
         <v>7144</v>
@@ -33313,7 +33313,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1136" t="n">
         <v>1370</v>
@@ -33342,7 +33342,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1137" t="n">
         <v>1735</v>
@@ -33429,7 +33429,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1140" t="n">
         <v>1400</v>
@@ -33458,7 +33458,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.54037237167358</v>
+        <v>1.54037249088287</v>
       </c>
       <c r="H1141" t="n">
         <v>14818</v>
@@ -33632,7 +33632,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1147" t="n">
         <v>7208</v>
@@ -33806,7 +33806,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1153" t="n">
-        <v>1.46921384334564</v>
+        <v>1.46921396255493</v>
       </c>
       <c r="H1153" t="n">
         <v>12350</v>
@@ -33835,7 +33835,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1154" t="n">
-        <v>1.46921384334564</v>
+        <v>1.46921396255493</v>
       </c>
       <c r="H1154" t="n">
         <v>0</v>
@@ -33864,7 +33864,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.48595714569092</v>
+        <v>1.48595702648163</v>
       </c>
       <c r="H1155" t="n">
         <v>6963</v>
@@ -33893,7 +33893,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1156" t="n">
         <v>44600</v>
@@ -33922,7 +33922,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1157" t="n">
         <v>6271</v>
@@ -33951,7 +33951,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1158" t="n">
         <v>3500</v>
@@ -33980,7 +33980,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.40642702579498</v>
+        <v>1.40642690658569</v>
       </c>
       <c r="H1159" t="n">
         <v>4677</v>
@@ -34038,7 +34038,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.36875486373901</v>
+        <v>1.36875474452972</v>
       </c>
       <c r="H1161" t="n">
         <v>2579</v>
@@ -34154,7 +34154,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1165" t="n">
-        <v>1.33108282089233</v>
+        <v>1.33108270168304</v>
       </c>
       <c r="H1165" t="n">
         <v>16064</v>
@@ -34241,7 +34241,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.40642702579498</v>
+        <v>1.40642690658569</v>
       </c>
       <c r="H1168" t="n">
         <v>400</v>
@@ -34270,7 +34270,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1169" t="n">
         <v>100</v>
@@ -34299,7 +34299,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1170" t="n">
-        <v>1.41479873657227</v>
+        <v>1.41479861736298</v>
       </c>
       <c r="H1170" t="n">
         <v>15335</v>
@@ -34328,7 +34328,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1171" t="n">
         <v>1810</v>
@@ -34386,7 +34386,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1173" t="n">
         <v>630</v>
@@ -34415,7 +34415,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1174" t="n">
         <v>10251</v>
@@ -34444,7 +34444,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1175" t="n">
         <v>6777</v>
@@ -34473,7 +34473,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.40642702579498</v>
+        <v>1.40642690658569</v>
       </c>
       <c r="H1176" t="n">
         <v>3245</v>
@@ -34502,7 +34502,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1177" t="n">
         <v>250</v>
@@ -34531,7 +34531,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1178" t="n">
-        <v>1.41479873657227</v>
+        <v>1.41479861736298</v>
       </c>
       <c r="H1178" t="n">
         <v>450</v>
@@ -34589,7 +34589,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.40642702579498</v>
+        <v>1.40642690658569</v>
       </c>
       <c r="H1180" t="n">
         <v>175</v>
@@ -34618,7 +34618,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.44409918785095</v>
+        <v>1.44409930706024</v>
       </c>
       <c r="H1181" t="n">
         <v>3066</v>
@@ -34647,7 +34647,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1182" t="n">
         <v>1326</v>
@@ -34705,7 +34705,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1184" t="n">
         <v>3317</v>
@@ -34734,7 +34734,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1185" t="n">
         <v>14317</v>
@@ -34763,7 +34763,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.43991339206696</v>
+        <v>1.43991327285767</v>
       </c>
       <c r="H1186" t="n">
         <v>9963</v>
@@ -34792,7 +34792,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1187" t="n">
         <v>4762</v>
@@ -34821,7 +34821,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -34850,7 +34850,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1189" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1189" t="n">
         <v>15395</v>
@@ -34995,7 +34995,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1194" t="n">
         <v>20123</v>
@@ -35024,7 +35024,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1195" t="n">
         <v>14200</v>
@@ -35053,7 +35053,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1196" t="n">
         <v>12020</v>
@@ -35082,7 +35082,7 @@
         <v>1.75499999523163</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.46921384334564</v>
+        <v>1.46921396255493</v>
       </c>
       <c r="H1197" t="n">
         <v>28945</v>
@@ -35111,7 +35111,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1198" t="n">
         <v>38221</v>
@@ -35198,7 +35198,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.62408828735352</v>
+        <v>1.62408840656281</v>
       </c>
       <c r="H1201" t="n">
         <v>62126</v>
@@ -35256,7 +35256,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1203" t="n">
         <v>1151</v>
@@ -35285,7 +35285,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1204" t="n">
         <v>1750</v>
@@ -35343,7 +35343,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1206" t="n">
         <v>14696</v>
@@ -35575,7 +35575,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.52781510353088</v>
+        <v>1.52781498432159</v>
       </c>
       <c r="H1214" t="n">
         <v>8499</v>
@@ -35691,7 +35691,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1218" t="n">
         <v>6600</v>
@@ -35749,7 +35749,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1220" t="n">
         <v>25475</v>
@@ -35778,7 +35778,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1221" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1221" t="n">
         <v>20940</v>
@@ -35836,7 +35836,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1223" t="n">
         <v>3650</v>
@@ -36039,7 +36039,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1230" t="n">
         <v>17178</v>
@@ -36155,7 +36155,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.42317020893097</v>
+        <v>1.42317032814026</v>
       </c>
       <c r="H1234" t="n">
         <v>57052</v>
@@ -36184,7 +36184,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1235" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1235" t="n">
         <v>24039</v>
@@ -36213,7 +36213,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1236" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1236" t="n">
         <v>4217</v>
@@ -36329,7 +36329,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1240" t="n">
-        <v>1.45665657520294</v>
+        <v>1.45665645599365</v>
       </c>
       <c r="H1240" t="n">
         <v>17123</v>
@@ -36358,7 +36358,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339975833893</v>
       </c>
       <c r="H1241" t="n">
         <v>14984</v>
@@ -36387,7 +36387,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.5152575969696</v>
+        <v>1.51525771617889</v>
       </c>
       <c r="H1242" t="n">
         <v>18208</v>
@@ -36416,7 +36416,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1243" t="n">
         <v>3672</v>
@@ -36503,7 +36503,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1246" t="n">
         <v>35710</v>
@@ -36619,7 +36619,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1250" t="n">
         <v>22196</v>
@@ -36648,7 +36648,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.62408828735352</v>
+        <v>1.62408840656281</v>
       </c>
       <c r="H1251" t="n">
         <v>21214</v>
@@ -36677,7 +36677,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1252" t="n">
         <v>22429</v>
@@ -36706,7 +36706,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1253" t="n">
         <v>11120</v>
@@ -36793,7 +36793,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.62408828735352</v>
+        <v>1.62408840656281</v>
       </c>
       <c r="H1256" t="n">
         <v>29462</v>
@@ -36880,7 +36880,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1259" t="n">
         <v>23378</v>
@@ -36909,7 +36909,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1260" t="n">
         <v>24094</v>
@@ -36938,7 +36938,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1261" t="n">
         <v>23239</v>
@@ -36967,7 +36967,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.64920318126678</v>
+        <v>1.6492030620575</v>
       </c>
       <c r="H1262" t="n">
         <v>23031</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1263" t="n">
         <v>31133</v>
@@ -37025,7 +37025,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1264" t="n">
         <v>22054</v>
@@ -37054,7 +37054,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1265" t="n">
-        <v>1.54037237167358</v>
+        <v>1.54037249088287</v>
       </c>
       <c r="H1265" t="n">
         <v>24728</v>
@@ -37170,7 +37170,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1269" t="n">
         <v>9976</v>
@@ -37199,7 +37199,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1270" t="n">
         <v>13263</v>
@@ -37228,7 +37228,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1271" t="n">
         <v>17035</v>
@@ -37286,7 +37286,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1273" t="n">
         <v>7377</v>
@@ -37373,7 +37373,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1276" t="n">
         <v>7499</v>
@@ -37605,7 +37605,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1284" t="n">
         <v>15439</v>
@@ -37808,7 +37808,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.48595714569092</v>
+        <v>1.48595702648163</v>
       </c>
       <c r="H1291" t="n">
         <v>11472</v>
@@ -37866,7 +37866,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.48595714569092</v>
+        <v>1.48595702648163</v>
       </c>
       <c r="H1293" t="n">
         <v>4601</v>
@@ -38156,7 +38156,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1303" t="n">
         <v>11336</v>
@@ -38185,7 +38185,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1304" t="n">
-        <v>1.54037237167358</v>
+        <v>1.54037249088287</v>
       </c>
       <c r="H1304" t="n">
         <v>1493</v>
@@ -38301,7 +38301,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.52781510353088</v>
+        <v>1.52781498432159</v>
       </c>
       <c r="H1308" t="n">
         <v>5727</v>
@@ -38330,7 +38330,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.5152575969696</v>
+        <v>1.51525771617889</v>
       </c>
       <c r="H1309" t="n">
         <v>5186</v>
@@ -38388,7 +38388,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.5152575969696</v>
+        <v>1.51525771617889</v>
       </c>
       <c r="H1311" t="n">
         <v>2957</v>
@@ -38417,7 +38417,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.5152575969696</v>
+        <v>1.51525771617889</v>
       </c>
       <c r="H1312" t="n">
         <v>0</v>
@@ -38446,7 +38446,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1313" t="n">
-        <v>1.54037237167358</v>
+        <v>1.54037249088287</v>
       </c>
       <c r="H1313" t="n">
         <v>24030</v>
@@ -38736,7 +38736,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1323" t="n">
         <v>6150</v>
@@ -38765,7 +38765,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1324" t="n">
         <v>5020</v>
@@ -38823,7 +38823,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1326" t="n">
         <v>4660</v>
@@ -38852,7 +38852,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1327" t="n">
         <v>2570</v>
@@ -38881,7 +38881,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1328" t="n">
         <v>0</v>
@@ -39142,7 +39142,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1337" t="n">
         <v>1010</v>
@@ -39171,7 +39171,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1338" t="n">
         <v>22599</v>
@@ -39200,7 +39200,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1339" t="n">
         <v>14985</v>
@@ -39229,7 +39229,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1340" t="n">
         <v>6500</v>
@@ -39287,7 +39287,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1342" t="n">
         <v>5805</v>
@@ -39316,7 +39316,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1343" t="n">
         <v>5668</v>
@@ -39374,7 +39374,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1345" t="n">
         <v>43701</v>
@@ -39403,7 +39403,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1346" t="n">
         <v>31092</v>
@@ -39461,7 +39461,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1348" t="n">
         <v>3276</v>
@@ -39490,7 +39490,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1349" t="n">
         <v>1</v>
@@ -39577,7 +39577,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1352" t="n">
         <v>1068</v>
@@ -39809,7 +39809,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.55711567401886</v>
+        <v>1.55711555480957</v>
       </c>
       <c r="H1360" t="n">
         <v>3538</v>
@@ -40012,7 +40012,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1367" t="n">
         <v>1000</v>
@@ -40099,7 +40099,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1370" t="n">
         <v>5999</v>
@@ -40128,7 +40128,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1371" t="n">
         <v>10437</v>
@@ -40186,7 +40186,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1373" t="n">
         <v>3457</v>
@@ -40215,7 +40215,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1374" t="n">
         <v>27312</v>
@@ -40244,7 +40244,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1375" t="n">
         <v>3283</v>
@@ -40273,7 +40273,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1376" t="n">
         <v>5985</v>
@@ -40389,7 +40389,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1380" t="n">
         <v>4607</v>
@@ -40418,7 +40418,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1381" t="n">
         <v>7296</v>
@@ -40447,7 +40447,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1382" t="n">
         <v>400</v>
@@ -40476,7 +40476,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1383" t="n">
         <v>3336</v>
@@ -40505,7 +40505,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1384" t="n">
         <v>808</v>
@@ -40563,7 +40563,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1386" t="n">
         <v>3693</v>
@@ -40592,7 +40592,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1387" t="n">
         <v>2849</v>
@@ -40650,7 +40650,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1389" t="n">
         <v>12896</v>
@@ -40679,7 +40679,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.63664579391479</v>
+        <v>1.63664567470551</v>
       </c>
       <c r="H1390" t="n">
         <v>38449</v>
@@ -40708,7 +40708,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.62408828735352</v>
+        <v>1.62408840656281</v>
       </c>
       <c r="H1391" t="n">
         <v>2182</v>
@@ -40737,7 +40737,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.62408828735352</v>
+        <v>1.62408840656281</v>
       </c>
       <c r="H1392" t="n">
         <v>1010</v>
@@ -40766,7 +40766,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1393" t="n">
         <v>9710</v>
@@ -40795,7 +40795,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.59897363185883</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1394" t="n">
         <v>30509</v>
@@ -40853,7 +40853,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.62408828735352</v>
+        <v>1.62408840656281</v>
       </c>
       <c r="H1396" t="n">
         <v>12484</v>
@@ -41027,7 +41027,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G1402" t="n">
-        <v>1.54037237167358</v>
+        <v>1.54037249088287</v>
       </c>
       <c r="H1402" t="n">
         <v>8600</v>
@@ -41056,7 +41056,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1403" t="n">
         <v>9459</v>
@@ -41114,7 +41114,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1405" t="n">
         <v>5227</v>
@@ -41201,7 +41201,7 @@
         <v>1.875</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.56967306137085</v>
+        <v>1.56967294216156</v>
       </c>
       <c r="H1408" t="n">
         <v>5807</v>
@@ -41230,7 +41230,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.52781510353088</v>
+        <v>1.52781498432159</v>
       </c>
       <c r="H1409" t="n">
         <v>19356</v>
@@ -41375,7 +41375,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1414" t="n">
         <v>1024</v>
@@ -41433,7 +41433,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1416" t="n">
         <v>5452</v>
@@ -41636,7 +41636,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58223021030426</v>
+        <v>1.58223032951355</v>
       </c>
       <c r="H1423" t="n">
         <v>80</v>
@@ -41810,7 +41810,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.55292975902557</v>
+        <v>1.55292987823486</v>
       </c>
       <c r="H1429" t="n">
         <v>3476</v>
@@ -41984,7 +41984,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.60734510421753</v>
+        <v>1.60734498500824</v>
       </c>
       <c r="H1435" t="n">
         <v>3753</v>
@@ -42042,7 +42042,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.60315918922424</v>
+        <v>1.60315930843353</v>
       </c>
       <c r="H1437" t="n">
         <v>6886</v>
@@ -42187,7 +42187,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.66594612598419</v>
+        <v>1.66594636440277</v>
       </c>
       <c r="H1442" t="n">
         <v>21374</v>
@@ -42216,7 +42216,7 @@
         <v>2</v>
       </c>
       <c r="G1443" t="n">
-        <v>1.67431795597076</v>
+        <v>1.67431783676147</v>
       </c>
       <c r="H1443" t="n">
         <v>15500</v>
@@ -42332,7 +42332,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.74966204166412</v>
+        <v>1.74966216087341</v>
       </c>
       <c r="H1447" t="n">
         <v>9597</v>
@@ -42419,7 +42419,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.76640522480011</v>
+        <v>1.76640510559082</v>
       </c>
       <c r="H1450" t="n">
         <v>11352</v>
@@ -42477,7 +42477,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.41101765632629</v>
+        <v>2.41101789474487</v>
       </c>
       <c r="H1452" t="n">
         <v>538492</v>
@@ -42651,7 +42651,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.21469020843506</v>
+        <v>3.21468997001648</v>
       </c>
       <c r="H1458" t="n">
         <v>296859</v>
@@ -42767,7 +42767,7 @@
         <v>3.25</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.72076630592346</v>
+        <v>2.72076654434204</v>
       </c>
       <c r="H1462" t="n">
         <v>163089</v>
@@ -42796,7 +42796,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.84634041786194</v>
+        <v>2.84634065628052</v>
       </c>
       <c r="H1463" t="n">
         <v>169786</v>
@@ -42825,7 +42825,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.97191429138184</v>
+        <v>2.97191405296326</v>
       </c>
       <c r="H1464" t="n">
         <v>85469</v>
@@ -42883,7 +42883,7 @@
         <v>4</v>
       </c>
       <c r="G1466" t="n">
-        <v>3.34863591194153</v>
+        <v>3.34863567352295</v>
       </c>
       <c r="H1466" t="n">
         <v>448231</v>
@@ -42912,7 +42912,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1467" t="n">
         <v>416520</v>
@@ -42970,7 +42970,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.30677795410156</v>
+        <v>3.30677771568298</v>
       </c>
       <c r="H1469" t="n">
         <v>331715</v>
@@ -42999,7 +42999,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.33189225196838</v>
+        <v>3.33189272880554</v>
       </c>
       <c r="H1470" t="n">
         <v>150632</v>
@@ -43028,7 +43028,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.2649199962616</v>
+        <v>3.26491975784302</v>
       </c>
       <c r="H1471" t="n">
         <v>88712</v>
@@ -43086,7 +43086,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1473" t="n">
         <v>44985</v>
@@ -43115,7 +43115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.16446042060852</v>
+        <v>3.1644606590271</v>
       </c>
       <c r="H1474" t="n">
         <v>31963</v>
@@ -43144,7 +43144,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.30677795410156</v>
+        <v>3.30677771568298</v>
       </c>
       <c r="H1475" t="n">
         <v>139109</v>
@@ -43173,7 +43173,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.33189225196838</v>
+        <v>3.33189272880554</v>
       </c>
       <c r="H1476" t="n">
         <v>93362</v>
@@ -43202,7 +43202,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.2649199962616</v>
+        <v>3.26491975784302</v>
       </c>
       <c r="H1477" t="n">
         <v>101648</v>
@@ -43231,7 +43231,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.20631837844849</v>
+        <v>3.20631861686707</v>
       </c>
       <c r="H1478" t="n">
         <v>47143</v>
@@ -43260,7 +43260,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1479" t="n">
         <v>32517</v>
@@ -43289,7 +43289,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1480" t="n">
-        <v>3.08074474334717</v>
+        <v>3.08074498176575</v>
       </c>
       <c r="H1480" t="n">
         <v>121881</v>
@@ -43318,7 +43318,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.11423134803772</v>
+        <v>3.11423110961914</v>
       </c>
       <c r="H1481" t="n">
         <v>34370</v>
@@ -43347,7 +43347,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.05563020706177</v>
+        <v>3.05562996864319</v>
       </c>
       <c r="H1482" t="n">
         <v>24371</v>
@@ -43405,7 +43405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G1484" t="n">
-        <v>3.08074474334717</v>
+        <v>3.08074498176575</v>
       </c>
       <c r="H1484" t="n">
         <v>11897</v>
@@ -43463,7 +43463,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1486" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1486" t="n">
         <v>16788</v>
@@ -43579,7 +43579,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1490" t="n">
         <v>34442</v>
@@ -43608,7 +43608,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.05563020706177</v>
+        <v>3.05562996864319</v>
       </c>
       <c r="H1491" t="n">
         <v>21800</v>
@@ -43695,7 +43695,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1494" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1494" t="n">
         <v>18297</v>
@@ -43724,7 +43724,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1495" t="n">
         <v>21670</v>
@@ -43753,7 +43753,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.8881983757019</v>
+        <v>2.88819861412048</v>
       </c>
       <c r="H1496" t="n">
         <v>20557</v>
@@ -43782,7 +43782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1497" t="n">
         <v>25116</v>
@@ -43811,7 +43811,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.8881983757019</v>
+        <v>2.88819861412048</v>
       </c>
       <c r="H1498" t="n">
         <v>30724</v>
@@ -43898,7 +43898,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.73750972747803</v>
+        <v>2.73750948905945</v>
       </c>
       <c r="H1501" t="n">
         <v>11033</v>
@@ -44101,7 +44101,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1508" t="n">
         <v>20064</v>
@@ -44159,7 +44159,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1510" t="n">
         <v>10718</v>
@@ -44188,7 +44188,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1511" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1511" t="n">
         <v>4045</v>
@@ -44217,7 +44217,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1512" t="n">
         <v>5516</v>
@@ -44246,7 +44246,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.8881983757019</v>
+        <v>2.88819861412048</v>
       </c>
       <c r="H1513" t="n">
         <v>12031</v>
@@ -44304,7 +44304,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.8881983757019</v>
+        <v>2.88819861412048</v>
       </c>
       <c r="H1515" t="n">
         <v>6455</v>
@@ -44391,7 +44391,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G1518" t="n">
-        <v>2.82959747314453</v>
+        <v>2.82959723472595</v>
       </c>
       <c r="H1518" t="n">
         <v>8048</v>
@@ -44478,7 +44478,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1521" t="n">
         <v>168387</v>
@@ -44536,7 +44536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.84634041786194</v>
+        <v>2.84634065628052</v>
       </c>
       <c r="H1523" t="n">
         <v>24638</v>
@@ -44565,7 +44565,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1524" t="n">
         <v>14377</v>
@@ -44623,7 +44623,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.81285405158997</v>
+        <v>2.81285381317139</v>
       </c>
       <c r="H1526" t="n">
         <v>8245</v>
@@ -44681,7 +44681,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.87982678413391</v>
+        <v>2.87982654571533</v>
       </c>
       <c r="H1528" t="n">
         <v>34392</v>
@@ -44710,7 +44710,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.87982678413391</v>
+        <v>2.87982654571533</v>
       </c>
       <c r="H1529" t="n">
         <v>28915</v>
@@ -44768,7 +44768,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1531" t="n">
         <v>78995</v>
@@ -44826,7 +44826,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.78773903846741</v>
+        <v>2.78773927688599</v>
       </c>
       <c r="H1533" t="n">
         <v>22330</v>
@@ -45029,7 +45029,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G1540" t="n">
-        <v>2.66216564178467</v>
+        <v>2.66216540336609</v>
       </c>
       <c r="H1540" t="n">
         <v>10946</v>
@@ -45058,7 +45058,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.62030744552612</v>
+        <v>2.62030720710754</v>
       </c>
       <c r="H1541" t="n">
         <v>14445</v>
@@ -45087,7 +45087,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1542" t="n">
-        <v>2.44450426101685</v>
+        <v>2.44450402259827</v>
       </c>
       <c r="H1542" t="n">
         <v>50287</v>
@@ -45116,7 +45116,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.57844948768616</v>
+        <v>2.57844924926758</v>
       </c>
       <c r="H1543" t="n">
         <v>31864</v>
@@ -45232,7 +45232,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.53659152984619</v>
+        <v>2.53659129142761</v>
       </c>
       <c r="H1547" t="n">
         <v>20002</v>
@@ -45319,7 +45319,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.57844948768616</v>
+        <v>2.57844924926758</v>
       </c>
       <c r="H1550" t="n">
         <v>2875</v>
@@ -45377,7 +45377,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.57007765769958</v>
+        <v>2.57007789611816</v>
       </c>
       <c r="H1552" t="n">
         <v>6057</v>
@@ -45464,7 +45464,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.5282199382782</v>
+        <v>2.52821969985962</v>
       </c>
       <c r="H1555" t="n">
         <v>3108</v>
@@ -45493,7 +45493,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G1556" t="n">
-        <v>2.44450426101685</v>
+        <v>2.44450402259827</v>
       </c>
       <c r="H1556" t="n">
         <v>2524</v>
@@ -45580,7 +45580,7 @@
         <v>3.25</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.72076630592346</v>
+        <v>2.72076654434204</v>
       </c>
       <c r="H1559" t="n">
         <v>109589</v>
@@ -45638,7 +45638,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.84634041786194</v>
+        <v>2.84634065628052</v>
       </c>
       <c r="H1561" t="n">
         <v>65014</v>
@@ -45754,7 +45754,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.52065753936768</v>
+        <v>4.52065849304199</v>
       </c>
       <c r="H1565" t="n">
         <v>526424</v>
@@ -45783,7 +45783,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.95139002799988</v>
+        <v>3.95139026641846</v>
       </c>
       <c r="H1566" t="n">
         <v>546808</v>
@@ -45812,7 +45812,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1567" t="n">
-        <v>4.82203531265259</v>
+        <v>4.82203578948975</v>
       </c>
       <c r="H1567" t="n">
         <v>1195642</v>
@@ -45870,7 +45870,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.52065753936768</v>
+        <v>4.52065849304199</v>
       </c>
       <c r="H1569" t="n">
         <v>627344</v>
@@ -45928,7 +45928,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.30677795410156</v>
+        <v>3.30677771568298</v>
       </c>
       <c r="H1571" t="n">
         <v>877685</v>
@@ -45957,7 +45957,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>3.94301819801331</v>
+        <v>3.94301843643188</v>
       </c>
       <c r="H1572" t="n">
         <v>891209</v>
@@ -46015,7 +46015,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.49095273017883</v>
+        <v>3.49095296859741</v>
       </c>
       <c r="H1574" t="n">
         <v>561178</v>
@@ -46044,7 +46044,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.61652660369873</v>
+        <v>3.61652684211731</v>
       </c>
       <c r="H1575" t="n">
         <v>562506</v>
@@ -46102,7 +46102,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.19794726371765</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1577" t="n">
         <v>465196</v>
@@ -46160,7 +46160,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1579" t="n">
         <v>675453</v>
@@ -46218,7 +46218,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1581" t="n">
         <v>200040</v>
@@ -46276,7 +46276,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.81285405158997</v>
+        <v>2.81285381317139</v>
       </c>
       <c r="H1583" t="n">
         <v>140429</v>
@@ -46392,7 +46392,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1587" t="n">
         <v>115647</v>
@@ -46421,7 +46421,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1588" t="n">
-        <v>2.91331315040588</v>
+        <v>2.9133129119873</v>
       </c>
       <c r="H1588" t="n">
         <v>163154</v>
@@ -46479,7 +46479,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.24817657470703</v>
+        <v>3.24817681312561</v>
       </c>
       <c r="H1590" t="n">
         <v>684923</v>
@@ -46508,7 +46508,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.30677795410156</v>
+        <v>3.30677771568298</v>
       </c>
       <c r="H1591" t="n">
         <v>631090</v>
@@ -46537,7 +46537,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.40723705291748</v>
+        <v>3.40723729133606</v>
       </c>
       <c r="H1592" t="n">
         <v>255356</v>
@@ -46566,7 +46566,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.2649199962616</v>
+        <v>3.26491975784302</v>
       </c>
       <c r="H1593" t="n">
         <v>200134</v>
@@ -46624,7 +46624,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.2649199962616</v>
+        <v>3.26491975784302</v>
       </c>
       <c r="H1595" t="n">
         <v>121872</v>
@@ -46711,7 +46711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.27329158782959</v>
+        <v>3.27329134941101</v>
       </c>
       <c r="H1598" t="n">
         <v>72989</v>
@@ -46740,7 +46740,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.2649199962616</v>
+        <v>3.26491975784302</v>
       </c>
       <c r="H1599" t="n">
         <v>73475</v>
@@ -46798,7 +46798,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.11423134803772</v>
+        <v>3.11423110961914</v>
       </c>
       <c r="H1601" t="n">
         <v>70662</v>
@@ -46885,7 +46885,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1604" t="n">
         <v>98829</v>
@@ -46972,7 +46972,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.20631837844849</v>
+        <v>3.20631861686707</v>
       </c>
       <c r="H1607" t="n">
         <v>519633</v>
@@ -47001,7 +47001,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.32352089881897</v>
+        <v>3.32352113723755</v>
       </c>
       <c r="H1608" t="n">
         <v>573253</v>
@@ -47030,7 +47030,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.33189225196838</v>
+        <v>3.33189272880554</v>
       </c>
       <c r="H1609" t="n">
         <v>186704</v>
@@ -47117,7 +47117,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.22306180000305</v>
+        <v>3.22306203842163</v>
       </c>
       <c r="H1612" t="n">
         <v>80841</v>
@@ -47175,7 +47175,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.05563020706177</v>
+        <v>3.05562996864319</v>
       </c>
       <c r="H1614" t="n">
         <v>154159</v>
@@ -47233,7 +47233,7 @@
         <v>3.50999999046326</v>
       </c>
       <c r="G1616" t="n">
-        <v>2.93842768669128</v>
+        <v>2.93842792510986</v>
       </c>
       <c r="H1616" t="n">
         <v>60086</v>
@@ -47349,7 +47349,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.10585951805115</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1620" t="n">
         <v>156987</v>
@@ -47407,7 +47407,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.10585951805115</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1622" t="n">
         <v>36333</v>
@@ -47436,7 +47436,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.11423134803772</v>
+        <v>3.11423110961914</v>
       </c>
       <c r="H1623" t="n">
         <v>30281</v>
@@ -47494,7 +47494,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.03051519393921</v>
+        <v>3.03051543235779</v>
       </c>
       <c r="H1625" t="n">
         <v>28510</v>
@@ -47523,7 +47523,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1626" t="n">
         <v>57019</v>
@@ -47610,7 +47610,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1629" t="n">
         <v>96173</v>
@@ -47639,7 +47639,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1630" t="n">
         <v>52093</v>
@@ -47726,7 +47726,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1633" t="n">
         <v>86464</v>
@@ -47784,7 +47784,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.87982678413391</v>
+        <v>2.87982654571533</v>
       </c>
       <c r="H1635" t="n">
         <v>29252</v>
@@ -47813,7 +47813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.84634041786194</v>
+        <v>2.84634065628052</v>
       </c>
       <c r="H1636" t="n">
         <v>53802</v>
@@ -47900,7 +47900,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.57007765769958</v>
+        <v>2.57007789611816</v>
       </c>
       <c r="H1639" t="n">
         <v>87542</v>
@@ -47929,7 +47929,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.43613266944885</v>
+        <v>2.43613219261169</v>
       </c>
       <c r="H1640" t="n">
         <v>96756</v>
@@ -47958,7 +47958,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.54496312141418</v>
+        <v>2.54496335983276</v>
       </c>
       <c r="H1641" t="n">
         <v>35144</v>
@@ -48016,7 +48016,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.24817657470703</v>
+        <v>3.24817681312561</v>
       </c>
       <c r="H1643" t="n">
         <v>391001</v>
@@ -48045,7 +48045,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.96354269981384</v>
+        <v>2.96354246139526</v>
       </c>
       <c r="H1644" t="n">
         <v>451229</v>
@@ -48074,7 +48074,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.10585951805115</v>
+        <v>3.10585975646973</v>
       </c>
       <c r="H1645" t="n">
         <v>368081</v>
@@ -48132,7 +48132,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1647" t="n">
         <v>72225</v>
@@ -48277,7 +48277,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.94679927825928</v>
+        <v>2.94679951667786</v>
       </c>
       <c r="H1652" t="n">
         <v>45483</v>
@@ -48306,7 +48306,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1653" t="n">
         <v>83540</v>
@@ -48335,7 +48335,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.87982678413391</v>
+        <v>2.87982654571533</v>
       </c>
       <c r="H1654" t="n">
         <v>52814</v>
@@ -48364,7 +48364,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1655" t="n">
-        <v>2.91331315040588</v>
+        <v>2.9133129119873</v>
       </c>
       <c r="H1655" t="n">
         <v>63210</v>
@@ -48393,7 +48393,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.78773903846741</v>
+        <v>2.78773927688599</v>
       </c>
       <c r="H1656" t="n">
         <v>47624</v>
@@ -48596,7 +48596,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.81285405158997</v>
+        <v>2.81285381317139</v>
       </c>
       <c r="H1663" t="n">
         <v>111061</v>
@@ -48625,7 +48625,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.87982678413391</v>
+        <v>2.87982654571533</v>
       </c>
       <c r="H1664" t="n">
         <v>40532</v>
@@ -48654,7 +48654,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.87982678413391</v>
+        <v>2.87982654571533</v>
       </c>
       <c r="H1665" t="n">
         <v>58822</v>
@@ -50046,7 +50046,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G1713" t="n">
-        <v>1.82643890380859</v>
+        <v>1.8264387845993</v>
       </c>
       <c r="H1713" t="n">
         <v>199506</v>
@@ -50104,7 +50104,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.86041915416718</v>
+        <v>1.86041903495789</v>
       </c>
       <c r="H1715" t="n">
         <v>100685</v>
@@ -50394,7 +50394,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.86041915416718</v>
+        <v>1.86041903495789</v>
       </c>
       <c r="H1725" t="n">
         <v>60387</v>
@@ -50452,7 +50452,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.87740910053253</v>
+        <v>1.87740921974182</v>
       </c>
       <c r="H1727" t="n">
         <v>34676</v>
@@ -52656,7 +52656,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.08129072189331</v>
+        <v>2.08129048347473</v>
       </c>
       <c r="H1803" t="n">
         <v>42223</v>
@@ -53381,7 +53381,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.08129072189331</v>
+        <v>2.08129048347473</v>
       </c>
       <c r="H1828" t="n">
         <v>40153</v>
@@ -53932,7 +53932,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.08129072189331</v>
+        <v>2.08129048347473</v>
       </c>
       <c r="H1847" t="n">
         <v>4495</v>
@@ -54541,7 +54541,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.02607250213623</v>
+        <v>2.02607274055481</v>
       </c>
       <c r="H1868" t="n">
         <v>5157</v>
@@ -54715,7 +54715,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.11102318763733</v>
+        <v>2.11102342605591</v>
       </c>
       <c r="H1874" t="n">
         <v>29190</v>
@@ -54831,7 +54831,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.13650894165039</v>
+        <v>2.13650870323181</v>
       </c>
       <c r="H1878" t="n">
         <v>33905</v>
@@ -54860,7 +54860,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.15349864959717</v>
+        <v>2.15349888801575</v>
       </c>
       <c r="H1879" t="n">
         <v>23605</v>
@@ -54976,7 +54976,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.11102318763733</v>
+        <v>2.11102342605591</v>
       </c>
       <c r="H1883" t="n">
         <v>5640</v>
@@ -55353,7 +55353,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.15349864959717</v>
+        <v>2.15349888801575</v>
       </c>
       <c r="H1896" t="n">
         <v>21172</v>
@@ -55730,7 +55730,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.17898416519165</v>
+        <v>2.17898392677307</v>
       </c>
       <c r="H1909" t="n">
         <v>6067</v>
@@ -55933,7 +55933,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.17898416519165</v>
+        <v>2.17898392677307</v>
       </c>
       <c r="H1916" t="n">
         <v>6058</v>
@@ -56078,7 +56078,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.13650894165039</v>
+        <v>2.13650870323181</v>
       </c>
       <c r="H1921" t="n">
         <v>3405</v>
@@ -56281,7 +56281,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.22145962715149</v>
+        <v>2.22145938873291</v>
       </c>
       <c r="H1928" t="n">
         <v>46632</v>
@@ -56832,7 +56832,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.23804235458374</v>
+        <v>2.23804259300232</v>
       </c>
       <c r="H1947" t="n">
         <v>8716</v>
@@ -57209,7 +57209,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.30730509757996</v>
+        <v>2.30730485916138</v>
       </c>
       <c r="H1960" t="n">
         <v>60245</v>
@@ -57296,7 +57296,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.23804235458374</v>
+        <v>2.23804259300232</v>
       </c>
       <c r="H1963" t="n">
         <v>53763</v>
@@ -57412,7 +57412,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.22072720527649</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H1967" t="n">
         <v>48189</v>
@@ -57470,7 +57470,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.23804235458374</v>
+        <v>2.23804259300232</v>
       </c>
       <c r="H1969" t="n">
         <v>29068</v>
@@ -57557,7 +57557,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.22072720527649</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H1972" t="n">
         <v>71046</v>
@@ -57644,7 +57644,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.15146422386169</v>
+        <v>2.15146446228027</v>
       </c>
       <c r="H1975" t="n">
         <v>30736</v>
@@ -57731,7 +57731,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.12116241455078</v>
+        <v>2.1211621761322</v>
       </c>
       <c r="H1978" t="n">
         <v>26735</v>
@@ -57789,7 +57789,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.15146422386169</v>
+        <v>2.15146446228027</v>
       </c>
       <c r="H1980" t="n">
         <v>150533</v>
@@ -57818,7 +57818,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.13414907455444</v>
+        <v>2.13414883613586</v>
       </c>
       <c r="H1981" t="n">
         <v>93229</v>
@@ -57847,7 +57847,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H1982" t="n">
         <v>72218</v>
@@ -57905,7 +57905,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.17743825912476</v>
+        <v>2.17743802070618</v>
       </c>
       <c r="H1984" t="n">
         <v>98672</v>
@@ -58021,7 +58021,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.12116241455078</v>
+        <v>2.1211621761322</v>
       </c>
       <c r="H1988" t="n">
         <v>50886</v>
@@ -58079,7 +58079,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1990" t="n">
-        <v>2.12116241455078</v>
+        <v>2.1211621761322</v>
       </c>
       <c r="H1990" t="n">
         <v>9960</v>
@@ -58427,7 +58427,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2002" t="n">
         <v>7643</v>
@@ -58485,7 +58485,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2004" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2004" t="n">
         <v>19580</v>
@@ -58630,7 +58630,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2009" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2009" t="n">
         <v>16304</v>
@@ -58862,7 +58862,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G2017" t="n">
-        <v>2.28133130073547</v>
+        <v>2.28133153915405</v>
       </c>
       <c r="H2017" t="n">
         <v>47535</v>
@@ -59268,7 +59268,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.26401615142822</v>
+        <v>2.26401591300964</v>
       </c>
       <c r="H2031" t="n">
         <v>61751</v>
@@ -59500,7 +59500,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2039" t="n">
-        <v>2.22072720527649</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H2039" t="n">
         <v>21358</v>
@@ -59529,7 +59529,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2040" t="n">
-        <v>2.22072720527649</v>
+        <v>2.22072696685791</v>
       </c>
       <c r="H2040" t="n">
         <v>21786</v>
@@ -59616,7 +59616,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.13414907455444</v>
+        <v>2.13414883613586</v>
       </c>
       <c r="H2043" t="n">
         <v>35433</v>
@@ -59703,7 +59703,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G2046" t="n">
-        <v>2.17743825912476</v>
+        <v>2.17743802070618</v>
       </c>
       <c r="H2046" t="n">
         <v>38900</v>
@@ -59877,7 +59877,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2052" t="n">
         <v>14287</v>
@@ -59935,7 +59935,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2054" t="n">
         <v>38639</v>
@@ -59964,7 +59964,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2055" t="n">
-        <v>2.12116241455078</v>
+        <v>2.1211621761322</v>
       </c>
       <c r="H2055" t="n">
         <v>52903</v>
@@ -60399,7 +60399,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2070" t="n">
-        <v>2.12116241455078</v>
+        <v>2.1211621761322</v>
       </c>
       <c r="H2070" t="n">
         <v>52929</v>
@@ -60486,7 +60486,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.06488633155823</v>
+        <v>2.06488656997681</v>
       </c>
       <c r="H2073" t="n">
         <v>12660</v>
@@ -60573,7 +60573,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G2076" t="n">
-        <v>2.02159714698792</v>
+        <v>2.02159738540649</v>
       </c>
       <c r="H2076" t="n">
         <v>29653</v>
@@ -60602,7 +60602,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G2077" t="n">
-        <v>2.02159714698792</v>
+        <v>2.02159738540649</v>
       </c>
       <c r="H2077" t="n">
         <v>17344</v>
@@ -60805,7 +60805,7 @@
         <v>2.33500003814697</v>
       </c>
       <c r="G2084" t="n">
-        <v>2.02159714698792</v>
+        <v>2.02159738540649</v>
       </c>
       <c r="H2084" t="n">
         <v>30803</v>
@@ -60979,7 +60979,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2090" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2090" t="n">
         <v>18648</v>
@@ -61327,7 +61327,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2102" t="n">
-        <v>2.12116241455078</v>
+        <v>2.1211621761322</v>
       </c>
       <c r="H2102" t="n">
         <v>66523</v>
@@ -62893,7 +62893,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2156" t="n">
-        <v>2.12116241455078</v>
+        <v>2.1211621761322</v>
       </c>
       <c r="H2156" t="n">
         <v>60813</v>
@@ -80096,6 +80096,35 @@
         <v>511777</v>
       </c>
       <c r="I2749" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2750">
+      <c r="A2750" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2750" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C2750" t="n">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="D2750" t="n">
+        <v>7.51000022888184</v>
+      </c>
+      <c r="E2750" t="n">
+        <v>7.30000019073486</v>
+      </c>
+      <c r="F2750" t="n">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="G2750" t="n">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="H2750" t="n">
+        <v>160980</v>
+      </c>
+      <c r="I2750" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G3" t="n">
-        <v>2.93566417694092</v>
+        <v>2.93566393852234</v>
       </c>
       <c r="H3" t="n">
         <v>1711</v>
@@ -485,7 +485,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94375109672546</v>
+        <v>2.94375133514404</v>
       </c>
       <c r="H4" t="n">
         <v>2430</v>
@@ -514,7 +514,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G5" t="n">
-        <v>2.91948914527893</v>
+        <v>2.91948938369751</v>
       </c>
       <c r="H5" t="n">
         <v>10591</v>
@@ -543,7 +543,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G6" t="n">
-        <v>2.91948914527893</v>
+        <v>2.91948938369751</v>
       </c>
       <c r="H6" t="n">
         <v>3694</v>
@@ -572,7 +572,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G7" t="n">
-        <v>2.91948914527893</v>
+        <v>2.91948938369751</v>
       </c>
       <c r="H7" t="n">
         <v>588</v>
@@ -601,7 +601,7 @@
         <v>3.60999989509583</v>
       </c>
       <c r="G8" t="n">
-        <v>2.91948914527893</v>
+        <v>2.91948938369751</v>
       </c>
       <c r="H8" t="n">
         <v>928</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74965786933899</v>
+        <v>2.74965739250183</v>
       </c>
       <c r="H12" t="n">
         <v>9032</v>
@@ -775,7 +775,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G14" t="n">
-        <v>2.52321529388428</v>
+        <v>2.5232150554657</v>
       </c>
       <c r="H14" t="n">
         <v>5650</v>
@@ -862,7 +862,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G17" t="n">
-        <v>2.57173848152161</v>
+        <v>2.57173871994019</v>
       </c>
       <c r="H17" t="n">
         <v>10526</v>
@@ -920,7 +920,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G19" t="n">
-        <v>2.55556440353394</v>
+        <v>2.55556416511536</v>
       </c>
       <c r="H19" t="n">
         <v>1500</v>
@@ -949,7 +949,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G20" t="n">
-        <v>2.55556440353394</v>
+        <v>2.55556416511536</v>
       </c>
       <c r="H20" t="n">
         <v>5266</v>
@@ -978,7 +978,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H21" t="n">
         <v>2307</v>
@@ -1007,7 +1007,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G22" t="n">
-        <v>2.49895358085632</v>
+        <v>2.49895334243774</v>
       </c>
       <c r="H22" t="n">
         <v>6946</v>
@@ -1036,7 +1036,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G23" t="n">
-        <v>2.57173848152161</v>
+        <v>2.57173871994019</v>
       </c>
       <c r="H23" t="n">
         <v>7787</v>
@@ -1094,7 +1094,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.49895358085632</v>
+        <v>2.49895334243774</v>
       </c>
       <c r="H25" t="n">
         <v>10756</v>
@@ -1181,7 +1181,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>2.15929007530212</v>
+        <v>2.1592903137207</v>
       </c>
       <c r="H28" t="n">
         <v>5931</v>
@@ -1268,7 +1268,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G31" t="n">
-        <v>2.24339723587036</v>
+        <v>2.24339699745178</v>
       </c>
       <c r="H31" t="n">
         <v>4200</v>
@@ -1355,7 +1355,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G34" t="n">
-        <v>2.45042991638184</v>
+        <v>2.45043015480042</v>
       </c>
       <c r="H34" t="n">
         <v>1550</v>
@@ -1413,7 +1413,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G36" t="n">
-        <v>2.46498703956604</v>
+        <v>2.46498727798462</v>
       </c>
       <c r="H36" t="n">
         <v>565</v>
@@ -1442,7 +1442,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G37" t="n">
-        <v>2.50704050064087</v>
+        <v>2.50704073905945</v>
       </c>
       <c r="H37" t="n">
         <v>1284</v>
@@ -1471,7 +1471,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G38" t="n">
-        <v>2.57659101486206</v>
+        <v>2.57659077644348</v>
       </c>
       <c r="H38" t="n">
         <v>626</v>
@@ -1500,7 +1500,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49895358085632</v>
+        <v>2.49895334243774</v>
       </c>
       <c r="H39" t="n">
         <v>10945</v>
@@ -1674,7 +1674,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G45" t="n">
-        <v>2.50542306900024</v>
+        <v>2.5054235458374</v>
       </c>
       <c r="H45" t="n">
         <v>1234</v>
@@ -1703,7 +1703,7 @@
         <v>3.16799998283386</v>
       </c>
       <c r="G46" t="n">
-        <v>2.56203413009644</v>
+        <v>2.56203389167786</v>
       </c>
       <c r="H46" t="n">
         <v>11008</v>
@@ -1732,7 +1732,7 @@
         <v>3.04800009727478</v>
       </c>
       <c r="G47" t="n">
-        <v>2.46498703956604</v>
+        <v>2.46498727798462</v>
       </c>
       <c r="H47" t="n">
         <v>16528</v>
@@ -1761,7 +1761,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52159810066223</v>
+        <v>2.52159762382507</v>
       </c>
       <c r="H48" t="n">
         <v>3370</v>
@@ -1790,7 +1790,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G49" t="n">
-        <v>2.57497358322144</v>
+        <v>2.57497382164001</v>
       </c>
       <c r="H49" t="n">
         <v>1856</v>
@@ -1877,7 +1877,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G52" t="n">
-        <v>2.66069793701172</v>
+        <v>2.6606981754303</v>
       </c>
       <c r="H52" t="n">
         <v>1950</v>
@@ -1964,7 +1964,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54747700691223</v>
+        <v>2.54747724533081</v>
       </c>
       <c r="H55" t="n">
         <v>2341</v>
@@ -1993,7 +1993,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>2.54747700691223</v>
+        <v>2.54747724533081</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>2.54747700691223</v>
+        <v>2.54747724533081</v>
       </c>
       <c r="H59" t="n">
         <v>1600</v>
@@ -2109,7 +2109,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G60" t="n">
-        <v>2.50704050064087</v>
+        <v>2.50704073905945</v>
       </c>
       <c r="H60" t="n">
         <v>1650</v>
@@ -2138,7 +2138,7 @@
         <v>3.15799999237061</v>
       </c>
       <c r="G61" t="n">
-        <v>2.55394649505615</v>
+        <v>2.55394673347473</v>
       </c>
       <c r="H61" t="n">
         <v>560</v>
@@ -2167,7 +2167,7 @@
         <v>3.19600009918213</v>
       </c>
       <c r="G62" t="n">
-        <v>2.58467793464661</v>
+        <v>2.58467817306519</v>
       </c>
       <c r="H62" t="n">
         <v>1431</v>
@@ -2196,7 +2196,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G63" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H63" t="n">
         <v>101</v>
@@ -2225,7 +2225,7 @@
         <v>3.18799996376038</v>
       </c>
       <c r="G64" t="n">
-        <v>2.57820844650269</v>
+        <v>2.57820820808411</v>
       </c>
       <c r="H64" t="n">
         <v>873</v>
@@ -2254,7 +2254,7 @@
         <v>3.18400001525879</v>
       </c>
       <c r="G65" t="n">
-        <v>2.57497358322144</v>
+        <v>2.57497382164001</v>
       </c>
       <c r="H65" t="n">
         <v>2648</v>
@@ -2399,7 +2399,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G70" t="n">
-        <v>2.49895358085632</v>
+        <v>2.49895334243774</v>
       </c>
       <c r="H70" t="n">
         <v>4213</v>
@@ -2428,7 +2428,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G71" t="n">
-        <v>2.51512813568115</v>
+        <v>2.51512789726257</v>
       </c>
       <c r="H71" t="n">
         <v>2334</v>
@@ -2457,7 +2457,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G72" t="n">
-        <v>2.49895358085632</v>
+        <v>2.49895334243774</v>
       </c>
       <c r="H72" t="n">
         <v>9046</v>
@@ -2486,7 +2486,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G73" t="n">
-        <v>2.55556440353394</v>
+        <v>2.55556416511536</v>
       </c>
       <c r="H73" t="n">
         <v>793</v>
@@ -2573,7 +2573,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>2.59600019454956</v>
+        <v>2.59600067138672</v>
       </c>
       <c r="H76" t="n">
         <v>50</v>
@@ -2660,7 +2660,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G79" t="n">
-        <v>2.54100704193115</v>
+        <v>2.54100728034973</v>
       </c>
       <c r="H79" t="n">
         <v>5900</v>
@@ -2689,7 +2689,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G80" t="n">
-        <v>2.54100704193115</v>
+        <v>2.54100728034973</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H81" t="n">
         <v>1030</v>
@@ -2747,7 +2747,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.56365156173706</v>
+        <v>2.56365132331848</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2834,7 +2834,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G85" t="n">
-        <v>2.54262471199036</v>
+        <v>2.54262447357178</v>
       </c>
       <c r="H85" t="n">
         <v>12001</v>
@@ -2979,7 +2979,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G90" t="n">
-        <v>2.44072532653809</v>
+        <v>2.44072556495667</v>
       </c>
       <c r="H90" t="n">
         <v>1954</v>
@@ -3095,7 +3095,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G94" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H94" t="n">
         <v>1915</v>
@@ -3124,7 +3124,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G95" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G96" t="n">
-        <v>2.45690011978149</v>
+        <v>2.45689988136292</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.40837645530701</v>
+        <v>2.40837669372559</v>
       </c>
       <c r="H97" t="n">
         <v>12462</v>
@@ -3211,7 +3211,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G98" t="n">
-        <v>2.38411474227905</v>
+        <v>2.38411498069763</v>
       </c>
       <c r="H98" t="n">
         <v>4757</v>
@@ -3269,7 +3269,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>2.45622420310974</v>
+        <v>2.45622444152832</v>
       </c>
       <c r="H100" t="n">
         <v>711</v>
@@ -3298,7 +3298,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>2.45622420310974</v>
+        <v>2.45622444152832</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G102" t="n">
-        <v>2.45622420310974</v>
+        <v>2.45622444152832</v>
       </c>
       <c r="H102" t="n">
         <v>5002</v>
@@ -3501,7 +3501,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G108" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H108" t="n">
         <v>1200</v>
@@ -3588,7 +3588,7 @@
         <v>2.75</v>
       </c>
       <c r="G111" t="n">
-        <v>2.30218720436096</v>
+        <v>2.30218696594238</v>
       </c>
       <c r="H111" t="n">
         <v>3120</v>
@@ -3617,7 +3617,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G112" t="n">
-        <v>2.22684264183044</v>
+        <v>2.22684288024902</v>
       </c>
       <c r="H112" t="n">
         <v>8946</v>
@@ -3704,7 +3704,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>2.12638378143311</v>
+        <v>2.12638354301453</v>
       </c>
       <c r="H115" t="n">
         <v>9869</v>
@@ -3762,7 +3762,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G117" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H117" t="n">
         <v>1936</v>
@@ -3791,7 +3791,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G118" t="n">
-        <v>2.17493915557861</v>
+        <v>2.17493891716003</v>
       </c>
       <c r="H118" t="n">
         <v>1145</v>
@@ -3820,7 +3820,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G119" t="n">
-        <v>2.16656732559204</v>
+        <v>2.16656756401062</v>
       </c>
       <c r="H119" t="n">
         <v>601</v>
@@ -3849,7 +3849,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G120" t="n">
-        <v>2.26702642440796</v>
+        <v>2.26702666282654</v>
       </c>
       <c r="H120" t="n">
         <v>3339</v>
@@ -3936,7 +3936,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H123" t="n">
         <v>5450</v>
@@ -4023,7 +4023,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G126" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H126" t="n">
         <v>850</v>
@@ -4052,7 +4052,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G127" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>2.54800009727478</v>
       </c>
       <c r="G130" t="n">
-        <v>2.13308119773865</v>
+        <v>2.13308095932007</v>
       </c>
       <c r="H130" t="n">
         <v>7449</v>
@@ -4313,7 +4313,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G136" t="n">
-        <v>2.13140678405762</v>
+        <v>2.13140630722046</v>
       </c>
       <c r="H136" t="n">
         <v>2546</v>
@@ -4342,7 +4342,7 @@
         <v>2.55399990081787</v>
       </c>
       <c r="G137" t="n">
-        <v>2.13810396194458</v>
+        <v>2.138103723526</v>
       </c>
       <c r="H137" t="n">
         <v>2397</v>
@@ -4458,7 +4458,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G141" t="n">
-        <v>2.18498468399048</v>
+        <v>2.1849844455719</v>
       </c>
       <c r="H141" t="n">
         <v>1900</v>
@@ -4487,7 +4487,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G142" t="n">
-        <v>2.18498468399048</v>
+        <v>2.1849844455719</v>
       </c>
       <c r="H142" t="n">
         <v>500</v>
@@ -4516,7 +4516,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G143" t="n">
-        <v>2.18498468399048</v>
+        <v>2.1849844455719</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G144" t="n">
-        <v>2.18498468399048</v>
+        <v>2.1849844455719</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G145" t="n">
-        <v>2.20675110816956</v>
+        <v>2.20675086975098</v>
       </c>
       <c r="H145" t="n">
         <v>200</v>
@@ -4690,7 +4690,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G150" t="n">
-        <v>2.14814972877502</v>
+        <v>2.1481499671936</v>
       </c>
       <c r="H150" t="n">
         <v>376</v>
@@ -4748,7 +4748,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G151" t="n">
-        <v>2.18331050872803</v>
+        <v>2.18331074714661</v>
       </c>
       <c r="H151" t="n">
         <v>905</v>
@@ -4777,7 +4777,7 @@
         <v>2.60800004005432</v>
       </c>
       <c r="G152" t="n">
-        <v>2.18331050872803</v>
+        <v>2.18331074714661</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G156" t="n">
-        <v>2.26702642440796</v>
+        <v>2.26702666282654</v>
       </c>
       <c r="H156" t="n">
         <v>8194</v>
@@ -4922,7 +4922,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G157" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H157" t="n">
         <v>2500</v>
@@ -5009,7 +5009,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G160" t="n">
-        <v>2.26702642440796</v>
+        <v>2.26702666282654</v>
       </c>
       <c r="H160" t="n">
         <v>326</v>
@@ -5096,7 +5096,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G163" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014570236206</v>
       </c>
       <c r="H163" t="n">
         <v>2000</v>
@@ -5473,7 +5473,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G176" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H176" t="n">
         <v>10046</v>
@@ -5502,7 +5502,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014570236206</v>
       </c>
       <c r="H177" t="n">
         <v>3110</v>
@@ -5531,7 +5531,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>2.23521447181702</v>
+        <v>2.2352147102356</v>
       </c>
       <c r="H178" t="n">
         <v>2610</v>
@@ -5589,7 +5589,7 @@
         <v>2.63599991798401</v>
       </c>
       <c r="G180" t="n">
-        <v>2.20675110816956</v>
+        <v>2.20675086975098</v>
       </c>
       <c r="H180" t="n">
         <v>3361</v>
@@ -5618,7 +5618,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.21177411079407</v>
+        <v>2.21177387237549</v>
       </c>
       <c r="H181" t="n">
         <v>126</v>
@@ -5705,7 +5705,7 @@
         <v>2.60199999809265</v>
       </c>
       <c r="G184" t="n">
-        <v>2.17828750610352</v>
+        <v>2.17828774452209</v>
       </c>
       <c r="H184" t="n">
         <v>500</v>
@@ -5763,7 +5763,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G186" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H186" t="n">
         <v>1200</v>
@@ -5792,7 +5792,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G187" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G188" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>2.59800004959106</v>
       </c>
       <c r="G191" t="n">
-        <v>2.17493915557861</v>
+        <v>2.17493891716003</v>
       </c>
       <c r="H191" t="n">
         <v>2700</v>
@@ -5937,7 +5937,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G192" t="n">
-        <v>2.0995945930481</v>
+        <v>2.09959435462952</v>
       </c>
       <c r="H192" t="n">
         <v>1674</v>
@@ -5966,7 +5966,7 @@
         <v>2.5</v>
       </c>
       <c r="G193" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H193" t="n">
         <v>1790</v>
@@ -6082,7 +6082,7 @@
         <v>2.5</v>
       </c>
       <c r="G197" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H197" t="n">
         <v>4577</v>
@@ -6111,7 +6111,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G198" t="n">
-        <v>2.03764462471008</v>
+        <v>2.03764510154724</v>
       </c>
       <c r="H198" t="n">
         <v>3980</v>
@@ -6198,7 +6198,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G201" t="n">
-        <v>2.0694568157196</v>
+        <v>2.06945705413818</v>
       </c>
       <c r="H201" t="n">
         <v>3744</v>
@@ -6227,7 +6227,7 @@
         <v>2.5</v>
       </c>
       <c r="G202" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H202" t="n">
         <v>5495</v>
@@ -6285,7 +6285,7 @@
         <v>2.5</v>
       </c>
       <c r="G204" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H204" t="n">
         <v>3149</v>
@@ -6343,7 +6343,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G206" t="n">
-        <v>2.03429627418518</v>
+        <v>2.0342960357666</v>
       </c>
       <c r="H206" t="n">
         <v>4559</v>
@@ -6430,7 +6430,7 @@
         <v>2.40199995040894</v>
       </c>
       <c r="G209" t="n">
-        <v>2.01085567474365</v>
+        <v>2.01085591316223</v>
       </c>
       <c r="H209" t="n">
         <v>8377</v>
@@ -6459,7 +6459,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G210" t="n">
-        <v>2.01922726631165</v>
+        <v>2.01922702789307</v>
       </c>
       <c r="H210" t="n">
         <v>2644</v>
@@ -6488,7 +6488,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H211" t="n">
         <v>8288</v>
@@ -6575,7 +6575,7 @@
         <v>2.40799999237061</v>
       </c>
       <c r="G214" t="n">
-        <v>2.01587867736816</v>
+        <v>2.01587891578674</v>
       </c>
       <c r="H214" t="n">
         <v>2100</v>
@@ -6604,7 +6604,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H215" t="n">
         <v>295</v>
@@ -6633,7 +6633,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G216" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H216" t="n">
         <v>1705</v>
@@ -6662,7 +6662,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G217" t="n">
-        <v>1.98908972740173</v>
+        <v>1.98908948898315</v>
       </c>
       <c r="H217" t="n">
         <v>262</v>
@@ -6749,7 +6749,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G220" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H220" t="n">
         <v>6050</v>
@@ -6807,7 +6807,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G222" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H222" t="n">
         <v>2208</v>
@@ -6836,7 +6836,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G223" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G224" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H224" t="n">
         <v>4828</v>
@@ -6894,7 +6894,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G225" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H225" t="n">
         <v>554</v>
@@ -6981,7 +6981,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G228" t="n">
-        <v>1.93216300010681</v>
+        <v>1.93216288089752</v>
       </c>
       <c r="H228" t="n">
         <v>7567</v>
@@ -7039,7 +7039,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G230" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H230" t="n">
         <v>1213</v>
@@ -7126,7 +7126,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G233" t="n">
-        <v>1.94890582561493</v>
+        <v>1.94890606403351</v>
       </c>
       <c r="H233" t="n">
         <v>105</v>
@@ -7155,7 +7155,7 @@
         <v>2.32800006866455</v>
       </c>
       <c r="G234" t="n">
-        <v>1.94890582561493</v>
+        <v>1.94890606403351</v>
       </c>
       <c r="H234" t="n">
         <v>1000</v>
@@ -7184,7 +7184,7 @@
         <v>2.2720000743866</v>
       </c>
       <c r="G235" t="n">
-        <v>1.90202486515045</v>
+        <v>1.90202510356903</v>
       </c>
       <c r="H235" t="n">
         <v>400</v>
@@ -7213,7 +7213,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G236" t="n">
-        <v>1.9405345916748</v>
+        <v>1.94053435325623</v>
       </c>
       <c r="H236" t="n">
         <v>6530</v>
@@ -7242,7 +7242,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G237" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H237" t="n">
         <v>100</v>
@@ -7271,7 +7271,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G238" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H238" t="n">
         <v>100</v>
@@ -7300,7 +7300,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H239" t="n">
         <v>300</v>
@@ -7329,7 +7329,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G240" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H240" t="n">
         <v>9741</v>
@@ -7358,7 +7358,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G241" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H241" t="n">
         <v>5732</v>
@@ -7503,7 +7503,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.06778287887573</v>
+        <v>2.06778240203857</v>
       </c>
       <c r="H246" t="n">
         <v>6984</v>
@@ -7532,7 +7532,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.06778287887573</v>
+        <v>2.06778240203857</v>
       </c>
       <c r="H247" t="n">
         <v>1952</v>
@@ -7793,7 +7793,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G256" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H256" t="n">
         <v>15415</v>
@@ -7851,7 +7851,7 @@
         <v>2.5</v>
       </c>
       <c r="G258" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H258" t="n">
         <v>11294</v>
@@ -7880,7 +7880,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>2.46794438362122</v>
+        <v>2.46794462203979</v>
       </c>
       <c r="H259" t="n">
         <v>27965</v>
@@ -8025,7 +8025,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G264" t="n">
-        <v>2.61193585395813</v>
+        <v>2.61193561553955</v>
       </c>
       <c r="H264" t="n">
         <v>15577</v>
@@ -8054,7 +8054,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G265" t="n">
-        <v>2.58347225189209</v>
+        <v>2.58347249031067</v>
       </c>
       <c r="H265" t="n">
         <v>10919</v>
@@ -8083,7 +8083,7 @@
         <v>3.01799988746643</v>
       </c>
       <c r="G266" t="n">
-        <v>2.52654552459717</v>
+        <v>2.52654576301575</v>
       </c>
       <c r="H266" t="n">
         <v>6706</v>
@@ -8170,7 +8170,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G269" t="n">
-        <v>2.55835771560669</v>
+        <v>2.55835795402527</v>
       </c>
       <c r="H269" t="n">
         <v>5829</v>
@@ -8199,7 +8199,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G270" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H270" t="n">
         <v>15928</v>
@@ -8257,7 +8257,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G272" t="n">
-        <v>2.56505465507507</v>
+        <v>2.56505489349365</v>
       </c>
       <c r="H272" t="n">
         <v>3710</v>
@@ -8286,7 +8286,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G273" t="n">
-        <v>2.53659129142761</v>
+        <v>2.53659152984619</v>
       </c>
       <c r="H273" t="n">
         <v>3204</v>
@@ -8315,7 +8315,7 @@
         <v>3.00200009346008</v>
       </c>
       <c r="G274" t="n">
-        <v>2.51315140724182</v>
+        <v>2.51315116882324</v>
       </c>
       <c r="H274" t="n">
         <v>5505</v>
@@ -8344,7 +8344,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G275" t="n">
-        <v>2.50477933883667</v>
+        <v>2.50477981567383</v>
       </c>
       <c r="H275" t="n">
         <v>11977</v>
@@ -8373,7 +8373,7 @@
         <v>3.10199999809265</v>
       </c>
       <c r="G276" t="n">
-        <v>2.59686684608459</v>
+        <v>2.59686708450317</v>
       </c>
       <c r="H276" t="n">
         <v>75318</v>
@@ -8402,7 +8402,7 @@
         <v>3.08599996566772</v>
       </c>
       <c r="G277" t="n">
-        <v>2.58347225189209</v>
+        <v>2.58347249031067</v>
       </c>
       <c r="H277" t="n">
         <v>10559</v>
@@ -8460,7 +8460,7 @@
         <v>3.03200006484985</v>
       </c>
       <c r="G279" t="n">
-        <v>2.5382661819458</v>
+        <v>2.53826570510864</v>
       </c>
       <c r="H279" t="n">
         <v>1753</v>
@@ -8518,7 +8518,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.63705062866211</v>
+        <v>2.63705086708069</v>
       </c>
       <c r="H281" t="n">
         <v>6600</v>
@@ -8605,7 +8605,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G284" t="n">
-        <v>2.53491735458374</v>
+        <v>2.53491759300232</v>
       </c>
       <c r="H284" t="n">
         <v>1583</v>
@@ -8663,7 +8663,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G286" t="n">
-        <v>2.50310516357422</v>
+        <v>2.5031054019928</v>
       </c>
       <c r="H286" t="n">
         <v>1752</v>
@@ -8692,7 +8692,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G287" t="n">
-        <v>2.50477933883667</v>
+        <v>2.50477981567383</v>
       </c>
       <c r="H287" t="n">
         <v>1050</v>
@@ -8721,7 +8721,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G288" t="n">
-        <v>2.53659129142761</v>
+        <v>2.53659152984619</v>
       </c>
       <c r="H288" t="n">
         <v>7934</v>
@@ -8750,7 +8750,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G289" t="n">
-        <v>2.53491735458374</v>
+        <v>2.53491759300232</v>
       </c>
       <c r="H289" t="n">
         <v>902</v>
@@ -8779,7 +8779,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G290" t="n">
-        <v>2.50477933883667</v>
+        <v>2.50477981567383</v>
       </c>
       <c r="H290" t="n">
         <v>13966</v>
@@ -8837,7 +8837,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>2.50143074989319</v>
+        <v>2.50143051147461</v>
       </c>
       <c r="H292" t="n">
         <v>4202</v>
@@ -8866,7 +8866,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G293" t="n">
-        <v>2.47296714782715</v>
+        <v>2.47296762466431</v>
       </c>
       <c r="H293" t="n">
         <v>1769</v>
@@ -8895,7 +8895,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G294" t="n">
-        <v>2.54328894615173</v>
+        <v>2.54328870773315</v>
       </c>
       <c r="H294" t="n">
         <v>2752</v>
@@ -8924,7 +8924,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53324317932129</v>
+        <v>2.53324270248413</v>
       </c>
       <c r="H295" t="n">
         <v>10626</v>
@@ -8953,7 +8953,7 @@
         <v>3.04200005531311</v>
       </c>
       <c r="G296" t="n">
-        <v>2.54663729667664</v>
+        <v>2.54663753509521</v>
       </c>
       <c r="H296" t="n">
         <v>3490</v>
@@ -8982,7 +8982,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G297" t="n">
-        <v>2.52821969985962</v>
+        <v>2.5282199382782</v>
       </c>
       <c r="H297" t="n">
         <v>3951</v>
@@ -9040,7 +9040,7 @@
         <v>2.99200010299683</v>
       </c>
       <c r="G299" t="n">
-        <v>2.50477933883667</v>
+        <v>2.50477981567383</v>
       </c>
       <c r="H299" t="n">
         <v>5295</v>
@@ -9069,7 +9069,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G300" t="n">
-        <v>2.45287585258484</v>
+        <v>2.45287537574768</v>
       </c>
       <c r="H300" t="n">
         <v>2774</v>
@@ -9127,7 +9127,7 @@
         <v>2.93600010871887</v>
       </c>
       <c r="G302" t="n">
-        <v>2.45789837837219</v>
+        <v>2.45789861679077</v>
       </c>
       <c r="H302" t="n">
         <v>7753</v>
@@ -9243,7 +9243,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G306" t="n">
-        <v>2.39260029792786</v>
+        <v>2.39260053634644</v>
       </c>
       <c r="H306" t="n">
         <v>2136</v>
@@ -9272,7 +9272,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G307" t="n">
-        <v>2.39594912528992</v>
+        <v>2.39594888687134</v>
       </c>
       <c r="H307" t="n">
         <v>3117</v>
@@ -9359,7 +9359,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G310" t="n">
-        <v>2.46961903572083</v>
+        <v>2.46961879730225</v>
       </c>
       <c r="H310" t="n">
         <v>51</v>
@@ -9388,7 +9388,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G311" t="n">
-        <v>2.46794438362122</v>
+        <v>2.46794462203979</v>
       </c>
       <c r="H311" t="n">
         <v>401</v>
@@ -9446,7 +9446,7 @@
         <v>2.91799998283386</v>
       </c>
       <c r="G313" t="n">
-        <v>2.44282984733582</v>
+        <v>2.44282960891724</v>
       </c>
       <c r="H313" t="n">
         <v>2152</v>
@@ -9504,7 +9504,7 @@
         <v>2.87599992752075</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40766882896423</v>
+        <v>2.40766906738281</v>
       </c>
       <c r="H315" t="n">
         <v>4362</v>
@@ -9533,7 +9533,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G316" t="n">
-        <v>2.39594912528992</v>
+        <v>2.39594888687134</v>
       </c>
       <c r="H316" t="n">
         <v>2861</v>
@@ -9591,7 +9591,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G318" t="n">
-        <v>2.47631597518921</v>
+        <v>2.47631621360779</v>
       </c>
       <c r="H318" t="n">
         <v>6900</v>
@@ -9620,7 +9620,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G319" t="n">
-        <v>2.48133897781372</v>
+        <v>2.4813392162323</v>
       </c>
       <c r="H319" t="n">
         <v>65060</v>
@@ -9649,7 +9649,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42943501472473</v>
+        <v>2.42943525314331</v>
       </c>
       <c r="H320" t="n">
         <v>35143</v>
@@ -9678,7 +9678,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.50310516357422</v>
+        <v>2.5031054019928</v>
       </c>
       <c r="H321" t="n">
         <v>5160</v>
@@ -9765,7 +9765,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G324" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H324" t="n">
         <v>1615</v>
@@ -9794,7 +9794,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43613219261169</v>
+        <v>2.43613243103027</v>
       </c>
       <c r="H325" t="n">
         <v>2400</v>
@@ -9823,7 +9823,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G326" t="n">
-        <v>2.46794438362122</v>
+        <v>2.46794462203979</v>
       </c>
       <c r="H326" t="n">
         <v>5877</v>
@@ -9852,7 +9852,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G327" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H327" t="n">
         <v>1890</v>
@@ -9968,7 +9968,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G331" t="n">
-        <v>2.42943501472473</v>
+        <v>2.42943525314331</v>
       </c>
       <c r="H331" t="n">
         <v>21229</v>
@@ -9997,7 +9997,7 @@
         <v>2.86199998855591</v>
       </c>
       <c r="G332" t="n">
-        <v>2.39594912528992</v>
+        <v>2.39594888687134</v>
       </c>
       <c r="H332" t="n">
         <v>3946</v>
@@ -10026,7 +10026,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G333" t="n">
-        <v>2.4378068447113</v>
+        <v>2.43780660629272</v>
       </c>
       <c r="H333" t="n">
         <v>2786</v>
@@ -10055,7 +10055,7 @@
         <v>2.89400005340576</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42273807525635</v>
+        <v>2.42273783683777</v>
       </c>
       <c r="H334" t="n">
         <v>1064</v>
@@ -10113,7 +10113,7 @@
         <v>2.91199994087219</v>
       </c>
       <c r="G336" t="n">
-        <v>2.4378068447113</v>
+        <v>2.43780660629272</v>
       </c>
       <c r="H336" t="n">
         <v>1854</v>
@@ -10200,7 +10200,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G339" t="n">
-        <v>2.43445825576782</v>
+        <v>2.4344584941864</v>
       </c>
       <c r="H339" t="n">
         <v>10452</v>
@@ -10403,7 +10403,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G346" t="n">
-        <v>2.4629213809967</v>
+        <v>2.46292161941528</v>
       </c>
       <c r="H346" t="n">
         <v>4819</v>
@@ -10490,7 +10490,7 @@
         <v>2.96399998664856</v>
       </c>
       <c r="G349" t="n">
-        <v>2.48133897781372</v>
+        <v>2.4813392162323</v>
       </c>
       <c r="H349" t="n">
         <v>9683</v>
@@ -10606,7 +10606,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G353" t="n">
-        <v>2.4846875667572</v>
+        <v>2.48468732833862</v>
       </c>
       <c r="H353" t="n">
         <v>12736</v>
@@ -10664,7 +10664,7 @@
         <v>2.9539999961853</v>
       </c>
       <c r="G355" t="n">
-        <v>2.47296714782715</v>
+        <v>2.47296762466431</v>
       </c>
       <c r="H355" t="n">
         <v>888</v>
@@ -10751,7 +10751,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>2.45622420310974</v>
+        <v>2.45622444152832</v>
       </c>
       <c r="H358" t="n">
         <v>3191</v>
@@ -10780,7 +10780,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>2.45622420310974</v>
+        <v>2.45622444152832</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -11012,7 +11012,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G367" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H367" t="n">
         <v>13209</v>
@@ -11070,7 +11070,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G369" t="n">
-        <v>2.31892991065979</v>
+        <v>2.31893014907837</v>
       </c>
       <c r="H369" t="n">
         <v>1602</v>
@@ -11099,7 +11099,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G370" t="n">
-        <v>2.31725597381592</v>
+        <v>2.31725573539734</v>
       </c>
       <c r="H370" t="n">
         <v>2000</v>
@@ -11186,7 +11186,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G373" t="n">
-        <v>2.22349405288696</v>
+        <v>2.22349381446838</v>
       </c>
       <c r="H373" t="n">
         <v>8601</v>
@@ -11244,7 +11244,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G375" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H375" t="n">
         <v>2969</v>
@@ -11273,7 +11273,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G376" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014570236206</v>
       </c>
       <c r="H376" t="n">
         <v>4195</v>
@@ -11331,7 +11331,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G378" t="n">
-        <v>2.28376936912537</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H378" t="n">
         <v>1000</v>
@@ -11389,7 +11389,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G380" t="n">
-        <v>2.20842504501343</v>
+        <v>2.20842528343201</v>
       </c>
       <c r="H380" t="n">
         <v>750</v>
@@ -11418,7 +11418,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G381" t="n">
-        <v>2.21009993553162</v>
+        <v>2.21009969711304</v>
       </c>
       <c r="H381" t="n">
         <v>1050</v>
@@ -11447,7 +11447,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G382" t="n">
-        <v>2.20005369186401</v>
+        <v>2.20005393028259</v>
       </c>
       <c r="H382" t="n">
         <v>603</v>
@@ -11505,7 +11505,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>2.20340204238892</v>
+        <v>2.2034022808075</v>
       </c>
       <c r="H384" t="n">
         <v>5239</v>
@@ -11534,7 +11534,7 @@
         <v>2.71799993515015</v>
       </c>
       <c r="G385" t="n">
-        <v>2.27539801597595</v>
+        <v>2.27539777755737</v>
       </c>
       <c r="H385" t="n">
         <v>5752</v>
@@ -11563,7 +11563,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H386" t="n">
         <v>2103</v>
@@ -11592,7 +11592,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11621,7 +11621,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G388" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H388" t="n">
         <v>971</v>
@@ -11650,7 +11650,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G389" t="n">
-        <v>2.22684264183044</v>
+        <v>2.22684288024902</v>
       </c>
       <c r="H389" t="n">
         <v>1926</v>
@@ -11679,7 +11679,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G390" t="n">
-        <v>2.216796875</v>
+        <v>2.21679663658142</v>
       </c>
       <c r="H390" t="n">
         <v>4101</v>
@@ -11708,7 +11708,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G391" t="n">
-        <v>2.25865459442139</v>
+        <v>2.25865483283997</v>
       </c>
       <c r="H391" t="n">
         <v>1101</v>
@@ -11737,7 +11737,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>2.20842504501343</v>
+        <v>2.20842528343201</v>
       </c>
       <c r="H392" t="n">
         <v>750</v>
@@ -11766,7 +11766,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G393" t="n">
-        <v>2.21009993553162</v>
+        <v>2.21009969711304</v>
       </c>
       <c r="H393" t="n">
         <v>700</v>
@@ -11940,7 +11940,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G399" t="n">
-        <v>2.28376936912537</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H399" t="n">
         <v>13861</v>
@@ -11969,7 +11969,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G400" t="n">
-        <v>2.30051255226135</v>
+        <v>2.30051279067993</v>
       </c>
       <c r="H400" t="n">
         <v>3716</v>
@@ -12027,7 +12027,7 @@
         <v>2.76999998092651</v>
       </c>
       <c r="G402" t="n">
-        <v>2.31892991065979</v>
+        <v>2.31893014907837</v>
       </c>
       <c r="H402" t="n">
         <v>2066</v>
@@ -12085,7 +12085,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G404" t="n">
-        <v>2.25195741653442</v>
+        <v>2.251957654953</v>
       </c>
       <c r="H404" t="n">
         <v>4741</v>
@@ -12201,7 +12201,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G408" t="n">
-        <v>2.22684264183044</v>
+        <v>2.22684288024902</v>
       </c>
       <c r="H408" t="n">
         <v>670</v>
@@ -12259,7 +12259,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G410" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H410" t="n">
         <v>9850</v>
@@ -12346,7 +12346,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G413" t="n">
-        <v>2.54328894615173</v>
+        <v>2.54328870773315</v>
       </c>
       <c r="H413" t="n">
         <v>46684</v>
@@ -12404,7 +12404,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G415" t="n">
-        <v>2.4846875667572</v>
+        <v>2.48468732833862</v>
       </c>
       <c r="H415" t="n">
         <v>1551</v>
@@ -12462,7 +12462,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G417" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H417" t="n">
         <v>2024</v>
@@ -12578,7 +12578,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G421" t="n">
-        <v>2.30051255226135</v>
+        <v>2.30051279067993</v>
       </c>
       <c r="H421" t="n">
         <v>27452</v>
@@ -12607,7 +12607,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G422" t="n">
-        <v>2.25195741653442</v>
+        <v>2.251957654953</v>
       </c>
       <c r="H422" t="n">
         <v>10757</v>
@@ -12723,7 +12723,7 @@
         <v>2.75799989700317</v>
       </c>
       <c r="G426" t="n">
-        <v>2.30888414382935</v>
+        <v>2.30888438224792</v>
       </c>
       <c r="H426" t="n">
         <v>3750</v>
@@ -12810,7 +12810,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G429" t="n">
-        <v>2.28042101860046</v>
+        <v>2.28042078018188</v>
       </c>
       <c r="H429" t="n">
         <v>2600</v>
@@ -12984,7 +12984,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>2.27204918861389</v>
+        <v>2.27204942703247</v>
       </c>
       <c r="H435" t="n">
         <v>900</v>
@@ -13100,7 +13100,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G439" t="n">
-        <v>2.31725597381592</v>
+        <v>2.31725573539734</v>
       </c>
       <c r="H439" t="n">
         <v>3442</v>
@@ -13158,7 +13158,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G441" t="n">
-        <v>2.39427423477173</v>
+        <v>2.39427447319031</v>
       </c>
       <c r="H441" t="n">
         <v>6951</v>
@@ -13187,7 +13187,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G442" t="n">
-        <v>2.35409116744995</v>
+        <v>2.35409092903137</v>
       </c>
       <c r="H442" t="n">
         <v>297</v>
@@ -13216,7 +13216,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G443" t="n">
-        <v>2.34571957588196</v>
+        <v>2.34571933746338</v>
       </c>
       <c r="H443" t="n">
         <v>3719</v>
@@ -13303,7 +13303,7 @@
         <v>2.82200002670288</v>
       </c>
       <c r="G446" t="n">
-        <v>2.36246228218079</v>
+        <v>2.36246275901794</v>
       </c>
       <c r="H446" t="n">
         <v>10257</v>
@@ -13361,7 +13361,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G448" t="n">
-        <v>2.39260029792786</v>
+        <v>2.39260053634644</v>
       </c>
       <c r="H448" t="n">
         <v>4893</v>
@@ -13390,7 +13390,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G449" t="n">
-        <v>2.39427423477173</v>
+        <v>2.39427447319031</v>
       </c>
       <c r="H449" t="n">
         <v>1492</v>
@@ -13535,7 +13535,7 @@
         <v>2.80200004577637</v>
       </c>
       <c r="G454" t="n">
-        <v>2.34571957588196</v>
+        <v>2.34571933746338</v>
       </c>
       <c r="H454" t="n">
         <v>6227</v>
@@ -13680,7 +13680,7 @@
         <v>2.81200003623962</v>
       </c>
       <c r="G459" t="n">
-        <v>2.35409116744995</v>
+        <v>2.35409092903137</v>
       </c>
       <c r="H459" t="n">
         <v>800</v>
@@ -13709,7 +13709,7 @@
         <v>2.77999997138977</v>
       </c>
       <c r="G460" t="n">
-        <v>2.32730197906494</v>
+        <v>2.32730174064636</v>
       </c>
       <c r="H460" t="n">
         <v>4081</v>
@@ -13767,7 +13767,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G462" t="n">
-        <v>2.39427423477173</v>
+        <v>2.39427447319031</v>
       </c>
       <c r="H462" t="n">
         <v>16300</v>
@@ -13883,7 +13883,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G466" t="n">
-        <v>2.31055879592896</v>
+        <v>2.31055855751038</v>
       </c>
       <c r="H466" t="n">
         <v>2372</v>
@@ -13912,7 +13912,7 @@
         <v>2.7739999294281</v>
       </c>
       <c r="G467" t="n">
-        <v>2.32227897644043</v>
+        <v>2.32227873802185</v>
       </c>
       <c r="H467" t="n">
         <v>5887</v>
@@ -13941,7 +13941,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G468" t="n">
-        <v>2.30720996856689</v>
+        <v>2.30721020698547</v>
       </c>
       <c r="H468" t="n">
         <v>9061</v>
@@ -13999,7 +13999,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G470" t="n">
-        <v>2.36078810691833</v>
+        <v>2.36078834533691</v>
       </c>
       <c r="H470" t="n">
         <v>4395</v>
@@ -14173,7 +14173,7 @@
         <v>2.76799988746643</v>
       </c>
       <c r="G476" t="n">
-        <v>2.31725597381592</v>
+        <v>2.31725573539734</v>
       </c>
       <c r="H476" t="n">
         <v>6198</v>
@@ -14202,7 +14202,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G477" t="n">
-        <v>2.31055879592896</v>
+        <v>2.31055855751038</v>
       </c>
       <c r="H477" t="n">
         <v>7084</v>
@@ -14231,7 +14231,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G478" t="n">
-        <v>2.23521447181702</v>
+        <v>2.2352147102356</v>
       </c>
       <c r="H478" t="n">
         <v>22224</v>
@@ -14260,7 +14260,7 @@
         <v>2.73799991607666</v>
       </c>
       <c r="G479" t="n">
-        <v>2.29214096069336</v>
+        <v>2.29214072227478</v>
       </c>
       <c r="H479" t="n">
         <v>11364</v>
@@ -14347,7 +14347,7 @@
         <v>2.74799990653992</v>
       </c>
       <c r="G482" t="n">
-        <v>2.30051255226135</v>
+        <v>2.30051279067993</v>
       </c>
       <c r="H482" t="n">
         <v>3600</v>
@@ -14434,7 +14434,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H485" t="n">
         <v>10072</v>
@@ -14463,7 +14463,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G486" t="n">
-        <v>2.2636775970459</v>
+        <v>2.26367783546448</v>
       </c>
       <c r="H486" t="n">
         <v>1722</v>
@@ -14492,7 +14492,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>2.2636775970459</v>
+        <v>2.26367783546448</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G488" t="n">
-        <v>2.28376936912537</v>
+        <v>2.28376960754395</v>
       </c>
       <c r="H488" t="n">
         <v>3338</v>
@@ -14666,7 +14666,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G493" t="n">
-        <v>2.25363206863403</v>
+        <v>2.25363183021545</v>
       </c>
       <c r="H493" t="n">
         <v>11875</v>
@@ -14782,7 +14782,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G497" t="n">
-        <v>2.2201452255249</v>
+        <v>2.22014570236206</v>
       </c>
       <c r="H497" t="n">
         <v>3373</v>
@@ -14927,7 +14927,7 @@
         <v>2.69199991226196</v>
       </c>
       <c r="G502" t="n">
-        <v>2.25363206863403</v>
+        <v>2.25363183021545</v>
       </c>
       <c r="H502" t="n">
         <v>495</v>
@@ -14985,7 +14985,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G504" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H504" t="n">
         <v>2250</v>
@@ -15043,7 +15043,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G506" t="n">
-        <v>2.216796875</v>
+        <v>2.21679663658142</v>
       </c>
       <c r="H506" t="n">
         <v>4326</v>
@@ -15072,7 +15072,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G507" t="n">
-        <v>2.16154432296753</v>
+        <v>2.16154408454895</v>
       </c>
       <c r="H507" t="n">
         <v>16456</v>
@@ -15101,7 +15101,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G508" t="n">
-        <v>2.16321897506714</v>
+        <v>2.16321849822998</v>
       </c>
       <c r="H508" t="n">
         <v>8399</v>
@@ -15130,7 +15130,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G509" t="n">
-        <v>2.16154432296753</v>
+        <v>2.16154408454895</v>
       </c>
       <c r="H509" t="n">
         <v>5173</v>
@@ -15159,7 +15159,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G510" t="n">
-        <v>2.18665909767151</v>
+        <v>2.18665885925293</v>
       </c>
       <c r="H510" t="n">
         <v>3620</v>
@@ -15217,7 +15217,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G512" t="n">
-        <v>2.18498468399048</v>
+        <v>2.1849844455719</v>
       </c>
       <c r="H512" t="n">
         <v>5017</v>
@@ -15362,7 +15362,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G517" t="n">
-        <v>2.21009993553162</v>
+        <v>2.21009969711304</v>
       </c>
       <c r="H517" t="n">
         <v>3706</v>
@@ -15391,7 +15391,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H518" t="n">
         <v>6410</v>
@@ -15565,7 +15565,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G524" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H524" t="n">
         <v>1330</v>
@@ -15652,7 +15652,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G527" t="n">
-        <v>2.21009993553162</v>
+        <v>2.21009969711304</v>
       </c>
       <c r="H527" t="n">
         <v>6584</v>
@@ -15739,7 +15739,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G530" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H530" t="n">
         <v>3093</v>
@@ -15768,7 +15768,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G531" t="n">
-        <v>2.18498468399048</v>
+        <v>2.1849844455719</v>
       </c>
       <c r="H531" t="n">
         <v>4511</v>
@@ -15797,7 +15797,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G532" t="n">
-        <v>2.22684264183044</v>
+        <v>2.22684288024902</v>
       </c>
       <c r="H532" t="n">
         <v>4342</v>
@@ -15826,7 +15826,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G533" t="n">
-        <v>2.18498468399048</v>
+        <v>2.1849844455719</v>
       </c>
       <c r="H533" t="n">
         <v>597</v>
@@ -15855,7 +15855,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H534" t="n">
         <v>984</v>
@@ -15913,7 +15913,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G536" t="n">
-        <v>2.15987014770508</v>
+        <v>2.1598699092865</v>
       </c>
       <c r="H536" t="n">
         <v>2307</v>
@@ -15971,7 +15971,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>2.12638378143311</v>
+        <v>2.12638354301453</v>
       </c>
       <c r="H538" t="n">
         <v>18029</v>
@@ -16029,7 +16029,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G540" t="n">
-        <v>2.15987014770508</v>
+        <v>2.1598699092865</v>
       </c>
       <c r="H540" t="n">
         <v>1963</v>
@@ -16058,7 +16058,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G541" t="n">
-        <v>2.15987014770508</v>
+        <v>2.1598699092865</v>
       </c>
       <c r="H541" t="n">
         <v>0</v>
@@ -16116,7 +16116,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G543" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H543" t="n">
         <v>7722</v>
@@ -16174,7 +16174,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G545" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H545" t="n">
         <v>1800</v>
@@ -16203,7 +16203,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H546" t="n">
         <v>1300</v>
@@ -16348,7 +16348,7 @@
         <v>2.5</v>
       </c>
       <c r="G551" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H551" t="n">
         <v>7464</v>
@@ -16406,7 +16406,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G553" t="n">
-        <v>2.06778287887573</v>
+        <v>2.06778240203857</v>
       </c>
       <c r="H553" t="n">
         <v>10951</v>
@@ -16435,7 +16435,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G554" t="n">
-        <v>2.13475489616394</v>
+        <v>2.1347553730011</v>
       </c>
       <c r="H554" t="n">
         <v>19861</v>
@@ -16464,7 +16464,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06778287887573</v>
+        <v>2.06778240203857</v>
       </c>
       <c r="H555" t="n">
         <v>3370</v>
@@ -16493,7 +16493,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H556" t="n">
         <v>3626</v>
@@ -16522,7 +16522,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G557" t="n">
-        <v>2.10126876831055</v>
+        <v>2.10126900672913</v>
       </c>
       <c r="H557" t="n">
         <v>8276</v>
@@ -16551,7 +16551,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G558" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H558" t="n">
         <v>1420</v>
@@ -16580,7 +16580,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H559" t="n">
         <v>1988</v>
@@ -16609,7 +16609,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H560" t="n">
         <v>2000</v>
@@ -16638,7 +16638,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H561" t="n">
         <v>75</v>
@@ -16725,7 +16725,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G564" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H564" t="n">
         <v>28258</v>
@@ -16899,7 +16899,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G570" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H570" t="n">
         <v>4499</v>
@@ -16928,7 +16928,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G571" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H571" t="n">
         <v>5450</v>
@@ -16957,7 +16957,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H572" t="n">
         <v>810</v>
@@ -17015,7 +17015,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G574" t="n">
-        <v>2.05941104888916</v>
+        <v>2.05941081047058</v>
       </c>
       <c r="H574" t="n">
         <v>5538</v>
@@ -17044,7 +17044,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G575" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H575" t="n">
         <v>19688</v>
@@ -17160,7 +17160,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G579" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H579" t="n">
         <v>8071</v>
@@ -17189,7 +17189,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G580" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H580" t="n">
         <v>11844</v>
@@ -17218,7 +17218,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G581" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H581" t="n">
         <v>28615</v>
@@ -17305,7 +17305,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G584" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H584" t="n">
         <v>14481</v>
@@ -17334,7 +17334,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G585" t="n">
-        <v>2.06778287887573</v>
+        <v>2.06778240203857</v>
       </c>
       <c r="H585" t="n">
         <v>16930</v>
@@ -17363,7 +17363,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G586" t="n">
-        <v>2.22684264183044</v>
+        <v>2.22684288024902</v>
       </c>
       <c r="H586" t="n">
         <v>62764</v>
@@ -17421,7 +17421,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.12638378143311</v>
+        <v>2.12638354301453</v>
       </c>
       <c r="H588" t="n">
         <v>10489</v>
@@ -17479,7 +17479,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G590" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H590" t="n">
         <v>4774</v>
@@ -17624,7 +17624,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.13475489616394</v>
+        <v>2.1347553730011</v>
       </c>
       <c r="H595" t="n">
         <v>8105</v>
@@ -17740,7 +17740,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.08452558517456</v>
+        <v>2.08452582359314</v>
       </c>
       <c r="H599" t="n">
         <v>16850</v>
@@ -17769,7 +17769,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.08452558517456</v>
+        <v>2.08452582359314</v>
       </c>
       <c r="H600" t="n">
         <v>15758</v>
@@ -17798,7 +17798,7 @@
         <v>2.5</v>
       </c>
       <c r="G601" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H601" t="n">
         <v>5909</v>
@@ -17827,7 +17827,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G602" t="n">
-        <v>2.08452558517456</v>
+        <v>2.08452582359314</v>
       </c>
       <c r="H602" t="n">
         <v>929</v>
@@ -17885,7 +17885,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G604" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H604" t="n">
         <v>1612</v>
@@ -17914,7 +17914,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H605" t="n">
         <v>10604</v>
@@ -17943,7 +17943,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>2.04266762733459</v>
+        <v>2.04266786575317</v>
       </c>
       <c r="H606" t="n">
         <v>8516</v>
@@ -17972,7 +17972,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G607" t="n">
-        <v>2.03429627418518</v>
+        <v>2.0342960357666</v>
       </c>
       <c r="H607" t="n">
         <v>12259</v>
@@ -18001,7 +18001,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G608" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H608" t="n">
         <v>34072</v>
@@ -18146,7 +18146,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G613" t="n">
-        <v>1.95895171165466</v>
+        <v>1.95895183086395</v>
       </c>
       <c r="H613" t="n">
         <v>9679</v>
@@ -18175,7 +18175,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G614" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H614" t="n">
         <v>11769</v>
@@ -18291,7 +18291,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G618" t="n">
-        <v>1.95895171165466</v>
+        <v>1.95895183086395</v>
       </c>
       <c r="H618" t="n">
         <v>13572</v>
@@ -18320,7 +18320,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G619" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H619" t="n">
         <v>2150</v>
@@ -18349,7 +18349,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H620" t="n">
         <v>11523</v>
@@ -18378,7 +18378,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G621" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H621" t="n">
         <v>18421</v>
@@ -18407,7 +18407,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G622" t="n">
-        <v>1.95895171165466</v>
+        <v>1.95895183086395</v>
       </c>
       <c r="H622" t="n">
         <v>7799</v>
@@ -18436,7 +18436,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H623" t="n">
         <v>6806</v>
@@ -18465,7 +18465,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H625" t="n">
         <v>2432</v>
@@ -18523,7 +18523,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G626" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H626" t="n">
         <v>8090</v>
@@ -18697,7 +18697,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G632" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H632" t="n">
         <v>750</v>
@@ -18726,7 +18726,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G633" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H633" t="n">
         <v>29390</v>
@@ -18755,7 +18755,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G634" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H634" t="n">
         <v>11440</v>
@@ -18842,7 +18842,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G637" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H637" t="n">
         <v>25094</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H640" t="n">
         <v>18356</v>
@@ -18958,7 +18958,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G641" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H641" t="n">
         <v>8054</v>
@@ -18987,7 +18987,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G642" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H642" t="n">
         <v>12670</v>
@@ -19016,7 +19016,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G643" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H643" t="n">
         <v>23302</v>
@@ -19045,7 +19045,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G644" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H644" t="n">
         <v>2768</v>
@@ -19074,7 +19074,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19103,7 +19103,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H646" t="n">
         <v>1650</v>
@@ -19190,7 +19190,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G649" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H649" t="n">
         <v>32920</v>
@@ -19219,7 +19219,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G650" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H650" t="n">
         <v>44057</v>
@@ -19277,7 +19277,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G652" t="n">
-        <v>1.95895171165466</v>
+        <v>1.95895183086395</v>
       </c>
       <c r="H652" t="n">
         <v>150</v>
@@ -19306,7 +19306,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G653" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H653" t="n">
         <v>5186</v>
@@ -19364,7 +19364,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G655" t="n">
-        <v>1.95895171165466</v>
+        <v>1.95895183086395</v>
       </c>
       <c r="H655" t="n">
         <v>1900</v>
@@ -19393,7 +19393,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G656" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H656" t="n">
         <v>8256</v>
@@ -19422,7 +19422,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G657" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H657" t="n">
         <v>14198</v>
@@ -19480,7 +19480,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H659" t="n">
         <v>5758</v>
@@ -19509,7 +19509,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>2.05941104888916</v>
+        <v>2.05941081047058</v>
       </c>
       <c r="H660" t="n">
         <v>27013</v>
@@ -19538,7 +19538,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G661" t="n">
-        <v>2.03429627418518</v>
+        <v>2.0342960357666</v>
       </c>
       <c r="H661" t="n">
         <v>1305</v>
@@ -19654,7 +19654,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G665" t="n">
-        <v>2.03429627418518</v>
+        <v>2.0342960357666</v>
       </c>
       <c r="H665" t="n">
         <v>1052</v>
@@ -19683,7 +19683,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H666" t="n">
         <v>4634</v>
@@ -19741,7 +19741,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H668" t="n">
         <v>1332</v>
@@ -19770,7 +19770,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H669" t="n">
         <v>4</v>
@@ -19828,7 +19828,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G671" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H671" t="n">
         <v>1761</v>
@@ -19857,7 +19857,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G672" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H672" t="n">
         <v>201</v>
@@ -19886,7 +19886,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G673" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H673" t="n">
         <v>62</v>
@@ -19915,7 +19915,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H674" t="n">
         <v>7700</v>
@@ -19973,7 +19973,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G676" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H676" t="n">
         <v>17668</v>
@@ -20060,7 +20060,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H679" t="n">
         <v>1532</v>
@@ -20089,7 +20089,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H680" t="n">
         <v>12081</v>
@@ -20118,7 +20118,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G681" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H681" t="n">
         <v>1528</v>
@@ -20176,7 +20176,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G683" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H683" t="n">
         <v>18382</v>
@@ -20234,7 +20234,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H685" t="n">
         <v>6020</v>
@@ -20263,7 +20263,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G686" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H686" t="n">
         <v>567</v>
@@ -20292,7 +20292,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H687" t="n">
         <v>9265</v>
@@ -20350,7 +20350,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G689" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H689" t="n">
         <v>5573</v>
@@ -20379,7 +20379,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H690" t="n">
         <v>24561</v>
@@ -20408,7 +20408,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H691" t="n">
         <v>13491</v>
@@ -20437,7 +20437,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G692" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H692" t="n">
         <v>1155</v>
@@ -20466,7 +20466,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G693" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H693" t="n">
         <v>8645</v>
@@ -20524,7 +20524,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H695" t="n">
         <v>11225</v>
@@ -20611,7 +20611,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H698" t="n">
         <v>913</v>
@@ -20640,7 +20640,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G699" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H699" t="n">
         <v>400</v>
@@ -20669,7 +20669,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G700" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H700" t="n">
         <v>500</v>
@@ -20698,7 +20698,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H701" t="n">
         <v>2949</v>
@@ -20756,7 +20756,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G703" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H703" t="n">
         <v>20278</v>
@@ -20785,7 +20785,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G704" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H704" t="n">
         <v>12905</v>
@@ -20814,7 +20814,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G705" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H705" t="n">
         <v>3197</v>
@@ -20843,7 +20843,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G706" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H706" t="n">
         <v>2800</v>
@@ -20930,7 +20930,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H709" t="n">
         <v>11172</v>
@@ -20988,7 +20988,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G711" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H711" t="n">
         <v>8295</v>
@@ -21133,7 +21133,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>1.75803363323212</v>
+        <v>1.75803351402283</v>
       </c>
       <c r="H716" t="n">
         <v>8743</v>
@@ -21191,7 +21191,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G718" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H718" t="n">
         <v>453</v>
@@ -21220,7 +21220,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G719" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H719" t="n">
         <v>7214</v>
@@ -21249,7 +21249,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G720" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H720" t="n">
         <v>2261</v>
@@ -21278,7 +21278,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G721" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H721" t="n">
         <v>1550</v>
@@ -21307,7 +21307,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G722" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H722" t="n">
         <v>7949</v>
@@ -21336,7 +21336,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G723" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H723" t="n">
         <v>4248</v>
@@ -21481,7 +21481,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G728" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H728" t="n">
         <v>2505</v>
@@ -21539,7 +21539,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H730" t="n">
         <v>13567</v>
@@ -21568,7 +21568,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H731" t="n">
         <v>2175</v>
@@ -21597,7 +21597,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H732" t="n">
         <v>1000</v>
@@ -21713,7 +21713,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H736" t="n">
         <v>3553</v>
@@ -21771,7 +21771,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G738" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H738" t="n">
         <v>18808</v>
@@ -21800,7 +21800,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G739" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H739" t="n">
         <v>18110</v>
@@ -21829,7 +21829,7 @@
         <v>2.25</v>
       </c>
       <c r="G740" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H740" t="n">
         <v>3848</v>
@@ -21858,7 +21858,7 @@
         <v>2.25</v>
       </c>
       <c r="G741" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H741" t="n">
         <v>0</v>
@@ -21887,7 +21887,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G742" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H742" t="n">
         <v>4228</v>
@@ -21916,7 +21916,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G743" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H743" t="n">
         <v>2159</v>
@@ -22003,7 +22003,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H746" t="n">
         <v>10786</v>
@@ -22032,7 +22032,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G747" t="n">
-        <v>1.95895171165466</v>
+        <v>1.95895183086395</v>
       </c>
       <c r="H747" t="n">
         <v>650</v>
@@ -22090,7 +22090,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H749" t="n">
         <v>1080</v>
@@ -22119,7 +22119,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>1.97569513320923</v>
+        <v>1.97569525241852</v>
       </c>
       <c r="H750" t="n">
         <v>2189</v>
@@ -22206,7 +22206,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G753" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H753" t="n">
         <v>10383</v>
@@ -22235,7 +22235,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H754" t="n">
         <v>3184</v>
@@ -22264,7 +22264,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G755" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H755" t="n">
         <v>5896</v>
@@ -22293,7 +22293,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G756" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H756" t="n">
         <v>3784</v>
@@ -22351,7 +22351,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G758" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H758" t="n">
         <v>2200</v>
@@ -22380,7 +22380,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H759" t="n">
         <v>5639</v>
@@ -22409,7 +22409,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G760" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H760" t="n">
         <v>2200</v>
@@ -22467,7 +22467,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G762" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H762" t="n">
         <v>1526</v>
@@ -22554,7 +22554,7 @@
         <v>2.25</v>
       </c>
       <c r="G765" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H765" t="n">
         <v>411</v>
@@ -22583,7 +22583,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G766" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H766" t="n">
         <v>2971</v>
@@ -22612,7 +22612,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G767" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H767" t="n">
         <v>10550</v>
@@ -22641,7 +22641,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G768" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H768" t="n">
         <v>5724</v>
@@ -22670,7 +22670,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G769" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H769" t="n">
         <v>2742</v>
@@ -22699,7 +22699,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G770" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H770" t="n">
         <v>450</v>
@@ -22728,7 +22728,7 @@
         <v>2.25</v>
       </c>
       <c r="G771" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H771" t="n">
         <v>1100</v>
@@ -22757,7 +22757,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G772" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H772" t="n">
         <v>4352</v>
@@ -22815,7 +22815,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H774" t="n">
         <v>3700</v>
@@ -22844,7 +22844,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H776" t="n">
         <v>1303</v>
@@ -22931,7 +22931,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H778" t="n">
         <v>6827</v>
@@ -22960,7 +22960,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H779" t="n">
         <v>780</v>
@@ -22989,7 +22989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H780" t="n">
         <v>5010</v>
@@ -23018,7 +23018,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G781" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H781" t="n">
         <v>3509</v>
@@ -23047,7 +23047,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H782" t="n">
         <v>256</v>
@@ -23076,7 +23076,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G783" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H783" t="n">
         <v>400</v>
@@ -23105,7 +23105,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G784" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H784" t="n">
         <v>3539</v>
@@ -23134,7 +23134,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G785" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H785" t="n">
         <v>2128</v>
@@ -23308,7 +23308,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G791" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H791" t="n">
         <v>1232</v>
@@ -23337,7 +23337,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H792" t="n">
         <v>5850</v>
@@ -23366,7 +23366,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G793" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H793" t="n">
         <v>5546</v>
@@ -23395,7 +23395,7 @@
         <v>2.25</v>
       </c>
       <c r="G794" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H794" t="n">
         <v>333</v>
@@ -23424,7 +23424,7 @@
         <v>2.25</v>
       </c>
       <c r="G795" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H795" t="n">
         <v>0</v>
@@ -23482,7 +23482,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H797" t="n">
         <v>3229</v>
@@ -23511,7 +23511,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G798" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H798" t="n">
         <v>11228</v>
@@ -23569,7 +23569,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H800" t="n">
         <v>2600</v>
@@ -23598,7 +23598,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G801" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H801" t="n">
         <v>100</v>
@@ -23627,7 +23627,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H802" t="n">
         <v>3832</v>
@@ -23656,7 +23656,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H803" t="n">
         <v>1268</v>
@@ -23685,7 +23685,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H804" t="n">
         <v>1209</v>
@@ -23714,7 +23714,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G805" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H805" t="n">
         <v>3425</v>
@@ -23772,7 +23772,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G807" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H807" t="n">
         <v>15527</v>
@@ -23801,7 +23801,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G808" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H808" t="n">
         <v>6096</v>
@@ -23830,7 +23830,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H809" t="n">
         <v>2001</v>
@@ -23859,7 +23859,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G810" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H810" t="n">
         <v>10120</v>
@@ -23888,7 +23888,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G811" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H811" t="n">
         <v>1012</v>
@@ -23946,7 +23946,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G813" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H813" t="n">
         <v>2826</v>
@@ -23975,7 +23975,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G814" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H814" t="n">
         <v>461</v>
@@ -24004,7 +24004,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G815" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H815" t="n">
         <v>3</v>
@@ -24033,7 +24033,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H816" t="n">
         <v>6014</v>
@@ -24062,7 +24062,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G817" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H817" t="n">
         <v>3239</v>
@@ -24120,7 +24120,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H819" t="n">
         <v>2968</v>
@@ -24149,7 +24149,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G820" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H820" t="n">
         <v>5121</v>
@@ -24178,7 +24178,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H821" t="n">
         <v>1562</v>
@@ -24207,7 +24207,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G822" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H822" t="n">
         <v>2411</v>
@@ -24236,7 +24236,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G823" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H823" t="n">
         <v>2356</v>
@@ -24265,7 +24265,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G824" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H824" t="n">
         <v>4424</v>
@@ -24294,7 +24294,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G825" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H825" t="n">
         <v>11252</v>
@@ -24323,7 +24323,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G826" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H826" t="n">
         <v>3729</v>
@@ -24352,7 +24352,7 @@
         <v>2.25</v>
       </c>
       <c r="G827" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H827" t="n">
         <v>3616</v>
@@ -24381,7 +24381,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H828" t="n">
         <v>11857</v>
@@ -24410,7 +24410,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G829" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H829" t="n">
         <v>2204</v>
@@ -24439,7 +24439,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H830" t="n">
         <v>3888</v>
@@ -24468,7 +24468,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H831" t="n">
         <v>683</v>
@@ -24497,7 +24497,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H832" t="n">
         <v>2898</v>
@@ -24555,7 +24555,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H834" t="n">
         <v>300</v>
@@ -24584,7 +24584,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H835" t="n">
         <v>2305</v>
@@ -24671,7 +24671,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G838" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H838" t="n">
         <v>3473</v>
@@ -24729,7 +24729,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G840" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H840" t="n">
         <v>501</v>
@@ -24758,7 +24758,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H841" t="n">
         <v>4430</v>
@@ -24787,7 +24787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H843" t="n">
         <v>497</v>
@@ -24845,7 +24845,7 @@
         <v>2.25</v>
       </c>
       <c r="G844" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H844" t="n">
         <v>6575</v>
@@ -24874,7 +24874,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H845" t="n">
         <v>4803</v>
@@ -24903,7 +24903,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G846" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H846" t="n">
         <v>1750</v>
@@ -24961,7 +24961,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G848" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H848" t="n">
         <v>8445</v>
@@ -24990,7 +24990,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G849" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H849" t="n">
         <v>9330</v>
@@ -25019,7 +25019,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G850" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H850" t="n">
         <v>765</v>
@@ -25048,7 +25048,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G851" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H851" t="n">
         <v>6863</v>
@@ -25106,7 +25106,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H853" t="n">
         <v>2000</v>
@@ -25280,7 +25280,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G859" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H859" t="n">
         <v>1117</v>
@@ -25309,7 +25309,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G860" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H860" t="n">
         <v>343</v>
@@ -25338,7 +25338,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G861" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H861" t="n">
         <v>4010</v>
@@ -25367,7 +25367,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G862" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H862" t="n">
         <v>3300</v>
@@ -25396,7 +25396,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G863" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H863" t="n">
         <v>1000</v>
@@ -25483,7 +25483,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G866" t="n">
-        <v>1.75803363323212</v>
+        <v>1.75803351402283</v>
       </c>
       <c r="H866" t="n">
         <v>6120</v>
@@ -25541,7 +25541,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G868" t="n">
-        <v>1.71617579460144</v>
+        <v>1.71617567539215</v>
       </c>
       <c r="H868" t="n">
         <v>5711</v>
@@ -25570,7 +25570,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G869" t="n">
-        <v>1.72454750537872</v>
+        <v>1.72454738616943</v>
       </c>
       <c r="H869" t="n">
         <v>8586</v>
@@ -25628,7 +25628,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>1.68268942832947</v>
+        <v>1.68268930912018</v>
       </c>
       <c r="H871" t="n">
         <v>7472</v>
@@ -25657,7 +25657,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G872" t="n">
-        <v>1.71617579460144</v>
+        <v>1.71617567539215</v>
       </c>
       <c r="H872" t="n">
         <v>3844</v>
@@ -25715,7 +25715,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.71617579460144</v>
+        <v>1.71617567539215</v>
       </c>
       <c r="H874" t="n">
         <v>1936</v>
@@ -25744,7 +25744,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G875" t="n">
-        <v>1.66594636440277</v>
+        <v>1.66594624519348</v>
       </c>
       <c r="H875" t="n">
         <v>12403</v>
@@ -25773,7 +25773,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>1.65757465362549</v>
+        <v>1.65757477283478</v>
       </c>
       <c r="H876" t="n">
         <v>12771</v>
@@ -25976,7 +25976,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G883" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H883" t="n">
         <v>536</v>
@@ -26005,7 +26005,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G884" t="n">
-        <v>1.6492030620575</v>
+        <v>1.64920318126678</v>
       </c>
       <c r="H884" t="n">
         <v>13029</v>
@@ -26034,7 +26034,7 @@
         <v>1.97500002384186</v>
       </c>
       <c r="G885" t="n">
-        <v>1.65338885784149</v>
+        <v>1.65338897705078</v>
       </c>
       <c r="H885" t="n">
         <v>503</v>
@@ -26121,7 +26121,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G888" t="n">
-        <v>1.71617579460144</v>
+        <v>1.71617567539215</v>
       </c>
       <c r="H888" t="n">
         <v>40809</v>
@@ -26295,7 +26295,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G894" t="n">
-        <v>1.71617579460144</v>
+        <v>1.71617567539215</v>
       </c>
       <c r="H894" t="n">
         <v>5162</v>
@@ -26382,7 +26382,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G897" t="n">
-        <v>1.76640510559082</v>
+        <v>1.76640522480011</v>
       </c>
       <c r="H897" t="n">
         <v>5396</v>
@@ -26469,7 +26469,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G900" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H900" t="n">
         <v>3694</v>
@@ -26498,7 +26498,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H901" t="n">
         <v>2716</v>
@@ -26527,7 +26527,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G902" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H902" t="n">
         <v>4588</v>
@@ -26614,7 +26614,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G905" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H905" t="n">
         <v>4903</v>
@@ -26643,7 +26643,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H906" t="n">
         <v>1414</v>
@@ -26672,7 +26672,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G907" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H907" t="n">
         <v>601</v>
@@ -26701,7 +26701,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G908" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H908" t="n">
         <v>3344</v>
@@ -26730,7 +26730,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -26904,7 +26904,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G915" t="n">
-        <v>1.76640510559082</v>
+        <v>1.76640522480011</v>
       </c>
       <c r="H915" t="n">
         <v>2527</v>
@@ -26962,7 +26962,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G917" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H917" t="n">
         <v>2716</v>
@@ -27078,7 +27078,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G921" t="n">
-        <v>1.76640510559082</v>
+        <v>1.76640522480011</v>
       </c>
       <c r="H921" t="n">
         <v>6074</v>
@@ -27136,7 +27136,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G923" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H923" t="n">
         <v>1865</v>
@@ -27542,7 +27542,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G937" t="n">
-        <v>1.76640510559082</v>
+        <v>1.76640522480011</v>
       </c>
       <c r="H937" t="n">
         <v>1540</v>
@@ -27600,7 +27600,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G939" t="n">
-        <v>1.75803363323212</v>
+        <v>1.75803351402283</v>
       </c>
       <c r="H939" t="n">
         <v>6005</v>
@@ -27716,7 +27716,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H943" t="n">
         <v>24151</v>
@@ -27745,7 +27745,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G944" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H944" t="n">
         <v>37350</v>
@@ -27774,7 +27774,7 @@
         <v>2.25</v>
       </c>
       <c r="G945" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H945" t="n">
         <v>13894</v>
@@ -27803,7 +27803,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H946" t="n">
         <v>6198</v>
@@ -27832,7 +27832,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G947" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H947" t="n">
         <v>10416</v>
@@ -27861,7 +27861,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G948" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H948" t="n">
         <v>5166</v>
@@ -28006,7 +28006,7 @@
         <v>2.25</v>
       </c>
       <c r="G953" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H953" t="n">
         <v>920</v>
@@ -28035,7 +28035,7 @@
         <v>2.25</v>
       </c>
       <c r="G954" t="n">
-        <v>1.88360774517059</v>
+        <v>1.88360750675201</v>
       </c>
       <c r="H954" t="n">
         <v>3991</v>
@@ -28064,7 +28064,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G955" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H955" t="n">
         <v>9230</v>
@@ -28325,7 +28325,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G964" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H964" t="n">
         <v>29139</v>
@@ -28383,7 +28383,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G966" t="n">
-        <v>1.76640510559082</v>
+        <v>1.76640522480011</v>
       </c>
       <c r="H966" t="n">
         <v>6985</v>
@@ -28499,7 +28499,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H970" t="n">
         <v>7180</v>
@@ -28557,7 +28557,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G972" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H972" t="n">
         <v>7551</v>
@@ -28673,7 +28673,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G976" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H976" t="n">
         <v>226</v>
@@ -28760,7 +28760,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G979" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H979" t="n">
         <v>23662</v>
@@ -28789,7 +28789,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G980" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H980" t="n">
         <v>12200</v>
@@ -28818,7 +28818,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G981" t="n">
-        <v>1.85012125968933</v>
+        <v>1.85012137889862</v>
       </c>
       <c r="H981" t="n">
         <v>2107</v>
@@ -28847,7 +28847,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G982" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H982" t="n">
         <v>4216</v>
@@ -28905,7 +28905,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G984" t="n">
-        <v>2.15987014770508</v>
+        <v>2.1598699092865</v>
       </c>
       <c r="H984" t="n">
         <v>228846</v>
@@ -28963,7 +28963,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G986" t="n">
-        <v>2.15987014770508</v>
+        <v>2.1598699092865</v>
       </c>
       <c r="H986" t="n">
         <v>38716</v>
@@ -29050,7 +29050,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>2.16824173927307</v>
+        <v>2.16824150085449</v>
       </c>
       <c r="H989" t="n">
         <v>11373</v>
@@ -29108,7 +29108,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>2.12638378143311</v>
+        <v>2.12638354301453</v>
       </c>
       <c r="H991" t="n">
         <v>12330</v>
@@ -29137,7 +29137,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G992" t="n">
-        <v>2.10126876831055</v>
+        <v>2.10126900672913</v>
       </c>
       <c r="H992" t="n">
         <v>3797</v>
@@ -29195,7 +29195,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G994" t="n">
-        <v>2.260329246521</v>
+        <v>2.26032900810242</v>
       </c>
       <c r="H994" t="n">
         <v>135284</v>
@@ -29224,7 +29224,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G995" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H995" t="n">
         <v>88276</v>
@@ -29282,7 +29282,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G997" t="n">
-        <v>2.20172786712646</v>
+        <v>2.20172810554504</v>
       </c>
       <c r="H997" t="n">
         <v>20429</v>
@@ -29311,7 +29311,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>2.13475489616394</v>
+        <v>2.1347553730011</v>
       </c>
       <c r="H998" t="n">
         <v>21041</v>
@@ -29398,7 +29398,7 @@
         <v>2.5</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H1001" t="n">
         <v>4904</v>
@@ -29427,7 +29427,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.12638378143311</v>
+        <v>2.12638354301453</v>
       </c>
       <c r="H1002" t="n">
         <v>6668</v>
@@ -29485,7 +29485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.13475489616394</v>
+        <v>2.1347553730011</v>
       </c>
       <c r="H1004" t="n">
         <v>4848</v>
@@ -29543,7 +29543,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.13475489616394</v>
+        <v>2.1347553730011</v>
       </c>
       <c r="H1006" t="n">
         <v>593</v>
@@ -29601,7 +29601,7 @@
         <v>2.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.09289717674255</v>
+        <v>2.09289741516113</v>
       </c>
       <c r="H1008" t="n">
         <v>7330</v>
@@ -29630,7 +29630,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1009" t="n">
-        <v>2.03429627418518</v>
+        <v>2.0342960357666</v>
       </c>
       <c r="H1009" t="n">
         <v>6374</v>
@@ -29659,7 +29659,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08452558517456</v>
+        <v>2.08452582359314</v>
       </c>
       <c r="H1010" t="n">
         <v>6972</v>
@@ -29717,7 +29717,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1012" t="n">
-        <v>2.03429627418518</v>
+        <v>2.0342960357666</v>
       </c>
       <c r="H1012" t="n">
         <v>27298</v>
@@ -29746,7 +29746,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H1013" t="n">
         <v>9251</v>
@@ -29804,7 +29804,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1015" t="n">
-        <v>2.02592492103577</v>
+        <v>2.02592468261719</v>
       </c>
       <c r="H1015" t="n">
         <v>5825</v>
@@ -29833,7 +29833,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1016" t="n">
-        <v>2.03429627418518</v>
+        <v>2.0342960357666</v>
       </c>
       <c r="H1016" t="n">
         <v>12595</v>
@@ -29862,7 +29862,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.05103945732117</v>
+        <v>2.05103921890259</v>
       </c>
       <c r="H1017" t="n">
         <v>7730</v>
@@ -30036,7 +30036,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1023" t="n">
-        <v>1.99243819713593</v>
+        <v>1.99243831634521</v>
       </c>
       <c r="H1023" t="n">
         <v>34472</v>
@@ -30123,7 +30123,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H1026" t="n">
         <v>3920</v>
@@ -30152,7 +30152,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H1027" t="n">
         <v>26611</v>
@@ -30181,7 +30181,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H1028" t="n">
         <v>6112</v>
@@ -30239,7 +30239,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H1030" t="n">
         <v>8304</v>
@@ -30268,7 +30268,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.96732342243195</v>
+        <v>1.96732330322266</v>
       </c>
       <c r="H1031" t="n">
         <v>3685</v>
@@ -30297,7 +30297,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H1032" t="n">
         <v>7041</v>
@@ -30326,7 +30326,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H1033" t="n">
         <v>3013</v>
@@ -30355,7 +30355,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H1034" t="n">
         <v>1887</v>
@@ -30384,7 +30384,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H1035" t="n">
         <v>500</v>
@@ -30413,7 +30413,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H1036" t="n">
         <v>2200</v>
@@ -30442,7 +30442,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.89197909832001</v>
+        <v>1.8919792175293</v>
       </c>
       <c r="H1037" t="n">
         <v>8973</v>
@@ -30471,7 +30471,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.87523579597473</v>
+        <v>1.87523591518402</v>
       </c>
       <c r="H1038" t="n">
         <v>18702</v>
@@ -30500,7 +30500,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.900350689888</v>
+        <v>1.90035080909729</v>
       </c>
       <c r="H1039" t="n">
         <v>1542</v>
@@ -30529,7 +30529,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.85849273204803</v>
+        <v>1.85849285125732</v>
       </c>
       <c r="H1040" t="n">
         <v>4415</v>
@@ -30558,7 +30558,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.95895171165466</v>
+        <v>1.95895183086395</v>
       </c>
       <c r="H1041" t="n">
         <v>8505</v>
@@ -30616,7 +30616,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H1043" t="n">
         <v>9504</v>
@@ -30645,7 +30645,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.90872240066528</v>
+        <v>1.90872228145599</v>
       </c>
       <c r="H1044" t="n">
         <v>9277</v>
@@ -30674,7 +30674,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H1045" t="n">
         <v>8755</v>
@@ -30703,7 +30703,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H1046" t="n">
         <v>7950</v>
@@ -30761,7 +30761,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.95058023929596</v>
+        <v>1.95058035850525</v>
       </c>
       <c r="H1048" t="n">
         <v>3001</v>
@@ -30848,7 +30848,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1051" t="n">
-        <v>1.92546546459198</v>
+        <v>1.92546534538269</v>
       </c>
       <c r="H1051" t="n">
         <v>1484</v>
@@ -30877,7 +30877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.93383717536926</v>
+        <v>1.93383693695068</v>
       </c>
       <c r="H1052" t="n">
         <v>3790</v>
@@ -30935,7 +30935,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.84174978733063</v>
+        <v>1.84174954891205</v>
       </c>
       <c r="H1054" t="n">
         <v>2093</v>
@@ -30964,7 +30964,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H1055" t="n">
         <v>3728</v>
@@ -30993,7 +30993,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.86686456203461</v>
+        <v>1.86686444282532</v>
       </c>
       <c r="H1056" t="n">
         <v>61</v>
@@ -31051,7 +31051,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.80826342105865</v>
+        <v>1.80826330184937</v>
       </c>
       <c r="H1058" t="n">
         <v>2815</v>
@@ -31080,7 +31080,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.74966216087341</v>
+        <v>1.74966204166412</v>
       </c>
       <c r="H1059" t="n">
         <v>10342</v>
@@ -31109,7 +31109,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.74966216087341</v>
+        <v>1.74966204166412</v>
       </c>
       <c r="H1060" t="n">
         <v>3550</v>
@@ -31138,7 +31138,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.68268942832947</v>
+        <v>1.68268930912018</v>
       </c>
       <c r="H1061" t="n">
         <v>9201</v>
@@ -31167,7 +31167,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1062" t="n">
         <v>19381</v>
@@ -31254,7 +31254,7 @@
         <v>1.47500002384186</v>
       </c>
       <c r="G1065" t="n">
-        <v>1.23480951786041</v>
+        <v>1.23480939865112</v>
       </c>
       <c r="H1065" t="n">
         <v>4894</v>
@@ -31370,7 +31370,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.22643792629242</v>
+        <v>1.22643768787384</v>
       </c>
       <c r="H1069" t="n">
         <v>2290</v>
@@ -31399,7 +31399,7 @@
         <v>1.38999998569489</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.16365098953247</v>
+        <v>1.16365087032318</v>
       </c>
       <c r="H1070" t="n">
         <v>15128</v>
@@ -31428,7 +31428,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.21806609630585</v>
+        <v>1.21806621551514</v>
       </c>
       <c r="H1071" t="n">
         <v>7190</v>
@@ -31457,7 +31457,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.22643792629242</v>
+        <v>1.22643768787384</v>
       </c>
       <c r="H1072" t="n">
         <v>32047</v>
@@ -31573,7 +31573,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1076" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1076" t="n">
         <v>4446</v>
@@ -31602,7 +31602,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1077" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1077" t="n">
         <v>14683</v>
@@ -31631,7 +31631,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1078" t="n">
         <v>0</v>
@@ -31776,7 +31776,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1083" t="n">
         <v>14296</v>
@@ -31863,7 +31863,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1086" t="n">
         <v>3453</v>
@@ -32037,7 +32037,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.49432873725891</v>
+        <v>1.49432861804962</v>
       </c>
       <c r="H1092" t="n">
         <v>41559</v>
@@ -32095,7 +32095,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1094" t="n">
         <v>12106</v>
@@ -32182,7 +32182,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1097" t="n">
         <v>14855</v>
@@ -32385,7 +32385,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1104" t="n">
-        <v>1.48177123069763</v>
+        <v>1.48177134990692</v>
       </c>
       <c r="H1104" t="n">
         <v>20622</v>
@@ -32472,7 +32472,7 @@
         <v>1.75</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.46502816677094</v>
+        <v>1.46502804756165</v>
       </c>
       <c r="H1107" t="n">
         <v>13638</v>
@@ -32530,7 +32530,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.47339975833893</v>
+        <v>1.47339963912964</v>
       </c>
       <c r="H1109" t="n">
         <v>21164</v>
@@ -32559,7 +32559,7 @@
         <v>1.75</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.46502816677094</v>
+        <v>1.46502804756165</v>
       </c>
       <c r="H1110" t="n">
         <v>1267</v>
@@ -32588,7 +32588,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.48177123069763</v>
+        <v>1.48177134990692</v>
       </c>
       <c r="H1111" t="n">
         <v>1230</v>
@@ -32646,7 +32646,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.46084237098694</v>
+        <v>1.46084249019623</v>
       </c>
       <c r="H1113" t="n">
         <v>13864</v>
@@ -32704,7 +32704,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1115" t="n">
-        <v>1.49432873725891</v>
+        <v>1.49432861804962</v>
       </c>
       <c r="H1115" t="n">
         <v>14722</v>
@@ -32791,7 +32791,7 @@
         <v>1.75</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.46502816677094</v>
+        <v>1.46502804756165</v>
       </c>
       <c r="H1118" t="n">
         <v>2847</v>
@@ -32907,7 +32907,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.53618657588959</v>
+        <v>1.53618669509888</v>
       </c>
       <c r="H1122" t="n">
         <v>5260</v>
@@ -32936,7 +32936,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.53618657588959</v>
+        <v>1.53618669509888</v>
       </c>
       <c r="H1123" t="n">
         <v>0</v>
@@ -33081,7 +33081,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1128" t="n">
         <v>3000</v>
@@ -33110,7 +33110,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.48177123069763</v>
+        <v>1.48177134990692</v>
       </c>
       <c r="H1129" t="n">
         <v>5185</v>
@@ -33284,7 +33284,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.48177123069763</v>
+        <v>1.48177134990692</v>
       </c>
       <c r="H1135" t="n">
         <v>7144</v>
@@ -33313,7 +33313,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1136" t="n">
         <v>1370</v>
@@ -33487,7 +33487,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.47758543491364</v>
+        <v>1.47758555412292</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33632,7 +33632,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.47339975833893</v>
+        <v>1.47339963912964</v>
       </c>
       <c r="H1147" t="n">
         <v>7208</v>
@@ -33690,7 +33690,7 @@
         <v>1.7849999666214</v>
       </c>
       <c r="G1149" t="n">
-        <v>1.49432873725891</v>
+        <v>1.49432861804962</v>
       </c>
       <c r="H1149" t="n">
         <v>8805</v>
@@ -33893,7 +33893,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1156" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1156" t="n">
         <v>44600</v>
@@ -33922,7 +33922,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1157" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1157" t="n">
         <v>6271</v>
@@ -33951,7 +33951,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1158" t="n">
         <v>3500</v>
@@ -34009,7 +34009,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1160" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1160" t="n">
         <v>3250</v>
@@ -34125,7 +34125,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.381312251091</v>
+        <v>1.38131237030029</v>
       </c>
       <c r="H1164" t="n">
         <v>16170</v>
@@ -34183,7 +34183,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1166" t="n">
-        <v>1.44828498363495</v>
+        <v>1.44828510284424</v>
       </c>
       <c r="H1166" t="n">
         <v>13869</v>
@@ -34212,7 +34212,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.43572759628296</v>
+        <v>1.43572747707367</v>
       </c>
       <c r="H1167" t="n">
         <v>9615</v>
@@ -34270,7 +34270,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1169" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1171" t="n">
         <v>1810</v>
@@ -34357,7 +34357,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1172" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1172" t="n">
         <v>1394</v>
@@ -34386,7 +34386,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1173" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1173" t="n">
         <v>630</v>
@@ -34415,7 +34415,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1174" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1174" t="n">
         <v>10251</v>
@@ -34444,7 +34444,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1175" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1175" t="n">
         <v>6777</v>
@@ -34502,7 +34502,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1177" t="n">
         <v>250</v>
@@ -34560,7 +34560,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1179" t="n">
-        <v>1.44828498363495</v>
+        <v>1.44828510284424</v>
       </c>
       <c r="H1179" t="n">
         <v>10281</v>
@@ -34618,7 +34618,7 @@
         <v>1.72500002384186</v>
       </c>
       <c r="G1181" t="n">
-        <v>1.44409930706024</v>
+        <v>1.44409918785095</v>
       </c>
       <c r="H1181" t="n">
         <v>3066</v>
@@ -34647,7 +34647,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1182" t="n">
         <v>1326</v>
@@ -34676,7 +34676,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1183" t="n">
-        <v>1.44828498363495</v>
+        <v>1.44828510284424</v>
       </c>
       <c r="H1183" t="n">
         <v>5000</v>
@@ -34705,7 +34705,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1184" t="n">
         <v>3317</v>
@@ -34734,7 +34734,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1185" t="n">
         <v>14317</v>
@@ -34763,7 +34763,7 @@
         <v>1.72000002861023</v>
       </c>
       <c r="G1186" t="n">
-        <v>1.43991327285767</v>
+        <v>1.43991339206696</v>
       </c>
       <c r="H1186" t="n">
         <v>9963</v>
@@ -34792,7 +34792,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1187" t="n">
         <v>4762</v>
@@ -34821,7 +34821,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -35140,7 +35140,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1199" t="n">
         <v>45958</v>
@@ -35256,7 +35256,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.53618657588959</v>
+        <v>1.53618669509888</v>
       </c>
       <c r="H1203" t="n">
         <v>1151</v>
@@ -35285,7 +35285,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.53618657588959</v>
+        <v>1.53618669509888</v>
       </c>
       <c r="H1204" t="n">
         <v>1750</v>
@@ -35575,7 +35575,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1214" t="n">
-        <v>1.52781498432159</v>
+        <v>1.52781510353088</v>
       </c>
       <c r="H1214" t="n">
         <v>8499</v>
@@ -35662,7 +35662,7 @@
         <v>1.75</v>
       </c>
       <c r="G1217" t="n">
-        <v>1.46502816677094</v>
+        <v>1.46502804756165</v>
       </c>
       <c r="H1217" t="n">
         <v>21540</v>
@@ -35691,7 +35691,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1218" t="n">
         <v>6600</v>
@@ -35749,7 +35749,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.47339975833893</v>
+        <v>1.47339963912964</v>
       </c>
       <c r="H1220" t="n">
         <v>25475</v>
@@ -35836,7 +35836,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.41061270236969</v>
+        <v>1.41061282157898</v>
       </c>
       <c r="H1223" t="n">
         <v>3650</v>
@@ -35923,7 +35923,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1226" t="n">
-        <v>1.3980553150177</v>
+        <v>1.39805543422699</v>
       </c>
       <c r="H1226" t="n">
         <v>10270</v>
@@ -36039,7 +36039,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1230" t="n">
         <v>17178</v>
@@ -36126,7 +36126,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.44828498363495</v>
+        <v>1.44828510284424</v>
       </c>
       <c r="H1233" t="n">
         <v>1800</v>
@@ -36155,7 +36155,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.42317032814026</v>
+        <v>1.42317008972168</v>
       </c>
       <c r="H1234" t="n">
         <v>57052</v>
@@ -36271,7 +36271,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.43572759628296</v>
+        <v>1.43572747707367</v>
       </c>
       <c r="H1238" t="n">
         <v>5018</v>
@@ -36358,7 +36358,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.47339975833893</v>
+        <v>1.47339963912964</v>
       </c>
       <c r="H1241" t="n">
         <v>14984</v>
@@ -36416,7 +36416,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.53618657588959</v>
+        <v>1.53618669509888</v>
       </c>
       <c r="H1243" t="n">
         <v>3672</v>
@@ -36503,7 +36503,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1246" t="n">
         <v>35710</v>
@@ -36619,7 +36619,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1250" t="n">
         <v>22196</v>
@@ -36677,7 +36677,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1252" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1252" t="n">
         <v>22429</v>
@@ -36706,7 +36706,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1253" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1253" t="n">
         <v>11120</v>
@@ -36880,7 +36880,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1259" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1259" t="n">
         <v>23378</v>
@@ -36938,7 +36938,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1261" t="n">
         <v>23239</v>
@@ -36967,7 +36967,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.6492030620575</v>
+        <v>1.64920318126678</v>
       </c>
       <c r="H1262" t="n">
         <v>23031</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1263" t="n">
         <v>31133</v>
@@ -37025,7 +37025,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1264" t="n">
         <v>22054</v>
@@ -37141,7 +37141,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1268" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1268" t="n">
         <v>17615</v>
@@ -37199,7 +37199,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1270" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1270" t="n">
         <v>13263</v>
@@ -37228,7 +37228,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1271" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1271" t="n">
         <v>17035</v>
@@ -37286,7 +37286,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1273" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1273" t="n">
         <v>7377</v>
@@ -37373,7 +37373,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.61153101921082</v>
+        <v>1.61153090000153</v>
       </c>
       <c r="H1276" t="n">
         <v>7499</v>
@@ -37402,7 +37402,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1277" t="n">
         <v>15301</v>
@@ -37605,7 +37605,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1284" t="n">
         <v>15439</v>
@@ -38098,7 +38098,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1301" t="n">
         <v>6655</v>
@@ -38301,7 +38301,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1308" t="n">
-        <v>1.52781498432159</v>
+        <v>1.52781510353088</v>
       </c>
       <c r="H1308" t="n">
         <v>5727</v>
@@ -38765,7 +38765,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1324" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1324" t="n">
         <v>5020</v>
@@ -38823,7 +38823,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1326" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1326" t="n">
         <v>4660</v>
@@ -38852,7 +38852,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1327" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1327" t="n">
         <v>2570</v>
@@ -38881,7 +38881,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1328" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1328" t="n">
         <v>0</v>
@@ -38910,7 +38910,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1329" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1329" t="n">
         <v>50</v>
@@ -39142,7 +39142,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1337" t="n">
         <v>1010</v>
@@ -39200,7 +39200,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1339" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1339" t="n">
         <v>14985</v>
@@ -39287,7 +39287,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61153101921082</v>
+        <v>1.61153090000153</v>
       </c>
       <c r="H1342" t="n">
         <v>5805</v>
@@ -39345,7 +39345,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.65757465362549</v>
+        <v>1.65757477283478</v>
       </c>
       <c r="H1344" t="n">
         <v>11108</v>
@@ -39374,7 +39374,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1345" t="n">
         <v>43701</v>
@@ -39403,7 +39403,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1346" t="n">
         <v>31092</v>
@@ -39461,7 +39461,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1348" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1348" t="n">
         <v>3276</v>
@@ -39490,7 +39490,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1349" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1349" t="n">
         <v>1</v>
@@ -39577,7 +39577,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1352" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1352" t="n">
         <v>1068</v>
@@ -39664,7 +39664,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1355" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1355" t="n">
         <v>1297</v>
@@ -39809,7 +39809,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1360" t="n">
-        <v>1.55711555480957</v>
+        <v>1.55711567401886</v>
       </c>
       <c r="H1360" t="n">
         <v>3538</v>
@@ -40012,7 +40012,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1367" t="n">
         <v>1000</v>
@@ -40128,7 +40128,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1371" t="n">
         <v>10437</v>
@@ -40186,7 +40186,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1373" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1373" t="n">
         <v>3457</v>
@@ -40215,7 +40215,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1374" t="n">
         <v>27312</v>
@@ -40244,7 +40244,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1375" t="n">
         <v>3283</v>
@@ -40389,7 +40389,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.61153101921082</v>
+        <v>1.61153090000153</v>
       </c>
       <c r="H1380" t="n">
         <v>4607</v>
@@ -40418,7 +40418,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.61153101921082</v>
+        <v>1.61153090000153</v>
       </c>
       <c r="H1381" t="n">
         <v>7296</v>
@@ -40447,7 +40447,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.61153101921082</v>
+        <v>1.61153090000153</v>
       </c>
       <c r="H1382" t="n">
         <v>400</v>
@@ -40476,7 +40476,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1383" t="n">
         <v>3336</v>
@@ -40563,7 +40563,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1386" t="n">
         <v>3693</v>
@@ -40592,7 +40592,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1387" t="n">
         <v>2849</v>
@@ -40650,7 +40650,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1389" t="n">
         <v>12896</v>
@@ -40679,7 +40679,7 @@
         <v>1.95500004291534</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.63664567470551</v>
+        <v>1.63664579391479</v>
       </c>
       <c r="H1390" t="n">
         <v>38449</v>
@@ -40766,7 +40766,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1393" t="n">
         <v>9710</v>
@@ -40795,7 +40795,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.59897351264954</v>
+        <v>1.59897339344025</v>
       </c>
       <c r="H1394" t="n">
         <v>30509</v>
@@ -41085,7 +41085,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1404" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1404" t="n">
         <v>14917</v>
@@ -41114,7 +41114,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1405" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1405" t="n">
         <v>5227</v>
@@ -41201,7 +41201,7 @@
         <v>1.875</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.56967294216156</v>
+        <v>1.56967282295227</v>
       </c>
       <c r="H1408" t="n">
         <v>5807</v>
@@ -41230,7 +41230,7 @@
         <v>1.82500004768372</v>
       </c>
       <c r="G1409" t="n">
-        <v>1.52781498432159</v>
+        <v>1.52781510353088</v>
       </c>
       <c r="H1409" t="n">
         <v>19356</v>
@@ -41317,7 +41317,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1412" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1412" t="n">
         <v>12042</v>
@@ -41375,7 +41375,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1414" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1414" t="n">
         <v>1024</v>
@@ -41433,7 +41433,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1416" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1416" t="n">
         <v>5452</v>
@@ -41549,7 +41549,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1420" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1420" t="n">
         <v>1840</v>
@@ -41636,7 +41636,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G1423" t="n">
-        <v>1.58223032951355</v>
+        <v>1.58223044872284</v>
       </c>
       <c r="H1423" t="n">
         <v>80</v>
@@ -41955,7 +41955,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1434" t="n">
-        <v>1.56548726558685</v>
+        <v>1.56548714637756</v>
       </c>
       <c r="H1434" t="n">
         <v>37169</v>
@@ -41984,7 +41984,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1435" t="n">
-        <v>1.60734498500824</v>
+        <v>1.60734510421753</v>
       </c>
       <c r="H1435" t="n">
         <v>3753</v>
@@ -42187,7 +42187,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1442" t="n">
-        <v>1.66594636440277</v>
+        <v>1.66594624519348</v>
       </c>
       <c r="H1442" t="n">
         <v>21374</v>
@@ -42332,7 +42332,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.74966216087341</v>
+        <v>1.74966204166412</v>
       </c>
       <c r="H1447" t="n">
         <v>9597</v>
@@ -42419,7 +42419,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G1450" t="n">
-        <v>1.76640510559082</v>
+        <v>1.76640522480011</v>
       </c>
       <c r="H1450" t="n">
         <v>11352</v>
@@ -42477,7 +42477,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G1452" t="n">
-        <v>2.41101789474487</v>
+        <v>2.41101765632629</v>
       </c>
       <c r="H1452" t="n">
         <v>538492</v>
@@ -42535,7 +42535,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.76262450218201</v>
+        <v>2.76262474060059</v>
       </c>
       <c r="H1454" t="n">
         <v>741208</v>
@@ -42651,7 +42651,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G1458" t="n">
-        <v>3.21468997001648</v>
+        <v>3.21469020843506</v>
       </c>
       <c r="H1458" t="n">
         <v>296859</v>
@@ -42709,7 +42709,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.92168474197388</v>
+        <v>2.92168498039246</v>
       </c>
       <c r="H1460" t="n">
         <v>253906</v>
@@ -42738,7 +42738,7 @@
         <v>3.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>2.93005633354187</v>
+        <v>2.93005609512329</v>
       </c>
       <c r="H1461" t="n">
         <v>77423</v>
@@ -42796,7 +42796,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.84634065628052</v>
+        <v>2.84634017944336</v>
       </c>
       <c r="H1463" t="n">
         <v>169786</v>
@@ -42912,7 +42912,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.19794702529907</v>
+        <v>3.19794678688049</v>
       </c>
       <c r="H1467" t="n">
         <v>416520</v>
@@ -42970,7 +42970,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1469" t="n">
-        <v>3.30677771568298</v>
+        <v>3.30677795410156</v>
       </c>
       <c r="H1469" t="n">
         <v>331715</v>
@@ -42999,7 +42999,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1470" t="n">
-        <v>3.33189272880554</v>
+        <v>3.33189249038696</v>
       </c>
       <c r="H1470" t="n">
         <v>150632</v>
@@ -43086,7 +43086,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.19794702529907</v>
+        <v>3.19794678688049</v>
       </c>
       <c r="H1473" t="n">
         <v>44985</v>
@@ -43115,7 +43115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G1474" t="n">
-        <v>3.1644606590271</v>
+        <v>3.16446089744568</v>
       </c>
       <c r="H1474" t="n">
         <v>31963</v>
@@ -43144,7 +43144,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1475" t="n">
-        <v>3.30677771568298</v>
+        <v>3.30677795410156</v>
       </c>
       <c r="H1475" t="n">
         <v>139109</v>
@@ -43173,7 +43173,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1476" t="n">
-        <v>3.33189272880554</v>
+        <v>3.33189249038696</v>
       </c>
       <c r="H1476" t="n">
         <v>93362</v>
@@ -43260,7 +43260,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.19794702529907</v>
+        <v>3.19794678688049</v>
       </c>
       <c r="H1479" t="n">
         <v>32517</v>
@@ -43318,7 +43318,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1481" t="n">
-        <v>3.11423110961914</v>
+        <v>3.11423134803772</v>
       </c>
       <c r="H1481" t="n">
         <v>34370</v>
@@ -43347,7 +43347,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1482" t="n">
-        <v>3.05562996864319</v>
+        <v>3.05563020706177</v>
       </c>
       <c r="H1482" t="n">
         <v>24371</v>
@@ -43492,7 +43492,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1487" t="n">
-        <v>2.98865747451782</v>
+        <v>2.98865723609924</v>
       </c>
       <c r="H1487" t="n">
         <v>12827</v>
@@ -43579,7 +43579,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1490" t="n">
         <v>34442</v>
@@ -43608,7 +43608,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1491" t="n">
-        <v>3.05562996864319</v>
+        <v>3.05563020706177</v>
       </c>
       <c r="H1491" t="n">
         <v>21800</v>
@@ -43666,7 +43666,7 @@
         <v>3.5</v>
       </c>
       <c r="G1493" t="n">
-        <v>2.93005633354187</v>
+        <v>2.93005609512329</v>
       </c>
       <c r="H1493" t="n">
         <v>28534</v>
@@ -43724,7 +43724,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1495" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1495" t="n">
         <v>21670</v>
@@ -43753,7 +43753,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1496" t="n">
-        <v>2.88819861412048</v>
+        <v>2.8881983757019</v>
       </c>
       <c r="H1496" t="n">
         <v>20557</v>
@@ -43782,7 +43782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H1497" t="n">
         <v>25116</v>
@@ -43811,7 +43811,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1498" t="n">
-        <v>2.88819861412048</v>
+        <v>2.8881983757019</v>
       </c>
       <c r="H1498" t="n">
         <v>30724</v>
@@ -43956,7 +43956,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.87145519256592</v>
+        <v>2.87145495414734</v>
       </c>
       <c r="H1503" t="n">
         <v>83064</v>
@@ -44043,7 +44043,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1506" t="n">
         <v>12699</v>
@@ -44072,7 +44072,7 @@
         <v>3.5</v>
       </c>
       <c r="G1507" t="n">
-        <v>2.93005633354187</v>
+        <v>2.93005609512329</v>
       </c>
       <c r="H1507" t="n">
         <v>19593</v>
@@ -44101,7 +44101,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1508" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1508" t="n">
         <v>20064</v>
@@ -44130,7 +44130,7 @@
         <v>3.5</v>
       </c>
       <c r="G1509" t="n">
-        <v>2.93005633354187</v>
+        <v>2.93005609512329</v>
       </c>
       <c r="H1509" t="n">
         <v>44031</v>
@@ -44159,7 +44159,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1510" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1510" t="n">
         <v>10718</v>
@@ -44217,7 +44217,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H1512" t="n">
         <v>5516</v>
@@ -44246,7 +44246,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1513" t="n">
-        <v>2.88819861412048</v>
+        <v>2.8881983757019</v>
       </c>
       <c r="H1513" t="n">
         <v>12031</v>
@@ -44304,7 +44304,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G1515" t="n">
-        <v>2.88819861412048</v>
+        <v>2.8881983757019</v>
       </c>
       <c r="H1515" t="n">
         <v>6455</v>
@@ -44478,7 +44478,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H1521" t="n">
         <v>168387</v>
@@ -44507,7 +44507,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.87145519256592</v>
+        <v>2.87145495414734</v>
       </c>
       <c r="H1522" t="n">
         <v>65356</v>
@@ -44536,7 +44536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.84634065628052</v>
+        <v>2.84634017944336</v>
       </c>
       <c r="H1523" t="n">
         <v>24638</v>
@@ -44565,7 +44565,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1524" t="n">
         <v>14377</v>
@@ -44681,7 +44681,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1528" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1528" t="n">
         <v>34392</v>
@@ -44710,7 +44710,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1529" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1529" t="n">
         <v>28915</v>
@@ -44768,7 +44768,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1531" t="n">
         <v>78995</v>
@@ -44884,7 +44884,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G1535" t="n">
-        <v>2.7961106300354</v>
+        <v>2.79611086845398</v>
       </c>
       <c r="H1535" t="n">
         <v>18646</v>
@@ -45145,7 +45145,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1544" t="n">
         <v>11428</v>
@@ -45174,7 +45174,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1545" t="n">
         <v>22323</v>
@@ -45203,7 +45203,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1546" t="n">
         <v>16840</v>
@@ -45232,7 +45232,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G1547" t="n">
-        <v>2.53659129142761</v>
+        <v>2.53659152984619</v>
       </c>
       <c r="H1547" t="n">
         <v>20002</v>
@@ -45348,7 +45348,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.58682107925415</v>
+        <v>2.58682084083557</v>
       </c>
       <c r="H1551" t="n">
         <v>3392</v>
@@ -45464,7 +45464,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G1555" t="n">
-        <v>2.52821969985962</v>
+        <v>2.5282199382782</v>
       </c>
       <c r="H1555" t="n">
         <v>3108</v>
@@ -45609,7 +45609,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.87145519256592</v>
+        <v>2.87145495414734</v>
       </c>
       <c r="H1560" t="n">
         <v>68265</v>
@@ -45638,7 +45638,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.84634065628052</v>
+        <v>2.84634017944336</v>
       </c>
       <c r="H1561" t="n">
         <v>65014</v>
@@ -45754,7 +45754,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1565" t="n">
-        <v>4.52065849304199</v>
+        <v>4.52065801620483</v>
       </c>
       <c r="H1565" t="n">
         <v>526424</v>
@@ -45783,7 +45783,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.95139026641846</v>
+        <v>3.95139050483704</v>
       </c>
       <c r="H1566" t="n">
         <v>546808</v>
@@ -45812,7 +45812,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G1567" t="n">
-        <v>4.82203578948975</v>
+        <v>4.82203531265259</v>
       </c>
       <c r="H1567" t="n">
         <v>1195642</v>
@@ -45870,7 +45870,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G1569" t="n">
-        <v>4.52065849304199</v>
+        <v>4.52065801620483</v>
       </c>
       <c r="H1569" t="n">
         <v>627344</v>
@@ -45899,7 +45899,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1570" t="n">
-        <v>4.11882209777832</v>
+        <v>4.11882162094116</v>
       </c>
       <c r="H1570" t="n">
         <v>670103</v>
@@ -45928,7 +45928,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1571" t="n">
-        <v>3.30677771568298</v>
+        <v>3.30677795410156</v>
       </c>
       <c r="H1571" t="n">
         <v>877685</v>
@@ -46015,7 +46015,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.49095296859741</v>
+        <v>3.49095273017883</v>
       </c>
       <c r="H1574" t="n">
         <v>561178</v>
@@ -46044,7 +46044,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G1575" t="n">
-        <v>3.61652684211731</v>
+        <v>3.61652660369873</v>
       </c>
       <c r="H1575" t="n">
         <v>562506</v>
@@ -46073,7 +46073,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.42398023605347</v>
+        <v>3.42397999763489</v>
       </c>
       <c r="H1576" t="n">
         <v>290905</v>
@@ -46102,7 +46102,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.19794702529907</v>
+        <v>3.19794678688049</v>
       </c>
       <c r="H1577" t="n">
         <v>465196</v>
@@ -46160,7 +46160,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1579" t="n">
         <v>675453</v>
@@ -46189,7 +46189,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1580" t="n">
-        <v>2.8965699672699</v>
+        <v>2.89657020568848</v>
       </c>
       <c r="H1580" t="n">
         <v>553663</v>
@@ -46218,7 +46218,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1581" t="n">
         <v>200040</v>
@@ -46247,7 +46247,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1582" t="n">
-        <v>2.8965699672699</v>
+        <v>2.89657020568848</v>
       </c>
       <c r="H1582" t="n">
         <v>207104</v>
@@ -46334,7 +46334,7 @@
         <v>3.5</v>
       </c>
       <c r="G1585" t="n">
-        <v>2.93005633354187</v>
+        <v>2.93005609512329</v>
       </c>
       <c r="H1585" t="n">
         <v>582269</v>
@@ -46363,7 +46363,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.92168474197388</v>
+        <v>2.92168498039246</v>
       </c>
       <c r="H1586" t="n">
         <v>389966</v>
@@ -46392,7 +46392,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1587" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1587" t="n">
         <v>115647</v>
@@ -46450,7 +46450,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.42398023605347</v>
+        <v>3.42397999763489</v>
       </c>
       <c r="H1589" t="n">
         <v>574866</v>
@@ -46508,7 +46508,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G1591" t="n">
-        <v>3.30677771568298</v>
+        <v>3.30677795410156</v>
       </c>
       <c r="H1591" t="n">
         <v>631090</v>
@@ -46537,7 +46537,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.40723729133606</v>
+        <v>3.4072368144989</v>
       </c>
       <c r="H1592" t="n">
         <v>255356</v>
@@ -46595,7 +46595,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G1594" t="n">
-        <v>3.31514930725098</v>
+        <v>3.31514954566956</v>
       </c>
       <c r="H1594" t="n">
         <v>186800</v>
@@ -46682,7 +46682,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.28166317939758</v>
+        <v>3.281662940979</v>
       </c>
       <c r="H1597" t="n">
         <v>105117</v>
@@ -46711,7 +46711,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G1598" t="n">
-        <v>3.27329134941101</v>
+        <v>3.27329158782959</v>
       </c>
       <c r="H1598" t="n">
         <v>72989</v>
@@ -46798,7 +46798,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1601" t="n">
-        <v>3.11423110961914</v>
+        <v>3.11423134803772</v>
       </c>
       <c r="H1601" t="n">
         <v>70662</v>
@@ -46885,7 +46885,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1604" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1604" t="n">
         <v>98829</v>
@@ -47001,7 +47001,7 @@
         <v>3.97000002861023</v>
       </c>
       <c r="G1608" t="n">
-        <v>3.32352113723755</v>
+        <v>3.32352089881897</v>
       </c>
       <c r="H1608" t="n">
         <v>573253</v>
@@ -47030,7 +47030,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G1609" t="n">
-        <v>3.33189272880554</v>
+        <v>3.33189249038696</v>
       </c>
       <c r="H1609" t="n">
         <v>186704</v>
@@ -47088,7 +47088,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.28166317939758</v>
+        <v>3.281662940979</v>
       </c>
       <c r="H1611" t="n">
         <v>189409</v>
@@ -47117,7 +47117,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.22306203842163</v>
+        <v>3.22306180000305</v>
       </c>
       <c r="H1612" t="n">
         <v>80841</v>
@@ -47175,7 +47175,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G1614" t="n">
-        <v>3.05562996864319</v>
+        <v>3.05563020706177</v>
       </c>
       <c r="H1614" t="n">
         <v>154159</v>
@@ -47378,7 +47378,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G1621" t="n">
-        <v>3.13097453117371</v>
+        <v>3.13097429275513</v>
       </c>
       <c r="H1621" t="n">
         <v>28396</v>
@@ -47436,7 +47436,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G1623" t="n">
-        <v>3.11423110961914</v>
+        <v>3.11423134803772</v>
       </c>
       <c r="H1623" t="n">
         <v>30281</v>
@@ -47523,7 +47523,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1626" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1626" t="n">
         <v>57019</v>
@@ -47610,7 +47610,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1629" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1629" t="n">
         <v>96173</v>
@@ -47639,7 +47639,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1630" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1630" t="n">
         <v>52093</v>
@@ -47668,7 +47668,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1631" t="n">
-        <v>2.98865747451782</v>
+        <v>2.98865723609924</v>
       </c>
       <c r="H1631" t="n">
         <v>79758</v>
@@ -47697,7 +47697,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1632" t="n">
         <v>30748</v>
@@ -47726,7 +47726,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H1633" t="n">
         <v>86464</v>
@@ -47755,7 +47755,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.92168474197388</v>
+        <v>2.92168498039246</v>
       </c>
       <c r="H1634" t="n">
         <v>30432</v>
@@ -47784,7 +47784,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1635" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1635" t="n">
         <v>29252</v>
@@ -47813,7 +47813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.84634065628052</v>
+        <v>2.84634017944336</v>
       </c>
       <c r="H1636" t="n">
         <v>53802</v>
@@ -47871,7 +47871,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.76262450218201</v>
+        <v>2.76262474060059</v>
       </c>
       <c r="H1638" t="n">
         <v>39341</v>
@@ -47929,7 +47929,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.43613219261169</v>
+        <v>2.43613243103027</v>
       </c>
       <c r="H1640" t="n">
         <v>96756</v>
@@ -47958,7 +47958,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G1641" t="n">
-        <v>2.54496335983276</v>
+        <v>2.54496312141418</v>
       </c>
       <c r="H1641" t="n">
         <v>35144</v>
@@ -47987,7 +47987,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G1642" t="n">
-        <v>2.60356426239014</v>
+        <v>2.60356402397156</v>
       </c>
       <c r="H1642" t="n">
         <v>89746</v>
@@ -48045,7 +48045,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G1644" t="n">
-        <v>2.96354246139526</v>
+        <v>2.96354269981384</v>
       </c>
       <c r="H1644" t="n">
         <v>451229</v>
@@ -48132,7 +48132,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H1647" t="n">
         <v>72225</v>
@@ -48190,7 +48190,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1649" t="n">
         <v>79190</v>
@@ -48248,7 +48248,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.95517086982727</v>
+        <v>2.95517110824585</v>
       </c>
       <c r="H1651" t="n">
         <v>43598</v>
@@ -48277,7 +48277,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.94679951667786</v>
+        <v>2.94679927825928</v>
       </c>
       <c r="H1652" t="n">
         <v>45483</v>
@@ -48306,7 +48306,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.82122540473938</v>
+        <v>2.82122564315796</v>
       </c>
       <c r="H1653" t="n">
         <v>83540</v>
@@ -48335,7 +48335,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1654" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1654" t="n">
         <v>52814</v>
@@ -48480,7 +48480,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1659" t="n">
-        <v>2.8965699672699</v>
+        <v>2.89657020568848</v>
       </c>
       <c r="H1659" t="n">
         <v>97311</v>
@@ -48509,7 +48509,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G1660" t="n">
-        <v>2.98865747451782</v>
+        <v>2.98865723609924</v>
       </c>
       <c r="H1660" t="n">
         <v>75389</v>
@@ -48625,7 +48625,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G1664" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982678413391</v>
       </c>
       <c r="H1664" t="n">
         <v>40532</v>
@@ -48654,7 +48654,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1665" t="n">
-        <v>2.87982654571533</v>
+        <v>2.87982702255249</v>
       </c>
       <c r="H1665" t="n">
         <v>58822</v>
@@ -48828,7 +48828,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.88832187652588</v>
+        <v>2.8883216381073</v>
       </c>
       <c r="H1671" t="n">
         <v>65798</v>
@@ -48915,7 +48915,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1674" t="n">
-        <v>2.93929219245911</v>
+        <v>2.93929243087769</v>
       </c>
       <c r="H1674" t="n">
         <v>48233</v>
@@ -48973,7 +48973,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1676" t="n">
-        <v>2.93929219245911</v>
+        <v>2.93929243087769</v>
       </c>
       <c r="H1676" t="n">
         <v>24885</v>
@@ -49002,7 +49002,7 @@
         <v>3.5</v>
       </c>
       <c r="G1677" t="n">
-        <v>2.97327256202698</v>
+        <v>2.9732723236084</v>
       </c>
       <c r="H1677" t="n">
         <v>12727</v>
@@ -49060,7 +49060,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1679" t="n">
-        <v>2.93929219245911</v>
+        <v>2.93929243087769</v>
       </c>
       <c r="H1679" t="n">
         <v>40914</v>
@@ -49176,7 +49176,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1683" t="n">
-        <v>2.90531206130981</v>
+        <v>2.90531182289124</v>
       </c>
       <c r="H1683" t="n">
         <v>11160</v>
@@ -49234,7 +49234,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1685" t="n">
-        <v>2.90531206130981</v>
+        <v>2.90531182289124</v>
       </c>
       <c r="H1685" t="n">
         <v>19562</v>
@@ -49263,7 +49263,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.0582230091095</v>
+        <v>3.05822277069092</v>
       </c>
       <c r="H1686" t="n">
         <v>218592</v>
@@ -49350,7 +49350,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.4659857749939</v>
+        <v>3.46598601341248</v>
       </c>
       <c r="H1689" t="n">
         <v>381731</v>
@@ -49437,7 +49437,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1692" t="n">
-        <v>3.28758978843689</v>
+        <v>3.28758955001831</v>
       </c>
       <c r="H1692" t="n">
         <v>151875</v>
@@ -49582,7 +49582,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G1697" t="n">
-        <v>2.93929219245911</v>
+        <v>2.93929243087769</v>
       </c>
       <c r="H1697" t="n">
         <v>90502</v>
@@ -49640,7 +49640,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G1699" t="n">
-        <v>3.44050121307373</v>
+        <v>3.44050097465515</v>
       </c>
       <c r="H1699" t="n">
         <v>509584</v>
@@ -49669,7 +49669,7 @@
         <v>3.75</v>
       </c>
       <c r="G1700" t="n">
-        <v>3.18564915657043</v>
+        <v>3.18564891815186</v>
       </c>
       <c r="H1700" t="n">
         <v>347311</v>
@@ -49698,7 +49698,7 @@
         <v>3.5</v>
       </c>
       <c r="G1701" t="n">
-        <v>2.97327256202698</v>
+        <v>2.9732723236084</v>
       </c>
       <c r="H1701" t="n">
         <v>257017</v>
@@ -49843,7 +49843,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.17473649978638</v>
+        <v>2.1747362613678</v>
       </c>
       <c r="H1706" t="n">
         <v>366493</v>
@@ -49959,7 +49959,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.9963401556015</v>
+        <v>1.99634003639221</v>
       </c>
       <c r="H1710" t="n">
         <v>105794</v>
@@ -50017,7 +50017,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1712" t="n">
-        <v>1.96235954761505</v>
+        <v>1.96235978603363</v>
       </c>
       <c r="H1712" t="n">
         <v>46635</v>
@@ -50162,7 +50162,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.73299288749695</v>
+        <v>1.73299300670624</v>
       </c>
       <c r="H1717" t="n">
         <v>96639</v>
@@ -50191,7 +50191,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.78396344184875</v>
+        <v>1.78396320343018</v>
       </c>
       <c r="H1718" t="n">
         <v>89845</v>
@@ -50220,7 +50220,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1719" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1719" t="n">
         <v>654901</v>
@@ -50249,7 +50249,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.08978581428528</v>
+        <v>2.0897855758667</v>
       </c>
       <c r="H1720" t="n">
         <v>584054</v>
@@ -50307,7 +50307,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1722" t="n">
         <v>97215</v>
@@ -50336,7 +50336,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1723" t="n">
-        <v>1.95386493206024</v>
+        <v>1.95386457443237</v>
       </c>
       <c r="H1723" t="n">
         <v>113866</v>
@@ -50423,7 +50423,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.86891412734985</v>
+        <v>1.86891400814056</v>
       </c>
       <c r="H1726" t="n">
         <v>90364</v>
@@ -50510,7 +50510,7 @@
         <v>2.25</v>
       </c>
       <c r="G1729" t="n">
-        <v>1.91138958930969</v>
+        <v>1.91138935089111</v>
       </c>
       <c r="H1729" t="n">
         <v>45578</v>
@@ -50539,7 +50539,7 @@
         <v>2.25</v>
       </c>
       <c r="G1730" t="n">
-        <v>1.91138958930969</v>
+        <v>1.91138935089111</v>
       </c>
       <c r="H1730" t="n">
         <v>37910</v>
@@ -50568,7 +50568,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1731" t="n">
-        <v>1.91988432407379</v>
+        <v>1.91988456249237</v>
       </c>
       <c r="H1731" t="n">
         <v>17035</v>
@@ -50597,7 +50597,7 @@
         <v>2.25</v>
       </c>
       <c r="G1732" t="n">
-        <v>1.91138958930969</v>
+        <v>1.91138935089111</v>
       </c>
       <c r="H1732" t="n">
         <v>12771</v>
@@ -50713,7 +50713,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1736" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1736" t="n">
         <v>311763</v>
@@ -50742,7 +50742,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1737" t="n">
-        <v>2.18323135375977</v>
+        <v>2.18323159217834</v>
       </c>
       <c r="H1737" t="n">
         <v>269240</v>
@@ -50771,7 +50771,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1738" t="n">
-        <v>2.18323135375977</v>
+        <v>2.18323159217834</v>
       </c>
       <c r="H1738" t="n">
         <v>93399</v>
@@ -50829,7 +50829,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1740" t="n">
-        <v>2.10677599906921</v>
+        <v>2.10677576065063</v>
       </c>
       <c r="H1740" t="n">
         <v>77397</v>
@@ -51148,7 +51148,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1751" t="n">
-        <v>2.29366707801819</v>
+        <v>2.29366731643677</v>
       </c>
       <c r="H1751" t="n">
         <v>19554</v>
@@ -51206,7 +51206,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1753" t="n">
-        <v>2.20871663093567</v>
+        <v>2.20871639251709</v>
       </c>
       <c r="H1753" t="n">
         <v>81078</v>
@@ -51235,7 +51235,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1754" t="n">
-        <v>2.20871663093567</v>
+        <v>2.20871639251709</v>
       </c>
       <c r="H1754" t="n">
         <v>18399</v>
@@ -51264,7 +51264,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1755" t="n">
-        <v>2.21721172332764</v>
+        <v>2.21721148490906</v>
       </c>
       <c r="H1755" t="n">
         <v>22329</v>
@@ -51293,7 +51293,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1756" t="n">
-        <v>2.29366707801819</v>
+        <v>2.29366731643677</v>
       </c>
       <c r="H1756" t="n">
         <v>182118</v>
@@ -51322,7 +51322,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1757" t="n">
-        <v>2.29366707801819</v>
+        <v>2.29366731643677</v>
       </c>
       <c r="H1757" t="n">
         <v>86507</v>
@@ -51351,7 +51351,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1758" t="n">
-        <v>2.2851722240448</v>
+        <v>2.28517246246338</v>
       </c>
       <c r="H1758" t="n">
         <v>44903</v>
@@ -51496,7 +51496,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1763" t="n">
-        <v>2.29366707801819</v>
+        <v>2.29366731643677</v>
       </c>
       <c r="H1763" t="n">
         <v>11345</v>
@@ -51583,7 +51583,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.25119185447693</v>
+        <v>2.25119209289551</v>
       </c>
       <c r="H1766" t="n">
         <v>12158</v>
@@ -51670,7 +51670,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1769" t="n">
-        <v>2.2851722240448</v>
+        <v>2.28517246246338</v>
       </c>
       <c r="H1769" t="n">
         <v>24964</v>
@@ -51786,7 +51786,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.25119185447693</v>
+        <v>2.25119209289551</v>
       </c>
       <c r="H1773" t="n">
         <v>27318</v>
@@ -51844,7 +51844,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1775" t="n">
-        <v>2.16624140739441</v>
+        <v>2.16624116897583</v>
       </c>
       <c r="H1775" t="n">
         <v>6560</v>
@@ -51873,7 +51873,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1776" t="n">
-        <v>2.2851722240448</v>
+        <v>2.28517246246338</v>
       </c>
       <c r="H1776" t="n">
         <v>94121</v>
@@ -51931,7 +51931,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1778" t="n">
-        <v>2.18323135375977</v>
+        <v>2.18323159217834</v>
       </c>
       <c r="H1778" t="n">
         <v>13462</v>
@@ -51960,7 +51960,7 @@
         <v>2.5</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1779" t="n">
         <v>29760</v>
@@ -52250,7 +52250,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1789" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1789" t="n">
         <v>17133</v>
@@ -52279,7 +52279,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1790" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1790" t="n">
         <v>5538</v>
@@ -52424,7 +52424,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1795" t="n">
-        <v>2.10677599906921</v>
+        <v>2.10677576065063</v>
       </c>
       <c r="H1795" t="n">
         <v>22805</v>
@@ -52511,7 +52511,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1798" t="n">
         <v>42993</v>
@@ -52540,7 +52540,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1799" t="n">
         <v>27831</v>
@@ -52656,7 +52656,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.08129048347473</v>
+        <v>2.08129072189331</v>
       </c>
       <c r="H1803" t="n">
         <v>42223</v>
@@ -52801,7 +52801,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1808" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1808" t="n">
         <v>82605</v>
@@ -52830,7 +52830,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1809" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1809" t="n">
         <v>21588</v>
@@ -52859,7 +52859,7 @@
         <v>2.5</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1810" t="n">
         <v>28956</v>
@@ -52888,7 +52888,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1811" t="n">
-        <v>2.16624140739441</v>
+        <v>2.16624116897583</v>
       </c>
       <c r="H1811" t="n">
         <v>38473</v>
@@ -52917,7 +52917,7 @@
         <v>2.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1812" t="n">
         <v>92455</v>
@@ -52975,7 +52975,7 @@
         <v>2.5</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1814" t="n">
         <v>14815</v>
@@ -53004,7 +53004,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.08978581428528</v>
+        <v>2.0897855758667</v>
       </c>
       <c r="H1815" t="n">
         <v>22485</v>
@@ -53062,7 +53062,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1817" t="n">
-        <v>2.10677599906921</v>
+        <v>2.10677576065063</v>
       </c>
       <c r="H1817" t="n">
         <v>5685</v>
@@ -53091,7 +53091,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.04731059074402</v>
+        <v>2.04731035232544</v>
       </c>
       <c r="H1818" t="n">
         <v>43768</v>
@@ -53120,7 +53120,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1819" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1819" t="n">
         <v>18947</v>
@@ -53178,7 +53178,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1821" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1821" t="n">
         <v>17663</v>
@@ -53323,7 +53323,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1826" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1826" t="n">
         <v>25217</v>
@@ -53352,7 +53352,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1827" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1827" t="n">
         <v>5710</v>
@@ -53381,7 +53381,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.08129048347473</v>
+        <v>2.08129072189331</v>
       </c>
       <c r="H1828" t="n">
         <v>40153</v>
@@ -53410,7 +53410,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.08978581428528</v>
+        <v>2.0897855758667</v>
       </c>
       <c r="H1829" t="n">
         <v>10052</v>
@@ -53439,7 +53439,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1830" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1830" t="n">
         <v>10430</v>
@@ -53497,7 +53497,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1832" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1832" t="n">
         <v>22542</v>
@@ -53642,7 +53642,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1837" t="n">
-        <v>1.91988432407379</v>
+        <v>1.91988456249237</v>
       </c>
       <c r="H1837" t="n">
         <v>78372</v>
@@ -53671,7 +53671,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.86891412734985</v>
+        <v>1.86891400814056</v>
       </c>
       <c r="H1838" t="n">
         <v>73492</v>
@@ -53729,7 +53729,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1840" t="n">
-        <v>1.93687462806702</v>
+        <v>1.93687450885773</v>
       </c>
       <c r="H1840" t="n">
         <v>5321</v>
@@ -53758,7 +53758,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.9963401556015</v>
+        <v>1.99634003639221</v>
       </c>
       <c r="H1841" t="n">
         <v>38431</v>
@@ -53874,7 +53874,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1845" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1845" t="n">
         <v>25740</v>
@@ -53903,7 +53903,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1846" t="n">
-        <v>2.10677599906921</v>
+        <v>2.10677576065063</v>
       </c>
       <c r="H1846" t="n">
         <v>11988</v>
@@ -53932,7 +53932,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.08129048347473</v>
+        <v>2.08129072189331</v>
       </c>
       <c r="H1847" t="n">
         <v>4495</v>
@@ -54019,7 +54019,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.14500379562378</v>
+        <v>2.1450035572052</v>
       </c>
       <c r="H1850" t="n">
         <v>99311</v>
@@ -54135,7 +54135,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1854" t="n">
         <v>8615</v>
@@ -54164,7 +54164,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.10677599906921</v>
+        <v>2.10677576065063</v>
       </c>
       <c r="H1855" t="n">
         <v>86693</v>
@@ -54251,7 +54251,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.08978581428528</v>
+        <v>2.0897855758667</v>
       </c>
       <c r="H1858" t="n">
         <v>28977</v>
@@ -54280,7 +54280,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.10677599906921</v>
+        <v>2.10677576065063</v>
       </c>
       <c r="H1859" t="n">
         <v>8417</v>
@@ -54309,7 +54309,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.08978581428528</v>
+        <v>2.0897855758667</v>
       </c>
       <c r="H1860" t="n">
         <v>8971</v>
@@ -54338,7 +54338,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.07704305648804</v>
+        <v>2.07704329490662</v>
       </c>
       <c r="H1861" t="n">
         <v>6479</v>
@@ -54570,7 +54570,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.04306268692017</v>
+        <v>2.04306292533875</v>
       </c>
       <c r="H1869" t="n">
         <v>15272</v>
@@ -54628,7 +54628,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.08978581428528</v>
+        <v>2.0897855758667</v>
       </c>
       <c r="H1871" t="n">
         <v>26987</v>
@@ -54657,7 +54657,7 @@
         <v>2.5</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1872" t="n">
         <v>23600</v>
@@ -54686,7 +54686,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.14500379562378</v>
+        <v>2.1450035572052</v>
       </c>
       <c r="H1873" t="n">
         <v>34609</v>
@@ -54773,7 +54773,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.14500379562378</v>
+        <v>2.1450035572052</v>
       </c>
       <c r="H1876" t="n">
         <v>67024</v>
@@ -54802,7 +54802,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.10677599906921</v>
+        <v>2.10677576065063</v>
       </c>
       <c r="H1877" t="n">
         <v>35375</v>
@@ -54918,7 +54918,7 @@
         <v>2.5</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1881" t="n">
         <v>14370</v>
@@ -54947,7 +54947,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.12801337242126</v>
+        <v>2.12801361083984</v>
       </c>
       <c r="H1882" t="n">
         <v>9487</v>
@@ -55005,7 +55005,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.10252833366394</v>
+        <v>2.10252809524536</v>
       </c>
       <c r="H1884" t="n">
         <v>12201</v>
@@ -55092,7 +55092,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1887" t="n">
         <v>3535</v>
@@ -55208,7 +55208,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.06430077552795</v>
+        <v>2.06430053710938</v>
       </c>
       <c r="H1891" t="n">
         <v>10726</v>
@@ -55266,7 +55266,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.12801337242126</v>
+        <v>2.12801361083984</v>
       </c>
       <c r="H1893" t="n">
         <v>21014</v>
@@ -55295,7 +55295,7 @@
         <v>2.5</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1894" t="n">
         <v>17372</v>
@@ -55324,7 +55324,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1895" t="n">
         <v>21821</v>
@@ -55556,7 +55556,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.18323135375977</v>
+        <v>2.18323159217834</v>
       </c>
       <c r="H1903" t="n">
         <v>1800</v>
@@ -55585,7 +55585,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.18323135375977</v>
+        <v>2.18323159217834</v>
       </c>
       <c r="H1904" t="n">
         <v>13761</v>
@@ -55759,7 +55759,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.14500379562378</v>
+        <v>2.1450035572052</v>
       </c>
       <c r="H1910" t="n">
         <v>6282</v>
@@ -55846,7 +55846,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.14500379562378</v>
+        <v>2.1450035572052</v>
       </c>
       <c r="H1913" t="n">
         <v>4038</v>
@@ -55875,7 +55875,7 @@
         <v>2.5</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1914" t="n">
         <v>15397</v>
@@ -55904,7 +55904,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.14075613021851</v>
+        <v>2.14075636863708</v>
       </c>
       <c r="H1915" t="n">
         <v>4208</v>
@@ -55991,7 +55991,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.18323135375977</v>
+        <v>2.18323159217834</v>
       </c>
       <c r="H1918" t="n">
         <v>13374</v>
@@ -56107,7 +56107,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.14500379562378</v>
+        <v>2.1450035572052</v>
       </c>
       <c r="H1922" t="n">
         <v>11908</v>
@@ -56165,7 +56165,7 @@
         <v>2.5</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.12376594543457</v>
+        <v>2.12376618385315</v>
       </c>
       <c r="H1924" t="n">
         <v>33504</v>
@@ -56194,7 +56194,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.25119185447693</v>
+        <v>2.25119209289551</v>
       </c>
       <c r="H1925" t="n">
         <v>97313</v>
@@ -56368,7 +56368,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.27700281143188</v>
+        <v>2.27700257301331</v>
       </c>
       <c r="H1931" t="n">
         <v>19426</v>
@@ -56426,7 +56426,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.26834464073181</v>
+        <v>2.26834487915039</v>
       </c>
       <c r="H1933" t="n">
         <v>37806</v>
@@ -56455,7 +56455,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.27700281143188</v>
+        <v>2.27700257301331</v>
       </c>
       <c r="H1934" t="n">
         <v>14355</v>
@@ -56513,7 +56513,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.26834464073181</v>
+        <v>2.26834487915039</v>
       </c>
       <c r="H1936" t="n">
         <v>39069</v>
@@ -56542,7 +56542,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H1937" t="n">
         <v>12871</v>
@@ -56571,7 +56571,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H1938" t="n">
         <v>15337</v>
@@ -56600,7 +56600,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.26834464073181</v>
+        <v>2.26834487915039</v>
       </c>
       <c r="H1939" t="n">
         <v>2777</v>
@@ -56658,7 +56658,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.27700281143188</v>
+        <v>2.27700257301331</v>
       </c>
       <c r="H1941" t="n">
         <v>15992</v>
@@ -56716,7 +56716,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.22505569458008</v>
+        <v>2.22505593299866</v>
       </c>
       <c r="H1943" t="n">
         <v>22215</v>
@@ -56745,7 +56745,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H1944" t="n">
         <v>3956</v>
@@ -56774,7 +56774,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.24670052528381</v>
+        <v>2.24670028686523</v>
       </c>
       <c r="H1945" t="n">
         <v>15334</v>
@@ -56832,7 +56832,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.23804259300232</v>
+        <v>2.23804235458374</v>
       </c>
       <c r="H1947" t="n">
         <v>8716</v>
@@ -56890,7 +56890,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H1949" t="n">
         <v>2442</v>
@@ -56919,7 +56919,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.22505569458008</v>
+        <v>2.22505593299866</v>
       </c>
       <c r="H1950" t="n">
         <v>25338</v>
@@ -57093,7 +57093,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.32894968986511</v>
+        <v>2.32894945144653</v>
       </c>
       <c r="H1956" t="n">
         <v>67347</v>
@@ -57122,7 +57122,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.36358070373535</v>
+        <v>2.36358046531677</v>
       </c>
       <c r="H1957" t="n">
         <v>56407</v>
@@ -57151,7 +57151,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.32029175758362</v>
+        <v>2.32029151916504</v>
       </c>
       <c r="H1958" t="n">
         <v>385108</v>
@@ -57180,7 +57180,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.33760714530945</v>
+        <v>2.33760738372803</v>
       </c>
       <c r="H1959" t="n">
         <v>117259</v>
@@ -57209,7 +57209,7 @@
         <v>2.66499996185303</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.30730485916138</v>
+        <v>2.30730509757996</v>
       </c>
       <c r="H1960" t="n">
         <v>60245</v>
@@ -57238,7 +57238,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.27700281143188</v>
+        <v>2.27700257301331</v>
       </c>
       <c r="H1961" t="n">
         <v>38162</v>
@@ -57296,7 +57296,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.23804259300232</v>
+        <v>2.23804235458374</v>
       </c>
       <c r="H1963" t="n">
         <v>53763</v>
@@ -57354,7 +57354,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H1965" t="n">
         <v>39777</v>
@@ -57383,7 +57383,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.21639800071716</v>
+        <v>2.21639776229858</v>
       </c>
       <c r="H1966" t="n">
         <v>34565</v>
@@ -57441,7 +57441,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H1968" t="n">
         <v>17972</v>
@@ -57470,7 +57470,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.23804259300232</v>
+        <v>2.23804235458374</v>
       </c>
       <c r="H1969" t="n">
         <v>29068</v>
@@ -57528,7 +57528,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.22505569458008</v>
+        <v>2.22505593299866</v>
       </c>
       <c r="H1971" t="n">
         <v>24472</v>
@@ -57847,7 +57847,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.10817551612854</v>
+        <v>2.10817527770996</v>
       </c>
       <c r="H1982" t="n">
         <v>72218</v>
@@ -57876,7 +57876,7 @@
         <v>2.5</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H1983" t="n">
         <v>146806</v>
@@ -58311,7 +58311,7 @@
         <v>2.5</v>
       </c>
       <c r="G1998" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H1998" t="n">
         <v>9181</v>
@@ -58340,7 +58340,7 @@
         <v>2.5</v>
       </c>
       <c r="G1999" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H1999" t="n">
         <v>9736</v>
@@ -58427,7 +58427,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.10817551612854</v>
+        <v>2.10817527770996</v>
       </c>
       <c r="H2002" t="n">
         <v>7643</v>
@@ -58485,7 +58485,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2004" t="n">
-        <v>2.10817551612854</v>
+        <v>2.10817527770996</v>
       </c>
       <c r="H2004" t="n">
         <v>19580</v>
@@ -58630,7 +58630,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2009" t="n">
-        <v>2.10817551612854</v>
+        <v>2.10817527770996</v>
       </c>
       <c r="H2009" t="n">
         <v>16304</v>
@@ -58717,7 +58717,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.22505569458008</v>
+        <v>2.22505593299866</v>
       </c>
       <c r="H2012" t="n">
         <v>51087</v>
@@ -58746,7 +58746,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H2013" t="n">
         <v>34103</v>
@@ -58775,7 +58775,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.22505569458008</v>
+        <v>2.22505593299866</v>
       </c>
       <c r="H2014" t="n">
         <v>28614</v>
@@ -58804,7 +58804,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2015" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H2015" t="n">
         <v>4228</v>
@@ -58862,7 +58862,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G2017" t="n">
-        <v>2.28133153915405</v>
+        <v>2.28133130073547</v>
       </c>
       <c r="H2017" t="n">
         <v>47535</v>
@@ -58891,7 +58891,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2018" t="n">
-        <v>2.31163382530212</v>
+        <v>2.3116340637207</v>
       </c>
       <c r="H2018" t="n">
         <v>15964</v>
@@ -58949,7 +58949,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2020" t="n">
-        <v>2.31163382530212</v>
+        <v>2.3116340637207</v>
       </c>
       <c r="H2020" t="n">
         <v>74722</v>
@@ -58978,7 +58978,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G2021" t="n">
-        <v>2.28998947143555</v>
+        <v>2.28998923301697</v>
       </c>
       <c r="H2021" t="n">
         <v>16904</v>
@@ -59007,7 +59007,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2022" t="n">
-        <v>2.27700281143188</v>
+        <v>2.27700257301331</v>
       </c>
       <c r="H2022" t="n">
         <v>37165</v>
@@ -59065,7 +59065,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.26834464073181</v>
+        <v>2.26834487915039</v>
       </c>
       <c r="H2024" t="n">
         <v>99740</v>
@@ -59094,7 +59094,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H2025" t="n">
         <v>29836</v>
@@ -59210,7 +59210,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G2029" t="n">
-        <v>2.29431819915771</v>
+        <v>2.29431843757629</v>
       </c>
       <c r="H2029" t="n">
         <v>87581</v>
@@ -59268,7 +59268,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.26401591300964</v>
+        <v>2.26401615142822</v>
       </c>
       <c r="H2031" t="n">
         <v>61751</v>
@@ -59297,7 +59297,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G2032" t="n">
-        <v>2.24670052528381</v>
+        <v>2.24670028686523</v>
       </c>
       <c r="H2032" t="n">
         <v>34167</v>
@@ -59442,7 +59442,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2037" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H2037" t="n">
         <v>80811</v>
@@ -59471,7 +59471,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.21639800071716</v>
+        <v>2.21639776229858</v>
       </c>
       <c r="H2038" t="n">
         <v>91995</v>
@@ -59761,7 +59761,7 @@
         <v>2.5</v>
       </c>
       <c r="G2048" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H2048" t="n">
         <v>31978</v>
@@ -59877,7 +59877,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.10817551612854</v>
+        <v>2.10817527770996</v>
       </c>
       <c r="H2052" t="n">
         <v>14287</v>
@@ -59935,7 +59935,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.10817551612854</v>
+        <v>2.10817527770996</v>
       </c>
       <c r="H2054" t="n">
         <v>38639</v>
@@ -60486,7 +60486,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.06488656997681</v>
+        <v>2.06488633155823</v>
       </c>
       <c r="H2073" t="n">
         <v>12660</v>
@@ -60747,7 +60747,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2082" t="n">
-        <v>2.00861048698425</v>
+        <v>2.00861072540283</v>
       </c>
       <c r="H2082" t="n">
         <v>49858</v>
@@ -60979,7 +60979,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2090" t="n">
-        <v>2.10817551612854</v>
+        <v>2.10817527770996</v>
       </c>
       <c r="H2090" t="n">
         <v>18648</v>
@@ -61675,7 +61675,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.99995279312134</v>
+        <v>1.99995267391205</v>
       </c>
       <c r="H2114" t="n">
         <v>37963</v>
@@ -61704,7 +61704,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.98263728618622</v>
+        <v>1.98263740539551</v>
       </c>
       <c r="H2115" t="n">
         <v>95057</v>
@@ -61733,7 +61733,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.99995279312134</v>
+        <v>1.99995267391205</v>
       </c>
       <c r="H2116" t="n">
         <v>71174</v>
@@ -61762,7 +61762,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2117" t="n">
-        <v>2.00861048698425</v>
+        <v>2.00861072540283</v>
       </c>
       <c r="H2117" t="n">
         <v>30905</v>
@@ -61791,7 +61791,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2118" t="n">
-        <v>2.00861048698425</v>
+        <v>2.00861072540283</v>
       </c>
       <c r="H2118" t="n">
         <v>46906</v>
@@ -61820,7 +61820,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.99995279312134</v>
+        <v>1.99995267391205</v>
       </c>
       <c r="H2119" t="n">
         <v>85913</v>
@@ -61849,7 +61849,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2120" t="n">
-        <v>2.00861048698425</v>
+        <v>2.00861072540283</v>
       </c>
       <c r="H2120" t="n">
         <v>18617</v>
@@ -61878,7 +61878,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2121" t="n">
-        <v>1.99129509925842</v>
+        <v>1.99129498004913</v>
       </c>
       <c r="H2121" t="n">
         <v>92532</v>
@@ -61907,7 +61907,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G2122" t="n">
-        <v>1.99129509925842</v>
+        <v>1.99129498004913</v>
       </c>
       <c r="H2122" t="n">
         <v>25251</v>
@@ -61936,7 +61936,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.99995279312134</v>
+        <v>1.99995267391205</v>
       </c>
       <c r="H2123" t="n">
         <v>1027945</v>
@@ -61994,7 +61994,7 @@
         <v>2.5</v>
       </c>
       <c r="G2125" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H2125" t="n">
         <v>213333</v>
@@ -62342,7 +62342,7 @@
         <v>2.5</v>
       </c>
       <c r="G2137" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H2137" t="n">
         <v>59513</v>
@@ -62400,7 +62400,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.22505569458008</v>
+        <v>2.22505593299866</v>
       </c>
       <c r="H2139" t="n">
         <v>76303</v>
@@ -62719,7 +62719,7 @@
         <v>2.5</v>
       </c>
       <c r="G2150" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H2150" t="n">
         <v>14508</v>
@@ -62980,7 +62980,7 @@
         <v>2.5</v>
       </c>
       <c r="G2159" t="n">
-        <v>2.16445136070251</v>
+        <v>2.16445112228394</v>
       </c>
       <c r="H2159" t="n">
         <v>40690</v>
@@ -63183,7 +63183,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.21639800071716</v>
+        <v>2.21639776229858</v>
       </c>
       <c r="H2166" t="n">
         <v>33353</v>
@@ -63270,7 +63270,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2169" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2169" t="n">
         <v>25421</v>
@@ -63328,7 +63328,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.21639800071716</v>
+        <v>2.21639776229858</v>
       </c>
       <c r="H2171" t="n">
         <v>46396</v>
@@ -63386,7 +63386,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2173" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2173" t="n">
         <v>146693</v>
@@ -63444,7 +63444,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2175" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2175" t="n">
         <v>154363</v>
@@ -63473,7 +63473,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G2176" t="n">
-        <v>2.20774030685425</v>
+        <v>2.20774006843567</v>
       </c>
       <c r="H2176" t="n">
         <v>62626</v>
@@ -63502,7 +63502,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2177" t="n">
-        <v>2.21639800071716</v>
+        <v>2.21639776229858</v>
       </c>
       <c r="H2177" t="n">
         <v>43216</v>
@@ -63531,7 +63531,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2178" t="n">
-        <v>2.25102925300598</v>
+        <v>2.2510290145874</v>
       </c>
       <c r="H2178" t="n">
         <v>155843</v>
@@ -63647,7 +63647,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2182" t="n">
-        <v>2.21639800071716</v>
+        <v>2.21639776229858</v>
       </c>
       <c r="H2182" t="n">
         <v>196275</v>
@@ -63734,7 +63734,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2185" t="n">
-        <v>2.24398827552795</v>
+        <v>2.24398803710938</v>
       </c>
       <c r="H2185" t="n">
         <v>35558</v>
@@ -63879,7 +63879,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2190" t="n">
-        <v>2.24398827552795</v>
+        <v>2.24398803710938</v>
       </c>
       <c r="H2190" t="n">
         <v>22315</v>
@@ -64053,7 +64053,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2196" t="n">
-        <v>2.28077459335327</v>
+        <v>2.28077483177185</v>
       </c>
       <c r="H2196" t="n">
         <v>20919</v>
@@ -64111,7 +64111,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2198" t="n">
-        <v>2.25318455696106</v>
+        <v>2.25318479537964</v>
       </c>
       <c r="H2198" t="n">
         <v>22806</v>
@@ -64169,7 +64169,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2200" t="n">
-        <v>2.28077459335327</v>
+        <v>2.28077483177185</v>
       </c>
       <c r="H2200" t="n">
         <v>19279</v>
@@ -64314,7 +64314,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2205" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2205" t="n">
         <v>22803</v>
@@ -64633,7 +64633,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2216" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2216" t="n">
         <v>14121</v>
@@ -64923,7 +64923,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2226" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2226" t="n">
         <v>85857</v>
@@ -64981,7 +64981,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2228" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2228" t="n">
         <v>28130</v>
@@ -65126,7 +65126,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2233" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2233" t="n">
         <v>32974</v>
@@ -65300,7 +65300,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2239" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2239" t="n">
         <v>11450</v>
@@ -65735,7 +65735,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2254" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2254" t="n">
         <v>14564</v>
@@ -65822,7 +65822,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2257" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2257" t="n">
         <v>31186</v>
@@ -65851,7 +65851,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2258" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2258" t="n">
         <v>53745</v>
@@ -65938,7 +65938,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2261" t="n">
-        <v>2.18880796432495</v>
+        <v>2.18880820274353</v>
       </c>
       <c r="H2261" t="n">
         <v>12821</v>
@@ -66112,7 +66112,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2267" t="n">
-        <v>2.25318455696106</v>
+        <v>2.25318479537964</v>
       </c>
       <c r="H2267" t="n">
         <v>101991</v>
@@ -66141,7 +66141,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2268" t="n">
-        <v>2.25318455696106</v>
+        <v>2.25318479537964</v>
       </c>
       <c r="H2268" t="n">
         <v>11484</v>
@@ -66170,7 +66170,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2269" t="n">
-        <v>2.24398827552795</v>
+        <v>2.24398803710938</v>
       </c>
       <c r="H2269" t="n">
         <v>56857</v>
@@ -66228,7 +66228,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2271" t="n">
-        <v>2.24398827552795</v>
+        <v>2.24398803710938</v>
       </c>
       <c r="H2271" t="n">
         <v>10402</v>
@@ -66286,7 +66286,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2273" t="n">
-        <v>2.25318455696106</v>
+        <v>2.25318479537964</v>
       </c>
       <c r="H2273" t="n">
         <v>25660</v>
@@ -66315,7 +66315,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2274" t="n">
-        <v>2.25318455696106</v>
+        <v>2.25318479537964</v>
       </c>
       <c r="H2274" t="n">
         <v>42556</v>
@@ -66344,7 +66344,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2275" t="n">
-        <v>2.24398827552795</v>
+        <v>2.24398803710938</v>
       </c>
       <c r="H2275" t="n">
         <v>17479</v>
@@ -66373,7 +66373,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2276" t="n">
-        <v>2.25318455696106</v>
+        <v>2.25318479537964</v>
       </c>
       <c r="H2276" t="n">
         <v>32052</v>
@@ -66779,7 +66779,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2290" t="n">
-        <v>3.19124531745911</v>
+        <v>3.19124507904053</v>
       </c>
       <c r="H2290" t="n">
         <v>2192430</v>
@@ -66866,7 +66866,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2293" t="n">
-        <v>3.126868724823</v>
+        <v>3.12686848640442</v>
       </c>
       <c r="H2293" t="n">
         <v>762108</v>
@@ -66924,7 +66924,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2295" t="n">
-        <v>2.95213174819946</v>
+        <v>2.95213198661804</v>
       </c>
       <c r="H2295" t="n">
         <v>549590</v>
@@ -67185,7 +67185,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2304" t="n">
-        <v>2.74060821533203</v>
+        <v>2.74060845375061</v>
       </c>
       <c r="H2304" t="n">
         <v>105862</v>
@@ -67678,7 +67678,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2321" t="n">
-        <v>2.73141169548035</v>
+        <v>2.73141145706177</v>
       </c>
       <c r="H2321" t="n">
         <v>56770</v>
@@ -67707,7 +67707,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2322" t="n">
-        <v>2.74060821533203</v>
+        <v>2.74060845375061</v>
       </c>
       <c r="H2322" t="n">
         <v>52488</v>
@@ -67765,7 +67765,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2324" t="n">
-        <v>2.70382189750671</v>
+        <v>2.70382165908813</v>
       </c>
       <c r="H2324" t="n">
         <v>41779</v>
@@ -67852,7 +67852,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2327" t="n">
-        <v>2.6210515499115</v>
+        <v>2.62105131149292</v>
       </c>
       <c r="H2327" t="n">
         <v>43009</v>
@@ -67881,7 +67881,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G2328" t="n">
-        <v>2.57506823539734</v>
+        <v>2.57506799697876</v>
       </c>
       <c r="H2328" t="n">
         <v>93957</v>
@@ -67910,7 +67910,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G2329" t="n">
-        <v>2.58426475524902</v>
+        <v>2.5842649936676</v>
       </c>
       <c r="H2329" t="n">
         <v>53401</v>
@@ -68055,7 +68055,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G2334" t="n">
-        <v>2.53828144073486</v>
+        <v>2.53828167915344</v>
       </c>
       <c r="H2334" t="n">
         <v>43413</v>
@@ -68113,7 +68113,7 @@
         <v>2.75</v>
       </c>
       <c r="G2336" t="n">
-        <v>2.5290846824646</v>
+        <v>2.52908492088318</v>
       </c>
       <c r="H2336" t="n">
         <v>42770</v>
@@ -68171,7 +68171,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G2338" t="n">
-        <v>2.53828144073486</v>
+        <v>2.53828167915344</v>
       </c>
       <c r="H2338" t="n">
         <v>46594</v>
@@ -68258,7 +68258,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2341" t="n">
-        <v>2.71301817893982</v>
+        <v>2.7130184173584</v>
       </c>
       <c r="H2341" t="n">
         <v>184387</v>
@@ -68345,7 +68345,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2344" t="n">
-        <v>2.71301817893982</v>
+        <v>2.7130184173584</v>
       </c>
       <c r="H2344" t="n">
         <v>56285</v>
@@ -68548,7 +68548,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2351" t="n">
-        <v>2.70382189750671</v>
+        <v>2.70382165908813</v>
       </c>
       <c r="H2351" t="n">
         <v>62242</v>
@@ -68722,7 +68722,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G2357" t="n">
-        <v>2.51988840103149</v>
+        <v>2.51988816261292</v>
       </c>
       <c r="H2357" t="n">
         <v>178024</v>
@@ -68780,7 +68780,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G2359" t="n">
-        <v>2.51069164276123</v>
+        <v>2.51069140434265</v>
       </c>
       <c r="H2359" t="n">
         <v>46334</v>
@@ -68983,7 +68983,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2366" t="n">
-        <v>2.99811506271362</v>
+        <v>2.9981153011322</v>
       </c>
       <c r="H2366" t="n">
         <v>213231</v>
@@ -69012,7 +69012,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G2367" t="n">
-        <v>2.95213174819946</v>
+        <v>2.95213198661804</v>
       </c>
       <c r="H2367" t="n">
         <v>141029</v>
@@ -69041,7 +69041,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2368" t="n">
-        <v>2.97052526473999</v>
+        <v>2.97052502632141</v>
       </c>
       <c r="H2368" t="n">
         <v>73283</v>
@@ -69099,7 +69099,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2370" t="n">
-        <v>3.08088517189026</v>
+        <v>3.08088493347168</v>
       </c>
       <c r="H2370" t="n">
         <v>96993</v>
@@ -69128,7 +69128,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2371" t="n">
-        <v>3.0349018573761</v>
+        <v>3.03490161895752</v>
       </c>
       <c r="H2371" t="n">
         <v>65601</v>
@@ -69157,7 +69157,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G2372" t="n">
-        <v>3.0349018573761</v>
+        <v>3.03490161895752</v>
       </c>
       <c r="H2372" t="n">
         <v>75734</v>
@@ -69215,7 +69215,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2374" t="n">
-        <v>3.08088517189026</v>
+        <v>3.08088493347168</v>
       </c>
       <c r="H2374" t="n">
         <v>28549</v>
@@ -69273,7 +69273,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2376" t="n">
-        <v>3.08088517189026</v>
+        <v>3.08088493347168</v>
       </c>
       <c r="H2376" t="n">
         <v>17557</v>
@@ -69360,7 +69360,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2379" t="n">
-        <v>3.08088517189026</v>
+        <v>3.08088493347168</v>
       </c>
       <c r="H2379" t="n">
         <v>45995</v>
@@ -69389,7 +69389,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G2380" t="n">
-        <v>3.10847520828247</v>
+        <v>3.10847544670105</v>
       </c>
       <c r="H2380" t="n">
         <v>43001</v>
@@ -69418,7 +69418,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2381" t="n">
-        <v>3.126868724823</v>
+        <v>3.12686848640442</v>
       </c>
       <c r="H2381" t="n">
         <v>58808</v>
@@ -69447,7 +69447,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2382" t="n">
-        <v>3.19124531745911</v>
+        <v>3.19124507904053</v>
       </c>
       <c r="H2382" t="n">
         <v>143932</v>
@@ -69592,7 +69592,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2387" t="n">
-        <v>3.19124531745911</v>
+        <v>3.19124507904053</v>
       </c>
       <c r="H2387" t="n">
         <v>54046</v>
@@ -69679,7 +69679,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G2390" t="n">
-        <v>3.3567852973938</v>
+        <v>3.35678553581238</v>
       </c>
       <c r="H2390" t="n">
         <v>217978</v>
@@ -69708,7 +69708,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G2391" t="n">
-        <v>3.43035888671875</v>
+        <v>3.43035864830017</v>
       </c>
       <c r="H2391" t="n">
         <v>152002</v>
@@ -69853,7 +69853,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G2396" t="n">
-        <v>3.45794868469238</v>
+        <v>3.45794892311096</v>
       </c>
       <c r="H2396" t="n">
         <v>164895</v>
@@ -69882,7 +69882,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G2397" t="n">
-        <v>3.54071879386902</v>
+        <v>3.54071855545044</v>
       </c>
       <c r="H2397" t="n">
         <v>104946</v>
@@ -69940,7 +69940,7 @@
         <v>4.48999977111816</v>
       </c>
       <c r="G2399" t="n">
-        <v>4.12930583953857</v>
+        <v>4.12930536270142</v>
       </c>
       <c r="H2399" t="n">
         <v>575982</v>
@@ -69969,7 +69969,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G2400" t="n">
-        <v>4.0373387336731</v>
+        <v>4.03733921051025</v>
       </c>
       <c r="H2400" t="n">
         <v>266714</v>
@@ -70085,7 +70085,7 @@
         <v>4.69000005722046</v>
       </c>
       <c r="G2404" t="n">
-        <v>4.31323957443237</v>
+        <v>4.31323909759521</v>
       </c>
       <c r="H2404" t="n">
         <v>381345</v>
@@ -70114,7 +70114,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2405" t="n">
-        <v>4.3776159286499</v>
+        <v>4.37761640548706</v>
       </c>
       <c r="H2405" t="n">
         <v>193331</v>
@@ -70143,7 +70143,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G2406" t="n">
-        <v>4.44199275970459</v>
+        <v>4.44199228286743</v>
       </c>
       <c r="H2406" t="n">
         <v>149135</v>
@@ -70172,7 +70172,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G2407" t="n">
-        <v>4.67190980911255</v>
+        <v>4.67190933227539</v>
       </c>
       <c r="H2407" t="n">
         <v>603108</v>
@@ -70404,7 +70404,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G2415" t="n">
-        <v>4.24886226654053</v>
+        <v>4.24886274337769</v>
       </c>
       <c r="H2415" t="n">
         <v>102869</v>
@@ -70462,7 +70462,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G2417" t="n">
-        <v>4.27645301818848</v>
+        <v>4.27645254135132</v>
       </c>
       <c r="H2417" t="n">
         <v>66060</v>
@@ -70491,7 +70491,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G2418" t="n">
-        <v>4.23046922683716</v>
+        <v>4.23046875</v>
       </c>
       <c r="H2418" t="n">
         <v>69442</v>
@@ -70636,7 +70636,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2423" t="n">
-        <v>4.3776159286499</v>
+        <v>4.37761640548706</v>
       </c>
       <c r="H2423" t="n">
         <v>147907</v>
@@ -70839,7 +70839,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G2430" t="n">
-        <v>4.3776159286499</v>
+        <v>4.37761640548706</v>
       </c>
       <c r="H2430" t="n">
         <v>60554</v>
@@ -80125,6 +80125,35 @@
         <v>160980</v>
       </c>
       <c r="I2750" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2751">
+      <c r="A2751" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2751" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C2751" t="n">
+        <v>7.55000019073486</v>
+      </c>
+      <c r="D2751" t="n">
+        <v>7.84000015258789</v>
+      </c>
+      <c r="E2751" t="n">
+        <v>7.46999979019165</v>
+      </c>
+      <c r="F2751" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="G2751" t="n">
+        <v>7.71999979019165</v>
+      </c>
+      <c r="H2751" t="n">
+        <v>446458</v>
+      </c>
+      <c r="I2751" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/GSP.MI.xlsx
+++ b/data/GSP.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G2" t="n">
-        <v>2.92757678031921</v>
+        <v>2.92757630348206</v>
       </c>
       <c r="H2" t="n">
         <v>2877</v>
@@ -485,7 +485,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G4" t="n">
-        <v>2.94375133514404</v>
+        <v>2.94375109672546</v>
       </c>
       <c r="H4" t="n">
         <v>2430</v>
@@ -659,7 +659,7 @@
         <v>3.69000005722046</v>
       </c>
       <c r="G10" t="n">
-        <v>2.98418736457825</v>
+        <v>2.98418712615967</v>
       </c>
       <c r="H10" t="n">
         <v>2302</v>
@@ -688,7 +688,7 @@
         <v>3.64800000190735</v>
       </c>
       <c r="G11" t="n">
-        <v>2.95022106170654</v>
+        <v>2.95022082328796</v>
       </c>
       <c r="H11" t="n">
         <v>1306</v>
@@ -717,7 +717,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G12" t="n">
-        <v>2.74965739250183</v>
+        <v>2.74965763092041</v>
       </c>
       <c r="H12" t="n">
         <v>9032</v>
@@ -746,7 +746,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G13" t="n">
-        <v>2.668785572052</v>
+        <v>2.66878509521484</v>
       </c>
       <c r="H13" t="n">
         <v>9675</v>
@@ -804,7 +804,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G15" t="n">
-        <v>2.53939008712769</v>
+        <v>2.53938961029053</v>
       </c>
       <c r="H15" t="n">
         <v>4837</v>
@@ -978,7 +978,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G21" t="n">
-        <v>2.56365132331848</v>
+        <v>2.56365156173706</v>
       </c>
       <c r="H21" t="n">
         <v>2307</v>
@@ -1007,7 +1007,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G22" t="n">
-        <v>2.49895334243774</v>
+        <v>2.4989538192749</v>
       </c>
       <c r="H22" t="n">
         <v>6946</v>
@@ -1094,7 +1094,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G25" t="n">
-        <v>2.49895334243774</v>
+        <v>2.4989538192749</v>
       </c>
       <c r="H25" t="n">
         <v>10756</v>
@@ -1123,7 +1123,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G26" t="n">
-        <v>2.41808152198792</v>
+        <v>2.41808128356934</v>
       </c>
       <c r="H26" t="n">
         <v>1304</v>
@@ -1181,7 +1181,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G28" t="n">
-        <v>2.1592903137207</v>
+        <v>2.15929007530212</v>
       </c>
       <c r="H28" t="n">
         <v>5931</v>
@@ -1297,7 +1297,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G32" t="n">
-        <v>2.36470556259155</v>
+        <v>2.36470580101013</v>
       </c>
       <c r="H32" t="n">
         <v>6565</v>
@@ -1471,7 +1471,7 @@
         <v>3.18600010871887</v>
       </c>
       <c r="G38" t="n">
-        <v>2.57659077644348</v>
+        <v>2.57659101486206</v>
       </c>
       <c r="H38" t="n">
         <v>626</v>
@@ -1500,7 +1500,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G39" t="n">
-        <v>2.49895334243774</v>
+        <v>2.4989538192749</v>
       </c>
       <c r="H39" t="n">
         <v>10945</v>
@@ -1558,7 +1558,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G41" t="n">
-        <v>2.49086618423462</v>
+        <v>2.49086666107178</v>
       </c>
       <c r="H41" t="n">
         <v>166</v>
@@ -1587,7 +1587,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G42" t="n">
-        <v>2.48277902603149</v>
+        <v>2.48277878761292</v>
       </c>
       <c r="H42" t="n">
         <v>742</v>
@@ -1616,7 +1616,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G43" t="n">
-        <v>2.48277902603149</v>
+        <v>2.48277878761292</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G44" t="n">
-        <v>2.47469186782837</v>
+        <v>2.47469162940979</v>
       </c>
       <c r="H44" t="n">
         <v>7281</v>
@@ -1674,7 +1674,7 @@
         <v>3.09800004959106</v>
       </c>
       <c r="G45" t="n">
-        <v>2.5054235458374</v>
+        <v>2.50542330741882</v>
       </c>
       <c r="H45" t="n">
         <v>1234</v>
@@ -1761,7 +1761,7 @@
         <v>3.11800003051758</v>
       </c>
       <c r="G48" t="n">
-        <v>2.52159762382507</v>
+        <v>2.52159786224365</v>
       </c>
       <c r="H48" t="n">
         <v>3370</v>
@@ -1819,7 +1819,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G50" t="n">
-        <v>2.668785572052</v>
+        <v>2.66878509521484</v>
       </c>
       <c r="H50" t="n">
         <v>2150</v>
@@ -1848,7 +1848,7 @@
         <v>3.23200011253357</v>
       </c>
       <c r="G51" t="n">
-        <v>2.61379218101501</v>
+        <v>2.61379265785217</v>
       </c>
       <c r="H51" t="n">
         <v>4260</v>
@@ -1906,7 +1906,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G53" t="n">
-        <v>2.58791303634644</v>
+        <v>2.58791327476501</v>
       </c>
       <c r="H53" t="n">
         <v>1256</v>
@@ -1964,7 +1964,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G55" t="n">
-        <v>2.54747724533081</v>
+        <v>2.54747700691223</v>
       </c>
       <c r="H55" t="n">
         <v>2341</v>
@@ -1993,7 +1993,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G56" t="n">
-        <v>2.54747724533081</v>
+        <v>2.54747700691223</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>3.23600006103516</v>
       </c>
       <c r="G57" t="n">
-        <v>2.61702728271484</v>
+        <v>2.61702704429626</v>
       </c>
       <c r="H57" t="n">
         <v>605</v>
@@ -2051,7 +2051,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G58" t="n">
-        <v>2.58791303634644</v>
+        <v>2.58791327476501</v>
       </c>
       <c r="H58" t="n">
         <v>1000</v>
@@ -2080,7 +2080,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G59" t="n">
-        <v>2.54747724533081</v>
+        <v>2.54747700691223</v>
       </c>
       <c r="H59" t="n">
         <v>1600</v>
@@ -2196,7 +2196,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G63" t="n">
-        <v>2.56365132331848</v>
+        <v>2.56365156173706</v>
       </c>
       <c r="H63" t="n">
         <v>101</v>
@@ -2283,7 +2283,7 @@
         <v>3.17400002479553</v>
       </c>
       <c r="G66" t="n">
-        <v>2.56688618659973</v>
+        <v>2.56688594818115</v>
       </c>
       <c r="H66" t="n">
         <v>792</v>
@@ -2341,7 +2341,7 @@
         <v>3.12800002098083</v>
       </c>
       <c r="G68" t="n">
-        <v>2.52968502044678</v>
+        <v>2.52968525886536</v>
       </c>
       <c r="H68" t="n">
         <v>300</v>
@@ -2370,7 +2370,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G69" t="n">
-        <v>2.53130221366882</v>
+        <v>2.5313024520874</v>
       </c>
       <c r="H69" t="n">
         <v>600</v>
@@ -2399,7 +2399,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G70" t="n">
-        <v>2.49895334243774</v>
+        <v>2.4989538192749</v>
       </c>
       <c r="H70" t="n">
         <v>4213</v>
@@ -2457,7 +2457,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G72" t="n">
-        <v>2.49895334243774</v>
+        <v>2.4989538192749</v>
       </c>
       <c r="H72" t="n">
         <v>9046</v>
@@ -2544,7 +2544,7 @@
         <v>3.20799994468689</v>
       </c>
       <c r="G75" t="n">
-        <v>2.59438252449036</v>
+        <v>2.59438276290894</v>
       </c>
       <c r="H75" t="n">
         <v>1200</v>
@@ -2573,7 +2573,7 @@
         <v>3.21000003814697</v>
       </c>
       <c r="G76" t="n">
-        <v>2.59600067138672</v>
+        <v>2.59600043296814</v>
       </c>
       <c r="H76" t="n">
         <v>50</v>
@@ -2660,7 +2660,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G79" t="n">
-        <v>2.54100728034973</v>
+        <v>2.54100704193115</v>
       </c>
       <c r="H79" t="n">
         <v>5900</v>
@@ -2689,7 +2689,7 @@
         <v>3.14199995994568</v>
       </c>
       <c r="G80" t="n">
-        <v>2.54100728034973</v>
+        <v>2.54100704193115</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G81" t="n">
-        <v>2.56365132331848</v>
+        <v>2.56365156173706</v>
       </c>
       <c r="H81" t="n">
         <v>1030</v>
@@ -2747,7 +2747,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G82" t="n">
-        <v>2.56365132331848</v>
+        <v>2.56365156173706</v>
       </c>
       <c r="H82" t="n">
         <v>900</v>
@@ -2805,7 +2805,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G84" t="n">
-        <v>2.53939008712769</v>
+        <v>2.53938961029053</v>
       </c>
       <c r="H84" t="n">
         <v>3909</v>
@@ -2834,7 +2834,7 @@
         <v>3.14400005340576</v>
       </c>
       <c r="G85" t="n">
-        <v>2.54262447357178</v>
+        <v>2.54262471199036</v>
       </c>
       <c r="H85" t="n">
         <v>12001</v>
@@ -2863,7 +2863,7 @@
         <v>3.13800001144409</v>
       </c>
       <c r="G86" t="n">
-        <v>2.5377721786499</v>
+        <v>2.53777241706848</v>
       </c>
       <c r="H86" t="n">
         <v>201</v>
@@ -3095,7 +3095,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G94" t="n">
-        <v>2.45689988136292</v>
+        <v>2.45690011978149</v>
       </c>
       <c r="H94" t="n">
         <v>1915</v>
@@ -3124,7 +3124,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G95" t="n">
-        <v>2.45689988136292</v>
+        <v>2.45690011978149</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G96" t="n">
-        <v>2.45689988136292</v>
+        <v>2.45690011978149</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>2.9779999256134</v>
       </c>
       <c r="G97" t="n">
-        <v>2.40837669372559</v>
+        <v>2.40837645530701</v>
       </c>
       <c r="H97" t="n">
         <v>12462</v>
@@ -3211,7 +3211,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G98" t="n">
-        <v>2.38411498069763</v>
+        <v>2.38411521911621</v>
       </c>
       <c r="H98" t="n">
         <v>4757</v>
@@ -3240,7 +3240,7 @@
         <v>2.94400000572205</v>
       </c>
       <c r="G99" t="n">
-        <v>2.38088011741638</v>
+        <v>2.3808798789978</v>
       </c>
       <c r="H99" t="n">
         <v>1000</v>
@@ -3269,7 +3269,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G100" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H100" t="n">
         <v>711</v>
@@ -3298,7 +3298,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G101" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G102" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H102" t="n">
         <v>5002</v>
@@ -3559,7 +3559,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G110" t="n">
-        <v>2.28544402122498</v>
+        <v>2.2854437828064</v>
       </c>
       <c r="H110" t="n">
         <v>9307</v>
@@ -3646,7 +3646,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G113" t="n">
-        <v>2.24191164970398</v>
+        <v>2.24191188812256</v>
       </c>
       <c r="H113" t="n">
         <v>237</v>
@@ -3675,7 +3675,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G114" t="n">
-        <v>2.28879237174988</v>
+        <v>2.28879284858704</v>
       </c>
       <c r="H114" t="n">
         <v>6870</v>
@@ -3704,7 +3704,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G115" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H115" t="n">
         <v>9869</v>
@@ -3762,7 +3762,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G117" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H117" t="n">
         <v>1936</v>
@@ -3820,7 +3820,7 @@
         <v>2.58800005912781</v>
       </c>
       <c r="G119" t="n">
-        <v>2.16656756401062</v>
+        <v>2.16656732559204</v>
       </c>
       <c r="H119" t="n">
         <v>601</v>
@@ -3849,7 +3849,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G120" t="n">
-        <v>2.26702666282654</v>
+        <v>2.26702642440796</v>
       </c>
       <c r="H120" t="n">
         <v>3339</v>
@@ -3878,7 +3878,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G121" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H121" t="n">
         <v>3184</v>
@@ -3907,7 +3907,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G122" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H122" t="n">
         <v>2550</v>
@@ -3936,7 +3936,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G123" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H123" t="n">
         <v>5450</v>
@@ -3965,7 +3965,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G124" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H124" t="n">
         <v>2621</v>
@@ -3994,7 +3994,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G125" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H125" t="n">
         <v>3129</v>
@@ -4081,7 +4081,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G128" t="n">
-        <v>2.14480113983154</v>
+        <v>2.14480090141296</v>
       </c>
       <c r="H128" t="n">
         <v>100</v>
@@ -4110,7 +4110,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G129" t="n">
-        <v>2.14480113983154</v>
+        <v>2.14480090141296</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>2.56200003623962</v>
       </c>
       <c r="G131" t="n">
-        <v>2.14480113983154</v>
+        <v>2.14480090141296</v>
       </c>
       <c r="H131" t="n">
         <v>2200</v>
@@ -4197,7 +4197,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G132" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H132" t="n">
         <v>1600</v>
@@ -4284,7 +4284,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G135" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H135" t="n">
         <v>830</v>
@@ -4313,7 +4313,7 @@
         <v>2.5460000038147</v>
       </c>
       <c r="G136" t="n">
-        <v>2.13140630722046</v>
+        <v>2.13140654563904</v>
       </c>
       <c r="H136" t="n">
         <v>2546</v>
@@ -4371,7 +4371,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G138" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H138" t="n">
         <v>2150</v>
@@ -4400,7 +4400,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G139" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H139" t="n">
         <v>1487</v>
@@ -4429,7 +4429,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G140" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G149" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H149" t="n">
         <v>2000</v>
@@ -4719,7 +4719,7 @@
         <v>2.56599998474121</v>
       </c>
       <c r="G150" t="n">
-        <v>2.1481499671936</v>
+        <v>2.14814972877502</v>
       </c>
       <c r="H150" t="n">
         <v>376</v>
@@ -4806,7 +4806,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G153" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H153" t="n">
         <v>2211</v>
@@ -4835,7 +4835,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G154" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H154" t="n">
         <v>1061</v>
@@ -4864,7 +4864,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G155" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H155" t="n">
         <v>2004</v>
@@ -4893,7 +4893,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G156" t="n">
-        <v>2.26702666282654</v>
+        <v>2.26702642440796</v>
       </c>
       <c r="H156" t="n">
         <v>8194</v>
@@ -4922,7 +4922,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G157" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H157" t="n">
         <v>2500</v>
@@ -4951,7 +4951,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H158" t="n">
         <v>7741</v>
@@ -5009,7 +5009,7 @@
         <v>2.70799994468689</v>
       </c>
       <c r="G160" t="n">
-        <v>2.26702666282654</v>
+        <v>2.26702642440796</v>
       </c>
       <c r="H160" t="n">
         <v>326</v>
@@ -5038,7 +5038,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H161" t="n">
         <v>1839</v>
@@ -5067,7 +5067,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G162" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G163" t="n">
-        <v>2.22014570236206</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H163" t="n">
         <v>2000</v>
@@ -5125,7 +5125,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G164" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H164" t="n">
         <v>2682</v>
@@ -5212,7 +5212,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G167" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H167" t="n">
         <v>1371</v>
@@ -5241,7 +5241,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G168" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H168" t="n">
         <v>1861</v>
@@ -5270,7 +5270,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G169" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G171" t="n">
-        <v>2.25698041915894</v>
+        <v>2.25698065757751</v>
       </c>
       <c r="H171" t="n">
         <v>25</v>
@@ -5357,7 +5357,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G172" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H172" t="n">
         <v>5002</v>
@@ -5386,7 +5386,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G173" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H173" t="n">
         <v>51</v>
@@ -5502,7 +5502,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G177" t="n">
-        <v>2.22014570236206</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H177" t="n">
         <v>3110</v>
@@ -5531,7 +5531,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G178" t="n">
-        <v>2.2352147102356</v>
+        <v>2.23521447181702</v>
       </c>
       <c r="H178" t="n">
         <v>2610</v>
@@ -5618,7 +5618,7 @@
         <v>2.64199995994568</v>
       </c>
       <c r="G181" t="n">
-        <v>2.21177387237549</v>
+        <v>2.21177363395691</v>
       </c>
       <c r="H181" t="n">
         <v>126</v>
@@ -5676,7 +5676,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G183" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H183" t="n">
         <v>1410</v>
@@ -5734,7 +5734,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G185" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H185" t="n">
         <v>3000</v>
@@ -5850,7 +5850,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G189" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H189" t="n">
         <v>631</v>
@@ -5879,7 +5879,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G190" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H190" t="n">
         <v>315</v>
@@ -5937,7 +5937,7 @@
         <v>2.50799989700317</v>
       </c>
       <c r="G192" t="n">
-        <v>2.09959435462952</v>
+        <v>2.0995945930481</v>
       </c>
       <c r="H192" t="n">
         <v>1674</v>
@@ -5966,7 +5966,7 @@
         <v>2.5</v>
       </c>
       <c r="G193" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H193" t="n">
         <v>1790</v>
@@ -6082,7 +6082,7 @@
         <v>2.5</v>
       </c>
       <c r="G197" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H197" t="n">
         <v>4577</v>
@@ -6111,7 +6111,7 @@
         <v>2.43400001525879</v>
       </c>
       <c r="G198" t="n">
-        <v>2.03764510154724</v>
+        <v>2.03764486312866</v>
       </c>
       <c r="H198" t="n">
         <v>3980</v>
@@ -6140,7 +6140,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G199" t="n">
-        <v>2.06610798835754</v>
+        <v>2.06610822677612</v>
       </c>
       <c r="H199" t="n">
         <v>2340</v>
@@ -6169,7 +6169,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G200" t="n">
-        <v>2.06610798835754</v>
+        <v>2.06610822677612</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>2.47199988365173</v>
       </c>
       <c r="G201" t="n">
-        <v>2.06945705413818</v>
+        <v>2.0694568157196</v>
       </c>
       <c r="H201" t="n">
         <v>3744</v>
@@ -6227,7 +6227,7 @@
         <v>2.5</v>
       </c>
       <c r="G202" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H202" t="n">
         <v>5495</v>
@@ -6285,7 +6285,7 @@
         <v>2.5</v>
       </c>
       <c r="G204" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H204" t="n">
         <v>3149</v>
@@ -6314,7 +6314,7 @@
         <v>2.46199989318848</v>
       </c>
       <c r="G205" t="n">
-        <v>2.06108498573303</v>
+        <v>2.06108522415161</v>
       </c>
       <c r="H205" t="n">
         <v>731</v>
@@ -6459,7 +6459,7 @@
         <v>2.41199994087219</v>
       </c>
       <c r="G210" t="n">
-        <v>2.01922702789307</v>
+        <v>2.01922726631165</v>
       </c>
       <c r="H210" t="n">
         <v>2644</v>
@@ -6488,7 +6488,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G211" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H211" t="n">
         <v>8288</v>
@@ -6517,7 +6517,7 @@
         <v>2.44799995422363</v>
       </c>
       <c r="G212" t="n">
-        <v>2.04936504364014</v>
+        <v>2.04936480522156</v>
       </c>
       <c r="H212" t="n">
         <v>1668</v>
@@ -6604,7 +6604,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G215" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H215" t="n">
         <v>295</v>
@@ -6662,7 +6662,7 @@
         <v>2.37599992752075</v>
       </c>
       <c r="G217" t="n">
-        <v>1.98908948898315</v>
+        <v>1.98908972740173</v>
       </c>
       <c r="H217" t="n">
         <v>262</v>
@@ -6778,7 +6778,7 @@
         <v>2.38199996948242</v>
       </c>
       <c r="G221" t="n">
-        <v>1.99411249160767</v>
+        <v>1.99411261081696</v>
       </c>
       <c r="H221" t="n">
         <v>2900</v>
@@ -6865,7 +6865,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G224" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H224" t="n">
         <v>4828</v>
@@ -6894,7 +6894,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G225" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H225" t="n">
         <v>554</v>
@@ -6923,7 +6923,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G226" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H226" t="n">
         <v>2701</v>
@@ -6952,7 +6952,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G227" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>2.30800008773804</v>
       </c>
       <c r="G228" t="n">
-        <v>1.93216288089752</v>
+        <v>1.93216300010681</v>
       </c>
       <c r="H228" t="n">
         <v>7567</v>
@@ -7068,7 +7068,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G231" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H231" t="n">
         <v>3239</v>
@@ -7097,7 +7097,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G232" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H232" t="n">
         <v>500</v>
@@ -7213,7 +7213,7 @@
         <v>2.31800007820129</v>
       </c>
       <c r="G236" t="n">
-        <v>1.94053435325623</v>
+        <v>1.94053423404694</v>
       </c>
       <c r="H236" t="n">
         <v>6530</v>
@@ -7300,7 +7300,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G239" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H239" t="n">
         <v>300</v>
@@ -7387,7 +7387,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G242" t="n">
-        <v>2.06610798835754</v>
+        <v>2.06610822677612</v>
       </c>
       <c r="H242" t="n">
         <v>7658</v>
@@ -7445,7 +7445,7 @@
         <v>2.40400004386902</v>
       </c>
       <c r="G244" t="n">
-        <v>2.01253008842468</v>
+        <v>2.0125298500061</v>
       </c>
       <c r="H244" t="n">
         <v>13022</v>
@@ -7474,7 +7474,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G245" t="n">
-        <v>2.06610798835754</v>
+        <v>2.06610822677612</v>
       </c>
       <c r="H245" t="n">
         <v>3362</v>
@@ -7503,7 +7503,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G246" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H246" t="n">
         <v>6984</v>
@@ -7532,7 +7532,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G247" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H247" t="n">
         <v>1952</v>
@@ -7590,7 +7590,7 @@
         <v>2.46799993515015</v>
       </c>
       <c r="G249" t="n">
-        <v>2.06610798835754</v>
+        <v>2.06610822677612</v>
       </c>
       <c r="H249" t="n">
         <v>2070</v>
@@ -7822,7 +7822,7 @@
         <v>2.42600011825562</v>
       </c>
       <c r="G257" t="n">
-        <v>2.0309476852417</v>
+        <v>2.03094792366028</v>
       </c>
       <c r="H257" t="n">
         <v>5764</v>
@@ -7851,7 +7851,7 @@
         <v>2.5</v>
       </c>
       <c r="G258" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H258" t="n">
         <v>11294</v>
@@ -7880,7 +7880,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G259" t="n">
-        <v>2.46794462203979</v>
+        <v>2.46794486045837</v>
       </c>
       <c r="H259" t="n">
         <v>27965</v>
@@ -7938,7 +7938,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G261" t="n">
-        <v>2.70402336120605</v>
+        <v>2.70402312278748</v>
       </c>
       <c r="H261" t="n">
         <v>87541</v>
@@ -7967,7 +7967,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G262" t="n">
-        <v>2.70402336120605</v>
+        <v>2.70402312278748</v>
       </c>
       <c r="H262" t="n">
         <v>8252</v>
@@ -7996,7 +7996,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G263" t="n">
-        <v>2.70402336120605</v>
+        <v>2.70402312278748</v>
       </c>
       <c r="H263" t="n">
         <v>38698</v>
@@ -8112,7 +8112,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G267" t="n">
-        <v>2.57844924926758</v>
+        <v>2.57844972610474</v>
       </c>
       <c r="H267" t="n">
         <v>30844</v>
@@ -8170,7 +8170,7 @@
         <v>3.05599999427795</v>
       </c>
       <c r="G269" t="n">
-        <v>2.55835795402527</v>
+        <v>2.55835771560669</v>
       </c>
       <c r="H269" t="n">
         <v>5829</v>
@@ -8199,7 +8199,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G270" t="n">
-        <v>2.58682084083557</v>
+        <v>2.58682131767273</v>
       </c>
       <c r="H270" t="n">
         <v>15928</v>
@@ -8257,7 +8257,7 @@
         <v>3.06399989128113</v>
       </c>
       <c r="G272" t="n">
-        <v>2.56505489349365</v>
+        <v>2.56505465507507</v>
       </c>
       <c r="H272" t="n">
         <v>3710</v>
@@ -8431,7 +8431,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G278" t="n">
-        <v>2.57007789611816</v>
+        <v>2.57007765769958</v>
       </c>
       <c r="H278" t="n">
         <v>11457</v>
@@ -8518,7 +8518,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G281" t="n">
-        <v>2.63705086708069</v>
+        <v>2.63705062866211</v>
       </c>
       <c r="H281" t="n">
         <v>6600</v>
@@ -8576,7 +8576,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G283" t="n">
-        <v>2.57007789611816</v>
+        <v>2.57007765769958</v>
       </c>
       <c r="H283" t="n">
         <v>18978</v>
@@ -8605,7 +8605,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G284" t="n">
-        <v>2.53491759300232</v>
+        <v>2.53491735458374</v>
       </c>
       <c r="H284" t="n">
         <v>1583</v>
@@ -8663,7 +8663,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G286" t="n">
-        <v>2.5031054019928</v>
+        <v>2.50310516357422</v>
       </c>
       <c r="H286" t="n">
         <v>1752</v>
@@ -8750,7 +8750,7 @@
         <v>3.02800011634827</v>
       </c>
       <c r="G289" t="n">
-        <v>2.53491759300232</v>
+        <v>2.53491735458374</v>
       </c>
       <c r="H289" t="n">
         <v>902</v>
@@ -8808,7 +8808,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G291" t="n">
-        <v>2.4947338104248</v>
+        <v>2.49473357200623</v>
       </c>
       <c r="H291" t="n">
         <v>10449</v>
@@ -8837,7 +8837,7 @@
         <v>2.98799991607666</v>
       </c>
       <c r="G292" t="n">
-        <v>2.50143051147461</v>
+        <v>2.50143074989319</v>
       </c>
       <c r="H292" t="n">
         <v>4202</v>
@@ -8895,7 +8895,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G294" t="n">
-        <v>2.54328870773315</v>
+        <v>2.54328894615173</v>
       </c>
       <c r="H294" t="n">
         <v>2752</v>
@@ -8924,7 +8924,7 @@
         <v>3.02600002288818</v>
       </c>
       <c r="G295" t="n">
-        <v>2.53324270248413</v>
+        <v>2.53324294090271</v>
       </c>
       <c r="H295" t="n">
         <v>10626</v>
@@ -9069,7 +9069,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G300" t="n">
-        <v>2.45287537574768</v>
+        <v>2.45287585258484</v>
       </c>
       <c r="H300" t="n">
         <v>2774</v>
@@ -9243,7 +9243,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G306" t="n">
-        <v>2.39260053634644</v>
+        <v>2.39260029792786</v>
       </c>
       <c r="H306" t="n">
         <v>2136</v>
@@ -9330,7 +9330,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G309" t="n">
-        <v>2.4461784362793</v>
+        <v>2.44617819786072</v>
       </c>
       <c r="H309" t="n">
         <v>12902</v>
@@ -9388,7 +9388,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G311" t="n">
-        <v>2.46794462203979</v>
+        <v>2.46794486045837</v>
       </c>
       <c r="H311" t="n">
         <v>401</v>
@@ -9417,7 +9417,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G312" t="n">
-        <v>2.4026460647583</v>
+        <v>2.40264582633972</v>
       </c>
       <c r="H312" t="n">
         <v>6202</v>
@@ -9591,7 +9591,7 @@
         <v>2.95799994468689</v>
       </c>
       <c r="G318" t="n">
-        <v>2.47631621360779</v>
+        <v>2.47631597518921</v>
       </c>
       <c r="H318" t="n">
         <v>6900</v>
@@ -9649,7 +9649,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G320" t="n">
-        <v>2.42943525314331</v>
+        <v>2.42943501472473</v>
       </c>
       <c r="H320" t="n">
         <v>35143</v>
@@ -9678,7 +9678,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G321" t="n">
-        <v>2.5031054019928</v>
+        <v>2.50310516357422</v>
       </c>
       <c r="H321" t="n">
         <v>5160</v>
@@ -9707,7 +9707,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G322" t="n">
-        <v>2.4461784362793</v>
+        <v>2.44617819786072</v>
       </c>
       <c r="H322" t="n">
         <v>6960</v>
@@ -9736,7 +9736,7 @@
         <v>2.91599988937378</v>
       </c>
       <c r="G323" t="n">
-        <v>2.44115543365479</v>
+        <v>2.44115567207336</v>
       </c>
       <c r="H323" t="n">
         <v>5400</v>
@@ -9794,7 +9794,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43613243103027</v>
+        <v>2.43613266944885</v>
       </c>
       <c r="H325" t="n">
         <v>2400</v>
@@ -9823,7 +9823,7 @@
         <v>2.94799995422363</v>
       </c>
       <c r="G326" t="n">
-        <v>2.46794462203979</v>
+        <v>2.46794486045837</v>
       </c>
       <c r="H326" t="n">
         <v>5877</v>
@@ -9968,7 +9968,7 @@
         <v>2.90199995040894</v>
       </c>
       <c r="G331" t="n">
-        <v>2.42943525314331</v>
+        <v>2.42943501472473</v>
       </c>
       <c r="H331" t="n">
         <v>21229</v>
@@ -10084,7 +10084,7 @@
         <v>2.8659999370575</v>
       </c>
       <c r="G335" t="n">
-        <v>2.39929723739624</v>
+        <v>2.39929747581482</v>
       </c>
       <c r="H335" t="n">
         <v>500</v>
@@ -10142,7 +10142,7 @@
         <v>2.92199993133545</v>
       </c>
       <c r="G337" t="n">
-        <v>2.4461784362793</v>
+        <v>2.44617819786072</v>
       </c>
       <c r="H337" t="n">
         <v>1</v>
@@ -10171,7 +10171,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G338" t="n">
-        <v>2.4026460647583</v>
+        <v>2.40264582633972</v>
       </c>
       <c r="H338" t="n">
         <v>9070</v>
@@ -10200,7 +10200,7 @@
         <v>2.90799999237061</v>
       </c>
       <c r="G339" t="n">
-        <v>2.4344584941864</v>
+        <v>2.43445825576782</v>
       </c>
       <c r="H339" t="n">
         <v>10452</v>
@@ -10287,7 +10287,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G342" t="n">
-        <v>2.4026460647583</v>
+        <v>2.40264582633972</v>
       </c>
       <c r="H342" t="n">
         <v>7455</v>
@@ -10316,7 +10316,7 @@
         <v>2.92600011825562</v>
       </c>
       <c r="G343" t="n">
-        <v>2.44952702522278</v>
+        <v>2.4495267868042</v>
       </c>
       <c r="H343" t="n">
         <v>10691</v>
@@ -10403,7 +10403,7 @@
         <v>2.94199991226196</v>
       </c>
       <c r="G346" t="n">
-        <v>2.46292161941528</v>
+        <v>2.4629213809967</v>
       </c>
       <c r="H346" t="n">
         <v>4819</v>
@@ -10461,7 +10461,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G348" t="n">
-        <v>2.44785261154175</v>
+        <v>2.44785284996033</v>
       </c>
       <c r="H348" t="n">
         <v>1200</v>
@@ -10548,7 +10548,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G351" t="n">
-        <v>2.4947338104248</v>
+        <v>2.49473357200623</v>
       </c>
       <c r="H351" t="n">
         <v>392</v>
@@ -10606,7 +10606,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G353" t="n">
-        <v>2.48468732833862</v>
+        <v>2.4846875667572</v>
       </c>
       <c r="H353" t="n">
         <v>12736</v>
@@ -10693,7 +10693,7 @@
         <v>2.92400002479553</v>
       </c>
       <c r="G356" t="n">
-        <v>2.44785261154175</v>
+        <v>2.44785284996033</v>
       </c>
       <c r="H356" t="n">
         <v>309</v>
@@ -10751,7 +10751,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G358" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H358" t="n">
         <v>3191</v>
@@ -10780,7 +10780,7 @@
         <v>2.93400001525879</v>
       </c>
       <c r="G359" t="n">
-        <v>2.45622444152832</v>
+        <v>2.45622420310974</v>
       </c>
       <c r="H359" t="n">
         <v>0</v>
@@ -10838,7 +10838,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G361" t="n">
-        <v>2.4026460647583</v>
+        <v>2.40264582633972</v>
       </c>
       <c r="H361" t="n">
         <v>1571</v>
@@ -10896,7 +10896,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G363" t="n">
-        <v>2.4026460647583</v>
+        <v>2.40264582633972</v>
       </c>
       <c r="H363" t="n">
         <v>3970</v>
@@ -11041,7 +11041,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G368" t="n">
-        <v>2.28879237174988</v>
+        <v>2.28879284858704</v>
       </c>
       <c r="H368" t="n">
         <v>107</v>
@@ -11128,7 +11128,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G371" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H371" t="n">
         <v>4561</v>
@@ -11157,7 +11157,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G372" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H372" t="n">
         <v>0</v>
@@ -11186,7 +11186,7 @@
         <v>2.65599989891052</v>
       </c>
       <c r="G373" t="n">
-        <v>2.22349381446838</v>
+        <v>2.22349405288696</v>
       </c>
       <c r="H373" t="n">
         <v>8601</v>
@@ -11215,7 +11215,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G374" t="n">
-        <v>2.28879237174988</v>
+        <v>2.28879284858704</v>
       </c>
       <c r="H374" t="n">
         <v>1060</v>
@@ -11273,7 +11273,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G376" t="n">
-        <v>2.22014570236206</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H376" t="n">
         <v>4195</v>
@@ -11302,7 +11302,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G377" t="n">
-        <v>2.24191164970398</v>
+        <v>2.24191188812256</v>
       </c>
       <c r="H377" t="n">
         <v>1050</v>
@@ -11331,7 +11331,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G378" t="n">
-        <v>2.28376960754395</v>
+        <v>2.28376936912537</v>
       </c>
       <c r="H378" t="n">
         <v>1000</v>
@@ -11360,7 +11360,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G379" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H379" t="n">
         <v>11587</v>
@@ -11389,7 +11389,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G380" t="n">
-        <v>2.20842528343201</v>
+        <v>2.20842504501343</v>
       </c>
       <c r="H380" t="n">
         <v>750</v>
@@ -11447,7 +11447,7 @@
         <v>2.62800002098083</v>
       </c>
       <c r="G382" t="n">
-        <v>2.20005393028259</v>
+        <v>2.20005369186401</v>
       </c>
       <c r="H382" t="n">
         <v>603</v>
@@ -11476,7 +11476,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G383" t="n">
-        <v>2.25698041915894</v>
+        <v>2.25698065757751</v>
       </c>
       <c r="H383" t="n">
         <v>210</v>
@@ -11505,7 +11505,7 @@
         <v>2.63199996948242</v>
       </c>
       <c r="G384" t="n">
-        <v>2.2034022808075</v>
+        <v>2.20340204238892</v>
       </c>
       <c r="H384" t="n">
         <v>5239</v>
@@ -11563,7 +11563,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G386" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H386" t="n">
         <v>2103</v>
@@ -11592,7 +11592,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G387" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H387" t="n">
         <v>0</v>
@@ -11679,7 +11679,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G390" t="n">
-        <v>2.21679663658142</v>
+        <v>2.216796875</v>
       </c>
       <c r="H390" t="n">
         <v>4101</v>
@@ -11708,7 +11708,7 @@
         <v>2.69799995422363</v>
       </c>
       <c r="G391" t="n">
-        <v>2.25865483283997</v>
+        <v>2.25865459442139</v>
       </c>
       <c r="H391" t="n">
         <v>1101</v>
@@ -11737,7 +11737,7 @@
         <v>2.63800001144409</v>
       </c>
       <c r="G392" t="n">
-        <v>2.20842528343201</v>
+        <v>2.20842504501343</v>
       </c>
       <c r="H392" t="n">
         <v>750</v>
@@ -11795,7 +11795,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G394" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H394" t="n">
         <v>3419</v>
@@ -11824,7 +11824,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G395" t="n">
-        <v>2.23186588287354</v>
+        <v>2.23186564445496</v>
       </c>
       <c r="H395" t="n">
         <v>10542</v>
@@ -11853,7 +11853,7 @@
         <v>2.66599988937378</v>
       </c>
       <c r="G396" t="n">
-        <v>2.23186588287354</v>
+        <v>2.23186564445496</v>
       </c>
       <c r="H396" t="n">
         <v>850</v>
@@ -11882,7 +11882,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G397" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H397" t="n">
         <v>1</v>
@@ -11940,7 +11940,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G399" t="n">
-        <v>2.28376960754395</v>
+        <v>2.28376936912537</v>
       </c>
       <c r="H399" t="n">
         <v>13861</v>
@@ -11998,7 +11998,7 @@
         <v>2.79800009727478</v>
       </c>
       <c r="G401" t="n">
-        <v>2.3423707485199</v>
+        <v>2.34237098693848</v>
       </c>
       <c r="H401" t="n">
         <v>1800</v>
@@ -12114,7 +12114,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G405" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H405" t="n">
         <v>2580</v>
@@ -12143,7 +12143,7 @@
         <v>2.65400004386902</v>
       </c>
       <c r="G406" t="n">
-        <v>2.22181963920593</v>
+        <v>2.22181987762451</v>
       </c>
       <c r="H406" t="n">
         <v>2807</v>
@@ -12172,7 +12172,7 @@
         <v>2.69600009918213</v>
       </c>
       <c r="G407" t="n">
-        <v>2.25698041915894</v>
+        <v>2.25698065757751</v>
       </c>
       <c r="H407" t="n">
         <v>19</v>
@@ -12230,7 +12230,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G409" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H409" t="n">
         <v>3960</v>
@@ -12317,7 +12317,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G412" t="n">
-        <v>2.4947338104248</v>
+        <v>2.49473357200623</v>
       </c>
       <c r="H412" t="n">
         <v>58936</v>
@@ -12346,7 +12346,7 @@
         <v>3.03800010681152</v>
       </c>
       <c r="G413" t="n">
-        <v>2.54328870773315</v>
+        <v>2.54328894615173</v>
       </c>
       <c r="H413" t="n">
         <v>46684</v>
@@ -12404,7 +12404,7 @@
         <v>2.96799993515015</v>
       </c>
       <c r="G415" t="n">
-        <v>2.48468732833862</v>
+        <v>2.4846875667572</v>
       </c>
       <c r="H415" t="n">
         <v>1551</v>
@@ -12520,7 +12520,7 @@
         <v>2.84599995613098</v>
       </c>
       <c r="G419" t="n">
-        <v>2.38255429267883</v>
+        <v>2.38255405426025</v>
       </c>
       <c r="H419" t="n">
         <v>3250</v>
@@ -12549,7 +12549,7 @@
         <v>2.77800011634827</v>
       </c>
       <c r="G420" t="n">
-        <v>2.32562756538391</v>
+        <v>2.32562780380249</v>
       </c>
       <c r="H420" t="n">
         <v>9986</v>
@@ -12810,7 +12810,7 @@
         <v>2.72399997711182</v>
       </c>
       <c r="G429" t="n">
-        <v>2.28042078018188</v>
+        <v>2.28042101860046</v>
       </c>
       <c r="H429" t="n">
         <v>2600</v>
@@ -12839,7 +12839,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G430" t="n">
-        <v>2.28879237174988</v>
+        <v>2.28879284858704</v>
       </c>
       <c r="H430" t="n">
         <v>925</v>
@@ -12868,7 +12868,7 @@
         <v>2.73399996757507</v>
       </c>
       <c r="G431" t="n">
-        <v>2.28879237174988</v>
+        <v>2.28879284858704</v>
       </c>
       <c r="H431" t="n">
         <v>0</v>
@@ -12926,7 +12926,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G433" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H433" t="n">
         <v>7787</v>
@@ -12955,7 +12955,7 @@
         <v>2.74000000953674</v>
       </c>
       <c r="G434" t="n">
-        <v>2.29381537437439</v>
+        <v>2.29381561279297</v>
       </c>
       <c r="H434" t="n">
         <v>7223</v>
@@ -12984,7 +12984,7 @@
         <v>2.71399998664856</v>
       </c>
       <c r="G435" t="n">
-        <v>2.27204942703247</v>
+        <v>2.27204918861389</v>
       </c>
       <c r="H435" t="n">
         <v>900</v>
@@ -13013,7 +13013,7 @@
         <v>2.76600003242493</v>
       </c>
       <c r="G436" t="n">
-        <v>2.31558156013489</v>
+        <v>2.31558179855347</v>
       </c>
       <c r="H436" t="n">
         <v>18816</v>
@@ -13129,7 +13129,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G440" t="n">
-        <v>2.35241651535034</v>
+        <v>2.35241675376892</v>
       </c>
       <c r="H440" t="n">
         <v>13100</v>
@@ -13245,7 +13245,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G444" t="n">
-        <v>2.4026460647583</v>
+        <v>2.40264582633972</v>
       </c>
       <c r="H444" t="n">
         <v>1211</v>
@@ -13274,7 +13274,7 @@
         <v>2.83200001716614</v>
       </c>
       <c r="G445" t="n">
-        <v>2.37083411216736</v>
+        <v>2.37083387374878</v>
       </c>
       <c r="H445" t="n">
         <v>3011</v>
@@ -13361,7 +13361,7 @@
         <v>2.85800004005432</v>
       </c>
       <c r="G448" t="n">
-        <v>2.39260053634644</v>
+        <v>2.39260029792786</v>
       </c>
       <c r="H448" t="n">
         <v>4893</v>
@@ -13419,7 +13419,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G450" t="n">
-        <v>2.35241651535034</v>
+        <v>2.35241675376892</v>
       </c>
       <c r="H450" t="n">
         <v>3361</v>
@@ -13448,7 +13448,7 @@
         <v>2.81599998474121</v>
       </c>
       <c r="G451" t="n">
-        <v>2.35743927955627</v>
+        <v>2.35743951797485</v>
       </c>
       <c r="H451" t="n">
         <v>2696</v>
@@ -13477,7 +13477,7 @@
         <v>2.85400009155273</v>
       </c>
       <c r="G452" t="n">
-        <v>2.3892514705658</v>
+        <v>2.38925170898438</v>
       </c>
       <c r="H452" t="n">
         <v>13423</v>
@@ -13593,7 +13593,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G456" t="n">
-        <v>2.33065056800842</v>
+        <v>2.33065032958984</v>
       </c>
       <c r="H456" t="n">
         <v>16903</v>
@@ -13622,7 +13622,7 @@
         <v>2.78399991989136</v>
       </c>
       <c r="G457" t="n">
-        <v>2.33065056800842</v>
+        <v>2.33065032958984</v>
       </c>
       <c r="H457" t="n">
         <v>121</v>
@@ -13941,7 +13941,7 @@
         <v>2.75600004196167</v>
       </c>
       <c r="G468" t="n">
-        <v>2.30721020698547</v>
+        <v>2.30720996856689</v>
       </c>
       <c r="H468" t="n">
         <v>9061</v>
@@ -14231,7 +14231,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G478" t="n">
-        <v>2.2352147102356</v>
+        <v>2.23521447181702</v>
       </c>
       <c r="H478" t="n">
         <v>22224</v>
@@ -14289,7 +14289,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G480" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H480" t="n">
         <v>2763</v>
@@ -14318,7 +14318,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G481" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H481" t="n">
         <v>10423</v>
@@ -14376,7 +14376,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G483" t="n">
-        <v>2.22516846656799</v>
+        <v>2.22516870498657</v>
       </c>
       <c r="H483" t="n">
         <v>5045</v>
@@ -14405,7 +14405,7 @@
         <v>2.65799999237061</v>
       </c>
       <c r="G484" t="n">
-        <v>2.22516846656799</v>
+        <v>2.22516870498657</v>
       </c>
       <c r="H484" t="n">
         <v>2796</v>
@@ -14463,7 +14463,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G486" t="n">
-        <v>2.26367783546448</v>
+        <v>2.2636775970459</v>
       </c>
       <c r="H486" t="n">
         <v>1722</v>
@@ -14492,7 +14492,7 @@
         <v>2.7039999961853</v>
       </c>
       <c r="G487" t="n">
-        <v>2.26367783546448</v>
+        <v>2.2636775970459</v>
       </c>
       <c r="H487" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>2.7279999256134</v>
       </c>
       <c r="G488" t="n">
-        <v>2.28376960754395</v>
+        <v>2.28376936912537</v>
       </c>
       <c r="H488" t="n">
         <v>3338</v>
@@ -14637,7 +14637,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H492" t="n">
         <v>1250</v>
@@ -14695,7 +14695,7 @@
         <v>2.67799997329712</v>
       </c>
       <c r="G494" t="n">
-        <v>2.24191164970398</v>
+        <v>2.24191188812256</v>
       </c>
       <c r="H494" t="n">
         <v>2854</v>
@@ -14724,7 +14724,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G495" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H495" t="n">
         <v>5435</v>
@@ -14753,7 +14753,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G496" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H496" t="n">
         <v>1605</v>
@@ -14782,7 +14782,7 @@
         <v>2.65199995040894</v>
       </c>
       <c r="G497" t="n">
-        <v>2.22014570236206</v>
+        <v>2.22014546394348</v>
       </c>
       <c r="H497" t="n">
         <v>3373</v>
@@ -14840,7 +14840,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G499" t="n">
-        <v>2.28544402122498</v>
+        <v>2.2854437828064</v>
       </c>
       <c r="H499" t="n">
         <v>1607</v>
@@ -14956,7 +14956,7 @@
         <v>2.71000003814697</v>
       </c>
       <c r="G503" t="n">
-        <v>2.26870083808899</v>
+        <v>2.26870107650757</v>
       </c>
       <c r="H503" t="n">
         <v>2900</v>
@@ -15014,7 +15014,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G505" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H505" t="n">
         <v>7001</v>
@@ -15043,7 +15043,7 @@
         <v>2.64800000190735</v>
       </c>
       <c r="G506" t="n">
-        <v>2.21679663658142</v>
+        <v>2.216796875</v>
       </c>
       <c r="H506" t="n">
         <v>4326</v>
@@ -15072,7 +15072,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G507" t="n">
-        <v>2.16154408454895</v>
+        <v>2.16154456138611</v>
       </c>
       <c r="H507" t="n">
         <v>16456</v>
@@ -15101,7 +15101,7 @@
         <v>2.58400011062622</v>
       </c>
       <c r="G508" t="n">
-        <v>2.16321849822998</v>
+        <v>2.16321897506714</v>
       </c>
       <c r="H508" t="n">
         <v>8399</v>
@@ -15130,7 +15130,7 @@
         <v>2.58200001716614</v>
       </c>
       <c r="G509" t="n">
-        <v>2.16154408454895</v>
+        <v>2.16154456138611</v>
       </c>
       <c r="H509" t="n">
         <v>5173</v>
@@ -15159,7 +15159,7 @@
         <v>2.61199998855591</v>
       </c>
       <c r="G510" t="n">
-        <v>2.18665885925293</v>
+        <v>2.18665909767151</v>
       </c>
       <c r="H510" t="n">
         <v>3620</v>
@@ -15188,7 +15188,7 @@
         <v>2.6159999370575</v>
       </c>
       <c r="G511" t="n">
-        <v>2.19000768661499</v>
+        <v>2.19000792503357</v>
       </c>
       <c r="H511" t="n">
         <v>4083</v>
@@ -15246,7 +15246,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G513" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H513" t="n">
         <v>7544</v>
@@ -15304,7 +15304,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G515" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H515" t="n">
         <v>1690</v>
@@ -15333,7 +15333,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G516" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H516" t="n">
         <v>5412</v>
@@ -15391,7 +15391,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G518" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H518" t="n">
         <v>6410</v>
@@ -15420,7 +15420,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G519" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H519" t="n">
         <v>2803</v>
@@ -15449,7 +15449,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G520" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H520" t="n">
         <v>60857</v>
@@ -15478,7 +15478,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G521" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H521" t="n">
         <v>14606</v>
@@ -15507,7 +15507,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G522" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H522" t="n">
         <v>5832</v>
@@ -15536,7 +15536,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G523" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H523" t="n">
         <v>3735</v>
@@ -15565,7 +15565,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G524" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H524" t="n">
         <v>1330</v>
@@ -15594,7 +15594,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G525" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H525" t="n">
         <v>4875</v>
@@ -15623,7 +15623,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G526" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H526" t="n">
         <v>1009</v>
@@ -15681,7 +15681,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G528" t="n">
-        <v>2.21847128868103</v>
+        <v>2.21847105026245</v>
       </c>
       <c r="H528" t="n">
         <v>4342</v>
@@ -15710,7 +15710,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G529" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H529" t="n">
         <v>1800</v>
@@ -15855,7 +15855,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G534" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H534" t="n">
         <v>984</v>
@@ -15884,7 +15884,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G535" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H535" t="n">
         <v>1855</v>
@@ -15942,7 +15942,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G537" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H537" t="n">
         <v>5685</v>
@@ -15971,7 +15971,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G538" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H538" t="n">
         <v>18029</v>
@@ -16000,7 +16000,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G539" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H539" t="n">
         <v>9044</v>
@@ -16087,7 +16087,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G542" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H542" t="n">
         <v>8581</v>
@@ -16116,7 +16116,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G543" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H543" t="n">
         <v>7722</v>
@@ -16145,7 +16145,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G544" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H544" t="n">
         <v>2673</v>
@@ -16174,7 +16174,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G545" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H545" t="n">
         <v>1800</v>
@@ -16203,7 +16203,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H546" t="n">
         <v>1300</v>
@@ -16232,7 +16232,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G547" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H547" t="n">
         <v>1985</v>
@@ -16261,7 +16261,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G548" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H548" t="n">
         <v>1390</v>
@@ -16290,7 +16290,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G549" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H549" t="n">
         <v>0</v>
@@ -16319,7 +16319,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G550" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H550" t="n">
         <v>10107</v>
@@ -16348,7 +16348,7 @@
         <v>2.5</v>
       </c>
       <c r="G551" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H551" t="n">
         <v>7464</v>
@@ -16377,7 +16377,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G552" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H552" t="n">
         <v>7203</v>
@@ -16406,7 +16406,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G553" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H553" t="n">
         <v>10951</v>
@@ -16435,7 +16435,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G554" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475513458252</v>
       </c>
       <c r="H554" t="n">
         <v>19861</v>
@@ -16464,7 +16464,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G555" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H555" t="n">
         <v>3370</v>
@@ -16522,7 +16522,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G557" t="n">
-        <v>2.10126900672913</v>
+        <v>2.10126876831055</v>
       </c>
       <c r="H557" t="n">
         <v>8276</v>
@@ -16551,7 +16551,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G558" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266810417175</v>
       </c>
       <c r="H558" t="n">
         <v>1420</v>
@@ -16580,7 +16580,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G559" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266810417175</v>
       </c>
       <c r="H559" t="n">
         <v>1988</v>
@@ -16609,7 +16609,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G560" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266810417175</v>
       </c>
       <c r="H560" t="n">
         <v>2000</v>
@@ -16638,7 +16638,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266810417175</v>
       </c>
       <c r="H561" t="n">
         <v>75</v>
@@ -16899,7 +16899,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G570" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H570" t="n">
         <v>4499</v>
@@ -16928,7 +16928,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G571" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H571" t="n">
         <v>5450</v>
@@ -16957,7 +16957,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G572" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H572" t="n">
         <v>810</v>
@@ -16986,7 +16986,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G573" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H573" t="n">
         <v>69257</v>
@@ -17015,7 +17015,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G574" t="n">
-        <v>2.05941081047058</v>
+        <v>2.05941104888916</v>
       </c>
       <c r="H574" t="n">
         <v>5538</v>
@@ -17334,7 +17334,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G585" t="n">
-        <v>2.06778240203857</v>
+        <v>2.06778264045715</v>
       </c>
       <c r="H585" t="n">
         <v>16930</v>
@@ -17392,7 +17392,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G587" t="n">
-        <v>2.19335627555847</v>
+        <v>2.19335651397705</v>
       </c>
       <c r="H587" t="n">
         <v>20156</v>
@@ -17421,7 +17421,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G588" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H588" t="n">
         <v>10489</v>
@@ -17450,7 +17450,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G589" t="n">
-        <v>2.17661309242249</v>
+        <v>2.17661285400391</v>
       </c>
       <c r="H589" t="n">
         <v>19056</v>
@@ -17479,7 +17479,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G590" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H590" t="n">
         <v>4774</v>
@@ -17508,7 +17508,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H591" t="n">
         <v>9720</v>
@@ -17537,7 +17537,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G592" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H592" t="n">
         <v>37954</v>
@@ -17595,7 +17595,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G594" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H594" t="n">
         <v>812</v>
@@ -17624,7 +17624,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G595" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475513458252</v>
       </c>
       <c r="H595" t="n">
         <v>8105</v>
@@ -17740,7 +17740,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G599" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H599" t="n">
         <v>16850</v>
@@ -17769,7 +17769,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G600" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H600" t="n">
         <v>15758</v>
@@ -17798,7 +17798,7 @@
         <v>2.5</v>
       </c>
       <c r="G601" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H601" t="n">
         <v>5909</v>
@@ -17827,7 +17827,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G602" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H602" t="n">
         <v>929</v>
@@ -17856,7 +17856,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G603" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H603" t="n">
         <v>16435</v>
@@ -17885,7 +17885,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G604" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266810417175</v>
       </c>
       <c r="H604" t="n">
         <v>1612</v>
@@ -17914,7 +17914,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G605" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H605" t="n">
         <v>10604</v>
@@ -17943,7 +17943,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G606" t="n">
-        <v>2.04266786575317</v>
+        <v>2.04266810417175</v>
       </c>
       <c r="H606" t="n">
         <v>8516</v>
@@ -18320,7 +18320,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G619" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H619" t="n">
         <v>2150</v>
@@ -18349,7 +18349,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G620" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H620" t="n">
         <v>11523</v>
@@ -18378,7 +18378,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G621" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H621" t="n">
         <v>18421</v>
@@ -18436,7 +18436,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G623" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H623" t="n">
         <v>6806</v>
@@ -18465,7 +18465,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G624" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H624" t="n">
         <v>0</v>
@@ -18494,7 +18494,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G625" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H625" t="n">
         <v>2432</v>
@@ -18552,7 +18552,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G627" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H627" t="n">
         <v>16352</v>
@@ -18581,7 +18581,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G628" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H628" t="n">
         <v>1464</v>
@@ -18610,7 +18610,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G629" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H629" t="n">
         <v>0</v>
@@ -18639,7 +18639,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G630" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H630" t="n">
         <v>17402</v>
@@ -18668,7 +18668,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G631" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H631" t="n">
         <v>17617</v>
@@ -18784,7 +18784,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H635" t="n">
         <v>11880</v>
@@ -18871,7 +18871,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G638" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H638" t="n">
         <v>9880</v>
@@ -18900,7 +18900,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G639" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H639" t="n">
         <v>5501</v>
@@ -19074,7 +19074,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G645" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H645" t="n">
         <v>3500</v>
@@ -19103,7 +19103,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G646" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H646" t="n">
         <v>1650</v>
@@ -19132,7 +19132,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G647" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H647" t="n">
         <v>2390</v>
@@ -19161,7 +19161,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G648" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H648" t="n">
         <v>19602</v>
@@ -19509,7 +19509,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G660" t="n">
-        <v>2.05941081047058</v>
+        <v>2.05941104888916</v>
       </c>
       <c r="H660" t="n">
         <v>27013</v>
@@ -19683,7 +19683,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G666" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H666" t="n">
         <v>4634</v>
@@ -19741,7 +19741,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G668" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H668" t="n">
         <v>1332</v>
@@ -19770,7 +19770,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G669" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H669" t="n">
         <v>4</v>
@@ -19828,7 +19828,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G671" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H671" t="n">
         <v>1761</v>
@@ -19915,7 +19915,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H674" t="n">
         <v>7700</v>
@@ -19944,7 +19944,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G675" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H675" t="n">
         <v>9581</v>
@@ -20060,7 +20060,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G679" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H679" t="n">
         <v>1532</v>
@@ -20089,7 +20089,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G680" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H680" t="n">
         <v>12081</v>
@@ -20147,7 +20147,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G682" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H682" t="n">
         <v>15003</v>
@@ -20205,7 +20205,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G684" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H684" t="n">
         <v>84</v>
@@ -20234,7 +20234,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G685" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H685" t="n">
         <v>6020</v>
@@ -20263,7 +20263,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G686" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H686" t="n">
         <v>567</v>
@@ -20292,7 +20292,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G687" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H687" t="n">
         <v>9265</v>
@@ -20350,7 +20350,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G689" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H689" t="n">
         <v>5573</v>
@@ -20379,7 +20379,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G690" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H690" t="n">
         <v>24561</v>
@@ -20408,7 +20408,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G691" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H691" t="n">
         <v>13491</v>
@@ -20437,7 +20437,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G692" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H692" t="n">
         <v>1155</v>
@@ -20524,7 +20524,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G695" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H695" t="n">
         <v>11225</v>
@@ -20611,7 +20611,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G698" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H698" t="n">
         <v>913</v>
@@ -20698,7 +20698,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G701" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H701" t="n">
         <v>2949</v>
@@ -20727,7 +20727,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G702" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H702" t="n">
         <v>200</v>
@@ -20814,7 +20814,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G705" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H705" t="n">
         <v>3197</v>
@@ -20901,7 +20901,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G708" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H708" t="n">
         <v>12307</v>
@@ -20930,7 +20930,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G709" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H709" t="n">
         <v>11172</v>
@@ -21017,7 +21017,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G712" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H712" t="n">
         <v>201</v>
@@ -21046,7 +21046,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G713" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H713" t="n">
         <v>1200</v>
@@ -21133,7 +21133,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G716" t="n">
-        <v>1.75803351402283</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H716" t="n">
         <v>8743</v>
@@ -21278,7 +21278,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G721" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H721" t="n">
         <v>1550</v>
@@ -21307,7 +21307,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G722" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H722" t="n">
         <v>7949</v>
@@ -21336,7 +21336,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G723" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H723" t="n">
         <v>4248</v>
@@ -21423,7 +21423,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G726" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H726" t="n">
         <v>5624</v>
@@ -21452,7 +21452,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G727" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H727" t="n">
         <v>6793</v>
@@ -21539,7 +21539,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G730" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H730" t="n">
         <v>13567</v>
@@ -21568,7 +21568,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G731" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H731" t="n">
         <v>2175</v>
@@ -21597,7 +21597,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G732" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H732" t="n">
         <v>1000</v>
@@ -21626,7 +21626,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G733" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H733" t="n">
         <v>9925</v>
@@ -21655,7 +21655,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G734" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H734" t="n">
         <v>6923</v>
@@ -21684,7 +21684,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G735" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H735" t="n">
         <v>1932</v>
@@ -21713,7 +21713,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G736" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H736" t="n">
         <v>3553</v>
@@ -21742,7 +21742,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G737" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H737" t="n">
         <v>11972</v>
@@ -21771,7 +21771,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G738" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H738" t="n">
         <v>18808</v>
@@ -21800,7 +21800,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G739" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H739" t="n">
         <v>18110</v>
@@ -21945,7 +21945,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G744" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H744" t="n">
         <v>10571</v>
@@ -21974,7 +21974,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G745" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H745" t="n">
         <v>4281</v>
@@ -22003,7 +22003,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G746" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H746" t="n">
         <v>10786</v>
@@ -22090,7 +22090,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G749" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H749" t="n">
         <v>1080</v>
@@ -22119,7 +22119,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G750" t="n">
-        <v>1.97569525241852</v>
+        <v>1.97569477558136</v>
       </c>
       <c r="H750" t="n">
         <v>2189</v>
@@ -22148,7 +22148,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G751" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H751" t="n">
         <v>15600</v>
@@ -22177,7 +22177,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H752" t="n">
         <v>500</v>
@@ -22235,7 +22235,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G754" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H754" t="n">
         <v>3184</v>
@@ -22322,7 +22322,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G757" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H757" t="n">
         <v>3690</v>
@@ -22351,7 +22351,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G758" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H758" t="n">
         <v>2200</v>
@@ -22380,7 +22380,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G759" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H759" t="n">
         <v>5639</v>
@@ -22496,7 +22496,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G763" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H763" t="n">
         <v>591</v>
@@ -22525,7 +22525,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G764" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22786,7 +22786,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G773" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H773" t="n">
         <v>3986</v>
@@ -22815,7 +22815,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G774" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H774" t="n">
         <v>3700</v>
@@ -22844,7 +22844,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G775" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H775" t="n">
         <v>0</v>
@@ -22873,7 +22873,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G776" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H776" t="n">
         <v>1303</v>
@@ -22902,7 +22902,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G777" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H777" t="n">
         <v>4737</v>
@@ -22931,7 +22931,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G778" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H778" t="n">
         <v>6827</v>
@@ -22989,7 +22989,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G780" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H780" t="n">
         <v>5010</v>
@@ -23047,7 +23047,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G782" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H782" t="n">
         <v>256</v>
@@ -23105,7 +23105,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G784" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H784" t="n">
         <v>3539</v>
@@ -23134,7 +23134,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G785" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H785" t="n">
         <v>2128</v>
@@ -23163,7 +23163,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G786" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H786" t="n">
         <v>800</v>
@@ -23192,7 +23192,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G787" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H787" t="n">
         <v>2220</v>
@@ -23221,7 +23221,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G788" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H788" t="n">
         <v>0</v>
@@ -23250,7 +23250,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G789" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H789" t="n">
         <v>1100</v>
@@ -23279,7 +23279,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G790" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H790" t="n">
         <v>12087</v>
@@ -23337,7 +23337,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G792" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H792" t="n">
         <v>5850</v>
@@ -23453,7 +23453,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G796" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H796" t="n">
         <v>1400</v>
@@ -23482,7 +23482,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G797" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H797" t="n">
         <v>3229</v>
@@ -23540,7 +23540,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G799" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H799" t="n">
         <v>11069</v>
@@ -23569,7 +23569,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G800" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H800" t="n">
         <v>2600</v>
@@ -23627,7 +23627,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G802" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H802" t="n">
         <v>3832</v>
@@ -23656,7 +23656,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H803" t="n">
         <v>1268</v>
@@ -23743,7 +23743,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G806" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H806" t="n">
         <v>802</v>
@@ -23830,7 +23830,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G809" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H809" t="n">
         <v>2001</v>
@@ -23917,7 +23917,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G812" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H812" t="n">
         <v>2405</v>
@@ -23946,7 +23946,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G813" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H813" t="n">
         <v>2826</v>
@@ -24033,7 +24033,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G816" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H816" t="n">
         <v>6014</v>
@@ -24091,7 +24091,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G818" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H818" t="n">
         <v>15083</v>
@@ -24236,7 +24236,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G823" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H823" t="n">
         <v>2356</v>
@@ -24265,7 +24265,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G824" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H824" t="n">
         <v>4424</v>
@@ -24439,7 +24439,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H830" t="n">
         <v>3888</v>
@@ -24468,7 +24468,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G831" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H831" t="n">
         <v>683</v>
@@ -24497,7 +24497,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G832" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H832" t="n">
         <v>2898</v>
@@ -24526,7 +24526,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G833" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H833" t="n">
         <v>2103</v>
@@ -24555,7 +24555,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G834" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H834" t="n">
         <v>300</v>
@@ -24584,7 +24584,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G835" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H835" t="n">
         <v>2305</v>
@@ -24613,7 +24613,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G836" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H836" t="n">
         <v>2886</v>
@@ -24642,7 +24642,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G837" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H837" t="n">
         <v>1000</v>
@@ -24671,7 +24671,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G838" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H838" t="n">
         <v>3473</v>
@@ -24700,7 +24700,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G839" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H839" t="n">
         <v>2588</v>
@@ -24729,7 +24729,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G840" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H840" t="n">
         <v>501</v>
@@ -24758,7 +24758,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G841" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H841" t="n">
         <v>4430</v>
@@ -24787,7 +24787,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G842" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H842" t="n">
         <v>2500</v>
@@ -24816,7 +24816,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G843" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H843" t="n">
         <v>497</v>
@@ -24874,7 +24874,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G845" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H845" t="n">
         <v>4803</v>
@@ -24932,7 +24932,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G847" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H847" t="n">
         <v>3200</v>
@@ -24961,7 +24961,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G848" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H848" t="n">
         <v>8445</v>
@@ -25077,7 +25077,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G852" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H852" t="n">
         <v>1000</v>
@@ -25106,7 +25106,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G853" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H853" t="n">
         <v>2000</v>
@@ -25135,7 +25135,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G854" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H854" t="n">
         <v>3872</v>
@@ -25164,7 +25164,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G855" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H855" t="n">
         <v>2728</v>
@@ -25309,7 +25309,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G860" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H860" t="n">
         <v>343</v>
@@ -25454,7 +25454,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G865" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H865" t="n">
         <v>5</v>
@@ -25483,7 +25483,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G866" t="n">
-        <v>1.75803351402283</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H866" t="n">
         <v>6120</v>
@@ -25628,7 +25628,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G871" t="n">
-        <v>1.68268930912018</v>
+        <v>1.68268942832947</v>
       </c>
       <c r="H871" t="n">
         <v>7472</v>
@@ -25831,7 +25831,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G878" t="n">
-        <v>1.63245987892151</v>
+        <v>1.6324599981308</v>
       </c>
       <c r="H878" t="n">
         <v>2912</v>
@@ -25860,7 +25860,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G879" t="n">
-        <v>1.63245987892151</v>
+        <v>1.6324599981308</v>
       </c>
       <c r="H879" t="n">
         <v>13775</v>
@@ -25976,7 +25976,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G883" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H883" t="n">
         <v>536</v>
@@ -26005,7 +26005,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G884" t="n">
-        <v>1.64920318126678</v>
+        <v>1.6492030620575</v>
       </c>
       <c r="H884" t="n">
         <v>13029</v>
@@ -26063,7 +26063,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G886" t="n">
-        <v>1.62408840656281</v>
+        <v>1.62408828735352</v>
       </c>
       <c r="H886" t="n">
         <v>7320</v>
@@ -26092,7 +26092,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G887" t="n">
-        <v>1.63245987892151</v>
+        <v>1.6324599981308</v>
       </c>
       <c r="H887" t="n">
         <v>19316</v>
@@ -26411,7 +26411,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G898" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H898" t="n">
         <v>13892</v>
@@ -26440,7 +26440,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G899" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H899" t="n">
         <v>5146</v>
@@ -26469,7 +26469,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G900" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H900" t="n">
         <v>3694</v>
@@ -26498,7 +26498,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G901" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H901" t="n">
         <v>2716</v>
@@ -26527,7 +26527,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G902" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H902" t="n">
         <v>4588</v>
@@ -26556,7 +26556,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G903" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H903" t="n">
         <v>4103</v>
@@ -26585,7 +26585,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G904" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H904" t="n">
         <v>2094</v>
@@ -26614,7 +26614,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G905" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H905" t="n">
         <v>4903</v>
@@ -26643,7 +26643,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G906" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H906" t="n">
         <v>1414</v>
@@ -26672,7 +26672,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G907" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H907" t="n">
         <v>601</v>
@@ -26701,7 +26701,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G908" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H908" t="n">
         <v>3344</v>
@@ -26730,7 +26730,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G909" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H909" t="n">
         <v>0</v>
@@ -26846,7 +26846,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G913" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H913" t="n">
         <v>1600</v>
@@ -27049,7 +27049,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G920" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H920" t="n">
         <v>7902</v>
@@ -27107,7 +27107,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G922" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H922" t="n">
         <v>2463</v>
@@ -27194,7 +27194,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G925" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H925" t="n">
         <v>5083</v>
@@ -27281,7 +27281,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G928" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H928" t="n">
         <v>977</v>
@@ -27310,7 +27310,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G929" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H929" t="n">
         <v>256</v>
@@ -27339,7 +27339,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G930" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H930" t="n">
         <v>2800</v>
@@ -27397,7 +27397,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G932" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H932" t="n">
         <v>3691</v>
@@ -27426,7 +27426,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G933" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H933" t="n">
         <v>770</v>
@@ -27484,7 +27484,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G935" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H935" t="n">
         <v>1650</v>
@@ -27600,7 +27600,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G939" t="n">
-        <v>1.75803351402283</v>
+        <v>1.75803363323212</v>
       </c>
       <c r="H939" t="n">
         <v>6005</v>
@@ -27716,7 +27716,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G943" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H943" t="n">
         <v>24151</v>
@@ -27919,7 +27919,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G950" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H950" t="n">
         <v>3240</v>
@@ -27977,7 +27977,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G952" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H952" t="n">
         <v>27709</v>
@@ -28064,7 +28064,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G955" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H955" t="n">
         <v>9230</v>
@@ -28093,7 +28093,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G956" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H956" t="n">
         <v>3149</v>
@@ -28122,7 +28122,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G957" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H957" t="n">
         <v>6241</v>
@@ -28644,7 +28644,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G975" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H975" t="n">
         <v>1259</v>
@@ -28731,7 +28731,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G978" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H978" t="n">
         <v>15981</v>
@@ -28760,7 +28760,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G979" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H979" t="n">
         <v>23662</v>
@@ -28847,7 +28847,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G982" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H982" t="n">
         <v>4216</v>
@@ -28876,7 +28876,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G983" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H983" t="n">
         <v>50294</v>
@@ -28934,7 +28934,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G985" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H985" t="n">
         <v>178991</v>
@@ -28992,7 +28992,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G987" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H987" t="n">
         <v>40415</v>
@@ -29050,7 +29050,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G989" t="n">
-        <v>2.16824150085449</v>
+        <v>2.16824173927307</v>
       </c>
       <c r="H989" t="n">
         <v>11373</v>
@@ -29079,7 +29079,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G990" t="n">
-        <v>2.11801218986511</v>
+        <v>2.11801195144653</v>
       </c>
       <c r="H990" t="n">
         <v>26705</v>
@@ -29108,7 +29108,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H991" t="n">
         <v>12330</v>
@@ -29137,7 +29137,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G992" t="n">
-        <v>2.10126900672913</v>
+        <v>2.10126876831055</v>
       </c>
       <c r="H992" t="n">
         <v>3797</v>
@@ -29166,7 +29166,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G993" t="n">
-        <v>2.14312672615051</v>
+        <v>2.14312696456909</v>
       </c>
       <c r="H993" t="n">
         <v>32055</v>
@@ -29253,7 +29253,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G996" t="n">
-        <v>2.24358606338501</v>
+        <v>2.24358582496643</v>
       </c>
       <c r="H996" t="n">
         <v>39508</v>
@@ -29311,7 +29311,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G998" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475513458252</v>
       </c>
       <c r="H998" t="n">
         <v>21041</v>
@@ -29398,7 +29398,7 @@
         <v>2.5</v>
       </c>
       <c r="G1001" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H1001" t="n">
         <v>4904</v>
@@ -29427,7 +29427,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1002" t="n">
-        <v>2.12638354301453</v>
+        <v>2.12638378143311</v>
       </c>
       <c r="H1002" t="n">
         <v>6668</v>
@@ -29485,7 +29485,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1004" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475513458252</v>
       </c>
       <c r="H1004" t="n">
         <v>4848</v>
@@ -29543,7 +29543,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G1006" t="n">
-        <v>2.1347553730011</v>
+        <v>2.13475513458252</v>
       </c>
       <c r="H1006" t="n">
         <v>593</v>
@@ -29601,7 +29601,7 @@
         <v>2.5</v>
       </c>
       <c r="G1008" t="n">
-        <v>2.09289741516113</v>
+        <v>2.09289717674255</v>
       </c>
       <c r="H1008" t="n">
         <v>7330</v>
@@ -29659,7 +29659,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1010" t="n">
-        <v>2.08452582359314</v>
+        <v>2.08452558517456</v>
       </c>
       <c r="H1010" t="n">
         <v>6972</v>
@@ -29688,7 +29688,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1011" t="n">
-        <v>2.07615423202515</v>
+        <v>2.07615399360657</v>
       </c>
       <c r="H1011" t="n">
         <v>7285</v>
@@ -29746,7 +29746,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1013" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H1013" t="n">
         <v>9251</v>
@@ -29862,7 +29862,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1017" t="n">
-        <v>2.05103921890259</v>
+        <v>2.05103969573975</v>
       </c>
       <c r="H1017" t="n">
         <v>7730</v>
@@ -30094,7 +30094,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1025" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1025" t="n">
         <v>3070</v>
@@ -30152,7 +30152,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H1027" t="n">
         <v>26611</v>
@@ -30181,7 +30181,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H1028" t="n">
         <v>6112</v>
@@ -30210,7 +30210,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H1029" t="n">
         <v>1805</v>
@@ -30239,7 +30239,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H1030" t="n">
         <v>8304</v>
@@ -30268,7 +30268,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.96732330322266</v>
+        <v>1.96732318401337</v>
       </c>
       <c r="H1031" t="n">
         <v>3685</v>
@@ -30471,7 +30471,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.87523591518402</v>
+        <v>1.87523603439331</v>
       </c>
       <c r="H1038" t="n">
         <v>18702</v>
@@ -30529,7 +30529,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.85849285125732</v>
+        <v>1.85849273204803</v>
       </c>
       <c r="H1040" t="n">
         <v>4415</v>
@@ -30587,7 +30587,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.91709387302399</v>
+        <v>1.91709399223328</v>
       </c>
       <c r="H1042" t="n">
         <v>2690</v>
@@ -30674,7 +30674,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H1045" t="n">
         <v>8755</v>
@@ -30732,7 +30732,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1047" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1047" t="n">
         <v>3128</v>
@@ -30790,7 +30790,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1049" t="n">
         <v>4945</v>
@@ -30819,7 +30819,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1050" t="n">
         <v>5064</v>
@@ -30877,7 +30877,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1052" t="n">
-        <v>1.93383693695068</v>
+        <v>1.93383705615997</v>
       </c>
       <c r="H1052" t="n">
         <v>3790</v>
@@ -30906,7 +30906,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.82500648498535</v>
+        <v>1.82500660419464</v>
       </c>
       <c r="H1053" t="n">
         <v>14075</v>
@@ -30935,7 +30935,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.84174954891205</v>
+        <v>1.84174966812134</v>
       </c>
       <c r="H1054" t="n">
         <v>2093</v>
@@ -30964,7 +30964,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H1055" t="n">
         <v>3728</v>
@@ -30993,7 +30993,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.86686444282532</v>
+        <v>1.86686432361603</v>
       </c>
       <c r="H1056" t="n">
         <v>61</v>
@@ -31022,7 +31022,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.83337807655334</v>
+        <v>1.83337831497192</v>
       </c>
       <c r="H1057" t="n">
         <v>8027</v>
@@ -31080,7 +31080,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.74966204166412</v>
+        <v>1.74966216087341</v>
       </c>
       <c r="H1059" t="n">
         <v>10342</v>
@@ -31109,7 +31109,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.74966204166412</v>
+        <v>1.74966216087341</v>
       </c>
       <c r="H1060" t="n">
         <v>3550</v>
@@ -31138,7 +31138,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.68268930912018</v>
+        <v>1.68268942832947</v>
       </c>
       <c r="H1061" t="n">
         <v>9201</v>
@@ -31283,7 +31283,7 @@
         <v>1.35500001907349</v>
       </c>
       <c r="G1066" t="n">
-        <v>1.13435041904449</v>
+        <v>1.13435053825378</v>
       </c>
       <c r="H1066" t="n">
         <v>6492</v>
@@ -31370,7 +31370,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1069" t="n">
-        <v>1.22643768787384</v>
+        <v>1.22643792629242</v>
       </c>
       <c r="H1069" t="n">
         <v>2290</v>
@@ -31428,7 +31428,7 @@
         <v>1.45500004291534</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.21806621551514</v>
+        <v>1.21806633472443</v>
       </c>
       <c r="H1071" t="n">
         <v>7190</v>
@@ -31457,7 +31457,7 @@
         <v>1.4650000333786</v>
       </c>
       <c r="G1072" t="n">
-        <v>1.22643768787384</v>
+        <v>1.22643792629242</v>
       </c>
       <c r="H1072" t="n">
         <v>32047</v>
@@ -31515,7 +31515,7 @@
         <v>1.58500003814697</v>
       </c>
       <c r="G1074" t="n">
-        <v>1.32689690589905</v>
+        <v>1.32689702510834</v>
       </c>
       <c r="H1074" t="n">
         <v>17265</v>
@@ -31660,7 +31660,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1079" t="n">
         <v>6800</v>
@@ -31747,7 +31747,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1082" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1082" t="n">
         <v>10304</v>
@@ -31950,7 +31950,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1089" t="n">
         <v>4026</v>
@@ -31979,7 +31979,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1090" t="n">
         <v>15050</v>
@@ -32008,7 +32008,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1091" t="n">
         <v>3000</v>
@@ -32066,7 +32066,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1093" t="n">
         <v>377</v>
@@ -32124,7 +32124,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.52362930774689</v>
+        <v>1.5236291885376</v>
       </c>
       <c r="H1095" t="n">
         <v>16845</v>
@@ -32153,7 +32153,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1096" t="n">
         <v>26453</v>
@@ -32240,7 +32240,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1099" t="n">
-        <v>1.55292987823486</v>
+        <v>1.55292975902557</v>
       </c>
       <c r="H1099" t="n">
         <v>6020</v>
@@ -32327,7 +32327,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1102" t="n">
         <v>21904</v>
@@ -32414,7 +32414,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1105" t="n">
         <v>22966</v>
@@ -32443,7 +32443,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1106" t="n">
         <v>23388</v>
@@ -32530,7 +32530,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339951992035</v>
       </c>
       <c r="H1109" t="n">
         <v>21164</v>
@@ -32617,7 +32617,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.43154180049896</v>
+        <v>1.43154168128967</v>
       </c>
       <c r="H1112" t="n">
         <v>1694</v>
@@ -32646,7 +32646,7 @@
         <v>1.74500000476837</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.46084249019623</v>
+        <v>1.46084237098694</v>
       </c>
       <c r="H1113" t="n">
         <v>13864</v>
@@ -32733,7 +32733,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1116" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1116" t="n">
         <v>14671</v>
@@ -32907,7 +32907,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1122" t="n">
         <v>5260</v>
@@ -32936,7 +32936,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1123" t="n">
         <v>0</v>
@@ -33052,7 +33052,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1127" t="n">
         <v>1050</v>
@@ -33139,7 +33139,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.43154180049896</v>
+        <v>1.43154168128967</v>
       </c>
       <c r="H1130" t="n">
         <v>7599</v>
@@ -33197,7 +33197,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1132" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1132" t="n">
         <v>4148</v>
@@ -33226,7 +33226,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1133" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1133" t="n">
         <v>11410</v>
@@ -33400,7 +33400,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1139" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1139" t="n">
         <v>20798</v>
@@ -33487,7 +33487,7 @@
         <v>1.76499998569489</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.47758555412292</v>
+        <v>1.47758543491364</v>
       </c>
       <c r="H1142" t="n">
         <v>500</v>
@@ -33603,7 +33603,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1146" t="n">
         <v>2800</v>
@@ -33632,7 +33632,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339951992035</v>
       </c>
       <c r="H1147" t="n">
         <v>7208</v>
@@ -33864,7 +33864,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1155" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1155" t="n">
         <v>6963</v>
@@ -33951,7 +33951,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1158" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1158" t="n">
         <v>3500</v>
@@ -33980,7 +33980,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1159" t="n">
-        <v>1.40642690658569</v>
+        <v>1.40642702579498</v>
       </c>
       <c r="H1159" t="n">
         <v>4677</v>
@@ -34038,7 +34038,7 @@
         <v>1.63499999046326</v>
       </c>
       <c r="G1161" t="n">
-        <v>1.36875474452972</v>
+        <v>1.36875486373901</v>
       </c>
       <c r="H1161" t="n">
         <v>2579</v>
@@ -34125,7 +34125,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1164" t="n">
-        <v>1.38131237030029</v>
+        <v>1.38131213188171</v>
       </c>
       <c r="H1164" t="n">
         <v>16170</v>
@@ -34212,7 +34212,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1167" t="n">
-        <v>1.43572747707367</v>
+        <v>1.43572759628296</v>
       </c>
       <c r="H1167" t="n">
         <v>9615</v>
@@ -34241,7 +34241,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1168" t="n">
-        <v>1.40642690658569</v>
+        <v>1.40642702579498</v>
       </c>
       <c r="H1168" t="n">
         <v>400</v>
@@ -34270,7 +34270,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1169" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1169" t="n">
         <v>100</v>
@@ -34328,7 +34328,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1171" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1171" t="n">
         <v>1810</v>
@@ -34473,7 +34473,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1176" t="n">
-        <v>1.40642690658569</v>
+        <v>1.40642702579498</v>
       </c>
       <c r="H1176" t="n">
         <v>3245</v>
@@ -34502,7 +34502,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1177" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1177" t="n">
         <v>250</v>
@@ -34589,7 +34589,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1180" t="n">
-        <v>1.40642690658569</v>
+        <v>1.40642702579498</v>
       </c>
       <c r="H1180" t="n">
         <v>175</v>
@@ -34647,7 +34647,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1182" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1182" t="n">
         <v>1326</v>
@@ -34734,7 +34734,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1185" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1185" t="n">
         <v>14317</v>
@@ -34792,7 +34792,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1187" t="n">
         <v>4762</v>
@@ -34821,7 +34821,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1188" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1188" t="n">
         <v>0</v>
@@ -34879,7 +34879,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.43154180049896</v>
+        <v>1.43154168128967</v>
       </c>
       <c r="H1190" t="n">
         <v>2</v>
@@ -35111,7 +35111,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.55292987823486</v>
+        <v>1.55292975902557</v>
       </c>
       <c r="H1198" t="n">
         <v>38221</v>
@@ -35169,7 +35169,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1200" t="n">
         <v>9907</v>
@@ -35198,7 +35198,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.62408840656281</v>
+        <v>1.62408828735352</v>
       </c>
       <c r="H1201" t="n">
         <v>62126</v>
@@ -35227,7 +35227,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1202" t="n">
         <v>17323</v>
@@ -35256,7 +35256,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1203" t="n">
         <v>1151</v>
@@ -35285,7 +35285,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1204" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1204" t="n">
         <v>1750</v>
@@ -35343,7 +35343,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1206" t="n">
         <v>14696</v>
@@ -35372,7 +35372,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1207" t="n">
         <v>8851</v>
@@ -35459,7 +35459,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1210" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1210" t="n">
         <v>27630</v>
@@ -35488,7 +35488,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1211" t="n">
-        <v>1.54455828666687</v>
+        <v>1.54455816745758</v>
       </c>
       <c r="H1211" t="n">
         <v>5804</v>
@@ -35546,7 +35546,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1213" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1213" t="n">
         <v>6817</v>
@@ -35691,7 +35691,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1218" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1218" t="n">
         <v>6600</v>
@@ -35720,7 +35720,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1219" t="n">
-        <v>1.43154180049896</v>
+        <v>1.43154168128967</v>
       </c>
       <c r="H1219" t="n">
         <v>6280</v>
@@ -35749,7 +35749,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1220" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339951992035</v>
       </c>
       <c r="H1220" t="n">
         <v>25475</v>
@@ -35836,7 +35836,7 @@
         <v>1.68499994277954</v>
       </c>
       <c r="G1223" t="n">
-        <v>1.41061282157898</v>
+        <v>1.41061270236969</v>
       </c>
       <c r="H1223" t="n">
         <v>3650</v>
@@ -35865,7 +35865,7 @@
         <v>1.69500005245209</v>
       </c>
       <c r="G1224" t="n">
-        <v>1.41898441314697</v>
+        <v>1.41898453235626</v>
       </c>
       <c r="H1224" t="n">
         <v>1712</v>
@@ -35894,7 +35894,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1225" t="n">
-        <v>1.38968372344971</v>
+        <v>1.389683842659</v>
       </c>
       <c r="H1225" t="n">
         <v>200</v>
@@ -35952,7 +35952,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1227" t="n">
-        <v>1.33945429325104</v>
+        <v>1.33945441246033</v>
       </c>
       <c r="H1227" t="n">
         <v>5941</v>
@@ -35981,7 +35981,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.33945429325104</v>
+        <v>1.33945441246033</v>
       </c>
       <c r="H1228" t="n">
         <v>4359</v>
@@ -36010,7 +36010,7 @@
         <v>1.6599999666214</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.38968372344971</v>
+        <v>1.389683842659</v>
       </c>
       <c r="H1229" t="n">
         <v>2050</v>
@@ -36039,7 +36039,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1230" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1230" t="n">
         <v>17178</v>
@@ -36068,7 +36068,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1231" t="n">
-        <v>1.43154180049896</v>
+        <v>1.43154168128967</v>
       </c>
       <c r="H1231" t="n">
         <v>3921</v>
@@ -36097,7 +36097,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1232" t="n">
-        <v>1.43154180049896</v>
+        <v>1.43154168128967</v>
       </c>
       <c r="H1232" t="n">
         <v>5096</v>
@@ -36155,7 +36155,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.42317008972168</v>
+        <v>1.42317020893097</v>
       </c>
       <c r="H1234" t="n">
         <v>57052</v>
@@ -36271,7 +36271,7 @@
         <v>1.7150000333786</v>
       </c>
       <c r="G1238" t="n">
-        <v>1.43572747707367</v>
+        <v>1.43572759628296</v>
       </c>
       <c r="H1238" t="n">
         <v>5018</v>
@@ -36300,7 +36300,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1239" t="n">
-        <v>1.43154180049896</v>
+        <v>1.43154168128967</v>
       </c>
       <c r="H1239" t="n">
         <v>20</v>
@@ -36358,7 +36358,7 @@
         <v>1.75999999046326</v>
       </c>
       <c r="G1241" t="n">
-        <v>1.47339963912964</v>
+        <v>1.47339951992035</v>
       </c>
       <c r="H1241" t="n">
         <v>14984</v>
@@ -36387,7 +36387,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1242" t="n">
         <v>18208</v>
@@ -36416,7 +36416,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G1243" t="n">
-        <v>1.53618669509888</v>
+        <v>1.53618657588959</v>
       </c>
       <c r="H1243" t="n">
         <v>3672</v>
@@ -36445,7 +36445,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1244" t="n">
         <v>3772</v>
@@ -36503,7 +36503,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1246" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1246" t="n">
         <v>35710</v>
@@ -36561,7 +36561,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1248" t="n">
         <v>10000</v>
@@ -36590,7 +36590,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1249" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1249" t="n">
         <v>19756</v>
@@ -36619,7 +36619,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1250" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1250" t="n">
         <v>22196</v>
@@ -36648,7 +36648,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1251" t="n">
-        <v>1.62408840656281</v>
+        <v>1.62408828735352</v>
       </c>
       <c r="H1251" t="n">
         <v>21214</v>
@@ -36735,7 +36735,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1254" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1254" t="n">
         <v>15059</v>
@@ -36793,7 +36793,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.62408840656281</v>
+        <v>1.62408828735352</v>
       </c>
       <c r="H1256" t="n">
         <v>29462</v>
@@ -36909,7 +36909,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1260" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1260" t="n">
         <v>24094</v>
@@ -36967,7 +36967,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G1262" t="n">
-        <v>1.64920318126678</v>
+        <v>1.6492030620575</v>
       </c>
       <c r="H1262" t="n">
         <v>23031</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1263" t="n">
         <v>31133</v>
@@ -37025,7 +37025,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1264" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1264" t="n">
         <v>22054</v>
@@ -37170,7 +37170,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1269" t="n">
-        <v>1.55292987823486</v>
+        <v>1.55292975902557</v>
       </c>
       <c r="H1269" t="n">
         <v>9976</v>
@@ -37315,7 +37315,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1274" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1274" t="n">
         <v>4470</v>
@@ -37344,7 +37344,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1275" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1275" t="n">
         <v>7091</v>
@@ -37373,7 +37373,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1276" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1276" t="n">
         <v>7499</v>
@@ -37431,7 +37431,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1278" t="n">
         <v>900</v>
@@ -37489,7 +37489,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G1280" t="n">
-        <v>1.52362930774689</v>
+        <v>1.5236291885376</v>
       </c>
       <c r="H1280" t="n">
         <v>5300</v>
@@ -37576,7 +37576,7 @@
         <v>1.93499994277954</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.61990249156952</v>
+        <v>1.61990237236023</v>
       </c>
       <c r="H1283" t="n">
         <v>11271</v>
@@ -37634,7 +37634,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1285" t="n">
-        <v>1.54455828666687</v>
+        <v>1.54455816745758</v>
       </c>
       <c r="H1285" t="n">
         <v>10519</v>
@@ -37750,7 +37750,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1289" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1289" t="n">
         <v>9470</v>
@@ -37808,7 +37808,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1291" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1291" t="n">
         <v>11472</v>
@@ -37837,7 +37837,7 @@
         <v>1.78999996185303</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.49851441383362</v>
+        <v>1.49851453304291</v>
       </c>
       <c r="H1292" t="n">
         <v>726</v>
@@ -37866,7 +37866,7 @@
         <v>1.77499997615814</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.48595702648163</v>
+        <v>1.48595714569092</v>
       </c>
       <c r="H1293" t="n">
         <v>4601</v>
@@ -37953,7 +37953,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1296" t="n">
         <v>17338</v>
@@ -38011,7 +38011,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1298" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1298" t="n">
         <v>20207</v>
@@ -38040,7 +38040,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1299" t="n">
         <v>55</v>
@@ -38069,7 +38069,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1300" t="n">
         <v>5936</v>
@@ -38127,7 +38127,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1302" t="n">
         <v>7041</v>
@@ -38156,7 +38156,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1303" t="n">
-        <v>1.55292987823486</v>
+        <v>1.55292975902557</v>
       </c>
       <c r="H1303" t="n">
         <v>11336</v>
@@ -38330,7 +38330,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1309" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1309" t="n">
         <v>5186</v>
@@ -38388,7 +38388,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1311" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1311" t="n">
         <v>2957</v>
@@ -38417,7 +38417,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1312" t="n">
-        <v>1.51525771617889</v>
+        <v>1.51525747776031</v>
       </c>
       <c r="H1312" t="n">
         <v>0</v>
@@ -38533,7 +38533,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1316" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1316" t="n">
         <v>30392</v>
@@ -38562,7 +38562,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1317" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1317" t="n">
         <v>8829</v>
@@ -38620,7 +38620,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1319" t="n">
-        <v>1.54455828666687</v>
+        <v>1.54455816745758</v>
       </c>
       <c r="H1319" t="n">
         <v>10198</v>
@@ -38707,7 +38707,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1322" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1322" t="n">
         <v>11505</v>
@@ -38736,7 +38736,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1323" t="n">
-        <v>1.55292987823486</v>
+        <v>1.55292975902557</v>
       </c>
       <c r="H1323" t="n">
         <v>6150</v>
@@ -38794,7 +38794,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1325" t="n">
-        <v>1.54455828666687</v>
+        <v>1.54455816745758</v>
       </c>
       <c r="H1325" t="n">
         <v>179</v>
@@ -38968,7 +38968,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1331" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1331" t="n">
         <v>30840</v>
@@ -38997,7 +38997,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1332" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1332" t="n">
         <v>8230</v>
@@ -39026,7 +39026,7 @@
         <v>1.84500002861023</v>
       </c>
       <c r="G1333" t="n">
-        <v>1.54455828666687</v>
+        <v>1.54455816745758</v>
       </c>
       <c r="H1333" t="n">
         <v>3515</v>
@@ -39113,7 +39113,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1336" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1336" t="n">
         <v>1529</v>
@@ -39142,7 +39142,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1337" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1337" t="n">
         <v>1010</v>
@@ -39171,7 +39171,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1338" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1338" t="n">
         <v>22599</v>
@@ -39229,7 +39229,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1340" t="n">
         <v>6500</v>
@@ -39258,7 +39258,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1341" t="n">
         <v>5222</v>
@@ -39287,7 +39287,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1342" t="n">
         <v>5805</v>
@@ -39316,7 +39316,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1343" t="n">
         <v>5668</v>
@@ -39374,7 +39374,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1345" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1345" t="n">
         <v>43701</v>
@@ -39606,7 +39606,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1353" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1353" t="n">
         <v>12100</v>
@@ -39693,7 +39693,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1356" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1356" t="n">
         <v>4400</v>
@@ -39722,7 +39722,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1357" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1357" t="n">
         <v>0</v>
@@ -39838,7 +39838,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1361" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1361" t="n">
         <v>2127</v>
@@ -39867,7 +39867,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1362" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1362" t="n">
         <v>0</v>
@@ -39896,7 +39896,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1363" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1363" t="n">
         <v>12451</v>
@@ -39925,7 +39925,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1364" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1364" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1367" t="n">
         <v>1000</v>
@@ -40099,7 +40099,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1370" t="n">
         <v>5999</v>
@@ -40128,7 +40128,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1371" t="n">
         <v>10437</v>
@@ -40157,7 +40157,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1372" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1372" t="n">
         <v>7070</v>
@@ -40215,7 +40215,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1374" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1374" t="n">
         <v>27312</v>
@@ -40244,7 +40244,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1375" t="n">
         <v>3283</v>
@@ -40273,7 +40273,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1376" t="n">
         <v>5985</v>
@@ -40389,7 +40389,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1380" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1380" t="n">
         <v>4607</v>
@@ -40418,7 +40418,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1381" t="n">
         <v>7296</v>
@@ -40447,7 +40447,7 @@
         <v>1.92499995231628</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.61153090000153</v>
+        <v>1.61153101921082</v>
       </c>
       <c r="H1382" t="n">
         <v>400</v>
@@ -40476,7 +40476,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1383" t="n">
         <v>3336</v>
@@ -40505,7 +40505,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1384" t="n">
         <v>808</v>
@@ -40563,7 +40563,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1386" t="n">
         <v>3693</v>
@@ -40708,7 +40708,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.62408840656281</v>
+        <v>1.62408828735352</v>
       </c>
       <c r="H1391" t="n">
         <v>2182</v>
@@ -40737,7 +40737,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1392" t="n">
-        <v>1.62408840656281</v>
+        <v>1.62408828735352</v>
       </c>
       <c r="H1392" t="n">
         <v>1010</v>
@@ -40766,7 +40766,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1393" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1393" t="n">
         <v>9710</v>
@@ -40795,7 +40795,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1394" t="n">
-        <v>1.59897339344025</v>
+        <v>1.59897351264954</v>
       </c>
       <c r="H1394" t="n">
         <v>30509</v>
@@ -40853,7 +40853,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1396" t="n">
-        <v>1.62408840656281</v>
+        <v>1.62408828735352</v>
       </c>
       <c r="H1396" t="n">
         <v>12484</v>
@@ -40911,7 +40911,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1398" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1398" t="n">
         <v>26790</v>
@@ -40969,7 +40969,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1400" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1400" t="n">
         <v>7590</v>
@@ -40998,7 +40998,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1401" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1401" t="n">
         <v>29032</v>
@@ -41056,7 +41056,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1403" t="n">
-        <v>1.55292987823486</v>
+        <v>1.55292975902557</v>
       </c>
       <c r="H1403" t="n">
         <v>9459</v>
@@ -41143,7 +41143,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1406" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1406" t="n">
         <v>6393</v>
@@ -41172,7 +41172,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1407" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1407" t="n">
         <v>5882</v>
@@ -41201,7 +41201,7 @@
         <v>1.875</v>
       </c>
       <c r="G1408" t="n">
-        <v>1.56967282295227</v>
+        <v>1.56967294216156</v>
       </c>
       <c r="H1408" t="n">
         <v>5807</v>
@@ -41259,7 +41259,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1410" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1410" t="n">
         <v>30252</v>
@@ -41462,7 +41462,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1417" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1417" t="n">
         <v>1500</v>
@@ -41491,7 +41491,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1418" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1418" t="n">
         <v>0</v>
@@ -41520,7 +41520,7 @@
         <v>1.86500000953674</v>
       </c>
       <c r="G1419" t="n">
-        <v>1.56130135059357</v>
+        <v>1.56130158901215</v>
       </c>
       <c r="H1419" t="n">
         <v>500</v>
@@ -41578,7 +41578,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1421" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1421" t="n">
         <v>11049</v>
@@ -41665,7 +41665,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1424" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1424" t="n">
         <v>3203</v>
@@ -41694,7 +41694,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1425" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1425" t="n">
         <v>0</v>
@@ -41723,7 +41723,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1426" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1426" t="n">
         <v>3720</v>
@@ -41752,7 +41752,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1427" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1427" t="n">
         <v>0</v>
@@ -41781,7 +41781,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1428" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1428" t="n">
         <v>0</v>
@@ -41810,7 +41810,7 @@
         <v>1.85500001907349</v>
       </c>
       <c r="G1429" t="n">
-        <v>1.55292987823486</v>
+        <v>1.55292975902557</v>
       </c>
       <c r="H1429" t="n">
         <v>3476</v>
@@ -41839,7 +41839,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1430" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1430" t="n">
         <v>1636</v>
@@ -41868,7 +41868,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1431" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1431" t="n">
         <v>4933</v>
@@ -41897,7 +41897,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1432" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1432" t="n">
         <v>0</v>
@@ -41926,7 +41926,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G1433" t="n">
-        <v>1.54874396324158</v>
+        <v>1.54874408245087</v>
       </c>
       <c r="H1433" t="n">
         <v>4400</v>
@@ -42013,7 +42013,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1436" t="n">
-        <v>1.57385885715485</v>
+        <v>1.57385873794556</v>
       </c>
       <c r="H1436" t="n">
         <v>2000</v>
@@ -42042,7 +42042,7 @@
         <v>1.91499996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>1.60315930843353</v>
+        <v>1.60315942764282</v>
       </c>
       <c r="H1437" t="n">
         <v>6886</v>
@@ -42100,7 +42100,7 @@
         <v>1.89499998092651</v>
       </c>
       <c r="G1439" t="n">
-        <v>1.58641612529755</v>
+        <v>1.58641600608826</v>
       </c>
       <c r="H1439" t="n">
         <v>48823</v>
@@ -42129,7 +42129,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1440" t="n">
-        <v>1.61571669578552</v>
+        <v>1.61571657657623</v>
       </c>
       <c r="H1440" t="n">
         <v>22298</v>
@@ -42332,7 +42332,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G1447" t="n">
-        <v>1.74966204166412</v>
+        <v>1.74966216087341</v>
       </c>
       <c r="H1447" t="n">
         <v>9597</v>
@@ -42361,7 +42361,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1448" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H1448" t="n">
         <v>38891</v>
@@ -42390,7 +42390,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1449" t="n">
-        <v>1.78314864635468</v>
+        <v>1.78314852714539</v>
       </c>
       <c r="H1449" t="n">
         <v>30470</v>
@@ -42448,7 +42448,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1451" t="n">
-        <v>1.94220864772797</v>
+        <v>1.94220888614655</v>
       </c>
       <c r="H1451" t="n">
         <v>94206</v>
@@ -42535,7 +42535,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1454" t="n">
-        <v>2.76262474060059</v>
+        <v>2.76262426376343</v>
       </c>
       <c r="H1454" t="n">
         <v>741208</v>
@@ -42564,7 +42564,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1455" t="n">
-        <v>3.09748792648315</v>
+        <v>3.09748816490173</v>
       </c>
       <c r="H1455" t="n">
         <v>644140</v>
@@ -42622,7 +42622,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G1457" t="n">
-        <v>3.17283225059509</v>
+        <v>3.17283201217651</v>
       </c>
       <c r="H1457" t="n">
         <v>441876</v>
@@ -42709,7 +42709,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1460" t="n">
-        <v>2.92168498039246</v>
+        <v>2.92168474197388</v>
       </c>
       <c r="H1460" t="n">
         <v>253906</v>
@@ -42767,7 +42767,7 @@
         <v>3.25</v>
       </c>
       <c r="G1462" t="n">
-        <v>2.72076654434204</v>
+        <v>2.72076630592346</v>
       </c>
       <c r="H1462" t="n">
         <v>163089</v>
@@ -42796,7 +42796,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1463" t="n">
-        <v>2.84634017944336</v>
+        <v>2.84634041786194</v>
       </c>
       <c r="H1463" t="n">
         <v>169786</v>
@@ -42825,7 +42825,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G1464" t="n">
-        <v>2.97191405296326</v>
+        <v>2.97191429138184</v>
       </c>
       <c r="H1464" t="n">
         <v>85469</v>
@@ -42912,7 +42912,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1467" t="n">
-        <v>3.19794678688049</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1467" t="n">
         <v>416520</v>
@@ -42941,7 +42941,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G1468" t="n">
-        <v>3.14771771430969</v>
+        <v>3.14771747589111</v>
       </c>
       <c r="H1468" t="n">
         <v>98600</v>
@@ -43028,7 +43028,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1471" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1471" t="n">
         <v>88712</v>
@@ -43057,7 +43057,7 @@
         <v>3.86999988555908</v>
       </c>
       <c r="G1472" t="n">
-        <v>3.23980498313904</v>
+        <v>3.23980474472046</v>
       </c>
       <c r="H1472" t="n">
         <v>91544</v>
@@ -43086,7 +43086,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1473" t="n">
-        <v>3.19794678688049</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1473" t="n">
         <v>44985</v>
@@ -43202,7 +43202,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1477" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1477" t="n">
         <v>101648</v>
@@ -43231,7 +43231,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1478" t="n">
-        <v>3.20631861686707</v>
+        <v>3.20631885528564</v>
       </c>
       <c r="H1478" t="n">
         <v>47143</v>
@@ -43260,7 +43260,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1479" t="n">
-        <v>3.19794678688049</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1479" t="n">
         <v>32517</v>
@@ -43376,7 +43376,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>2.99702882766724</v>
+        <v>2.99702906608582</v>
       </c>
       <c r="H1483" t="n">
         <v>65819</v>
@@ -43434,7 +43434,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1485" t="n">
-        <v>2.99702882766724</v>
+        <v>2.99702906608582</v>
       </c>
       <c r="H1485" t="n">
         <v>25266</v>
@@ -43550,7 +43550,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1489" t="n">
-        <v>2.86308360099792</v>
+        <v>2.86308336257935</v>
       </c>
       <c r="H1489" t="n">
         <v>50741</v>
@@ -43782,7 +43782,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1497" t="n">
-        <v>2.94679927825928</v>
+        <v>2.9467990398407</v>
       </c>
       <c r="H1497" t="n">
         <v>25116</v>
@@ -43869,7 +43869,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G1500" t="n">
-        <v>2.67890858650208</v>
+        <v>2.67890882492065</v>
       </c>
       <c r="H1500" t="n">
         <v>40221</v>
@@ -43898,7 +43898,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G1501" t="n">
-        <v>2.73750948905945</v>
+        <v>2.73750972747803</v>
       </c>
       <c r="H1501" t="n">
         <v>11033</v>
@@ -43956,7 +43956,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1503" t="n">
-        <v>2.87145495414734</v>
+        <v>2.87145519256592</v>
       </c>
       <c r="H1503" t="n">
         <v>83064</v>
@@ -44014,7 +44014,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>2.99702882766724</v>
+        <v>2.99702906608582</v>
       </c>
       <c r="H1505" t="n">
         <v>11090</v>
@@ -44043,7 +44043,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1506" t="n">
-        <v>2.95517110824585</v>
+        <v>2.95517086982727</v>
       </c>
       <c r="H1506" t="n">
         <v>12699</v>
@@ -44217,7 +44217,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1512" t="n">
-        <v>2.94679927825928</v>
+        <v>2.9467990398407</v>
       </c>
       <c r="H1512" t="n">
         <v>5516</v>
@@ -44333,7 +44333,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G1516" t="n">
-        <v>2.86308360099792</v>
+        <v>2.86308336257935</v>
       </c>
       <c r="H1516" t="n">
         <v>7817</v>
@@ -44362,7 +44362,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1517" t="n">
-        <v>2.83796882629395</v>
+        <v>2.83796906471252</v>
       </c>
       <c r="H1517" t="n">
         <v>2169</v>
@@ -44449,7 +44449,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1520" t="n">
-        <v>3.09748792648315</v>
+        <v>3.09748816490173</v>
       </c>
       <c r="H1520" t="n">
         <v>140430</v>
@@ -44478,7 +44478,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1521" t="n">
-        <v>2.94679927825928</v>
+        <v>2.9467990398407</v>
       </c>
       <c r="H1521" t="n">
         <v>168387</v>
@@ -44507,7 +44507,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1522" t="n">
-        <v>2.87145495414734</v>
+        <v>2.87145519256592</v>
       </c>
       <c r="H1522" t="n">
         <v>65356</v>
@@ -44536,7 +44536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1523" t="n">
-        <v>2.84634017944336</v>
+        <v>2.84634041786194</v>
       </c>
       <c r="H1523" t="n">
         <v>24638</v>
@@ -44565,7 +44565,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1524" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1524" t="n">
         <v>14377</v>
@@ -44594,7 +44594,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1525" t="n">
-        <v>2.83796882629395</v>
+        <v>2.83796906471252</v>
       </c>
       <c r="H1525" t="n">
         <v>19060</v>
@@ -44623,7 +44623,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1526" t="n">
-        <v>2.81285381317139</v>
+        <v>2.81285405158997</v>
       </c>
       <c r="H1526" t="n">
         <v>8245</v>
@@ -44768,7 +44768,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1531" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1531" t="n">
         <v>78995</v>
@@ -44797,7 +44797,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1532" t="n">
-        <v>2.77936744689941</v>
+        <v>2.77936768531799</v>
       </c>
       <c r="H1532" t="n">
         <v>15938</v>
@@ -44826,7 +44826,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1533" t="n">
-        <v>2.78773927688599</v>
+        <v>2.78773903846741</v>
       </c>
       <c r="H1533" t="n">
         <v>22330</v>
@@ -44971,7 +44971,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G1538" t="n">
-        <v>2.77936744689941</v>
+        <v>2.77936768531799</v>
       </c>
       <c r="H1538" t="n">
         <v>9351</v>
@@ -45058,7 +45058,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G1541" t="n">
-        <v>2.62030720710754</v>
+        <v>2.62030744552612</v>
       </c>
       <c r="H1541" t="n">
         <v>14445</v>
@@ -45116,7 +45116,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1543" t="n">
-        <v>2.57844924926758</v>
+        <v>2.57844972610474</v>
       </c>
       <c r="H1543" t="n">
         <v>31864</v>
@@ -45145,7 +45145,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1544" t="n">
-        <v>2.58682084083557</v>
+        <v>2.58682131767273</v>
       </c>
       <c r="H1544" t="n">
         <v>11428</v>
@@ -45174,7 +45174,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1545" t="n">
-        <v>2.58682084083557</v>
+        <v>2.58682131767273</v>
       </c>
       <c r="H1545" t="n">
         <v>22323</v>
@@ -45203,7 +45203,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1546" t="n">
-        <v>2.58682084083557</v>
+        <v>2.58682131767273</v>
       </c>
       <c r="H1546" t="n">
         <v>16840</v>
@@ -45319,7 +45319,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G1550" t="n">
-        <v>2.57844924926758</v>
+        <v>2.57844972610474</v>
       </c>
       <c r="H1550" t="n">
         <v>2875</v>
@@ -45348,7 +45348,7 @@
         <v>3.08999991416931</v>
       </c>
       <c r="G1551" t="n">
-        <v>2.58682084083557</v>
+        <v>2.58682131767273</v>
       </c>
       <c r="H1551" t="n">
         <v>3392</v>
@@ -45377,7 +45377,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1552" t="n">
-        <v>2.57007789611816</v>
+        <v>2.57007765769958</v>
       </c>
       <c r="H1552" t="n">
         <v>6057</v>
@@ -45551,7 +45551,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G1558" t="n">
-        <v>2.83796882629395</v>
+        <v>2.83796906471252</v>
       </c>
       <c r="H1558" t="n">
         <v>223000</v>
@@ -45580,7 +45580,7 @@
         <v>3.25</v>
       </c>
       <c r="G1559" t="n">
-        <v>2.72076654434204</v>
+        <v>2.72076630592346</v>
       </c>
       <c r="H1559" t="n">
         <v>109589</v>
@@ -45609,7 +45609,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G1560" t="n">
-        <v>2.87145495414734</v>
+        <v>2.87145519256592</v>
       </c>
       <c r="H1560" t="n">
         <v>68265</v>
@@ -45638,7 +45638,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1561" t="n">
-        <v>2.84634017944336</v>
+        <v>2.84634041786194</v>
       </c>
       <c r="H1561" t="n">
         <v>65014</v>
@@ -45783,7 +45783,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G1566" t="n">
-        <v>3.95139050483704</v>
+        <v>3.95138955116272</v>
       </c>
       <c r="H1566" t="n">
         <v>546808</v>
@@ -45899,7 +45899,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G1570" t="n">
-        <v>4.11882162094116</v>
+        <v>4.11882209777832</v>
       </c>
       <c r="H1570" t="n">
         <v>670103</v>
@@ -45957,7 +45957,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G1572" t="n">
-        <v>3.94301843643188</v>
+        <v>3.94301867485046</v>
       </c>
       <c r="H1572" t="n">
         <v>891209</v>
@@ -45986,7 +45986,7 @@
         <v>4.42999982833862</v>
       </c>
       <c r="G1573" t="n">
-        <v>3.70861411094666</v>
+        <v>3.70861387252808</v>
       </c>
       <c r="H1573" t="n">
         <v>893544</v>
@@ -46015,7 +46015,7 @@
         <v>4.17000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>3.49095273017883</v>
+        <v>3.49095249176025</v>
       </c>
       <c r="H1574" t="n">
         <v>561178</v>
@@ -46073,7 +46073,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1576" t="n">
-        <v>3.42397999763489</v>
+        <v>3.42398047447205</v>
       </c>
       <c r="H1576" t="n">
         <v>290905</v>
@@ -46102,7 +46102,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G1577" t="n">
-        <v>3.19794678688049</v>
+        <v>3.19794702529907</v>
       </c>
       <c r="H1577" t="n">
         <v>465196</v>
@@ -46160,7 +46160,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1579" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1579" t="n">
         <v>675453</v>
@@ -46218,7 +46218,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1581" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1581" t="n">
         <v>200040</v>
@@ -46276,7 +46276,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1583" t="n">
-        <v>2.81285381317139</v>
+        <v>2.81285405158997</v>
       </c>
       <c r="H1583" t="n">
         <v>140429</v>
@@ -46363,7 +46363,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1586" t="n">
-        <v>2.92168498039246</v>
+        <v>2.92168474197388</v>
       </c>
       <c r="H1586" t="n">
         <v>389966</v>
@@ -46450,7 +46450,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G1589" t="n">
-        <v>3.42397999763489</v>
+        <v>3.42398047447205</v>
       </c>
       <c r="H1589" t="n">
         <v>574866</v>
@@ -46479,7 +46479,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1590" t="n">
-        <v>3.24817681312561</v>
+        <v>3.24817657470703</v>
       </c>
       <c r="H1590" t="n">
         <v>684923</v>
@@ -46537,7 +46537,7 @@
         <v>4.07000017166138</v>
       </c>
       <c r="G1592" t="n">
-        <v>3.4072368144989</v>
+        <v>3.40723705291748</v>
       </c>
       <c r="H1592" t="n">
         <v>255356</v>
@@ -46566,7 +46566,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1593" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1593" t="n">
         <v>200134</v>
@@ -46624,7 +46624,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1595" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1595" t="n">
         <v>121872</v>
@@ -46682,7 +46682,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1597" t="n">
-        <v>3.281662940979</v>
+        <v>3.28166317939758</v>
       </c>
       <c r="H1597" t="n">
         <v>105117</v>
@@ -46740,7 +46740,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G1599" t="n">
-        <v>3.26491975784302</v>
+        <v>3.2649199962616</v>
       </c>
       <c r="H1599" t="n">
         <v>73475</v>
@@ -46856,7 +46856,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1603" t="n">
-        <v>2.99702882766724</v>
+        <v>2.99702906608582</v>
       </c>
       <c r="H1603" t="n">
         <v>206613</v>
@@ -46914,7 +46914,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1605" t="n">
-        <v>3.04725861549377</v>
+        <v>3.0472583770752</v>
       </c>
       <c r="H1605" t="n">
         <v>180444</v>
@@ -46972,7 +46972,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G1607" t="n">
-        <v>3.20631861686707</v>
+        <v>3.20631885528564</v>
       </c>
       <c r="H1607" t="n">
         <v>519633</v>
@@ -47059,7 +47059,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G1610" t="n">
-        <v>3.23143339157104</v>
+        <v>3.23143315315247</v>
       </c>
       <c r="H1610" t="n">
         <v>101620</v>
@@ -47088,7 +47088,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G1611" t="n">
-        <v>3.281662940979</v>
+        <v>3.28166317939758</v>
       </c>
       <c r="H1611" t="n">
         <v>189409</v>
@@ -47117,7 +47117,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G1612" t="n">
-        <v>3.22306180000305</v>
+        <v>3.22306203842163</v>
       </c>
       <c r="H1612" t="n">
         <v>80841</v>
@@ -47291,7 +47291,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G1618" t="n">
-        <v>3.04725861549377</v>
+        <v>3.0472583770752</v>
       </c>
       <c r="H1618" t="n">
         <v>142592</v>
@@ -47349,7 +47349,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1620" t="n">
-        <v>3.10585975646973</v>
+        <v>3.10585951805115</v>
       </c>
       <c r="H1620" t="n">
         <v>156987</v>
@@ -47407,7 +47407,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1622" t="n">
-        <v>3.10585975646973</v>
+        <v>3.10585951805115</v>
       </c>
       <c r="H1622" t="n">
         <v>36333</v>
@@ -47465,7 +47465,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1624" t="n">
-        <v>3.09748792648315</v>
+        <v>3.09748816490173</v>
       </c>
       <c r="H1624" t="n">
         <v>59155</v>
@@ -47494,7 +47494,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G1625" t="n">
-        <v>3.03051543235779</v>
+        <v>3.03051495552063</v>
       </c>
       <c r="H1625" t="n">
         <v>28510</v>
@@ -47697,7 +47697,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1632" t="n">
-        <v>2.95517110824585</v>
+        <v>2.95517086982727</v>
       </c>
       <c r="H1632" t="n">
         <v>30748</v>
@@ -47726,7 +47726,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1633" t="n">
-        <v>2.94679927825928</v>
+        <v>2.9467990398407</v>
       </c>
       <c r="H1633" t="n">
         <v>86464</v>
@@ -47755,7 +47755,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G1634" t="n">
-        <v>2.92168498039246</v>
+        <v>2.92168474197388</v>
       </c>
       <c r="H1634" t="n">
         <v>30432</v>
@@ -47813,7 +47813,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1636" t="n">
-        <v>2.84634017944336</v>
+        <v>2.84634041786194</v>
       </c>
       <c r="H1636" t="n">
         <v>53802</v>
@@ -47871,7 +47871,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G1638" t="n">
-        <v>2.76262474060059</v>
+        <v>2.76262426376343</v>
       </c>
       <c r="H1638" t="n">
         <v>39341</v>
@@ -47900,7 +47900,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G1639" t="n">
-        <v>2.57007789611816</v>
+        <v>2.57007765769958</v>
       </c>
       <c r="H1639" t="n">
         <v>87542</v>
@@ -47929,7 +47929,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G1640" t="n">
-        <v>2.43613243103027</v>
+        <v>2.43613266944885</v>
       </c>
       <c r="H1640" t="n">
         <v>96756</v>
@@ -48016,7 +48016,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G1643" t="n">
-        <v>3.24817681312561</v>
+        <v>3.24817657470703</v>
       </c>
       <c r="H1643" t="n">
         <v>391001</v>
@@ -48074,7 +48074,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G1645" t="n">
-        <v>3.10585975646973</v>
+        <v>3.10585951805115</v>
       </c>
       <c r="H1645" t="n">
         <v>368081</v>
@@ -48132,7 +48132,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1647" t="n">
-        <v>2.94679927825928</v>
+        <v>2.9467990398407</v>
       </c>
       <c r="H1647" t="n">
         <v>72225</v>
@@ -48190,7 +48190,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1649" t="n">
-        <v>2.95517110824585</v>
+        <v>2.95517086982727</v>
       </c>
       <c r="H1649" t="n">
         <v>79190</v>
@@ -48248,7 +48248,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G1651" t="n">
-        <v>2.95517110824585</v>
+        <v>2.95517086982727</v>
       </c>
       <c r="H1651" t="n">
         <v>43598</v>
@@ -48277,7 +48277,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1652" t="n">
-        <v>2.94679927825928</v>
+        <v>2.9467990398407</v>
       </c>
       <c r="H1652" t="n">
         <v>45483</v>
@@ -48306,7 +48306,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G1653" t="n">
-        <v>2.82122564315796</v>
+        <v>2.82122540473938</v>
       </c>
       <c r="H1653" t="n">
         <v>83540</v>
@@ -48393,7 +48393,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G1656" t="n">
-        <v>2.78773927688599</v>
+        <v>2.78773903846741</v>
       </c>
       <c r="H1656" t="n">
         <v>47624</v>
@@ -48451,7 +48451,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1658" t="n">
-        <v>2.99702882766724</v>
+        <v>2.99702906608582</v>
       </c>
       <c r="H1658" t="n">
         <v>160253</v>
@@ -48567,7 +48567,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G1662" t="n">
-        <v>2.99702882766724</v>
+        <v>2.99702906608582</v>
       </c>
       <c r="H1662" t="n">
         <v>68515</v>
@@ -48596,7 +48596,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G1663" t="n">
-        <v>2.81285381317139</v>
+        <v>2.81285405158997</v>
       </c>
       <c r="H1663" t="n">
         <v>111061</v>
@@ -48828,7 +48828,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G1671" t="n">
-        <v>2.8883216381073</v>
+        <v>2.88832187652588</v>
       </c>
       <c r="H1671" t="n">
         <v>65798</v>
@@ -48857,7 +48857,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1672" t="n">
-        <v>2.99026250839233</v>
+        <v>2.99026226997375</v>
       </c>
       <c r="H1672" t="n">
         <v>126538</v>
@@ -48886,7 +48886,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G1673" t="n">
-        <v>2.99026250839233</v>
+        <v>2.99026226997375</v>
       </c>
       <c r="H1673" t="n">
         <v>106475</v>
@@ -49147,7 +49147,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G1682" t="n">
-        <v>2.95628237724304</v>
+        <v>2.95628213882446</v>
       </c>
       <c r="H1682" t="n">
         <v>7189</v>
@@ -49263,7 +49263,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G1686" t="n">
-        <v>3.05822277069092</v>
+        <v>3.0582230091095</v>
       </c>
       <c r="H1686" t="n">
         <v>218592</v>
@@ -49350,7 +49350,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G1689" t="n">
-        <v>3.46598601341248</v>
+        <v>3.46598625183105</v>
       </c>
       <c r="H1689" t="n">
         <v>381731</v>
@@ -49408,7 +49408,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G1691" t="n">
-        <v>3.34705543518066</v>
+        <v>3.34705519676208</v>
       </c>
       <c r="H1691" t="n">
         <v>335762</v>
@@ -49524,7 +49524,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G1695" t="n">
-        <v>3.1431736946106</v>
+        <v>3.14317393302917</v>
       </c>
       <c r="H1695" t="n">
         <v>103087</v>
@@ -49756,7 +49756,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G1703" t="n">
-        <v>2.5400242805481</v>
+        <v>2.54002404212952</v>
       </c>
       <c r="H1703" t="n">
         <v>545519</v>
@@ -49814,7 +49814,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1705" t="n">
-        <v>2.2002215385437</v>
+        <v>2.20022177696228</v>
       </c>
       <c r="H1705" t="n">
         <v>816407</v>
@@ -49843,7 +49843,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1706" t="n">
-        <v>2.1747362613678</v>
+        <v>2.17473649978638</v>
       </c>
       <c r="H1706" t="n">
         <v>366493</v>
@@ -49959,7 +49959,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1710" t="n">
-        <v>1.99634003639221</v>
+        <v>1.99633979797363</v>
       </c>
       <c r="H1710" t="n">
         <v>105794</v>
@@ -50075,7 +50075,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1714" t="n">
-        <v>1.80944883823395</v>
+        <v>1.80944871902466</v>
       </c>
       <c r="H1714" t="n">
         <v>134323</v>
@@ -50104,7 +50104,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1715" t="n">
-        <v>1.86041903495789</v>
+        <v>1.86041927337646</v>
       </c>
       <c r="H1715" t="n">
         <v>100685</v>
@@ -50133,7 +50133,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1716" t="n">
-        <v>1.80944883823395</v>
+        <v>1.80944871902466</v>
       </c>
       <c r="H1716" t="n">
         <v>171140</v>
@@ -50162,7 +50162,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1717" t="n">
-        <v>1.73299300670624</v>
+        <v>1.73299312591553</v>
       </c>
       <c r="H1717" t="n">
         <v>96639</v>
@@ -50191,7 +50191,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1718" t="n">
-        <v>1.78396320343018</v>
+        <v>1.78396332263947</v>
       </c>
       <c r="H1718" t="n">
         <v>89845</v>
@@ -50249,7 +50249,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1720" t="n">
-        <v>2.0897855758667</v>
+        <v>2.08978581428528</v>
       </c>
       <c r="H1720" t="n">
         <v>584054</v>
@@ -50307,7 +50307,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1722" t="n">
-        <v>2.04731035232544</v>
+        <v>2.04731059074402</v>
       </c>
       <c r="H1722" t="n">
         <v>97215</v>
@@ -50365,7 +50365,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1724" t="n">
-        <v>1.89439928531647</v>
+        <v>1.89439916610718</v>
       </c>
       <c r="H1724" t="n">
         <v>57573</v>
@@ -50394,7 +50394,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G1725" t="n">
-        <v>1.86041903495789</v>
+        <v>1.86041927337646</v>
       </c>
       <c r="H1725" t="n">
         <v>60387</v>
@@ -50423,7 +50423,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1726" t="n">
-        <v>1.86891400814056</v>
+        <v>1.86891412734985</v>
       </c>
       <c r="H1726" t="n">
         <v>90364</v>
@@ -50452,7 +50452,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G1727" t="n">
-        <v>1.87740921974182</v>
+        <v>1.87740933895111</v>
       </c>
       <c r="H1727" t="n">
         <v>34676</v>
@@ -50481,7 +50481,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G1728" t="n">
-        <v>1.89439928531647</v>
+        <v>1.89439916610718</v>
       </c>
       <c r="H1728" t="n">
         <v>86699</v>
@@ -50800,7 +50800,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1739" t="n">
-        <v>2.14925122261047</v>
+        <v>2.14925098419189</v>
       </c>
       <c r="H1739" t="n">
         <v>51119</v>
@@ -50858,7 +50858,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1741" t="n">
-        <v>2.14925122261047</v>
+        <v>2.14925098419189</v>
       </c>
       <c r="H1741" t="n">
         <v>39018</v>
@@ -50974,7 +50974,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G1745" t="n">
-        <v>2.3701229095459</v>
+        <v>2.37012314796448</v>
       </c>
       <c r="H1745" t="n">
         <v>226412</v>
@@ -51032,7 +51032,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1747" t="n">
-        <v>2.31915259361267</v>
+        <v>2.31915235519409</v>
       </c>
       <c r="H1747" t="n">
         <v>77682</v>
@@ -51119,7 +51119,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1750" t="n">
-        <v>2.31915259361267</v>
+        <v>2.31915235519409</v>
       </c>
       <c r="H1750" t="n">
         <v>29157</v>
@@ -51380,7 +51380,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1759" t="n">
-        <v>2.3106575012207</v>
+        <v>2.31065726280212</v>
       </c>
       <c r="H1759" t="n">
         <v>21910</v>
@@ -51409,7 +51409,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1760" t="n">
-        <v>2.3106575012207</v>
+        <v>2.31065726280212</v>
       </c>
       <c r="H1760" t="n">
         <v>60801</v>
@@ -51438,7 +51438,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1761" t="n">
-        <v>2.27667737007141</v>
+        <v>2.27667713165283</v>
       </c>
       <c r="H1761" t="n">
         <v>32271</v>
@@ -51467,7 +51467,7 @@
         <v>2.6800000667572</v>
       </c>
       <c r="G1762" t="n">
-        <v>2.27667737007141</v>
+        <v>2.27667713165283</v>
       </c>
       <c r="H1762" t="n">
         <v>22244</v>
@@ -51525,7 +51525,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G1764" t="n">
-        <v>2.3106575012207</v>
+        <v>2.31065726280212</v>
       </c>
       <c r="H1764" t="n">
         <v>21655</v>
@@ -51583,7 +51583,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1766" t="n">
-        <v>2.25119209289551</v>
+        <v>2.25119185447693</v>
       </c>
       <c r="H1766" t="n">
         <v>12158</v>
@@ -51786,7 +51786,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1773" t="n">
-        <v>2.25119209289551</v>
+        <v>2.25119185447693</v>
       </c>
       <c r="H1773" t="n">
         <v>27318</v>
@@ -51960,7 +51960,7 @@
         <v>2.5</v>
       </c>
       <c r="G1779" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1779" t="n">
         <v>29760</v>
@@ -52018,7 +52018,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1781" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1781" t="n">
         <v>50189</v>
@@ -52134,7 +52134,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1785" t="n">
-        <v>2.14925122261047</v>
+        <v>2.14925098419189</v>
       </c>
       <c r="H1785" t="n">
         <v>73500</v>
@@ -52192,7 +52192,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1787" t="n">
-        <v>2.14925122261047</v>
+        <v>2.14925098419189</v>
       </c>
       <c r="H1787" t="n">
         <v>22087</v>
@@ -52308,7 +52308,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1791" t="n">
-        <v>2.14925122261047</v>
+        <v>2.14925098419189</v>
       </c>
       <c r="H1791" t="n">
         <v>27351</v>
@@ -52395,7 +52395,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1794" t="n">
-        <v>2.14925122261047</v>
+        <v>2.14925098419189</v>
       </c>
       <c r="H1794" t="n">
         <v>16540</v>
@@ -52482,7 +52482,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1797" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1797" t="n">
         <v>37009</v>
@@ -52511,7 +52511,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1798" t="n">
-        <v>2.04731035232544</v>
+        <v>2.04731059074402</v>
       </c>
       <c r="H1798" t="n">
         <v>42993</v>
@@ -52540,7 +52540,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1799" t="n">
-        <v>2.04731035232544</v>
+        <v>2.04731059074402</v>
       </c>
       <c r="H1799" t="n">
         <v>27831</v>
@@ -52627,7 +52627,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1802" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1802" t="n">
         <v>14961</v>
@@ -52656,7 +52656,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1803" t="n">
-        <v>2.08129072189331</v>
+        <v>2.08129096031189</v>
       </c>
       <c r="H1803" t="n">
         <v>42223</v>
@@ -52685,7 +52685,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1804" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1804" t="n">
         <v>47625</v>
@@ -52714,7 +52714,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1805" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1805" t="n">
         <v>4905</v>
@@ -52743,7 +52743,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1806" t="n">
-        <v>2.11527109146118</v>
+        <v>2.1152708530426</v>
       </c>
       <c r="H1806" t="n">
         <v>80677</v>
@@ -52859,7 +52859,7 @@
         <v>2.5</v>
       </c>
       <c r="G1810" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1810" t="n">
         <v>28956</v>
@@ -52917,7 +52917,7 @@
         <v>2.5</v>
       </c>
       <c r="G1812" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1812" t="n">
         <v>92455</v>
@@ -52946,7 +52946,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1813" t="n">
-        <v>2.11527109146118</v>
+        <v>2.1152708530426</v>
       </c>
       <c r="H1813" t="n">
         <v>15913</v>
@@ -52975,7 +52975,7 @@
         <v>2.5</v>
       </c>
       <c r="G1814" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1814" t="n">
         <v>14815</v>
@@ -53004,7 +53004,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1815" t="n">
-        <v>2.0897855758667</v>
+        <v>2.08978581428528</v>
       </c>
       <c r="H1815" t="n">
         <v>22485</v>
@@ -53091,7 +53091,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G1818" t="n">
-        <v>2.04731035232544</v>
+        <v>2.04731059074402</v>
       </c>
       <c r="H1818" t="n">
         <v>43768</v>
@@ -53207,7 +53207,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1822" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1822" t="n">
         <v>24201</v>
@@ -53294,7 +53294,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1825" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1825" t="n">
         <v>6417</v>
@@ -53381,7 +53381,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1828" t="n">
-        <v>2.08129072189331</v>
+        <v>2.08129096031189</v>
       </c>
       <c r="H1828" t="n">
         <v>40153</v>
@@ -53410,7 +53410,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1829" t="n">
-        <v>2.0897855758667</v>
+        <v>2.08978581428528</v>
       </c>
       <c r="H1829" t="n">
         <v>10052</v>
@@ -53468,7 +53468,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1831" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1831" t="n">
         <v>16312</v>
@@ -53671,7 +53671,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1838" t="n">
-        <v>1.86891400814056</v>
+        <v>1.86891412734985</v>
       </c>
       <c r="H1838" t="n">
         <v>73492</v>
@@ -53758,7 +53758,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G1841" t="n">
-        <v>1.99634003639221</v>
+        <v>1.99633979797363</v>
       </c>
       <c r="H1841" t="n">
         <v>38431</v>
@@ -53816,7 +53816,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1843" t="n">
-        <v>2.00483512878418</v>
+        <v>2.0048348903656</v>
       </c>
       <c r="H1843" t="n">
         <v>24139</v>
@@ -53932,7 +53932,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G1847" t="n">
-        <v>2.08129072189331</v>
+        <v>2.08129096031189</v>
       </c>
       <c r="H1847" t="n">
         <v>4495</v>
@@ -53961,7 +53961,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1848" t="n">
-        <v>2.11527109146118</v>
+        <v>2.1152708530426</v>
       </c>
       <c r="H1848" t="n">
         <v>64868</v>
@@ -54019,7 +54019,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1850" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1850" t="n">
         <v>99311</v>
@@ -54251,7 +54251,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.0897855758667</v>
+        <v>2.08978581428528</v>
       </c>
       <c r="H1858" t="n">
         <v>28977</v>
@@ -54309,7 +54309,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.0897855758667</v>
+        <v>2.08978581428528</v>
       </c>
       <c r="H1860" t="n">
         <v>8971</v>
@@ -54338,7 +54338,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.07704329490662</v>
+        <v>2.07704305648804</v>
       </c>
       <c r="H1861" t="n">
         <v>6479</v>
@@ -54541,7 +54541,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.02607274055481</v>
+        <v>2.02607297897339</v>
       </c>
       <c r="H1868" t="n">
         <v>5157</v>
@@ -54628,7 +54628,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.0897855758667</v>
+        <v>2.08978581428528</v>
       </c>
       <c r="H1871" t="n">
         <v>26987</v>
@@ -54657,7 +54657,7 @@
         <v>2.5</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1872" t="n">
         <v>23600</v>
@@ -54686,7 +54686,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1873" t="n">
         <v>34609</v>
@@ -54773,7 +54773,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1876" t="n">
         <v>67024</v>
@@ -54918,7 +54918,7 @@
         <v>2.5</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1881" t="n">
         <v>14370</v>
@@ -54947,7 +54947,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.12801361083984</v>
+        <v>2.12801384925842</v>
       </c>
       <c r="H1882" t="n">
         <v>9487</v>
@@ -55063,7 +55063,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1886" t="n">
         <v>7864</v>
@@ -55179,7 +55179,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.07279562950134</v>
+        <v>2.07279586791992</v>
       </c>
       <c r="H1890" t="n">
         <v>14842</v>
@@ -55266,7 +55266,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.12801361083984</v>
+        <v>2.12801384925842</v>
       </c>
       <c r="H1893" t="n">
         <v>21014</v>
@@ -55295,7 +55295,7 @@
         <v>2.5</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1894" t="n">
         <v>17372</v>
@@ -55469,7 +55469,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.2002215385437</v>
+        <v>2.20022177696228</v>
       </c>
       <c r="H1900" t="n">
         <v>12613</v>
@@ -55643,7 +55643,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1906" t="n">
         <v>500</v>
@@ -55672,7 +55672,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.14925122261047</v>
+        <v>2.14925098419189</v>
       </c>
       <c r="H1907" t="n">
         <v>1020</v>
@@ -55759,7 +55759,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1910" t="n">
         <v>6282</v>
@@ -55788,7 +55788,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1911" t="n">
         <v>3425</v>
@@ -55846,7 +55846,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1913" t="n">
         <v>4038</v>
@@ -55875,7 +55875,7 @@
         <v>2.5</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1914" t="n">
         <v>15397</v>
@@ -56049,7 +56049,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.16199398040771</v>
+        <v>2.16199374198914</v>
       </c>
       <c r="H1920" t="n">
         <v>17319</v>
@@ -56107,7 +56107,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.1450035572052</v>
+        <v>2.14500379562378</v>
       </c>
       <c r="H1922" t="n">
         <v>11908</v>
@@ -56165,7 +56165,7 @@
         <v>2.5</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.12376618385315</v>
+        <v>2.12376594543457</v>
       </c>
       <c r="H1924" t="n">
         <v>33504</v>
@@ -56194,7 +56194,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.25119209289551</v>
+        <v>2.25119185447693</v>
       </c>
       <c r="H1925" t="n">
         <v>97313</v>
@@ -56223,7 +56223,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.2002215385437</v>
+        <v>2.20022177696228</v>
       </c>
       <c r="H1926" t="n">
         <v>73288</v>
@@ -56252,7 +56252,7 @@
         <v>2.65499997138977</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.2554395198822</v>
+        <v>2.25543975830078</v>
       </c>
       <c r="H1927" t="n">
         <v>35207</v>
@@ -56426,7 +56426,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.26834487915039</v>
+        <v>2.26834464073181</v>
       </c>
       <c r="H1933" t="n">
         <v>37806</v>
@@ -56484,7 +56484,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.25535798072815</v>
+        <v>2.25535821914673</v>
       </c>
       <c r="H1935" t="n">
         <v>32108</v>
@@ -56513,7 +56513,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.26834487915039</v>
+        <v>2.26834464073181</v>
       </c>
       <c r="H1936" t="n">
         <v>39069</v>
@@ -56542,7 +56542,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H1937" t="n">
         <v>12871</v>
@@ -56571,7 +56571,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H1938" t="n">
         <v>15337</v>
@@ -56600,7 +56600,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.26834487915039</v>
+        <v>2.26834464073181</v>
       </c>
       <c r="H1939" t="n">
         <v>2777</v>
@@ -56716,7 +56716,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.22505593299866</v>
+        <v>2.22505569458008</v>
       </c>
       <c r="H1943" t="n">
         <v>22215</v>
@@ -56745,7 +56745,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H1944" t="n">
         <v>3956</v>
@@ -56832,7 +56832,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.23804235458374</v>
+        <v>2.23804259300232</v>
       </c>
       <c r="H1947" t="n">
         <v>8716</v>
@@ -56890,7 +56890,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H1949" t="n">
         <v>2442</v>
@@ -56919,7 +56919,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.22505593299866</v>
+        <v>2.22505569458008</v>
       </c>
       <c r="H1950" t="n">
         <v>25338</v>
@@ -56948,7 +56948,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.25535798072815</v>
+        <v>2.25535821914673</v>
       </c>
       <c r="H1951" t="n">
         <v>8927</v>
@@ -56977,7 +56977,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.25535798072815</v>
+        <v>2.25535821914673</v>
       </c>
       <c r="H1952" t="n">
         <v>6216</v>
@@ -57064,7 +57064,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.25535798072815</v>
+        <v>2.25535821914673</v>
       </c>
       <c r="H1955" t="n">
         <v>18464</v>
@@ -57122,7 +57122,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.36358046531677</v>
+        <v>2.36358070373535</v>
       </c>
       <c r="H1957" t="n">
         <v>56407</v>
@@ -57296,7 +57296,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.23804235458374</v>
+        <v>2.23804259300232</v>
       </c>
       <c r="H1963" t="n">
         <v>53763</v>
@@ -57383,7 +57383,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H1966" t="n">
         <v>34565</v>
@@ -57441,7 +57441,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H1968" t="n">
         <v>17972</v>
@@ -57470,7 +57470,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.23804235458374</v>
+        <v>2.23804259300232</v>
       </c>
       <c r="H1969" t="n">
         <v>29068</v>
@@ -57528,7 +57528,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.22505593299866</v>
+        <v>2.22505569458008</v>
       </c>
       <c r="H1971" t="n">
         <v>24472</v>
@@ -57615,7 +57615,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H1974" t="n">
         <v>63445</v>
@@ -57818,7 +57818,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.13414883613586</v>
+        <v>2.13414859771729</v>
       </c>
       <c r="H1981" t="n">
         <v>93229</v>
@@ -57847,7 +57847,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H1982" t="n">
         <v>72218</v>
@@ -57934,7 +57934,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.14280652999878</v>
+        <v>2.14280676841736</v>
       </c>
       <c r="H1985" t="n">
         <v>67637</v>
@@ -58050,7 +58050,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1989" t="n">
         <v>47022</v>
@@ -58108,7 +58108,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1991" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1991" t="n">
         <v>53903</v>
@@ -58137,7 +58137,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1992" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H1992" t="n">
         <v>7298</v>
@@ -58427,7 +58427,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2002" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2002" t="n">
         <v>7643</v>
@@ -58456,7 +58456,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2003" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2003" t="n">
         <v>4315</v>
@@ -58485,7 +58485,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2004" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2004" t="n">
         <v>19580</v>
@@ -58630,7 +58630,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2009" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2009" t="n">
         <v>16304</v>
@@ -58659,7 +58659,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2010" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2010" t="n">
         <v>3874</v>
@@ -58717,7 +58717,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2012" t="n">
-        <v>2.22505593299866</v>
+        <v>2.22505569458008</v>
       </c>
       <c r="H2012" t="n">
         <v>51087</v>
@@ -58746,7 +58746,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2013" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H2013" t="n">
         <v>34103</v>
@@ -58775,7 +58775,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2014" t="n">
-        <v>2.22505593299866</v>
+        <v>2.22505569458008</v>
       </c>
       <c r="H2014" t="n">
         <v>28614</v>
@@ -58804,7 +58804,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2015" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H2015" t="n">
         <v>4228</v>
@@ -58978,7 +58978,7 @@
         <v>2.64499998092651</v>
       </c>
       <c r="G2021" t="n">
-        <v>2.28998923301697</v>
+        <v>2.28998947143555</v>
       </c>
       <c r="H2021" t="n">
         <v>16904</v>
@@ -59065,7 +59065,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G2024" t="n">
-        <v>2.26834487915039</v>
+        <v>2.26834464073181</v>
       </c>
       <c r="H2024" t="n">
         <v>99740</v>
@@ -59094,7 +59094,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2025" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H2025" t="n">
         <v>29836</v>
@@ -59181,7 +59181,7 @@
         <v>2.60500001907349</v>
       </c>
       <c r="G2028" t="n">
-        <v>2.25535798072815</v>
+        <v>2.25535821914673</v>
       </c>
       <c r="H2028" t="n">
         <v>7937</v>
@@ -59268,7 +59268,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G2031" t="n">
-        <v>2.26401615142822</v>
+        <v>2.26401591300964</v>
       </c>
       <c r="H2031" t="n">
         <v>61751</v>
@@ -59442,7 +59442,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2037" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H2037" t="n">
         <v>80811</v>
@@ -59471,7 +59471,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2038" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2038" t="n">
         <v>91995</v>
@@ -59616,7 +59616,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2043" t="n">
-        <v>2.13414883613586</v>
+        <v>2.13414859771729</v>
       </c>
       <c r="H2043" t="n">
         <v>35433</v>
@@ -59674,7 +59674,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2045" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2045" t="n">
         <v>19181</v>
@@ -59790,7 +59790,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G2049" t="n">
-        <v>2.14280652999878</v>
+        <v>2.14280676841736</v>
       </c>
       <c r="H2049" t="n">
         <v>44244</v>
@@ -59877,7 +59877,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2052" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2052" t="n">
         <v>14287</v>
@@ -59935,7 +59935,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2054" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2054" t="n">
         <v>38639</v>
@@ -60022,7 +60022,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2057" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2057" t="n">
         <v>28397</v>
@@ -60138,7 +60138,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2061" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2061" t="n">
         <v>53906</v>
@@ -60167,7 +60167,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2062" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2062" t="n">
         <v>35915</v>
@@ -60196,7 +60196,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2063" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2063" t="n">
         <v>64626</v>
@@ -60254,7 +60254,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2065" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2065" t="n">
         <v>24701</v>
@@ -60283,7 +60283,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2066" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2066" t="n">
         <v>43246</v>
@@ -60341,7 +60341,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2068" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2068" t="n">
         <v>21946</v>
@@ -60457,7 +60457,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2072" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2072" t="n">
         <v>42294</v>
@@ -60486,7 +60486,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2073" t="n">
-        <v>2.06488633155823</v>
+        <v>2.06488656997681</v>
       </c>
       <c r="H2073" t="n">
         <v>12660</v>
@@ -60979,7 +60979,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G2090" t="n">
-        <v>2.10817527770996</v>
+        <v>2.10817551612854</v>
       </c>
       <c r="H2090" t="n">
         <v>18648</v>
@@ -61037,7 +61037,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2092" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2092" t="n">
         <v>30212</v>
@@ -61066,7 +61066,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2093" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2093" t="n">
         <v>88029</v>
@@ -61153,7 +61153,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2096" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2096" t="n">
         <v>40947</v>
@@ -61182,7 +61182,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G2097" t="n">
-        <v>2.11683320999146</v>
+        <v>2.11683297157288</v>
       </c>
       <c r="H2097" t="n">
         <v>83944</v>
@@ -61385,7 +61385,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2104" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2104" t="n">
         <v>38050</v>
@@ -61414,7 +61414,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2105" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2105" t="n">
         <v>46804</v>
@@ -61617,7 +61617,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2112" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2112" t="n">
         <v>128763</v>
@@ -61675,7 +61675,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2114" t="n">
-        <v>1.99995267391205</v>
+        <v>1.99995291233063</v>
       </c>
       <c r="H2114" t="n">
         <v>37963</v>
@@ -61704,7 +61704,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2115" t="n">
-        <v>1.98263740539551</v>
+        <v>1.98263716697693</v>
       </c>
       <c r="H2115" t="n">
         <v>95057</v>
@@ -61733,7 +61733,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2116" t="n">
-        <v>1.99995267391205</v>
+        <v>1.99995291233063</v>
       </c>
       <c r="H2116" t="n">
         <v>71174</v>
@@ -61820,7 +61820,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2119" t="n">
-        <v>1.99995267391205</v>
+        <v>1.99995291233063</v>
       </c>
       <c r="H2119" t="n">
         <v>85913</v>
@@ -61936,7 +61936,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2123" t="n">
-        <v>1.99995267391205</v>
+        <v>1.99995291233063</v>
       </c>
       <c r="H2123" t="n">
         <v>1027945</v>
@@ -62052,7 +62052,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2127" t="n">
-        <v>2.07787322998047</v>
+        <v>2.07787299156189</v>
       </c>
       <c r="H2127" t="n">
         <v>34909</v>
@@ -62226,7 +62226,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2133" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2133" t="n">
         <v>48803</v>
@@ -62255,7 +62255,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G2134" t="n">
-        <v>2.10384654998779</v>
+        <v>2.10384678840637</v>
       </c>
       <c r="H2134" t="n">
         <v>62357</v>
@@ -62313,7 +62313,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2136" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2136" t="n">
         <v>66509</v>
@@ -62400,7 +62400,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2139" t="n">
-        <v>2.22505593299866</v>
+        <v>2.22505569458008</v>
       </c>
       <c r="H2139" t="n">
         <v>76303</v>
@@ -62429,7 +62429,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2140" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2140" t="n">
         <v>124091</v>
@@ -62661,7 +62661,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2148" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2148" t="n">
         <v>28685</v>
@@ -62690,7 +62690,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2149" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2149" t="n">
         <v>41367</v>
@@ -63009,7 +63009,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2160" t="n">
-        <v>2.14713549613953</v>
+        <v>2.14713573455811</v>
       </c>
       <c r="H2160" t="n">
         <v>40274</v>
@@ -63183,7 +63183,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2166" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2166" t="n">
         <v>33353</v>
@@ -63328,7 +63328,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2171" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2171" t="n">
         <v>46396</v>
@@ -63502,7 +63502,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2177" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2177" t="n">
         <v>43216</v>
@@ -63531,7 +63531,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G2178" t="n">
-        <v>2.2510290145874</v>
+        <v>2.25102925300598</v>
       </c>
       <c r="H2178" t="n">
         <v>155843</v>
@@ -63647,7 +63647,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G2182" t="n">
-        <v>2.21639776229858</v>
+        <v>2.21639800071716</v>
       </c>
       <c r="H2182" t="n">
         <v>196275</v>
@@ -80154,6 +80154,35 @@
         <v>446458</v>
       </c>
       <c r="I2751" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2752" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C2752" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="D2752" t="n">
+        <v>8</v>
+      </c>
+      <c r="E2752" t="n">
+        <v>7.69999980926514</v>
+      </c>
+      <c r="F2752" t="n">
+        <v>7.90999984741211</v>
+      </c>
+      <c r="G2752" t="n">
+        <v>7.90999984741211</v>
+      </c>
+      <c r="H2752" t="n">
+        <v>372555</v>
+      </c>
+      <c r="I2752" t="s">
         <v>9</v>
       </c>
     </row>
